--- a/reports/expert_dispatch/report.xlsx
+++ b/reports/expert_dispatch/report.xlsx
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cc57-3252-7943-bbbd-64c7dcd456d0</t>
+    <t>01a0cce0-6735-7753-8e79-ce7749b5311e</t>
   </si>
   <si>
     <t>Recording</t>
@@ -183,7 +183,7 @@
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T03:35:56.284466Z</t>
+    <t>2026-09-23T06:06:28.037095Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,7 +306,7 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cc57-3257-7dd2-adac-562f7e2cef77</t>
+    <t>01a0cce0-673b-7381-86bc-4c8b7a3b3cd2</t>
   </si>
   <si>
     <t>Fresh input</t>
@@ -342,8 +342,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"type": "function_call", "name": "task", "arguments": "{\"description\":\"Answer the movie question: Who directed the film Spirited Away? Provide the director's name and, if useful, a brief identifying detail. Be accurate and concise.\",\"subagent_type\":\"movie_expert\"}", "call_id": "call_SPopESHDLYvkg5B9ouv8wMLu", "id": "fc_0e625983e394fc11006ab34986a63087d2a4b8c353d3037eef", "index": 0}]
-{"name": "task", "args": {"description": "Answer the movie question: Who directed the film Spirited Away? Provide the director's name and, if useful, a brief identifying detail. Be accurate and concise.", "subagent_type": "movie_expert"}, "id": "call_SPopESHDLYvkg5B9ouv8wMLu", "type": "tool_call"}</t>
+    <t>[{"type": "function_call", "name": "task", "arguments": "{\"description\":\"Answer the movie question: Who directed the film Spirited Away? Provide the director's name and, if useful, the film's release year. Keep it concise and factually accurate.\",\"subagent_type\":\"movie_expert\"}", "call_id": "call_fQTXffX0DYMpQJyRpeeyO3l0", "id": "fc_01bfb711a688d9f4006ab36ca6b8a087d28630c7c7c85a76ab", "index": 0}]
+{"name": "task", "args": {"description": "Answer the movie question: Who directed the film Spirited Away? Provide the director's name and, if useful, the film's release year. Keep it concise and factually accurate.", "subagent_type": "movie_expert"}, "id": "call_fQTXffX0DYMpQJyRpeeyO3l0", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -355,25 +355,25 @@
     <t>Tool · task</t>
   </si>
   <si>
-    <t>01a0cc57-3866-75c0-829a-6e4372e9aa09</t>
+    <t>01a0cce0-6dfc-7842-8cb4-715f37153254</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
   </si>
   <si>
-    <t>{'description': "Answer the movie question: Who directed the film Spirited Away? Provide the director's name and, if useful, a brief identifying detail. Be accurate and concise.", 'subagent_type': 'movie_expert'}</t>
+    <t>{'description': "Answer the movie question: Who directed the film Spirited Away? Provide the director's name and, if useful, the film's release year. Keep it concise and factually accurate.", 'subagent_type': 'movie_expert'}</t>
   </si>
   <si>
     <t xml:space="preserve">    Result</t>
   </si>
   <si>
-    <t>Command(update={'messages': [ToolMessage(content='*Spirited Away* was directed by **Hayao Miyazaki**, who also wrote the film. It was released in 2001. [Source](https://www.ghibli.jp/works/)', tool_call_id='call_SPopESHDLYvkg5B9ouv8wMLu')]})</t>
+    <t>Command(update={'messages': [ToolMessage(content='*Spirited Away* was directed by **Hayao Miyazaki** and released in **2001**. [Source](https://www.ghibli.jp/works/)', tool_call_id='call_fQTXffX0DYMpQJyRpeeyO3l0')]})</t>
   </si>
   <si>
     <t>R2</t>
   </si>
   <si>
-    <t>01a0cc57-3869-7ab1-8870-e8f0160ca5c1</t>
+    <t>01a0cce0-6dff-7d73-9fe8-97986ba55391</t>
   </si>
   <si>
     <t>You are the movies expert. Use search_movie_reference to retrieve evidence before answering the delegated question. Base factual claims on the returned passages and cite their source URLs. If no relevant evidence is found, explain the collection's limits instead of inventing an answer or claiming web research. Answer concisely. The collection is a small local teaching reference, not a complete or continually updated source.</t>
@@ -382,17 +382,17 @@
     <t>Reasoning</t>
   </si>
   <si>
-    <t>[{"id": "rs_0677c5af57e60f88006ab34987c4a087d28edcf718d87f3e2f", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0mH7Lcx6eTEy_lX8iFQB4-vUNBx2eq0J-Fq1n8VFRO5PmPMWLcaW7UtLyNJyX_BjeYirSkCPEThs-KzBlvuzZuoh7fnpf4U2YY5r434OoHDt0_L95gmd8KMXhe9PZ2YG0DjcZJDZLpjFjyOHOHGzS_RSNq0HICDaJXsXkNbF7fgJZ2syO6Fu-o47Cf5Sei9Rb6jjS24P-pCx71KkcVlf-WyAEsLfOUjNEGIicY8qAIaqHy-DThAGm38e0siuSEIAMUjciy6A7eE0KpFuGvKhhvnSLd0WngqY9qC4jN1nEUlMU4IeNALNT5CI4f41F-GAAxpCRm8-fjMSypNouJ_WQmVc-13B4NBrEhV1BIHt2U4GkLZ-jyoQwJbyGcKAj3MQxR3f8ir5iB8OS55NF4tQmhOOws7j1xjRa4eiSJAkR-gFZSZdGiSMt_lrGIt9ZoQmIw5BI6R3w0NwOxrMxQz4c74ai5Vr6KhvuMdT_XELDZXP3AIDin-_teav2hTAdFiEUhbV5kLvQBrETmfjuPRFdb2CwdW8GOCxmNzssH2y6-acm9nzhEPuMcgu8ZKuUHlh-WxUWeH1lFqIBD8Ez_G2WzBBq6_ZyIFOFP_rM_PBUFKyMdL_pLv_TH8XV5Uk61uQxcxK4APH7EDCM9QUBHblEmyqWbS6PkGt4y6u11wF05KORHddcYsNr_Zff0yk5drA5fbS9ZXn_Cx0q-sBQ_6hCoe0H33it1UzgARJEu3K-pAubB8VMciJbsGhGZeke8vBFIEo2HLo9O0USIV50RAVh3NUNIYMI6-w7sDiYSiZJzQiL9LWQ2s6cGiGViWEblpTESztnr-nHznV9tXjmL8xs9BA4LY-_gD-DpDRSc1a0ZElRNVoXrTGGMGZRwodcKJykI15aoJxTEWdtsbq0UaJidBxTYPHLJA9nzDunuXjYXxUm3X13CkfmIqAaUMAF5k9kUCAPjDvU-cnwdHy_S1yfjQ_D0FhM0bIsadEf285pe4n6RBKg87SrA4pFJ3iWS2q59OiWE7cq-jixLyGinyPwdJz31iRWSfM63x-PRwQnCXBGc4RY6PH0T5xdy62JnfxHa7q29oNS0JVJp0-i4PMsmzPwne3o0j5Z9d-QdaGe0t1zRgxS1cgk1ySaSJzIr0yP5Y8PEUU22gQ2F9mM48e5_DV3pqoykdrdpdApbavfFzi6B6FS6lW70QZLSJXMgyzpnU"}, {"type": "function_call", "name": "search_movie_reference", "arguments": "{\"query\":\"Who directed the film Spirited Away?\"}", "call_id": "call_SfiJM8fOhqmKfTfQoLURmnPS", "id": "fc_0677c5af57e60f88006ab34987ef4087d2b584d92fa95d4253", "index": 1}]
-{"name": "search_movie_reference", "args": {"query": "Who directed the film Spirited Away?"}, "id": "call_SfiJM8fOhqmKfTfQoLURmnPS", "type": "tool_call"}</t>
+    <t>[{"id": "rs_05560943d4ef939e006ab36ca80f7087d2b77a5361027a4f7d", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2yoCWDDiimauxpzFQ3_EKiK2i4ZtYpreIsGTtbzvvccn0tikmQBA5BdXOgfuPey9o-Fa19HrzklfM1aNhvtqppUq9MAKm1VjbbpMiZIZ9J9jYtCKC2Bck6cKo2f8xP3c78-lekyMqgbOjY_aTXr6B_e07_jxW7BfGkkJ-mB4JYdoiMGXDOpdEXbd1CV6Bev9nZWM_tvMDsBik90qOLZ2DzbY5sQbZ5YP-ECyT18MFuEGaK7CW2a5MuyohCWH1sX2BEzqWImNZtg9D16r8UrW4Hbs8TXCKFQFzkuvuTd5DP1psbPO4aknZAhl00G-jnEFvnsIRQ7u2tnCOUGWc-hkEy-WDYdizSVXVcrXwy48ahi_WHTWf_3M_7KD0b7z7SYP-m0JO6qHv4QK5LvTEG1YxlZxnp6-6jVTr1_XyB84uJnifgDrp8l--KyjGSwxGIRW8WN-bx--XbhqvMfwl0u4yHPLEks9Gqbvc1J26G5Omkqi1gVBAooaF7D7hHlc89RG1-4mGyii6evIP3btjp2HzB0MAa3otZAPIzneOy__THa5_xce3SuEj19P_v7VpY4P9jxYyqIJAaBb6Cn-kdJjFPtMTPtVV7ZWLI3HJv9QzDsOJroXfgEGwOU2BBKNCY9egX2-FrFCnGy4n5b-sJ_hU7QFsNDAoECxnq0ZL0HeUsKqi9jp1uz_ER0mfm_if-dK2HofJlV0JlEvIKiZWIsDec2_1qaTi62kdIxFrE6qRmY7oe2vU-Z0X520kgTT8Z86jcUhDSRtlxgL_arRA1uF42bPT90krRliF_rbPZ4eN5BWVHVjYGHXepyMG0RvKxRGOVLCul1XDNTO6AIwc7bqSeoauN31i3nIsN1CrLy2ZGLVkws418C1jZRKT3YDMKH-JMr2oTNI7ou2bqDDPtJPVqsjdQJ7Mtkx4Diu01KmfVYmzYPCAMLij4FrmW41mTgsCizuaob4yCiae8uqBm9CKWNddudaWOGvUxLokHuXsTd26JUCJ_BQUqP8UX4wz-MmuwAISplsiYmKiFXnpwwo0SkRHT6NH8JERyoBE2ATtNH9hCU3ebrMTo-E_0Kd0R-r_MZf9p-BtPuuk6Yi3wop4miXwvoYpW4oVjCnsmeK6yqi5mEhrV9ioRzBJxh2z0pgKuWoxDvxJQVlJkklrtUWidgwHEXBBxidTXQMJZf2RxJt6ZqFaJH0xT0tO4XBx4Gi0ej"}, {"type": "function_call", "name": "search_movie_reference", "arguments": "{\"query\":\"Who directed the film Spirited Away? Include director and release year.\"}", "call_id": "call_eRwbrLBgu4XYeUicLddKy3yk", "id": "fc_05560943d4ef939e006ab36ca83a4c87d2acc0a6b30564a3f8", "index": 1}]
+{"name": "search_movie_reference", "args": {"query": "Who directed the film Spirited Away? Include director and release year."}, "id": "call_eRwbrLBgu4XYeUicLddKy3yk", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · search_movie_reference</t>
   </si>
   <si>
-    <t>01a0cc57-3be3-7311-9535-cd8cc201035a</t>
-  </si>
-  <si>
-    <t>{'query': 'Who directed the film Spirited Away?'}</t>
+    <t>01a0cce0-72b4-7021-80e5-546ed0198f9f</t>
+  </si>
+  <si>
+    <t>{'query': 'Who directed the film Spirited Away? Include director and release year.'}</t>
   </si>
   <si>
     <t>Spirited Away
@@ -403,7 +403,7 @@
     <t>R3</t>
   </si>
   <si>
-    <t>01a0cc57-3be9-7d32-ad36-6ae79064e568</t>
+    <t>01a0cce0-72b6-72b2-9083-549c77f57bca</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
@@ -412,19 +412,19 @@
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "*Spirited Away* was directed by **Hayao Miyazaki**, who also wrote the film. It was released in 2001. [Source](https://www.ghibli.jp/works/)", "phase": "final_answer", "index": 0, "id": "msg_0677c5af57e60f88006ab34988acbc87d298113b7388ce0e0e"}]</t>
+    <t>[{"type": "text", "text": "*Spirited Away* was directed by **Hayao Miyazaki** and released in **2001**. [Source](https://www.ghibli.jp/works/)", "phase": "final_answer", "index": 0, "id": "msg_05560943d4ef939e006ab36ca9327887d2bd99ceacba810971"}]</t>
   </si>
   <si>
     <t>R4</t>
   </si>
   <si>
-    <t>01a0cc57-3f98-7e93-b471-a9c7a3f22710</t>
-  </si>
-  <si>
-    <t>*Spirited Away* was directed by **Hayao Miyazaki**, who also wrote the film. It was released in 2001. [Source](https://www.ghibli.jp/works/)</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "*Spirited Away* was directed by **Hayao Miyazaki**.", "phase": "final_answer", "index": 0, "id": "msg_0e625983e394fc11006ab34989ad2887d2beb801a4bdbee92e"}]</t>
+    <t>01a0cce0-76d3-7d11-997d-232ba008e854</t>
+  </si>
+  <si>
+    <t>*Spirited Away* was directed by **Hayao Miyazaki** and released in **2001**. [Source](https://www.ghibli.jp/works/)</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "*Spirited Away* was directed by **Hayao Miyazaki**.", "phase": "final_answer", "index": 0, "id": "msg_01bfb711a688d9f4006ab36caa2e8487d2989b20fb595cfbe3"}]</t>
   </si>
   <si>
     <t>Turn 2</t>
@@ -433,45 +433,45 @@
     <t>R5</t>
   </si>
   <si>
-    <t>01a0cc57-431c-7f82-8119-593f484cd618</t>
+    <t>01a0cce0-7a25-7800-b4a8-95fea5aebf69</t>
   </si>
   <si>
     <t>How many players does a basketball team have on court?</t>
   </si>
   <si>
-    <t>[{"type": "function_call", "name": "task", "arguments": "{\"description\":\"Answer the sports question: How many players from one basketball team are on the court at a time under standard basketball rules? Mention the per-team number and total players on court if helpful, while noting any common variation only if relevant.\",\"subagent_type\":\"sports_expert\"}", "call_id": "call_vvitK3UUlYCv1sbBHsIDgu3a", "id": "fc_0e625983e394fc11006ab3498a966887d2b8fa4e98936450e7", "index": 0}]
-{"name": "task", "args": {"description": "Answer the sports question: How many players from one basketball team are on the court at a time under standard basketball rules? Mention the per-team number and total players on court if helpful, while noting any common variation only if relevant.", "subagent_type": "sports_expert"}, "id": "call_vvitK3UUlYCv1sbBHsIDgu3a", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0cc57-48aa-75b3-80ee-ac55644134b0</t>
-  </si>
-  <si>
-    <t>{'description': 'Answer the sports question: How many players from one basketball team are on the court at a time under standard basketball rules? Mention the per-team number and total players on court if helpful, while noting any common variation only if relevant.', 'subagent_type': 'sports_expert'}</t>
-  </si>
-  <si>
-    <t>Command(update={'messages': [ToolMessage(content='Under standard basketball rules, **5 players from each team** are on the court—**10 players total**. This excludes the separate 3x3 format. [FIBA](https://about.fiba.basketball/en/our-sport/basketball)', tool_call_id='call_vvitK3UUlYCv1sbBHsIDgu3a')]})</t>
+    <t>[{"type": "function_call", "name": "task", "arguments": "{\"description\":\"Answer this sports rules question: How many players from one basketball team are on the court at a time during standard basketball play? Mention the usual five-player rule, and briefly note if relevant that rules can vary by format (such as 3x3). Keep it concise.\",\"subagent_type\":\"sports_expert\"}", "call_id": "call_kIUUc8kx5AP4y5q4UPHxCoDx", "id": "fc_01bfb711a688d9f4006ab36cab1b8487d29058068b0fc9517f", "index": 0}]
+{"name": "task", "args": {"description": "Answer this sports rules question: How many players from one basketball team are on the court at a time during standard basketball play? Mention the usual five-player rule, and briefly note if relevant that rules can vary by format (such as 3x3). Keep it concise.", "subagent_type": "sports_expert"}, "id": "call_kIUUc8kx5AP4y5q4UPHxCoDx", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0cce0-8083-70a2-8711-35071f6e667e</t>
+  </si>
+  <si>
+    <t>{'description': 'Answer this sports rules question: How many players from one basketball team are on the court at a time during standard basketball play? Mention the usual five-player rule, and briefly note if relevant that rules can vary by format (such as 3x3). Keep it concise.', 'subagent_type': 'sports_expert'}</t>
+  </si>
+  <si>
+    <t>Command(update={'messages': [ToolMessage(content='In standard basketball, **five players from each team** are on the court at a time. Other formats vary—for example, **3x3 basketball uses three players per team**. [FIBA](https://about.fiba.basketball/en/our-sport/basketball)', tool_call_id='call_kIUUc8kx5AP4y5q4UPHxCoDx')]})</t>
   </si>
   <si>
     <t>R6</t>
   </si>
   <si>
-    <t>01a0cc57-48b0-70f2-884c-275bcb1649bb</t>
+    <t>01a0cce0-8086-79c3-b591-884905dd4c6f</t>
   </si>
   <si>
     <t>You are the sports expert. Use search_sports_reference to retrieve evidence before answering the delegated question. Base factual claims on the returned passages and cite their source URLs. If no relevant evidence is found, explain the collection's limits instead of inventing an answer or claiming web research. Answer concisely. The collection is a small local teaching reference, not a complete or continually updated source.</t>
   </si>
   <si>
-    <t>[{"id": "rs_09b0e979e04b4ceb006ab3498be0b887d292a04c34f6fc459b", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0mMmtNXMjECB1LhySFpKBKZj4YkEYCDXNFeBIVf_KLfdTdSR_oukdmbNuQ_ehGCDVxxChrqiJbeWKBkE8ZJkIH30H8LXtnr_GILblaBpCAtxuf1VHjWjmFP_ij1rEz3MgfFmXTqWzmNI488fSJOVzm4zHGD8UsbtdnrTtsEHPd8LbCE_lvKyzAW4S_JNzlngW7oCP5rmyAX1OEBQhymzz_eUruEORjMJ6BpXp4PVVqlGRguyuik3ZO_j9s6mEfiQzKeywX7HpQUDUHCzpzN_lxRP_d7c6MjDvZH8-sPlCs5io8vM_BalUN7LaoBtcXDqDI4H8i5FluDoMnZIv4560ZncAHZsqTmx_atoeTNhWH0_8Ga9P-HsUP7vx3gNhmChlKDtb3cLnfe5OkeszwhNuFVoTtIhDdDllc6d380HEW9Nzr4HOLcrqpi7VA1jjMhDn07OCXXzhFnbAiUn6qKzt22zVulM5SSLel8SxdBCBMpTlww-_3jXwkEYv2kUAlbrruzCzeFIzQifq0pAVWQnjTmkk8qNv0Rg2Mg_8SVN97iZlo-gQNr9dzIktHlWEQRlQ0rk9GS7p1HrDd7iCe75LjY1HG8u46vNrYd4Was2d5ruhMe4-phSDdjGJpIWV5mShqg39ur_OlRSQ1GUnvmPrkIKeiYPnxVrS2cYVmZ0a8SWBo82CMYE0nSHhHJwUS-W5Rw7sClZffZwmB7ootge7_S8oYuKjlL7VZaTBe-QS_MEpEqhvi4koqOrl7Gql2JFT6bhaHp6_8uCVbrNEyhPbhXNpsr6RzzkvghPcZ5KMw8dprw49ovWrUyN6kDKpQAHhkqtbAd_Hm3HSmJWYp7zFV7SCd9HNnUJYvDhw1RP_BtKfAarXI1tTsX5_musWlcqiu1osWPaSQ9zOmIBybR0-hkt67Pyx9O8Dua4VawxgPvyEfPEMPfTVzGMYoOoEZpLXYAnpBDtLXUthJ-vLGm1s-uLAaWD2NwtSvWpIx9hsUdW_q5f6bViyYgVm10uHDkg8K4FIA_gD2Q7OpwTZIgAUXwy-cwl1StZidThAVmRq_qfEu0_XC-xCDbp1Gw1VoyG7OSOFgW--gb9Uj_FJZS34bRrTQIe-yCIE6O4znC-65n6QfMpCq02um0KvzY5pL1fvbROcMaUM_rQRE5VZ2OGro0QgyEHEi7GICd7D_xGYnyBAVOq9ezvnsjZBTWeHhbnd5d"}, {"type": "function_call", "name": "search_sports_reference", "arguments": "{\"query\":\"How many players from one basketball team are on the court at a time under standard basketball rules? Include per-team and total players.\"}", "call_id": "call_oWwCGyLYJ9g4lAG776XVYckv", "id": "fc_09b0e979e04b4ceb006ab3498c039c87d2b6c25e7ff1edb9c7", "index": 1}]
-{"name": "search_sports_reference", "args": {"query": "How many players from one basketball team are on the court at a time under standard basketball rules? Include per-team and total players."}, "id": "call_oWwCGyLYJ9g4lAG776XVYckv", "type": "tool_call"}</t>
+    <t>[{"id": "rs_0cca63b5ce4951db006ab36cacc97c87d2a1d7ff9442a60a81", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2yt_WDtmOf5wmkhq2NJ_Kfc3fBkWEDuj7RSfCh3gR-eJod2QnBJqhztpWq02r2i9WJgAdL6J48m0B7KVC8MFDjij7hrblcjVYHrkBHoG34-Ah4XSmUkhkLKxz7PJPqEVHRxwqrFmefK6BmVkUBu0RUPluNFTslEH7WPNqb85shvflIR4G1yovujbEUuWBQqtWIBlq0Ap2-HDYzHiA-O_fo17F1tOAyrH_sU0bQj70bwL5x2FP6Fbv1XC-3FtRYavEnT2IkQD5ZPvKGH-4qO9GApElZgWR6vNG2q21GC1cHQzvmHR_JvekvJBtPsaaDgWGoVvyzhZfxCU3gQ667Ix960XIqBmAYIzpsZ9n6Rnu_Y3aTvQoE-lF8lDim3VLxKvEcpoGkOcn17dhNz7eXckjpLprjLgk8z-8tWvaSaKm0YO0DAPLW8YZZUIayS6SLi7DoOtmTNGv9xNXR78zs0xad_AkUVgvU6gULIBxYjt3gltf3U3WQeVBhcm4cLbF8wWP6V1CcdI7HLnSLHxjDxZnT2eHxtK8UltJ8LxBJoQlXcegQg3ki3TwtGFFVNzSgzPyJc6ajfMAZb7wOhtDBR2teHp_AjSJM9Skfp-_kx0AcX7fKLeOpXmFcr_beY2sIUbyvkS3_RyWhRgpnhJJP4HDfHOp5ZlArwIB3uOb4KO1W3dOVrdfLrD-9nlKDTVOBAScSlDY12g_IU4KpDhUXObJtBCo92bYxXnwOfWL6-ZkJ5rqBB6ngjwuMkiCT8XoImkj0dAVSMbGClPrqk21FwWE2Fh9oPWs2yAToN6OD-yyWn1iwYFOZeaqDK8kUuVVPhEkLAd5IH-gvIPGsKe36mb0GUHjXwiTARytNQVch_mmS7auKTIjIDhSMf_loisaYwUiuWSGiSGRhTehFnFTFMLKk-l7T5b7O--1HEKahJi1EQsbZ9wQY_l6nJQW7PJqpLhcdsRXZzjzoB_cuFAyZynPr-K55is0GzpEahoy5JjzyjesyspClmXrrBzSdq35rDhqpabD-tZOfvHKrhNFS9wsjFbrj6w52FICc7HMUThjpUZYdQOM28a9XkjUURbZwfE-pJPXBhAGr7fobzEOX9LCGFTf0AwkkM3HwpjyV5UgvrRriVMCcpTwAnCBAK4qCWu-Q0YnpNhWKiuGVGpei50io_l2lV9TKB5-a-k0rAPqGbpxXWHO7VEi9sE2dVPKmBdxGw"}, {"type": "function_call", "name": "search_sports_reference", "arguments": "{\"query\":\"How many players from one basketball team are on the court at a time during standard basketball play? usual five-player rule and 3x3 variation\"}", "call_id": "call_5P5x3EaI3rhJfUdzCFdKaUvL", "id": "fc_0cca63b5ce4951db006ab36cad032487d2b15ba2c6a7d077f6", "index": 1}]
+{"name": "search_sports_reference", "args": {"query": "How many players from one basketball team are on the court at a time during standard basketball play? usual five-player rule and 3x3 variation"}, "id": "call_5P5x3EaI3rhJfUdzCFdKaUvL", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · search_sports_reference</t>
   </si>
   <si>
-    <t>01a0cc57-4c20-7081-829c-63402398d5af</t>
-  </si>
-  <si>
-    <t>{'query': 'How many players from one basketball team are on the court at a time under standard basketball rules? Include per-team and total players.'}</t>
+    <t>01a0cce0-86e8-7831-9f70-ab248e3fa642</t>
+  </si>
+  <si>
+    <t>{'query': 'How many players from one basketball team are on the court at a time during standard basketball play? usual five-player rule and 3x3 variation'}</t>
   </si>
   <si>
     <t>Standard basketball teams
@@ -482,22 +482,22 @@
     <t>R7</t>
   </si>
   <si>
-    <t>01a0cc57-4c22-7121-886e-629062250759</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "Under standard basketball rules, **5 players from each team** are on the court\u2014**10 players total**. This excludes the separate 3x3 format. [FIBA](https://about.fiba.basketball/en/our-sport/basketball)", "phase": "final_answer", "index": 0, "id": "msg_09b0e979e04b4ceb006ab3498cdb1c87d28293c62fc0271524"}]</t>
+    <t>01a0cce0-86ea-7592-b133-6c2752827ac5</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "In standard basketball, **five players from each team** are on the court at a time. Other formats vary\u2014for example, **3x3 basketball uses three players per team**. [FIBA](https://about.fiba.basketball/en/our-sport/basketball)", "phase": "final_answer", "index": 0, "id": "msg_0cca63b5ce4951db006ab36cae50e087d283ef0b2e43bd347a"}]</t>
   </si>
   <si>
     <t>R8</t>
   </si>
   <si>
-    <t>01a0cc57-519f-7132-8019-def557b7f88e</t>
-  </si>
-  <si>
-    <t>Under standard basketball rules, **5 players from each team** are on the court—**10 players total**. This excludes the separate 3x3 format. [FIBA](https://about.fiba.basketball/en/our-sport/basketball)</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "**Five players per team** are on the court at a time\u2014**10 players total**.", "phase": "final_answer", "index": 0, "id": "msg_0e625983e394fc11006ab3498e487c87d2bbf8882b96029bc3"}]</t>
+    <t>01a0cce0-8c38-7723-b72a-5b81b7556b81</t>
+  </si>
+  <si>
+    <t>In standard basketball, **five players from each team** are on the court at a time. Other formats vary—for example, **3x3 basketball uses three players per team**. [FIBA](https://about.fiba.basketball/en/our-sport/basketball)</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "In standard basketball, **five players per team** are on the court at a time.", "phase": "final_answer", "index": 0, "id": "msg_01bfb711a688d9f4006ab36cafcc9087d28a9f005ff4824f0b"}]</t>
   </si>
   <si>
     <t>Turn 3</t>
@@ -506,45 +506,45 @@
     <t>R9</t>
   </si>
   <si>
-    <t>01a0cc57-551a-77e3-abb8-5ca63238d76d</t>
+    <t>01a0cce0-9062-7552-9690-6278e93401d3</t>
   </si>
   <si>
     <t>In which year did the Berlin Wall fall?</t>
   </si>
   <si>
-    <t>[{"type": "function_call", "name": "task", "arguments": "{\"description\":\"Answer the history question: In which year did the Berlin Wall fall? Give the year and, if useful, the exact date briefly. Be concise and accurate.\",\"subagent_type\":\"history_expert\"}", "call_id": "call_iNC8lv4FELyx3XXIidkQ4pgh", "id": "fc_0e625983e394fc11006ab3498f402887d28afcfa29f77d9c41", "index": 0}]
-{"name": "task", "args": {"description": "Answer the history question: In which year did the Berlin Wall fall? Give the year and, if useful, the exact date briefly. Be concise and accurate.", "subagent_type": "history_expert"}, "id": "call_iNC8lv4FELyx3XXIidkQ4pgh", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0cc57-5960-7c80-ab11-264705f2c04b</t>
-  </si>
-  <si>
-    <t>{'description': 'Answer the history question: In which year did the Berlin Wall fall? Give the year and, if useful, the exact date briefly. Be concise and accurate.', 'subagent_type': 'history_expert'}</t>
-  </si>
-  <si>
-    <t>Command(update={'messages': [ToolMessage(content='The Berlin Wall fell in **1989**, opening on **9 November 1989**. ([Source](https://www.stiftung-berliner-mauer.de/de/ueber-uns/leichte-sprache/geschichte))', tool_call_id='call_iNC8lv4FELyx3XXIidkQ4pgh')]})</t>
+    <t>[{"type": "function_call", "name": "task", "arguments": "{\"description\":\"Answer this history question: In which year did the Berlin Wall fall? Give the year and, if useful, the date (9 November). Keep it concise and accurate.\",\"subagent_type\":\"history_expert\"}", "call_id": "call_gCytLnlCZd19JdIN3DhuOGoH", "id": "fc_01bfb711a688d9f4006ab36cb1638087d285e4d75556e6bfca", "index": 0}]
+{"name": "task", "args": {"description": "Answer this history question: In which year did the Berlin Wall fall? Give the year and, if useful, the date (9 November). Keep it concise and accurate.", "subagent_type": "history_expert"}, "id": "call_gCytLnlCZd19JdIN3DhuOGoH", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0cce0-9884-7282-9bd6-f28a2472d0cc</t>
+  </si>
+  <si>
+    <t>{'description': 'Answer this history question: In which year did the Berlin Wall fall? Give the year and, if useful, the date (9 November). Keep it concise and accurate.', 'subagent_type': 'history_expert'}</t>
+  </si>
+  <si>
+    <t>Command(update={'messages': [ToolMessage(content='The Berlin Wall fell in **1989**, on **9 November**. [Source](https://www.stiftung-berliner-mauer.de/de/ueber-uns/leichte-sprache/geschichte)', tool_call_id='call_gCytLnlCZd19JdIN3DhuOGoH')]})</t>
   </si>
   <si>
     <t>R10</t>
   </si>
   <si>
-    <t>01a0cc57-5967-7ba2-9e8a-a075058aba74</t>
+    <t>01a0cce0-9887-7ea3-a249-4e2712e4b63b</t>
   </si>
   <si>
     <t>You are the history expert. Use search_history_reference to retrieve evidence before answering the delegated question. Base factual claims on the returned passages and cite their source URLs. If no relevant evidence is found, explain the collection's limits instead of inventing an answer or claiming web research. Answer concisely. The collection is a small local teaching reference, not a complete or continually updated source.</t>
   </si>
   <si>
-    <t>[{"type": "function_call", "name": "search_history_reference", "arguments": "{\"query\":\"In which year did the Berlin Wall fall? exact date\"}", "call_id": "call_B8QUsLnalikneq4OfY4bJc4O", "id": "fc_01db159acadf188a006ab34990660087d281ae2c336cdc2be2", "index": 0}]
-{"name": "search_history_reference", "args": {"query": "In which year did the Berlin Wall fall? exact date"}, "id": "call_B8QUsLnalikneq4OfY4bJc4O", "type": "tool_call"}</t>
+    <t>[{"type": "function_call", "name": "search_history_reference", "arguments": "{\"query\":\"In which year did the Berlin Wall fall? Date 9 November\"}", "call_id": "call_wwPYoEAWNebiCjRkOFUED6Hs", "id": "fc_0bd57306de4d18b3006ab36cb339dc87d2ae9562865cc15b62", "index": 0}]
+{"name": "search_history_reference", "args": {"query": "In which year did the Berlin Wall fall? Date 9 November"}, "id": "call_wwPYoEAWNebiCjRkOFUED6Hs", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · search_history_reference</t>
   </si>
   <si>
-    <t>01a0cc57-5d9a-79f2-9f5d-8062fb9af416</t>
-  </si>
-  <si>
-    <t>{'query': 'In which year did the Berlin Wall fall? exact date'}</t>
+    <t>01a0cce0-9db8-7c60-9777-e9b2ee77195c</t>
+  </si>
+  <si>
+    <t>{'query': 'In which year did the Berlin Wall fall? Date 9 November'}</t>
   </si>
   <si>
     <t>Opening of the Berlin Wall
@@ -555,22 +555,22 @@
     <t>R11</t>
   </si>
   <si>
-    <t>01a0cc57-5d9c-75c1-bc27-c01e8f133858</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "The Berlin Wall fell in **1989**, opening on **9 November 1989**. ([Source](https://www.stiftung-berliner-mauer.de/de/ueber-uns/leichte-sprache/geschichte))", "phase": "final_answer", "index": 0, "id": "msg_01db159acadf188a006ab34991621087d286952eef0e3e910b"}]</t>
+    <t>01a0cce0-9dba-7b73-a33b-1ac39dbf419b</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "The Berlin Wall fell in **1989**, on **9 November**. [Source](https://www.stiftung-berliner-mauer.de/de/ueber-uns/leichte-sprache/geschichte)", "phase": "final_answer", "index": 0, "id": "msg_0bd57306de4d18b3006ab36cb48a0887d2b1efd650f7edcbd4"}]</t>
   </si>
   <si>
     <t>R12</t>
   </si>
   <si>
-    <t>01a0cc57-61f7-7713-94ab-4bfa41b2c80a</t>
-  </si>
-  <si>
-    <t>The Berlin Wall fell in **1989**, opening on **9 November 1989**. ([Source](https://www.stiftung-berliner-mauer.de/de/ueber-uns/leichte-sprache/geschichte))</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "The Berlin Wall fell in **1989**, on **November 9**.", "phase": "final_answer", "index": 0, "id": "msg_0e625983e394fc11006ab3499288e487d2a93e41a55020c3f8"}]</t>
+    <t>01a0cce0-a39b-7d32-b3a2-77bbfe691ac6</t>
+  </si>
+  <si>
+    <t>The Berlin Wall fell in **1989**, on **9 November**. [Source](https://www.stiftung-berliner-mauer.de/de/ueber-uns/leichte-sprache/geschichte)</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "The Berlin Wall fell in **1989**, on **November 9**.", "phase": "final_answer", "index": 0, "id": "msg_01bfb711a688d9f4006ab36cb6a54887d29d14193c12d4c596"}]</t>
   </si>
   <si>
     <t>dispatcher_agent</t>
@@ -591,7 +591,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0cc57-3255-7353-9e3a-7aab36b97590</t>
+    <t>01a0cce0-6739-77d0-8d8f-4f8e2b6b7f10</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -612,7 +612,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0cc57-3865-7480-8fc5-e2e34fd3d183</t>
+    <t>01a0cce0-6dfb-7562-82c4-b07fd21efb11</t>
   </si>
   <si>
     <t xml:space="preserve">        task</t>
@@ -633,13 +633,13 @@
     <t>Execute the movie_expert workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cc57-3866-75c0-829a-6e538dd7dd58</t>
+    <t>01a0cce0-6dfc-7842-8cb4-71621a174e6a</t>
   </si>
   <si>
     <t xml:space="preserve">                model</t>
   </si>
   <si>
-    <t>01a0cc57-3867-7ca1-b77c-388f24f3182d</t>
+    <t>01a0cce0-6dfd-7931-a66d-651cb3e0966a</t>
   </si>
   <si>
     <t xml:space="preserve">                    ChatOpenAI</t>
@@ -648,7 +648,7 @@
     <t xml:space="preserve">                tools</t>
   </si>
   <si>
-    <t>01a0cc57-3be2-7d50-a6f2-d4089f5dc1e5</t>
+    <t>01a0cce0-72b3-7931-98fd-4ba3e0494b8c</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -660,19 +660,19 @@
     <t>Look up local movie evidence by phrase; return sources or an explicit miss.</t>
   </si>
   <si>
-    <t>01a0cc57-3be7-73c2-bbff-577362126d2c</t>
-  </si>
-  <si>
-    <t>01a0cc57-3f97-7571-aeae-4cff2a6a7b62</t>
-  </si>
-  <si>
-    <t>01a0cc57-431a-78d0-b092-cfbaba3ea170</t>
-  </si>
-  <si>
-    <t>01a0cc57-431b-7451-91b5-0bd30739fc82</t>
-  </si>
-  <si>
-    <t>01a0cc57-48a9-7652-a678-b850bd606c40</t>
+    <t>01a0cce0-72b6-72b2-9083-5482a706f4e8</t>
+  </si>
+  <si>
+    <t>01a0cce0-76d2-71c0-997c-1ec4992f25c7</t>
+  </si>
+  <si>
+    <t>01a0cce0-7a23-7e50-bcc8-7c2011948a2c</t>
+  </si>
+  <si>
+    <t>01a0cce0-7a24-7381-be04-7ec2c9ebef39</t>
+  </si>
+  <si>
+    <t>01a0cce0-8083-70a2-8711-34fb64463027</t>
   </si>
   <si>
     <t xml:space="preserve">            sports_expert</t>
@@ -681,13 +681,13 @@
     <t>Execute the sports_expert workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cc57-48ab-7931-8dd9-ff0b8980cb89</t>
-  </si>
-  <si>
-    <t>01a0cc57-48ab-7931-8dd9-ff13c1d90b04</t>
-  </si>
-  <si>
-    <t>01a0cc57-4c1f-7572-98cb-dcd1c6167227</t>
+    <t>01a0cce0-8084-73f0-b870-b04ca38304cb</t>
+  </si>
+  <si>
+    <t>01a0cce0-8084-73f0-b870-b053bae845f6</t>
+  </si>
+  <si>
+    <t>01a0cce0-86e7-76a0-b17a-ca6bcaafdbe2</t>
   </si>
   <si>
     <t xml:space="preserve">                    search_sports_reference</t>
@@ -696,19 +696,19 @@
     <t>Look up local sports evidence by phrase; return sources or an explicit miss.</t>
   </si>
   <si>
-    <t>01a0cc57-4c21-7343-90e0-69f05c1d8932</t>
-  </si>
-  <si>
-    <t>01a0cc57-519e-74f3-b070-efa697f593fc</t>
-  </si>
-  <si>
-    <t>01a0cc57-5518-7462-b987-85c67754b29e</t>
-  </si>
-  <si>
-    <t>01a0cc57-5519-7520-8231-14d4266ba1ea</t>
-  </si>
-  <si>
-    <t>01a0cc57-595f-7662-b6a7-0b99fa72569f</t>
+    <t>01a0cce0-86ea-7592-b133-6c1720ff69da</t>
+  </si>
+  <si>
+    <t>01a0cce0-8c37-7ac2-ab19-eed5a841abd9</t>
+  </si>
+  <si>
+    <t>01a0cce0-9060-7c82-8556-4973efb47cb5</t>
+  </si>
+  <si>
+    <t>01a0cce0-9061-7172-8e3c-18ba4ec467d2</t>
+  </si>
+  <si>
+    <t>01a0cce0-9883-7b02-9233-be303c155e86</t>
   </si>
   <si>
     <t xml:space="preserve">            history_expert</t>
@@ -717,13 +717,13 @@
     <t>Execute the history_expert workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cc57-5961-7c02-a0f9-bb491ef2322b</t>
-  </si>
-  <si>
-    <t>01a0cc57-5963-73a3-9952-0e5355016741</t>
-  </si>
-  <si>
-    <t>01a0cc57-5d99-7e63-bfb3-ce9457f5928c</t>
+    <t>01a0cce0-9884-7282-9bd6-f290ab7207c2</t>
+  </si>
+  <si>
+    <t>01a0cce0-9885-7232-9d07-db0853895c8e</t>
+  </si>
+  <si>
+    <t>01a0cce0-9db7-7b81-a0c3-d6963e2eb0b3</t>
   </si>
   <si>
     <t xml:space="preserve">                    search_history_reference</t>
@@ -732,10 +732,10 @@
     <t>Look up local history evidence by phrase; return sources or an explicit miss.</t>
   </si>
   <si>
-    <t>01a0cc57-5d9b-7b91-8603-5b8804ea93a6</t>
-  </si>
-  <si>
-    <t>01a0cc57-61f6-71f3-9e37-ccb90bc27604</t>
+    <t>01a0cce0-9dba-7b73-a33b-1ab1a49b11bc</t>
+  </si>
+  <si>
+    <t>01a0cce0-a39a-73b3-b565-26fe9f145163</t>
   </si>
 </sst>
 </file>
@@ -1203,19 +1203,19 @@
       </c>
       <c r="E2" s="2">
         <f>IF(COUNT('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59,'Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115,'Turns'!E128,'Turns'!E143,'Turns'!E158,'Turns'!E170)=12,SUM('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59,'Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115,'Turns'!E128,'Turns'!E143,'Turns'!E158,'Turns'!E170),"Unknown")</f>
-        <v>0.001299307878</v>
+        <v>0.001329317406</v>
       </c>
       <c r="F2" s="2">
         <f>IF(COUNT('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59,'Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115,'Turns'!F128,'Turns'!F143,'Turns'!F158,'Turns'!F170)=12,SUM('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59,'Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115,'Turns'!F128,'Turns'!F143,'Turns'!F158,'Turns'!F170),"Unknown")</f>
-        <v>0.0014894</v>
+        <v>0.0015238</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>130.0</v>
+        <v>133.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>149.0</v>
+        <v>152.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1227,19 +1227,19 @@
       </c>
       <c r="E3" s="2">
         <f>IF(COUNT('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59)=4,SUM('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59),"Unknown")</f>
-        <v>0.00036116118</v>
+        <v>0.000367442244</v>
       </c>
       <c r="F3" s="2">
         <f>IF(COUNT('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59)=4,SUM('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59),"Unknown")</f>
-        <v>0.000414</v>
+        <v>0.0004212</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1364,7 +1364,7 @@
         <v>105</v>
       </c>
       <c r="D11" s="4">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
@@ -1378,15 +1378,15 @@
         <v>106</v>
       </c>
       <c r="D12" s="5">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E12" s="2">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.8623264e-05</v>
+        <v>6.281064e-05</v>
       </c>
       <c r="F12" s="2">
         <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!E17),D12*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>6.72e-05</v>
+        <v>7.2e-05</v>
       </c>
       <c r="G12" s="5">
         <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1445,15 +1445,15 @@
       </c>
       <c r="E16" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E12)=2,SUM('Turns'!E5,'Turns'!E12),"Unknown")</f>
-        <v>0.000104335452</v>
+        <v>0.000108522828</v>
       </c>
       <c r="F16" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F12)=2,SUM('Turns'!F5,'Turns'!F12),"Unknown")</f>
-        <v>0.0001196</v>
+        <v>0.0001244</v>
       </c>
       <c r="G16" s="5">
         <f>IF(ISNUMBER(E16),ROUND(E16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="H16" s="5">
         <f>IF(ISNUMBER(F16),ROUND(F16*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1510,7 +1510,7 @@
         <v>94</v>
       </c>
       <c r="D20" s="4">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>95</v>
@@ -1530,15 +1530,15 @@
         <v>97</v>
       </c>
       <c r="D21" s="5">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E21" s="2">
         <f>IF(AND(ISNUMBER(F21),ISNUMBER('Reference data'!$B$3)),F21*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.3673482e-05</v>
+        <v>3.4371378e-05</v>
       </c>
       <c r="F21" s="2">
         <f>IF(D21=0,0,IF(ISNUMBER('Reference data'!B17),D21*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>3.86e-05</v>
+        <v>3.94e-05</v>
       </c>
       <c r="G21" s="5">
         <f>IF(ISNUMBER(E21),ROUND(E21*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1607,7 +1607,7 @@
         <v>105</v>
       </c>
       <c r="D26" s="4">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="24" customHeight="1">
@@ -1651,26 +1651,26 @@
         <v>106</v>
       </c>
       <c r="D28" s="5">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E28" s="2">
         <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.9311632e-05</v>
+        <v>3.5592696e-05</v>
       </c>
       <c r="F28" s="2">
         <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!E17),D28*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>3.36e-05</v>
+        <v>4.08e-05</v>
       </c>
       <c r="G28" s="5">
         <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H28" s="5">
         <f>IF(ISNUMBER(F28),ROUND(F28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="281" customHeight="1">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="294" customHeight="1">
       <c r="A29" t="s">
         <v>117</v>
       </c>
@@ -1718,19 +1718,19 @@
       </c>
       <c r="E32" s="2">
         <f>IF(COUNT('Turns'!E21,'Turns'!E27,'Turns'!E28)=3,SUM('Turns'!E21,'Turns'!E27,'Turns'!E28),"Unknown")</f>
-        <v>7.240671e-05</v>
+        <v>7.938567e-05</v>
       </c>
       <c r="F32" s="2">
         <f>IF(COUNT('Turns'!F21,'Turns'!F27,'Turns'!F28)=3,SUM('Turns'!F21,'Turns'!F27,'Turns'!F28),"Unknown")</f>
-        <v>8.3e-05</v>
+        <v>9.1e-05</v>
       </c>
       <c r="G32" s="5">
         <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="H32" s="5">
         <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>110</v>
@@ -1783,7 +1783,7 @@
         <v>94</v>
       </c>
       <c r="D36" s="4">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>95</v>
@@ -1833,15 +1833,15 @@
         <v>97</v>
       </c>
       <c r="D38" s="5">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="E38" s="2">
         <f>IF(AND(ISNUMBER(F38),ISNUMBER('Reference data'!$B$3)),F38*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.8503772e-05</v>
+        <v>5.0248512e-05</v>
       </c>
       <c r="F38" s="2">
         <f>IF(D38=0,0,IF(ISNUMBER('Reference data'!B17),D38*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>5.56e-05</v>
+        <v>5.76e-05</v>
       </c>
       <c r="G38" s="5">
         <f>IF(ISNUMBER(E38),ROUND(E38*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1899,7 +1899,7 @@
         <v>105</v>
       </c>
       <c r="D42" s="4">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="24" customHeight="1">
@@ -1913,26 +1913,26 @@
         <v>106</v>
       </c>
       <c r="D43" s="5">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E43" s="2">
         <f>IF(AND(ISNUMBER(F43),ISNUMBER('Reference data'!$B$3)),F43*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.9201668e-05</v>
+        <v>4.2920604e-05</v>
       </c>
       <c r="F43" s="2">
         <f>IF(D43=0,0,IF(ISNUMBER('Reference data'!E17),D43*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>5.64e-05</v>
+        <v>4.92e-05</v>
       </c>
       <c r="G43" s="5">
         <f>IF(ISNUMBER(E43),ROUND(E43*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="H43" s="5">
         <f>IF(ISNUMBER(F43),ROUND(F43*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="60" customHeight="1">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="47" customHeight="1">
       <c r="A44" t="s">
         <v>126</v>
       </c>
@@ -1980,15 +1980,15 @@
       </c>
       <c r="E47" s="2">
         <f>IF(COUNT('Turns'!E37,'Turns'!E38,'Turns'!E43)=3,SUM('Turns'!E37,'Turns'!E38,'Turns'!E43),"Unknown")</f>
-        <v>9.770544e-05</v>
+        <v>9.3169116e-05</v>
       </c>
       <c r="F47" s="2">
         <f>IF(COUNT('Turns'!F37,'Turns'!F38,'Turns'!F43)=3,SUM('Turns'!F37,'Turns'!F38,'Turns'!F43),"Unknown")</f>
-        <v>0.000112</v>
+        <v>0.0001068</v>
       </c>
       <c r="G47" s="5">
         <f>IF(ISNUMBER(E47),ROUND(E47*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="H47" s="5">
         <f>IF(ISNUMBER(F47),ROUND(F47*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2009,7 +2009,7 @@
         <v>94</v>
       </c>
       <c r="D48" s="4">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>95</v>
@@ -2059,15 +2059,15 @@
         <v>97</v>
       </c>
       <c r="D50" s="5">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E50" s="2">
         <f>IF(AND(ISNUMBER(F50),ISNUMBER('Reference data'!$B$3)),F50*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.4729854e-05</v>
+        <v>6.4380906e-05</v>
       </c>
       <c r="F50" s="2">
         <f>IF(D50=0,0,IF(ISNUMBER('Reference data'!B17),D50*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>7.42e-05</v>
+        <v>7.38e-05</v>
       </c>
       <c r="G50" s="5">
         <f>IF(ISNUMBER(E50),ROUND(E50*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2206,11 +2206,11 @@
       </c>
       <c r="E59" s="2">
         <f>IF(COUNT('Turns'!E49,'Turns'!E50,'Turns'!E55)=3,SUM('Turns'!E49,'Turns'!E50,'Turns'!E55),"Unknown")</f>
-        <v>8.6713578e-05</v>
+        <v>8.636463e-05</v>
       </c>
       <c r="F59" s="2">
         <f>IF(COUNT('Turns'!F49,'Turns'!F50,'Turns'!F55)=3,SUM('Turns'!F49,'Turns'!F50,'Turns'!F55),"Unknown")</f>
-        <v>9.94e-05</v>
+        <v>9.9e-05</v>
       </c>
       <c r="G59" s="5">
         <f>IF(ISNUMBER(E59),ROUND(E59*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2233,19 +2233,19 @@
       </c>
       <c r="E60" s="2">
         <f>IF(COUNT('Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115)=4,SUM('Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115),"Unknown")</f>
-        <v>0.000473173488</v>
+        <v>0.000493063524</v>
       </c>
       <c r="F60" s="2">
         <f>IF(COUNT('Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115)=4,SUM('Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115),"Unknown")</f>
-        <v>0.0005424</v>
+        <v>0.0005652</v>
       </c>
       <c r="G60" s="5">
         <f>IF(ISNUMBER(E60),ROUND(E60*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
       <c r="H60" s="5">
         <f>IF(ISNUMBER(F60),ROUND(F60*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>54.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="61" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -2259,7 +2259,7 @@
         <v>94</v>
       </c>
       <c r="D61" s="4">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>95</v>
@@ -2309,15 +2309,15 @@
         <v>97</v>
       </c>
       <c r="D63" s="5">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E63" s="2">
         <f>IF(AND(ISNUMBER(F63),ISNUMBER('Reference data'!$B$3)),F63*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.1359866e-05</v>
+        <v>7.1010918e-05</v>
       </c>
       <c r="F63" s="2">
         <f>IF(D63=0,0,IF(ISNUMBER('Reference data'!B17),D63*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>8.18e-05</v>
+        <v>8.14e-05</v>
       </c>
       <c r="G63" s="5">
         <f>IF(ISNUMBER(E63),ROUND(E63*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2375,7 +2375,7 @@
         <v>105</v>
       </c>
       <c r="D67" s="4">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="24" customHeight="1">
@@ -2389,23 +2389,23 @@
         <v>106</v>
       </c>
       <c r="D68" s="5">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E68" s="2">
         <f>IF(AND(ISNUMBER(F68),ISNUMBER('Reference data'!$B$3)),F68*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.2232236e-05</v>
+        <v>8.1653832e-05</v>
       </c>
       <c r="F68" s="2">
         <f>IF(D68=0,0,IF(ISNUMBER('Reference data'!E17),D68*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>8.28e-05</v>
+        <v>9.36e-05</v>
       </c>
       <c r="G68" s="5">
         <f>IF(ISNUMBER(E68),ROUND(E68*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="H68" s="5">
         <f>IF(ISNUMBER(F68),ROUND(F68*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="151" customHeight="1">
@@ -2456,19 +2456,19 @@
       </c>
       <c r="E72" s="2">
         <f>IF(COUNT('Turns'!E62,'Turns'!E63,'Turns'!E68)=3,SUM('Turns'!E62,'Turns'!E63,'Turns'!E68),"Unknown")</f>
-        <v>0.000143592102</v>
+        <v>0.00015266475</v>
       </c>
       <c r="F72" s="2">
         <f>IF(COUNT('Turns'!F62,'Turns'!F63,'Turns'!F68)=3,SUM('Turns'!F62,'Turns'!F63,'Turns'!F68),"Unknown")</f>
-        <v>0.0001646</v>
+        <v>0.000175</v>
       </c>
       <c r="G72" s="5">
         <f>IF(ISNUMBER(E72),ROUND(E72*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="H72" s="5">
         <f>IF(ISNUMBER(F72),ROUND(F72*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="K72" s="4" t="s">
         <v>110</v>
@@ -2521,7 +2521,7 @@
         <v>94</v>
       </c>
       <c r="D76" s="4">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>95</v>
@@ -2541,15 +2541,15 @@
         <v>97</v>
       </c>
       <c r="D77" s="5">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E77" s="2">
         <f>IF(AND(ISNUMBER(F77),ISNUMBER('Reference data'!$B$3)),F77*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.5418222e-05</v>
+        <v>3.6988488e-05</v>
       </c>
       <c r="F77" s="2">
         <f>IF(D77=0,0,IF(ISNUMBER('Reference data'!B17),D77*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>4.06e-05</v>
+        <v>4.24e-05</v>
       </c>
       <c r="G77" s="5">
         <f>IF(ISNUMBER(E77),ROUND(E77*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2618,7 +2618,7 @@
         <v>105</v>
       </c>
       <c r="D82" s="4">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="24" customHeight="1">
@@ -2662,15 +2662,15 @@
         <v>106</v>
       </c>
       <c r="D84" s="5">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E84" s="2">
         <f>IF(AND(ISNUMBER(F84),ISNUMBER('Reference data'!$B$3)),F84*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.9201668e-05</v>
+        <v>5.23422e-05</v>
       </c>
       <c r="F84" s="2">
         <f>IF(D84=0,0,IF(ISNUMBER('Reference data'!E17),D84*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>5.64e-05</v>
+        <v>6e-05</v>
       </c>
       <c r="G84" s="5">
         <f>IF(ISNUMBER(E84),ROUND(E84*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2729,15 +2729,15 @@
       </c>
       <c r="E88" s="2">
         <f>IF(COUNT('Turns'!E77,'Turns'!E83,'Turns'!E84)=3,SUM('Turns'!E77,'Turns'!E83,'Turns'!E84),"Unknown")</f>
-        <v>9.4041486e-05</v>
+        <v>9.8752284e-05</v>
       </c>
       <c r="F88" s="2">
         <f>IF(COUNT('Turns'!F77,'Turns'!F83,'Turns'!F84)=3,SUM('Turns'!F77,'Turns'!F83,'Turns'!F84),"Unknown")</f>
-        <v>0.0001078</v>
+        <v>0.0001132</v>
       </c>
       <c r="G88" s="5">
         <f>IF(ISNUMBER(E88),ROUND(E88*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="H88" s="5">
         <f>IF(ISNUMBER(F88),ROUND(F88*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2794,7 +2794,7 @@
         <v>94</v>
       </c>
       <c r="D92" s="4">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="J92" s="4" t="s">
         <v>95</v>
@@ -2844,15 +2844,15 @@
         <v>97</v>
       </c>
       <c r="D94" s="5">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="E94" s="2">
         <f>IF(AND(ISNUMBER(F94),ISNUMBER('Reference data'!$B$3)),F94*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.5133784e-05</v>
+        <v>5.7227472e-05</v>
       </c>
       <c r="F94" s="2">
         <f>IF(D94=0,0,IF(ISNUMBER('Reference data'!B17),D94*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6.32e-05</v>
+        <v>6.56e-05</v>
       </c>
       <c r="G94" s="5">
         <f>IF(ISNUMBER(E94),ROUND(E94*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="H94" s="5">
         <f>IF(ISNUMBER(F94),ROUND(F94*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="60" customHeight="1">
@@ -2910,7 +2910,7 @@
         <v>105</v>
       </c>
       <c r="D98" s="4">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="24" customHeight="1">
@@ -2924,15 +2924,15 @@
         <v>106</v>
       </c>
       <c r="D99" s="5">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E99" s="2">
         <f>IF(AND(ISNUMBER(F99),ISNUMBER('Reference data'!$B$3)),F99*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.0716952e-05</v>
+        <v>6.4904328e-05</v>
       </c>
       <c r="F99" s="2">
         <f>IF(D99=0,0,IF(ISNUMBER('Reference data'!E17),D99*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>6.96e-05</v>
+        <v>7.44e-05</v>
       </c>
       <c r="G99" s="5">
         <f>IF(ISNUMBER(E99),ROUND(E99*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2943,7 +2943,7 @@
         <v>7.0</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="60" customHeight="1">
+    <row r="100" spans="1:13" ht="73" customHeight="1">
       <c r="A100" t="s">
         <v>151</v>
       </c>
@@ -2991,11 +2991,11 @@
       </c>
       <c r="E103" s="2">
         <f>IF(COUNT('Turns'!E93,'Turns'!E94,'Turns'!E99)=3,SUM('Turns'!E93,'Turns'!E94,'Turns'!E99),"Unknown")</f>
-        <v>0.000115850736</v>
+        <v>0.0001221318</v>
       </c>
       <c r="F103" s="2">
         <f>IF(COUNT('Turns'!F93,'Turns'!F94,'Turns'!F99)=3,SUM('Turns'!F93,'Turns'!F94,'Turns'!F99),"Unknown")</f>
-        <v>0.0001328</v>
+        <v>0.00014</v>
       </c>
       <c r="G103" s="5">
         <f>IF(ISNUMBER(E103),ROUND(E103*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="H103" s="5">
         <f>IF(ISNUMBER(F103),ROUND(F103*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="K103" s="4" t="s">
         <v>110</v>
@@ -3020,7 +3020,7 @@
         <v>94</v>
       </c>
       <c r="D104" s="4">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="J104" s="4" t="s">
         <v>95</v>
@@ -3070,19 +3070,19 @@
         <v>97</v>
       </c>
       <c r="D106" s="5">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="E106" s="2">
         <f>IF(AND(ISNUMBER(F106),ISNUMBER('Reference data'!$B$3)),F106*'Reference data'!$B$3,"Unknown")</f>
-        <v>9.4564908e-05</v>
+        <v>9.6484122e-05</v>
       </c>
       <c r="F106" s="2">
         <f>IF(D106=0,0,IF(ISNUMBER('Reference data'!B17),D106*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.0001084</v>
+        <v>0.0001106</v>
       </c>
       <c r="G106" s="5">
         <f>IF(ISNUMBER(E106),ROUND(E106*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="H106" s="5">
         <f>IF(ISNUMBER(F106),ROUND(F106*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3136,7 +3136,7 @@
         <v>105</v>
       </c>
       <c r="D110" s="4">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="24" customHeight="1">
@@ -3150,19 +3150,19 @@
         <v>106</v>
       </c>
       <c r="D111" s="5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E111" s="2">
         <f>IF(AND(ISNUMBER(F111),ISNUMBER('Reference data'!$B$3)),F111*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.5124256e-05</v>
+        <v>2.3030568e-05</v>
       </c>
       <c r="F111" s="2">
         <f>IF(D111=0,0,IF(ISNUMBER('Reference data'!E17),D111*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.88e-05</v>
+        <v>2.64e-05</v>
       </c>
       <c r="G111" s="5">
         <f>IF(ISNUMBER(E111),ROUND(E111*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H111" s="5">
         <f>IF(ISNUMBER(F111),ROUND(F111*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3217,11 +3217,11 @@
       </c>
       <c r="E115" s="2">
         <f>IF(COUNT('Turns'!E105,'Turns'!E106,'Turns'!E111)=3,SUM('Turns'!E105,'Turns'!E106,'Turns'!E111),"Unknown")</f>
-        <v>0.000119689164</v>
+        <v>0.00011951469</v>
       </c>
       <c r="F115" s="2">
         <f>IF(COUNT('Turns'!F105,'Turns'!F106,'Turns'!F111)=3,SUM('Turns'!F105,'Turns'!F106,'Turns'!F111),"Unknown")</f>
-        <v>0.0001372</v>
+        <v>0.000137</v>
       </c>
       <c r="G115" s="5">
         <f>IF(ISNUMBER(E115),ROUND(E115*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3244,19 +3244,19 @@
       </c>
       <c r="E116" s="2">
         <f>IF(COUNT('Turns'!E128,'Turns'!E143,'Turns'!E158,'Turns'!E170)=4,SUM('Turns'!E128,'Turns'!E143,'Turns'!E158,'Turns'!E170),"Unknown")</f>
-        <v>0.00046497321</v>
+        <v>0.000468811638</v>
       </c>
       <c r="F116" s="2">
         <f>IF(COUNT('Turns'!F128,'Turns'!F143,'Turns'!F158,'Turns'!F170)=4,SUM('Turns'!F128,'Turns'!F143,'Turns'!F158,'Turns'!F170),"Unknown")</f>
-        <v>0.000533</v>
+        <v>0.0005374</v>
       </c>
       <c r="G116" s="5">
         <f>IF(ISNUMBER(E116),ROUND(E116*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="H116" s="5">
         <f>IF(ISNUMBER(F116),ROUND(F116*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="117" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -3270,7 +3270,7 @@
         <v>94</v>
       </c>
       <c r="D117" s="4">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="J117" s="4" t="s">
         <v>95</v>
@@ -3320,15 +3320,15 @@
         <v>97</v>
       </c>
       <c r="D119" s="5">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="E119" s="2">
         <f>IF(AND(ISNUMBER(F119),ISNUMBER('Reference data'!$B$3)),F119*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000101369394</v>
+        <v>0.00010293966</v>
       </c>
       <c r="F119" s="2">
         <f>IF(D119=0,0,IF(ISNUMBER('Reference data'!B17),D119*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.0001162</v>
+        <v>0.000118</v>
       </c>
       <c r="G119" s="5">
         <f>IF(ISNUMBER(E119),ROUND(E119*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3386,7 +3386,7 @@
         <v>105</v>
       </c>
       <c r="D123" s="4">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="24" customHeight="1">
@@ -3400,15 +3400,15 @@
         <v>106</v>
       </c>
       <c r="D124" s="5">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E124" s="2">
         <f>IF(AND(ISNUMBER(F124),ISNUMBER('Reference data'!$B$3)),F124*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.757642e-05</v>
+        <v>5.9670108e-05</v>
       </c>
       <c r="F124" s="2">
         <f>IF(D124=0,0,IF(ISNUMBER('Reference data'!E17),D124*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>6.6e-05</v>
+        <v>6.84e-05</v>
       </c>
       <c r="G124" s="5">
         <f>IF(ISNUMBER(E124),ROUND(E124*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3467,11 +3467,11 @@
       </c>
       <c r="E128" s="2">
         <f>IF(COUNT('Turns'!E118,'Turns'!E119,'Turns'!E124)=3,SUM('Turns'!E118,'Turns'!E119,'Turns'!E124),"Unknown")</f>
-        <v>0.000158945814</v>
+        <v>0.000162609768</v>
       </c>
       <c r="F128" s="2">
         <f>IF(COUNT('Turns'!F118,'Turns'!F119,'Turns'!F124)=3,SUM('Turns'!F118,'Turns'!F119,'Turns'!F124),"Unknown")</f>
-        <v>0.0001822</v>
+        <v>0.0001864</v>
       </c>
       <c r="G128" s="5">
         <f>IF(ISNUMBER(E128),ROUND(E128*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="H128" s="5">
         <f>IF(ISNUMBER(F128),ROUND(F128*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="K128" s="4" t="s">
         <v>110</v>
@@ -3532,7 +3532,7 @@
         <v>94</v>
       </c>
       <c r="D132" s="4">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J132" s="4" t="s">
         <v>95</v>
@@ -3552,15 +3552,15 @@
         <v>97</v>
       </c>
       <c r="D133" s="5">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E133" s="2">
         <f>IF(AND(ISNUMBER(F133),ISNUMBER('Reference data'!$B$3)),F133*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.2626638e-05</v>
+        <v>3.2975586e-05</v>
       </c>
       <c r="F133" s="2">
         <f>IF(D133=0,0,IF(ISNUMBER('Reference data'!B17),D133*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>3.74e-05</v>
+        <v>3.78e-05</v>
       </c>
       <c r="G133" s="5">
         <f>IF(ISNUMBER(E133),ROUND(E133*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3629,7 +3629,7 @@
         <v>105</v>
       </c>
       <c r="D138" s="4">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="24" customHeight="1">
@@ -3643,15 +3643,15 @@
         <v>106</v>
       </c>
       <c r="D139" s="5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E139" s="2">
         <f>IF(AND(ISNUMBER(F139),ISNUMBER('Reference data'!$B$3)),F139*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.0358476e-05</v>
+        <v>3.2452164e-05</v>
       </c>
       <c r="F139" s="2">
         <f>IF(D139=0,0,IF(ISNUMBER('Reference data'!E17),D139*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>3.48e-05</v>
+        <v>3.72e-05</v>
       </c>
       <c r="G139" s="5">
         <f>IF(ISNUMBER(E139),ROUND(E139*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="H139" s="5">
         <f>IF(ISNUMBER(F139),ROUND(F139*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="140" spans="1:13" ht="86" customHeight="1">
@@ -3710,19 +3710,19 @@
       </c>
       <c r="E143" s="2">
         <f>IF(COUNT('Turns'!E133,'Turns'!E139)=2,SUM('Turns'!E133,'Turns'!E139),"Unknown")</f>
-        <v>6.2985114e-05</v>
+        <v>6.542775e-05</v>
       </c>
       <c r="F143" s="2">
         <f>IF(COUNT('Turns'!F133,'Turns'!F139)=2,SUM('Turns'!F133,'Turns'!F139),"Unknown")</f>
-        <v>7.22e-05</v>
+        <v>7.5e-05</v>
       </c>
       <c r="G143" s="5">
         <f>IF(ISNUMBER(E143),ROUND(E143*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="H143" s="5">
         <f>IF(ISNUMBER(F143),ROUND(F143*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="K143" s="4" t="s">
         <v>110</v>
@@ -3775,7 +3775,7 @@
         <v>94</v>
       </c>
       <c r="D147" s="4">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="J147" s="4" t="s">
         <v>95</v>
@@ -3825,15 +3825,15 @@
         <v>97</v>
       </c>
       <c r="D149" s="5">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E149" s="2">
         <f>IF(AND(ISNUMBER(F149),ISNUMBER('Reference data'!$B$3)),F149*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.9027194e-05</v>
+        <v>4.972509e-05</v>
       </c>
       <c r="F149" s="2">
         <f>IF(D149=0,0,IF(ISNUMBER('Reference data'!B17),D149*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>5.62e-05</v>
+        <v>5.7e-05</v>
       </c>
       <c r="G149" s="5">
         <f>IF(ISNUMBER(E149),ROUND(E149*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3891,7 +3891,7 @@
         <v>105</v>
       </c>
       <c r="D153" s="4">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="24" customHeight="1">
@@ -3905,15 +3905,15 @@
         <v>106</v>
       </c>
       <c r="D154" s="5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E154" s="2">
         <f>IF(AND(ISNUMBER(F154),ISNUMBER('Reference data'!$B$3)),F154*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-05</v>
+        <v>4.8154824e-05</v>
       </c>
       <c r="F154" s="2">
         <f>IF(D154=0,0,IF(ISNUMBER('Reference data'!E17),D154*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>6e-05</v>
+        <v>5.52e-05</v>
       </c>
       <c r="G154" s="5">
         <f>IF(ISNUMBER(E154),ROUND(E154*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3972,11 +3972,11 @@
       </c>
       <c r="E158" s="2">
         <f>IF(COUNT('Turns'!E148,'Turns'!E149,'Turns'!E154)=3,SUM('Turns'!E148,'Turns'!E149,'Turns'!E154),"Unknown")</f>
-        <v>0.000101369394</v>
+        <v>9.7879914e-05</v>
       </c>
       <c r="F158" s="2">
         <f>IF(COUNT('Turns'!F148,'Turns'!F149,'Turns'!F154)=3,SUM('Turns'!F148,'Turns'!F149,'Turns'!F154),"Unknown")</f>
-        <v>0.0001162</v>
+        <v>0.0001122</v>
       </c>
       <c r="G158" s="5">
         <f>IF(ISNUMBER(E158),ROUND(E158*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="H158" s="5">
         <f>IF(ISNUMBER(F158),ROUND(F158*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="K158" s="4" t="s">
         <v>110</v>
@@ -4001,7 +4001,7 @@
         <v>94</v>
       </c>
       <c r="D159" s="4">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="J159" s="4" t="s">
         <v>95</v>
@@ -4051,15 +4051,15 @@
         <v>97</v>
       </c>
       <c r="D161" s="5">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="E161" s="2">
         <f>IF(AND(ISNUMBER(F161),ISNUMBER('Reference data'!$B$3)),F161*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000120736008</v>
+        <v>0.000121957326</v>
       </c>
       <c r="F161" s="2">
         <f>IF(D161=0,0,IF(ISNUMBER('Reference data'!B17),D161*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.0001384</v>
+        <v>0.0001398</v>
       </c>
       <c r="G161" s="5">
         <f>IF(ISNUMBER(E161),ROUND(E161*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4198,11 +4198,11 @@
       </c>
       <c r="E170" s="2">
         <f>IF(COUNT('Turns'!E160,'Turns'!E161,'Turns'!E166)=3,SUM('Turns'!E160,'Turns'!E161,'Turns'!E166),"Unknown")</f>
-        <v>0.000141672888</v>
+        <v>0.000142894206</v>
       </c>
       <c r="F170" s="2">
         <f>IF(COUNT('Turns'!F160,'Turns'!F161,'Turns'!F166)=3,SUM('Turns'!F160,'Turns'!F161,'Turns'!F166),"Unknown")</f>
-        <v>0.0001624</v>
+        <v>0.0001638</v>
       </c>
       <c r="G170" s="5">
         <f>IF(ISNUMBER(E170),ROUND(E170*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4360,15 +4360,15 @@
       </c>
       <c r="J2" s="2">
         <f>IF(COUNT('Turns'!D5,'Turns'!D21,'Turns'!D38,'Turns'!D50)=4,SUM('Turns'!D5,'Turns'!D21,'Turns'!D38,'Turns'!D50),"Unknown")</f>
-        <v>1104.0</v>
+        <v>1116.0</v>
       </c>
       <c r="K2" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E21,'Turns'!E38,'Turns'!E50)=4,SUM('Turns'!E5,'Turns'!E21,'Turns'!E38,'Turns'!E50),"Unknown")</f>
-        <v>0.000192619296</v>
+        <v>0.000194712984</v>
       </c>
       <c r="L2" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F21,'Turns'!F38,'Turns'!F50)=4,SUM('Turns'!F5,'Turns'!F21,'Turns'!F38,'Turns'!F50),"Unknown")</f>
-        <v>0.0002208</v>
+        <v>0.0002232</v>
       </c>
       <c r="M2" s="2">
         <f>IF(COUNT('Turns'!D37,'Turns'!D49)=2,SUM('Turns'!D37,'Turns'!D49),"Unknown")</f>
@@ -4393,15 +4393,15 @@
       </c>
       <c r="S2" s="2">
         <f>IF(COUNT('Turns'!D12,'Turns'!D28,'Turns'!D43,'Turns'!D55)=4,SUM('Turns'!D12,'Turns'!D28,'Turns'!D43,'Turns'!D55),"Unknown")</f>
-        <v>152.0</v>
+        <v>156.0</v>
       </c>
       <c r="T2" s="2">
         <f>IF(COUNT('Turns'!E12,'Turns'!E28,'Turns'!E43,'Turns'!E55)=4,SUM('Turns'!E12,'Turns'!E28,'Turns'!E43,'Turns'!E55),"Unknown")</f>
-        <v>0.000159120288</v>
+        <v>0.000163307664</v>
       </c>
       <c r="U2" s="2">
         <f>IF(COUNT('Turns'!F12,'Turns'!F28,'Turns'!F43,'Turns'!F55)=4,SUM('Turns'!F12,'Turns'!F28,'Turns'!F43,'Turns'!F55),"Unknown")</f>
-        <v>0.0001824</v>
+        <v>0.0001872</v>
       </c>
       <c r="V2" s="2">
         <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
@@ -4417,22 +4417,22 @@
       </c>
       <c r="Y2" s="2">
         <f>IF(COUNT('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59)=4,SUM('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59),"Unknown")</f>
-        <v>0.00036116118</v>
+        <v>0.000367442244</v>
       </c>
       <c r="Z2" s="2">
         <f>IF(COUNT('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59)=4,SUM('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59),"Unknown")</f>
-        <v>0.000414</v>
+        <v>0.0004212</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>4257.662</v>
+        <v>4827.616</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>184</v>
@@ -4495,15 +4495,15 @@
       </c>
       <c r="S3" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>56.0</v>
+        <v>60.0</v>
       </c>
       <c r="T3" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>5.8623264e-05</v>
+        <v>6.281064e-05</v>
       </c>
       <c r="U3" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>6.72e-05</v>
+        <v>7.2e-05</v>
       </c>
       <c r="V3" s="2">
         <v>0</v>
@@ -4516,22 +4516,22 @@
       </c>
       <c r="Y3" s="2">
         <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
-        <v>0.000104335452</v>
+        <v>0.000108522828</v>
       </c>
       <c r="Z3" s="2">
         <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
-        <v>0.0001196</v>
+        <v>0.0001244</v>
       </c>
       <c r="AA3" s="5">
         <f>IF(ISNUMBER(Y3),ROUND(Y3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="AB3" s="5">
         <f>IF(ISNUMBER(Z3),ROUND(Z3*'Reference data'!$B$2,0),"Unknown")</f>
         <v>12.0</v>
       </c>
       <c r="AD3" s="1">
-        <v>1550.659</v>
+        <v>1728.893</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>184</v>
@@ -4597,15 +4597,15 @@
       </c>
       <c r="S4" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>56.0</v>
+        <v>60.0</v>
       </c>
       <c r="T4" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>5.8623264e-05</v>
+        <v>6.281064e-05</v>
       </c>
       <c r="U4" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>6.72e-05</v>
+        <v>7.2e-05</v>
       </c>
       <c r="V4" s="2">
         <v>0</v>
@@ -4618,15 +4618,15 @@
       </c>
       <c r="Y4" s="2">
         <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
-        <v>0.000104335452</v>
+        <v>0.000108522828</v>
       </c>
       <c r="Z4" s="2">
         <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
-        <v>0.0001196</v>
+        <v>0.0001244</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4636,7 +4636,7 @@
         <v>93</v>
       </c>
       <c r="AD4" s="1">
-        <v>1548.277</v>
+        <v>1725.688</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>191</v>
@@ -4669,15 +4669,15 @@
       </c>
       <c r="J5" s="2">
         <f>IF(COUNT('Turns'!D21,'Turns'!D38)=2,SUM('Turns'!D21,'Turns'!D38),"Unknown")</f>
-        <v>471.0</v>
+        <v>485.0</v>
       </c>
       <c r="K5" s="2">
         <f>IF(COUNT('Turns'!E21,'Turns'!E38)=2,SUM('Turns'!E21,'Turns'!E38),"Unknown")</f>
-        <v>8.2177254e-05</v>
+        <v>8.461989e-05</v>
       </c>
       <c r="L5" s="2">
         <f>IF(COUNT('Turns'!F21,'Turns'!F38)=2,SUM('Turns'!F21,'Turns'!F38),"Unknown")</f>
-        <v>9.42e-05</v>
+        <v>9.7e-05</v>
       </c>
       <c r="M5" s="2">
         <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
@@ -4726,11 +4726,11 @@
       </c>
       <c r="Y5" s="2">
         <f>IF(COUNT('Turns'!E32,'Turns'!E47)=2,SUM('Turns'!E32,'Turns'!E47),"Unknown")</f>
-        <v>0.00017011215</v>
+        <v>0.000172554786</v>
       </c>
       <c r="Z5" s="2">
         <f>IF(COUNT('Turns'!F32,'Turns'!F47)=2,SUM('Turns'!F32,'Turns'!F47),"Unknown")</f>
-        <v>0.000195</v>
+        <v>0.0001978</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4741,7 +4741,7 @@
         <v>20.0</v>
       </c>
       <c r="AD5" s="1">
-        <v>1840.967</v>
+        <v>2261.826</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>184</v>
@@ -4774,15 +4774,15 @@
       </c>
       <c r="J6" s="2">
         <f>IF(COUNT('Turns'!D21,'Turns'!D38)=2,SUM('Turns'!D21,'Turns'!D38),"Unknown")</f>
-        <v>471.0</v>
+        <v>485.0</v>
       </c>
       <c r="K6" s="2">
         <f>IF(COUNT('Turns'!E21,'Turns'!E38)=2,SUM('Turns'!E21,'Turns'!E38),"Unknown")</f>
-        <v>8.2177254e-05</v>
+        <v>8.461989e-05</v>
       </c>
       <c r="L6" s="2">
         <f>IF(COUNT('Turns'!F21,'Turns'!F38)=2,SUM('Turns'!F21,'Turns'!F38),"Unknown")</f>
-        <v>9.42e-05</v>
+        <v>9.7e-05</v>
       </c>
       <c r="M6" s="2">
         <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
@@ -4831,11 +4831,11 @@
       </c>
       <c r="Y6" s="2">
         <f>IF(COUNT('Turns'!E32,'Turns'!E47)=2,SUM('Turns'!E32,'Turns'!E47),"Unknown")</f>
-        <v>0.00017011215</v>
+        <v>0.000172554786</v>
       </c>
       <c r="Z6" s="2">
         <f>IF(COUNT('Turns'!F32,'Turns'!F47)=2,SUM('Turns'!F32,'Turns'!F47),"Unknown")</f>
-        <v>0.000195</v>
+        <v>0.0001978</v>
       </c>
       <c r="AA6" s="5">
         <f>IF(ISNUMBER(Y6),ROUND(Y6*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4846,7 +4846,7 @@
         <v>20.0</v>
       </c>
       <c r="AD6" s="1">
-        <v>1839.561</v>
+        <v>2260.541</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>184</v>
@@ -4879,15 +4879,15 @@
       </c>
       <c r="J7" s="2">
         <f>IF(COUNT('Turns'!D21,'Turns'!D38)=2,SUM('Turns'!D21,'Turns'!D38),"Unknown")</f>
-        <v>471.0</v>
+        <v>485.0</v>
       </c>
       <c r="K7" s="2">
         <f>IF(COUNT('Turns'!E21,'Turns'!E38)=2,SUM('Turns'!E21,'Turns'!E38),"Unknown")</f>
-        <v>8.2177254e-05</v>
+        <v>8.461989e-05</v>
       </c>
       <c r="L7" s="2">
         <f>IF(COUNT('Turns'!F21,'Turns'!F38)=2,SUM('Turns'!F21,'Turns'!F38),"Unknown")</f>
-        <v>9.42e-05</v>
+        <v>9.7e-05</v>
       </c>
       <c r="M7" s="2">
         <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
@@ -4936,11 +4936,11 @@
       </c>
       <c r="Y7" s="2">
         <f>IF(COUNT('Turns'!E32,'Turns'!E47)=2,SUM('Turns'!E32,'Turns'!E47),"Unknown")</f>
-        <v>0.00017011215</v>
+        <v>0.000172554786</v>
       </c>
       <c r="Z7" s="2">
         <f>IF(COUNT('Turns'!F32,'Turns'!F47)=2,SUM('Turns'!F32,'Turns'!F47),"Unknown")</f>
-        <v>0.000195</v>
+        <v>0.0001978</v>
       </c>
       <c r="AA7" s="5">
         <f>IF(ISNUMBER(Y7),ROUND(Y7*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4951,7 +4951,7 @@
         <v>20.0</v>
       </c>
       <c r="AD7" s="1">
-        <v>1838.287</v>
+        <v>2259.592</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>184</v>
@@ -4984,15 +4984,15 @@
       </c>
       <c r="J8" s="2">
         <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
-        <v>193.0</v>
+        <v>197.0</v>
       </c>
       <c r="K8" s="2">
         <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
-        <v>3.3673482e-05</v>
+        <v>3.4371378e-05</v>
       </c>
       <c r="L8" s="2">
         <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
-        <v>3.86e-05</v>
+        <v>3.94e-05</v>
       </c>
       <c r="M8" s="2">
         <v>0</v>
@@ -5014,15 +5014,15 @@
       </c>
       <c r="S8" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>28.0</v>
+        <v>34.0</v>
       </c>
       <c r="T8" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>2.9311632e-05</v>
+        <v>3.5592696e-05</v>
       </c>
       <c r="U8" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>3.36e-05</v>
+        <v>4.08e-05</v>
       </c>
       <c r="V8" s="2">
         <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
@@ -5038,22 +5038,22 @@
       </c>
       <c r="Y8" s="2">
         <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>7.240671e-05</v>
+        <v>7.938567e-05</v>
       </c>
       <c r="Z8" s="2">
         <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>8.3e-05</v>
+        <v>9.1e-05</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="AD8" s="1">
-        <v>889.51</v>
+        <v>1205.046</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>184</v>
@@ -5076,7 +5076,7 @@
         <v>110</v>
       </c>
       <c r="F9" s="1">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>190</v>
@@ -5089,15 +5089,15 @@
       </c>
       <c r="J9" s="2">
         <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
-        <v>193.0</v>
+        <v>197.0</v>
       </c>
       <c r="K9" s="2">
         <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
-        <v>3.3673482e-05</v>
+        <v>3.4371378e-05</v>
       </c>
       <c r="L9" s="2">
         <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
-        <v>3.86e-05</v>
+        <v>3.94e-05</v>
       </c>
       <c r="M9" s="2">
         <v>0</v>
@@ -5119,15 +5119,15 @@
       </c>
       <c r="S9" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>28.0</v>
+        <v>34.0</v>
       </c>
       <c r="T9" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>2.9311632e-05</v>
+        <v>3.5592696e-05</v>
       </c>
       <c r="U9" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>3.36e-05</v>
+        <v>4.08e-05</v>
       </c>
       <c r="V9" s="2">
         <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
@@ -5143,25 +5143,25 @@
       </c>
       <c r="Y9" s="2">
         <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>7.240671e-05</v>
+        <v>7.938567e-05</v>
       </c>
       <c r="Z9" s="2">
         <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>8.3e-05</v>
+        <v>9.1e-05</v>
       </c>
       <c r="AA9" s="5">
         <f>IF(ISNUMBER(Y9),ROUND(Y9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="AB9" s="5">
         <f>IF(ISNUMBER(Z9),ROUND(Z9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="AC9" s="1" t="s">
         <v>117</v>
       </c>
       <c r="AD9" s="1">
-        <v>885.907</v>
+        <v>1202.645</v>
       </c>
       <c r="AE9" s="1" t="s">
         <v>191</v>
@@ -5193,7 +5193,7 @@
         <v>200</v>
       </c>
       <c r="AD10" s="1">
-        <v>3.946</v>
+        <v>1.987</v>
       </c>
       <c r="AE10" s="1" t="s">
         <v>206</v>
@@ -5225,7 +5225,7 @@
         <v>205</v>
       </c>
       <c r="AD11" s="1">
-        <v>1.179</v>
+        <v>0.622</v>
       </c>
       <c r="AE11" s="1" t="s">
         <v>206</v>
@@ -5258,15 +5258,15 @@
       </c>
       <c r="J12" s="2">
         <f>IF(COUNT('Turns'!D38)=1,SUM('Turns'!D38),"Unknown")</f>
-        <v>278.0</v>
+        <v>288.0</v>
       </c>
       <c r="K12" s="2">
         <f>IF(COUNT('Turns'!E38)=1,SUM('Turns'!E38),"Unknown")</f>
-        <v>4.8503772e-05</v>
+        <v>5.0248512e-05</v>
       </c>
       <c r="L12" s="2">
         <f>IF(COUNT('Turns'!F38)=1,SUM('Turns'!F38),"Unknown")</f>
-        <v>5.56e-05</v>
+        <v>5.76e-05</v>
       </c>
       <c r="M12" s="2">
         <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
@@ -5291,15 +5291,15 @@
       </c>
       <c r="S12" s="2">
         <f>IF(COUNT('Turns'!D43)=1,SUM('Turns'!D43),"Unknown")</f>
-        <v>47.0</v>
+        <v>41.0</v>
       </c>
       <c r="T12" s="2">
         <f>IF(COUNT('Turns'!E43)=1,SUM('Turns'!E43),"Unknown")</f>
-        <v>4.9201668e-05</v>
+        <v>4.2920604e-05</v>
       </c>
       <c r="U12" s="2">
         <f>IF(COUNT('Turns'!F43)=1,SUM('Turns'!F43),"Unknown")</f>
-        <v>5.64e-05</v>
+        <v>4.92e-05</v>
       </c>
       <c r="V12" s="2">
         <v>0</v>
@@ -5312,22 +5312,22 @@
       </c>
       <c r="Y12" s="2">
         <f>IF(COUNT('Turns'!E47)=1,SUM('Turns'!E47),"Unknown")</f>
-        <v>9.770544e-05</v>
+        <v>9.3169116e-05</v>
       </c>
       <c r="Z12" s="2">
         <f>IF(COUNT('Turns'!F47)=1,SUM('Turns'!F47),"Unknown")</f>
-        <v>0.000112</v>
+        <v>0.0001068</v>
       </c>
       <c r="AA12" s="5">
         <f>IF(ISNUMBER(Y12),ROUND(Y12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="AB12" s="5">
         <f>IF(ISNUMBER(Z12),ROUND(Z12*'Reference data'!$B$2,0),"Unknown")</f>
         <v>11.0</v>
       </c>
       <c r="AD12" s="1">
-        <v>939.308</v>
+        <v>1049.556</v>
       </c>
       <c r="AE12" s="1" t="s">
         <v>184</v>
@@ -5350,7 +5350,7 @@
         <v>110</v>
       </c>
       <c r="F13" s="1">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>190</v>
@@ -5363,15 +5363,15 @@
       </c>
       <c r="J13" s="2">
         <f>IF(COUNT('Turns'!D38)=1,SUM('Turns'!D38),"Unknown")</f>
-        <v>278.0</v>
+        <v>288.0</v>
       </c>
       <c r="K13" s="2">
         <f>IF(COUNT('Turns'!E38)=1,SUM('Turns'!E38),"Unknown")</f>
-        <v>4.8503772e-05</v>
+        <v>5.0248512e-05</v>
       </c>
       <c r="L13" s="2">
         <f>IF(COUNT('Turns'!F38)=1,SUM('Turns'!F38),"Unknown")</f>
-        <v>5.56e-05</v>
+        <v>5.76e-05</v>
       </c>
       <c r="M13" s="2">
         <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
@@ -5396,15 +5396,15 @@
       </c>
       <c r="S13" s="2">
         <f>IF(COUNT('Turns'!D43)=1,SUM('Turns'!D43),"Unknown")</f>
-        <v>47.0</v>
+        <v>41.0</v>
       </c>
       <c r="T13" s="2">
         <f>IF(COUNT('Turns'!E43)=1,SUM('Turns'!E43),"Unknown")</f>
-        <v>4.9201668e-05</v>
+        <v>4.2920604e-05</v>
       </c>
       <c r="U13" s="2">
         <f>IF(COUNT('Turns'!F43)=1,SUM('Turns'!F43),"Unknown")</f>
-        <v>5.64e-05</v>
+        <v>4.92e-05</v>
       </c>
       <c r="V13" s="2">
         <v>0</v>
@@ -5417,15 +5417,15 @@
       </c>
       <c r="Y13" s="2">
         <f>IF(COUNT('Turns'!E47)=1,SUM('Turns'!E47),"Unknown")</f>
-        <v>9.770544e-05</v>
+        <v>9.3169116e-05</v>
       </c>
       <c r="Z13" s="2">
         <f>IF(COUNT('Turns'!F47)=1,SUM('Turns'!F47),"Unknown")</f>
-        <v>0.000112</v>
+        <v>0.0001068</v>
       </c>
       <c r="AA13" s="5">
         <f>IF(ISNUMBER(Y13),ROUND(Y13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="AB13" s="5">
         <f>IF(ISNUMBER(Z13),ROUND(Z13*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5435,7 +5435,7 @@
         <v>126</v>
       </c>
       <c r="AD13" s="1">
-        <v>936.703</v>
+        <v>1048.349</v>
       </c>
       <c r="AE13" s="1" t="s">
         <v>191</v>
@@ -5468,15 +5468,15 @@
       </c>
       <c r="J14" s="2">
         <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
-        <v>371.0</v>
+        <v>369.0</v>
       </c>
       <c r="K14" s="2">
         <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>6.4729854e-05</v>
+        <v>6.4380906e-05</v>
       </c>
       <c r="L14" s="2">
         <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
-        <v>7.42e-05</v>
+        <v>7.38e-05</v>
       </c>
       <c r="M14" s="2">
         <f>IF(COUNT('Turns'!D49)=1,SUM('Turns'!D49),"Unknown")</f>
@@ -5522,11 +5522,11 @@
       </c>
       <c r="Y14" s="2">
         <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
-        <v>8.6713578e-05</v>
+        <v>8.636463e-05</v>
       </c>
       <c r="Z14" s="2">
         <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
-        <v>9.94e-05</v>
+        <v>9.9e-05</v>
       </c>
       <c r="AA14" s="5">
         <f>IF(ISNUMBER(Y14),ROUND(Y14*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5537,7 +5537,7 @@
         <v>10.0</v>
       </c>
       <c r="AD14" s="1">
-        <v>861.414</v>
+        <v>832.146</v>
       </c>
       <c r="AE14" s="1" t="s">
         <v>184</v>
@@ -5560,7 +5560,7 @@
         <v>110</v>
       </c>
       <c r="F15" s="1">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>190</v>
@@ -5573,15 +5573,15 @@
       </c>
       <c r="J15" s="2">
         <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
-        <v>371.0</v>
+        <v>369.0</v>
       </c>
       <c r="K15" s="2">
         <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>6.4729854e-05</v>
+        <v>6.4380906e-05</v>
       </c>
       <c r="L15" s="2">
         <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
-        <v>7.42e-05</v>
+        <v>7.38e-05</v>
       </c>
       <c r="M15" s="2">
         <f>IF(COUNT('Turns'!D49)=1,SUM('Turns'!D49),"Unknown")</f>
@@ -5627,11 +5627,11 @@
       </c>
       <c r="Y15" s="2">
         <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
-        <v>8.6713578e-05</v>
+        <v>8.636463e-05</v>
       </c>
       <c r="Z15" s="2">
         <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
-        <v>9.94e-05</v>
+        <v>9.9e-05</v>
       </c>
       <c r="AA15" s="5">
         <f>IF(ISNUMBER(Y15),ROUND(Y15*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5645,7 +5645,7 @@
         <v>131</v>
       </c>
       <c r="AD15" s="1">
-        <v>858.687</v>
+        <v>830.5549999999999</v>
       </c>
       <c r="AE15" s="1" t="s">
         <v>191</v>
@@ -5675,15 +5675,15 @@
       </c>
       <c r="J16" s="2">
         <f>IF(COUNT('Turns'!D63,'Turns'!D77,'Turns'!D94,'Turns'!D106)=4,SUM('Turns'!D63,'Turns'!D77,'Turns'!D94,'Turns'!D106),"Unknown")</f>
-        <v>1470.0</v>
+        <v>1500.0</v>
       </c>
       <c r="K16" s="2">
         <f>IF(COUNT('Turns'!E63,'Turns'!E77,'Turns'!E94,'Turns'!E106)=4,SUM('Turns'!E63,'Turns'!E77,'Turns'!E94,'Turns'!E106),"Unknown")</f>
-        <v>0.00025647678</v>
+        <v>0.000261711</v>
       </c>
       <c r="L16" s="2">
         <f>IF(COUNT('Turns'!F63,'Turns'!F77,'Turns'!F94,'Turns'!F106)=4,SUM('Turns'!F63,'Turns'!F77,'Turns'!F94,'Turns'!F106),"Unknown")</f>
-        <v>0.000294</v>
+        <v>0.0003</v>
       </c>
       <c r="M16" s="2">
         <f>IF(COUNT('Turns'!D62,'Turns'!D93,'Turns'!D105)=3,SUM('Turns'!D62,'Turns'!D93,'Turns'!D105),"Unknown")</f>
@@ -5708,15 +5708,15 @@
       </c>
       <c r="S16" s="2">
         <f>IF(COUNT('Turns'!D68,'Turns'!D84,'Turns'!D99,'Turns'!D111)=4,SUM('Turns'!D68,'Turns'!D84,'Turns'!D99,'Turns'!D111),"Unknown")</f>
-        <v>198.0</v>
+        <v>212.0</v>
       </c>
       <c r="T16" s="2">
         <f>IF(COUNT('Turns'!E68,'Turns'!E84,'Turns'!E99,'Turns'!E111)=4,SUM('Turns'!E68,'Turns'!E84,'Turns'!E99,'Turns'!E111),"Unknown")</f>
-        <v>0.000207275112</v>
+        <v>0.000221930928</v>
       </c>
       <c r="U16" s="2">
         <f>IF(COUNT('Turns'!F68,'Turns'!F84,'Turns'!F99,'Turns'!F111)=4,SUM('Turns'!F68,'Turns'!F84,'Turns'!F99,'Turns'!F111),"Unknown")</f>
-        <v>0.0002376</v>
+        <v>0.0002544</v>
       </c>
       <c r="V16" s="2">
         <f>IF(COUNT('Turns'!D83)=1,SUM('Turns'!D83),"Unknown")</f>
@@ -5732,22 +5732,22 @@
       </c>
       <c r="Y16" s="2">
         <f>IF(COUNT('Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115)=4,SUM('Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115),"Unknown")</f>
-        <v>0.000473173488</v>
+        <v>0.000493063524</v>
       </c>
       <c r="Z16" s="2">
         <f>IF(COUNT('Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115)=4,SUM('Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115),"Unknown")</f>
-        <v>0.0005424</v>
+        <v>0.0005652</v>
       </c>
       <c r="AA16" s="5">
         <f>IF(ISNUMBER(Y16),ROUND(Y16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
       <c r="AB16" s="5">
         <f>IF(ISNUMBER(Z16),ROUND(Z16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>54.0</v>
+        <v>57.0</v>
       </c>
       <c r="AD16" s="1">
-        <v>4581.923</v>
+        <v>5675.891</v>
       </c>
       <c r="AE16" s="1" t="s">
         <v>184</v>
@@ -5780,15 +5780,15 @@
       </c>
       <c r="J17" s="2">
         <f>IF(COUNT('Turns'!D63)=1,SUM('Turns'!D63),"Unknown")</f>
-        <v>409.0</v>
+        <v>407.0</v>
       </c>
       <c r="K17" s="2">
         <f>IF(COUNT('Turns'!E63)=1,SUM('Turns'!E63),"Unknown")</f>
-        <v>7.1359866e-05</v>
+        <v>7.1010918e-05</v>
       </c>
       <c r="L17" s="2">
         <f>IF(COUNT('Turns'!F63)=1,SUM('Turns'!F63),"Unknown")</f>
-        <v>8.18e-05</v>
+        <v>8.14e-05</v>
       </c>
       <c r="M17" s="2">
         <f>IF(COUNT('Turns'!D62)=1,SUM('Turns'!D62),"Unknown")</f>
@@ -5813,15 +5813,15 @@
       </c>
       <c r="S17" s="2">
         <f>IF(COUNT('Turns'!D68)=1,SUM('Turns'!D68),"Unknown")</f>
-        <v>69.0</v>
+        <v>78.0</v>
       </c>
       <c r="T17" s="2">
         <f>IF(COUNT('Turns'!E68)=1,SUM('Turns'!E68),"Unknown")</f>
-        <v>7.2232236e-05</v>
+        <v>8.1653832e-05</v>
       </c>
       <c r="U17" s="2">
         <f>IF(COUNT('Turns'!F68)=1,SUM('Turns'!F68),"Unknown")</f>
-        <v>8.28e-05</v>
+        <v>9.36e-05</v>
       </c>
       <c r="V17" s="2">
         <v>0</v>
@@ -5834,22 +5834,22 @@
       </c>
       <c r="Y17" s="2">
         <f>IF(COUNT('Turns'!E72)=1,SUM('Turns'!E72),"Unknown")</f>
-        <v>0.000143592102</v>
+        <v>0.00015266475</v>
       </c>
       <c r="Z17" s="2">
         <f>IF(COUNT('Turns'!F72)=1,SUM('Turns'!F72),"Unknown")</f>
-        <v>0.0001646</v>
+        <v>0.000175</v>
       </c>
       <c r="AA17" s="5">
         <f>IF(ISNUMBER(Y17),ROUND(Y17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="AB17" s="5">
         <f>IF(ISNUMBER(Z17),ROUND(Z17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="AD17" s="1">
-        <v>1421.254</v>
+        <v>1629.667</v>
       </c>
       <c r="AE17" s="1" t="s">
         <v>184</v>
@@ -5872,7 +5872,7 @@
         <v>110</v>
       </c>
       <c r="F18" s="1">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>190</v>
@@ -5885,15 +5885,15 @@
       </c>
       <c r="J18" s="2">
         <f>IF(COUNT('Turns'!D63)=1,SUM('Turns'!D63),"Unknown")</f>
-        <v>409.0</v>
+        <v>407.0</v>
       </c>
       <c r="K18" s="2">
         <f>IF(COUNT('Turns'!E63)=1,SUM('Turns'!E63),"Unknown")</f>
-        <v>7.1359866e-05</v>
+        <v>7.1010918e-05</v>
       </c>
       <c r="L18" s="2">
         <f>IF(COUNT('Turns'!F63)=1,SUM('Turns'!F63),"Unknown")</f>
-        <v>8.18e-05</v>
+        <v>8.14e-05</v>
       </c>
       <c r="M18" s="2">
         <f>IF(COUNT('Turns'!D62)=1,SUM('Turns'!D62),"Unknown")</f>
@@ -5918,15 +5918,15 @@
       </c>
       <c r="S18" s="2">
         <f>IF(COUNT('Turns'!D68)=1,SUM('Turns'!D68),"Unknown")</f>
-        <v>69.0</v>
+        <v>78.0</v>
       </c>
       <c r="T18" s="2">
         <f>IF(COUNT('Turns'!E68)=1,SUM('Turns'!E68),"Unknown")</f>
-        <v>7.2232236e-05</v>
+        <v>8.1653832e-05</v>
       </c>
       <c r="U18" s="2">
         <f>IF(COUNT('Turns'!F68)=1,SUM('Turns'!F68),"Unknown")</f>
-        <v>8.28e-05</v>
+        <v>9.36e-05</v>
       </c>
       <c r="V18" s="2">
         <v>0</v>
@@ -5939,25 +5939,25 @@
       </c>
       <c r="Y18" s="2">
         <f>IF(COUNT('Turns'!E72)=1,SUM('Turns'!E72),"Unknown")</f>
-        <v>0.000143592102</v>
+        <v>0.00015266475</v>
       </c>
       <c r="Z18" s="2">
         <f>IF(COUNT('Turns'!F72)=1,SUM('Turns'!F72),"Unknown")</f>
-        <v>0.0001646</v>
+        <v>0.000175</v>
       </c>
       <c r="AA18" s="5">
         <f>IF(ISNUMBER(Y18),ROUND(Y18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="AB18" s="5">
         <f>IF(ISNUMBER(Z18),ROUND(Z18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="AC18" s="1" t="s">
         <v>136</v>
       </c>
       <c r="AD18" s="1">
-        <v>1419.544</v>
+        <v>1628.302</v>
       </c>
       <c r="AE18" s="1" t="s">
         <v>191</v>
@@ -5990,15 +5990,15 @@
       </c>
       <c r="J19" s="2">
         <f>IF(COUNT('Turns'!D77,'Turns'!D94)=2,SUM('Turns'!D77,'Turns'!D94),"Unknown")</f>
-        <v>519.0</v>
+        <v>540.0</v>
       </c>
       <c r="K19" s="2">
         <f>IF(COUNT('Turns'!E77,'Turns'!E94)=2,SUM('Turns'!E77,'Turns'!E94),"Unknown")</f>
-        <v>9.0552006e-05</v>
+        <v>9.421596e-05</v>
       </c>
       <c r="L19" s="2">
         <f>IF(COUNT('Turns'!F77,'Turns'!F94)=2,SUM('Turns'!F77,'Turns'!F94),"Unknown")</f>
-        <v>0.0001038</v>
+        <v>0.000108</v>
       </c>
       <c r="M19" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -6023,15 +6023,15 @@
       </c>
       <c r="S19" s="2">
         <f>IF(COUNT('Turns'!D84,'Turns'!D99)=2,SUM('Turns'!D84,'Turns'!D99),"Unknown")</f>
-        <v>105.0</v>
+        <v>112.0</v>
       </c>
       <c r="T19" s="2">
         <f>IF(COUNT('Turns'!E84,'Turns'!E99)=2,SUM('Turns'!E84,'Turns'!E99),"Unknown")</f>
-        <v>0.00010991862</v>
+        <v>0.000117246528</v>
       </c>
       <c r="U19" s="2">
         <f>IF(COUNT('Turns'!F84,'Turns'!F99)=2,SUM('Turns'!F84,'Turns'!F99),"Unknown")</f>
-        <v>0.000126</v>
+        <v>0.0001344</v>
       </c>
       <c r="V19" s="2">
         <f>IF(COUNT('Turns'!D83)=1,SUM('Turns'!D83),"Unknown")</f>
@@ -6047,22 +6047,22 @@
       </c>
       <c r="Y19" s="2">
         <f>IF(COUNT('Turns'!E88,'Turns'!E103)=2,SUM('Turns'!E88,'Turns'!E103),"Unknown")</f>
-        <v>0.000209892222</v>
+        <v>0.000220884084</v>
       </c>
       <c r="Z19" s="2">
         <f>IF(COUNT('Turns'!F88,'Turns'!F103)=2,SUM('Turns'!F88,'Turns'!F103),"Unknown")</f>
-        <v>0.0002406</v>
+        <v>0.0002532</v>
       </c>
       <c r="AA19" s="5">
         <f>IF(ISNUMBER(Y19),ROUND(Y19*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="AB19" s="5">
         <f>IF(ISNUMBER(Z19),ROUND(Z19*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="AD19" s="1">
-        <v>2291.804</v>
+        <v>2995.943</v>
       </c>
       <c r="AE19" s="1" t="s">
         <v>184</v>
@@ -6095,15 +6095,15 @@
       </c>
       <c r="J20" s="2">
         <f>IF(COUNT('Turns'!D77,'Turns'!D94)=2,SUM('Turns'!D77,'Turns'!D94),"Unknown")</f>
-        <v>519.0</v>
+        <v>540.0</v>
       </c>
       <c r="K20" s="2">
         <f>IF(COUNT('Turns'!E77,'Turns'!E94)=2,SUM('Turns'!E77,'Turns'!E94),"Unknown")</f>
-        <v>9.0552006e-05</v>
+        <v>9.421596e-05</v>
       </c>
       <c r="L20" s="2">
         <f>IF(COUNT('Turns'!F77,'Turns'!F94)=2,SUM('Turns'!F77,'Turns'!F94),"Unknown")</f>
-        <v>0.0001038</v>
+        <v>0.000108</v>
       </c>
       <c r="M20" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -6128,15 +6128,15 @@
       </c>
       <c r="S20" s="2">
         <f>IF(COUNT('Turns'!D84,'Turns'!D99)=2,SUM('Turns'!D84,'Turns'!D99),"Unknown")</f>
-        <v>105.0</v>
+        <v>112.0</v>
       </c>
       <c r="T20" s="2">
         <f>IF(COUNT('Turns'!E84,'Turns'!E99)=2,SUM('Turns'!E84,'Turns'!E99),"Unknown")</f>
-        <v>0.00010991862</v>
+        <v>0.000117246528</v>
       </c>
       <c r="U20" s="2">
         <f>IF(COUNT('Turns'!F84,'Turns'!F99)=2,SUM('Turns'!F84,'Turns'!F99),"Unknown")</f>
-        <v>0.000126</v>
+        <v>0.0001344</v>
       </c>
       <c r="V20" s="2">
         <f>IF(COUNT('Turns'!D83)=1,SUM('Turns'!D83),"Unknown")</f>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="Y20" s="2">
         <f>IF(COUNT('Turns'!E88,'Turns'!E103)=2,SUM('Turns'!E88,'Turns'!E103),"Unknown")</f>
-        <v>0.000209892222</v>
+        <v>0.000220884084</v>
       </c>
       <c r="Z20" s="2">
         <f>IF(COUNT('Turns'!F88,'Turns'!F103)=2,SUM('Turns'!F88,'Turns'!F103),"Unknown")</f>
-        <v>0.0002406</v>
+        <v>0.0002532</v>
       </c>
       <c r="AA20" s="5">
         <f>IF(ISNUMBER(Y20),ROUND(Y20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="AB20" s="5">
         <f>IF(ISNUMBER(Z20),ROUND(Z20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="AD20" s="1">
-        <v>2290.749</v>
+        <v>2995.011</v>
       </c>
       <c r="AE20" s="1" t="s">
         <v>184</v>
@@ -6200,15 +6200,15 @@
       </c>
       <c r="J21" s="2">
         <f>IF(COUNT('Turns'!D77,'Turns'!D94)=2,SUM('Turns'!D77,'Turns'!D94),"Unknown")</f>
-        <v>519.0</v>
+        <v>540.0</v>
       </c>
       <c r="K21" s="2">
         <f>IF(COUNT('Turns'!E77,'Turns'!E94)=2,SUM('Turns'!E77,'Turns'!E94),"Unknown")</f>
-        <v>9.0552006e-05</v>
+        <v>9.421596e-05</v>
       </c>
       <c r="L21" s="2">
         <f>IF(COUNT('Turns'!F77,'Turns'!F94)=2,SUM('Turns'!F77,'Turns'!F94),"Unknown")</f>
-        <v>0.0001038</v>
+        <v>0.000108</v>
       </c>
       <c r="M21" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -6233,15 +6233,15 @@
       </c>
       <c r="S21" s="2">
         <f>IF(COUNT('Turns'!D84,'Turns'!D99)=2,SUM('Turns'!D84,'Turns'!D99),"Unknown")</f>
-        <v>105.0</v>
+        <v>112.0</v>
       </c>
       <c r="T21" s="2">
         <f>IF(COUNT('Turns'!E84,'Turns'!E99)=2,SUM('Turns'!E84,'Turns'!E99),"Unknown")</f>
-        <v>0.00010991862</v>
+        <v>0.000117246528</v>
       </c>
       <c r="U21" s="2">
         <f>IF(COUNT('Turns'!F84,'Turns'!F99)=2,SUM('Turns'!F84,'Turns'!F99),"Unknown")</f>
-        <v>0.000126</v>
+        <v>0.0001344</v>
       </c>
       <c r="V21" s="2">
         <f>IF(COUNT('Turns'!D83)=1,SUM('Turns'!D83),"Unknown")</f>
@@ -6257,22 +6257,22 @@
       </c>
       <c r="Y21" s="2">
         <f>IF(COUNT('Turns'!E88,'Turns'!E103)=2,SUM('Turns'!E88,'Turns'!E103),"Unknown")</f>
-        <v>0.000209892222</v>
+        <v>0.000220884084</v>
       </c>
       <c r="Z21" s="2">
         <f>IF(COUNT('Turns'!F88,'Turns'!F103)=2,SUM('Turns'!F88,'Turns'!F103),"Unknown")</f>
-        <v>0.0002406</v>
+        <v>0.0002532</v>
       </c>
       <c r="AA21" s="5">
         <f>IF(ISNUMBER(Y21),ROUND(Y21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="AB21" s="5">
         <f>IF(ISNUMBER(Z21),ROUND(Z21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="AD21" s="1">
-        <v>2289.58</v>
+        <v>2994.071</v>
       </c>
       <c r="AE21" s="1" t="s">
         <v>184</v>
@@ -6305,15 +6305,15 @@
       </c>
       <c r="J22" s="2">
         <f>IF(COUNT('Turns'!D77)=1,SUM('Turns'!D77),"Unknown")</f>
-        <v>203.0</v>
+        <v>212.0</v>
       </c>
       <c r="K22" s="2">
         <f>IF(COUNT('Turns'!E77)=1,SUM('Turns'!E77),"Unknown")</f>
-        <v>3.5418222e-05</v>
+        <v>3.6988488e-05</v>
       </c>
       <c r="L22" s="2">
         <f>IF(COUNT('Turns'!F77)=1,SUM('Turns'!F77),"Unknown")</f>
-        <v>4.06e-05</v>
+        <v>4.24e-05</v>
       </c>
       <c r="M22" s="2">
         <v>0</v>
@@ -6335,15 +6335,15 @@
       </c>
       <c r="S22" s="2">
         <f>IF(COUNT('Turns'!D84)=1,SUM('Turns'!D84),"Unknown")</f>
-        <v>47.0</v>
+        <v>50.0</v>
       </c>
       <c r="T22" s="2">
         <f>IF(COUNT('Turns'!E84)=1,SUM('Turns'!E84),"Unknown")</f>
-        <v>4.9201668e-05</v>
+        <v>5.23422e-05</v>
       </c>
       <c r="U22" s="2">
         <f>IF(COUNT('Turns'!F84)=1,SUM('Turns'!F84),"Unknown")</f>
-        <v>5.64e-05</v>
+        <v>6e-05</v>
       </c>
       <c r="V22" s="2">
         <f>IF(COUNT('Turns'!D83)=1,SUM('Turns'!D83),"Unknown")</f>
@@ -6359,22 +6359,22 @@
       </c>
       <c r="Y22" s="2">
         <f>IF(COUNT('Turns'!E88)=1,SUM('Turns'!E88),"Unknown")</f>
-        <v>9.4041486e-05</v>
+        <v>9.8752284e-05</v>
       </c>
       <c r="Z22" s="2">
         <f>IF(COUNT('Turns'!F88)=1,SUM('Turns'!F88),"Unknown")</f>
-        <v>0.0001078</v>
+        <v>0.0001132</v>
       </c>
       <c r="AA22" s="5">
         <f>IF(ISNUMBER(Y22),ROUND(Y22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="AB22" s="5">
         <f>IF(ISNUMBER(Z22),ROUND(Z22*'Reference data'!$B$2,0),"Unknown")</f>
         <v>11.0</v>
       </c>
       <c r="AD22" s="1">
-        <v>883.141</v>
+        <v>1634.397</v>
       </c>
       <c r="AE22" s="1" t="s">
         <v>184</v>
@@ -6397,7 +6397,7 @@
         <v>110</v>
       </c>
       <c r="F23" s="1">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>190</v>
@@ -6410,15 +6410,15 @@
       </c>
       <c r="J23" s="2">
         <f>IF(COUNT('Turns'!D77)=1,SUM('Turns'!D77),"Unknown")</f>
-        <v>203.0</v>
+        <v>212.0</v>
       </c>
       <c r="K23" s="2">
         <f>IF(COUNT('Turns'!E77)=1,SUM('Turns'!E77),"Unknown")</f>
-        <v>3.5418222e-05</v>
+        <v>3.6988488e-05</v>
       </c>
       <c r="L23" s="2">
         <f>IF(COUNT('Turns'!F77)=1,SUM('Turns'!F77),"Unknown")</f>
-        <v>4.06e-05</v>
+        <v>4.24e-05</v>
       </c>
       <c r="M23" s="2">
         <v>0</v>
@@ -6440,15 +6440,15 @@
       </c>
       <c r="S23" s="2">
         <f>IF(COUNT('Turns'!D84)=1,SUM('Turns'!D84),"Unknown")</f>
-        <v>47.0</v>
+        <v>50.0</v>
       </c>
       <c r="T23" s="2">
         <f>IF(COUNT('Turns'!E84)=1,SUM('Turns'!E84),"Unknown")</f>
-        <v>4.9201668e-05</v>
+        <v>5.23422e-05</v>
       </c>
       <c r="U23" s="2">
         <f>IF(COUNT('Turns'!F84)=1,SUM('Turns'!F84),"Unknown")</f>
-        <v>5.64e-05</v>
+        <v>6e-05</v>
       </c>
       <c r="V23" s="2">
         <f>IF(COUNT('Turns'!D83)=1,SUM('Turns'!D83),"Unknown")</f>
@@ -6464,15 +6464,15 @@
       </c>
       <c r="Y23" s="2">
         <f>IF(COUNT('Turns'!E88)=1,SUM('Turns'!E88),"Unknown")</f>
-        <v>9.4041486e-05</v>
+        <v>9.8752284e-05</v>
       </c>
       <c r="Z23" s="2">
         <f>IF(COUNT('Turns'!F88)=1,SUM('Turns'!F88),"Unknown")</f>
-        <v>0.0001078</v>
+        <v>0.0001132</v>
       </c>
       <c r="AA23" s="5">
         <f>IF(ISNUMBER(Y23),ROUND(Y23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="AB23" s="5">
         <f>IF(ISNUMBER(Z23),ROUND(Z23*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6482,7 +6482,7 @@
         <v>143</v>
       </c>
       <c r="AD23" s="1">
-        <v>877.159</v>
+        <v>1631.824</v>
       </c>
       <c r="AE23" s="1" t="s">
         <v>191</v>
@@ -6514,7 +6514,7 @@
         <v>216</v>
       </c>
       <c r="AD24" s="1">
-        <v>1.561</v>
+        <v>1.546</v>
       </c>
       <c r="AE24" s="1" t="s">
         <v>206</v>
@@ -6546,7 +6546,7 @@
         <v>218</v>
       </c>
       <c r="AD25" s="1">
-        <v>0.457</v>
+        <v>0.423</v>
       </c>
       <c r="AE25" s="1" t="s">
         <v>206</v>
@@ -6579,15 +6579,15 @@
       </c>
       <c r="J26" s="2">
         <f>IF(COUNT('Turns'!D94)=1,SUM('Turns'!D94),"Unknown")</f>
-        <v>316.0</v>
+        <v>328.0</v>
       </c>
       <c r="K26" s="2">
         <f>IF(COUNT('Turns'!E94)=1,SUM('Turns'!E94),"Unknown")</f>
-        <v>5.5133784e-05</v>
+        <v>5.7227472e-05</v>
       </c>
       <c r="L26" s="2">
         <f>IF(COUNT('Turns'!F94)=1,SUM('Turns'!F94),"Unknown")</f>
-        <v>6.32e-05</v>
+        <v>6.56e-05</v>
       </c>
       <c r="M26" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -6612,15 +6612,15 @@
       </c>
       <c r="S26" s="2">
         <f>IF(COUNT('Turns'!D99)=1,SUM('Turns'!D99),"Unknown")</f>
-        <v>58.0</v>
+        <v>62.0</v>
       </c>
       <c r="T26" s="2">
         <f>IF(COUNT('Turns'!E99)=1,SUM('Turns'!E99),"Unknown")</f>
-        <v>6.0716952e-05</v>
+        <v>6.4904328e-05</v>
       </c>
       <c r="U26" s="2">
         <f>IF(COUNT('Turns'!F99)=1,SUM('Turns'!F99),"Unknown")</f>
-        <v>6.96e-05</v>
+        <v>7.44e-05</v>
       </c>
       <c r="V26" s="2">
         <v>0</v>
@@ -6633,11 +6633,11 @@
       </c>
       <c r="Y26" s="2">
         <f>IF(COUNT('Turns'!E103)=1,SUM('Turns'!E103),"Unknown")</f>
-        <v>0.000115850736</v>
+        <v>0.0001221318</v>
       </c>
       <c r="Z26" s="2">
         <f>IF(COUNT('Turns'!F103)=1,SUM('Turns'!F103),"Unknown")</f>
-        <v>0.0001328</v>
+        <v>0.00014</v>
       </c>
       <c r="AA26" s="5">
         <f>IF(ISNUMBER(Y26),ROUND(Y26*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6645,10 +6645,10 @@
       </c>
       <c r="AB26" s="5">
         <f>IF(ISNUMBER(Z26),ROUND(Z26*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="AD26" s="1">
-        <v>1402.04</v>
+        <v>1355.38</v>
       </c>
       <c r="AE26" s="1" t="s">
         <v>184</v>
@@ -6671,7 +6671,7 @@
         <v>110</v>
       </c>
       <c r="F27" s="1">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>190</v>
@@ -6684,15 +6684,15 @@
       </c>
       <c r="J27" s="2">
         <f>IF(COUNT('Turns'!D94)=1,SUM('Turns'!D94),"Unknown")</f>
-        <v>316.0</v>
+        <v>328.0</v>
       </c>
       <c r="K27" s="2">
         <f>IF(COUNT('Turns'!E94)=1,SUM('Turns'!E94),"Unknown")</f>
-        <v>5.5133784e-05</v>
+        <v>5.7227472e-05</v>
       </c>
       <c r="L27" s="2">
         <f>IF(COUNT('Turns'!F94)=1,SUM('Turns'!F94),"Unknown")</f>
-        <v>6.32e-05</v>
+        <v>6.56e-05</v>
       </c>
       <c r="M27" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -6717,15 +6717,15 @@
       </c>
       <c r="S27" s="2">
         <f>IF(COUNT('Turns'!D99)=1,SUM('Turns'!D99),"Unknown")</f>
-        <v>58.0</v>
+        <v>62.0</v>
       </c>
       <c r="T27" s="2">
         <f>IF(COUNT('Turns'!E99)=1,SUM('Turns'!E99),"Unknown")</f>
-        <v>6.0716952e-05</v>
+        <v>6.4904328e-05</v>
       </c>
       <c r="U27" s="2">
         <f>IF(COUNT('Turns'!F99)=1,SUM('Turns'!F99),"Unknown")</f>
-        <v>6.96e-05</v>
+        <v>7.44e-05</v>
       </c>
       <c r="V27" s="2">
         <v>0</v>
@@ -6738,11 +6738,11 @@
       </c>
       <c r="Y27" s="2">
         <f>IF(COUNT('Turns'!E103)=1,SUM('Turns'!E103),"Unknown")</f>
-        <v>0.000115850736</v>
+        <v>0.0001221318</v>
       </c>
       <c r="Z27" s="2">
         <f>IF(COUNT('Turns'!F103)=1,SUM('Turns'!F103),"Unknown")</f>
-        <v>0.0001328</v>
+        <v>0.00014</v>
       </c>
       <c r="AA27" s="5">
         <f>IF(ISNUMBER(Y27),ROUND(Y27*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6750,13 +6750,13 @@
       </c>
       <c r="AB27" s="5">
         <f>IF(ISNUMBER(Z27),ROUND(Z27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="AC27" s="1" t="s">
         <v>151</v>
       </c>
       <c r="AD27" s="1">
-        <v>1399.813</v>
+        <v>1353.89</v>
       </c>
       <c r="AE27" s="1" t="s">
         <v>191</v>
@@ -6789,15 +6789,15 @@
       </c>
       <c r="J28" s="2">
         <f>IF(COUNT('Turns'!D106)=1,SUM('Turns'!D106),"Unknown")</f>
-        <v>542.0</v>
+        <v>553.0</v>
       </c>
       <c r="K28" s="2">
         <f>IF(COUNT('Turns'!E106)=1,SUM('Turns'!E106),"Unknown")</f>
-        <v>9.4564908e-05</v>
+        <v>9.6484122e-05</v>
       </c>
       <c r="L28" s="2">
         <f>IF(COUNT('Turns'!F106)=1,SUM('Turns'!F106),"Unknown")</f>
-        <v>0.0001084</v>
+        <v>0.0001106</v>
       </c>
       <c r="M28" s="2">
         <f>IF(COUNT('Turns'!D105)=1,SUM('Turns'!D105),"Unknown")</f>
@@ -6822,15 +6822,15 @@
       </c>
       <c r="S28" s="2">
         <f>IF(COUNT('Turns'!D111)=1,SUM('Turns'!D111),"Unknown")</f>
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
       <c r="T28" s="2">
         <f>IF(COUNT('Turns'!E111)=1,SUM('Turns'!E111),"Unknown")</f>
-        <v>2.5124256e-05</v>
+        <v>2.3030568e-05</v>
       </c>
       <c r="U28" s="2">
         <f>IF(COUNT('Turns'!F111)=1,SUM('Turns'!F111),"Unknown")</f>
-        <v>2.88e-05</v>
+        <v>2.64e-05</v>
       </c>
       <c r="V28" s="2">
         <v>0</v>
@@ -6843,11 +6843,11 @@
       </c>
       <c r="Y28" s="2">
         <f>IF(COUNT('Turns'!E115)=1,SUM('Turns'!E115),"Unknown")</f>
-        <v>0.000119689164</v>
+        <v>0.00011951469</v>
       </c>
       <c r="Z28" s="2">
         <f>IF(COUNT('Turns'!F115)=1,SUM('Turns'!F115),"Unknown")</f>
-        <v>0.0001372</v>
+        <v>0.000137</v>
       </c>
       <c r="AA28" s="5">
         <f>IF(ISNUMBER(Y28),ROUND(Y28*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6858,7 +6858,7 @@
         <v>14.0</v>
       </c>
       <c r="AD28" s="1">
-        <v>863.809</v>
+        <v>1047.086</v>
       </c>
       <c r="AE28" s="1" t="s">
         <v>184</v>
@@ -6881,7 +6881,7 @@
         <v>110</v>
       </c>
       <c r="F29" s="1">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>190</v>
@@ -6894,15 +6894,15 @@
       </c>
       <c r="J29" s="2">
         <f>IF(COUNT('Turns'!D106)=1,SUM('Turns'!D106),"Unknown")</f>
-        <v>542.0</v>
+        <v>553.0</v>
       </c>
       <c r="K29" s="2">
         <f>IF(COUNT('Turns'!E106)=1,SUM('Turns'!E106),"Unknown")</f>
-        <v>9.4564908e-05</v>
+        <v>9.6484122e-05</v>
       </c>
       <c r="L29" s="2">
         <f>IF(COUNT('Turns'!F106)=1,SUM('Turns'!F106),"Unknown")</f>
-        <v>0.0001084</v>
+        <v>0.0001106</v>
       </c>
       <c r="M29" s="2">
         <f>IF(COUNT('Turns'!D105)=1,SUM('Turns'!D105),"Unknown")</f>
@@ -6927,15 +6927,15 @@
       </c>
       <c r="S29" s="2">
         <f>IF(COUNT('Turns'!D111)=1,SUM('Turns'!D111),"Unknown")</f>
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
       <c r="T29" s="2">
         <f>IF(COUNT('Turns'!E111)=1,SUM('Turns'!E111),"Unknown")</f>
-        <v>2.5124256e-05</v>
+        <v>2.3030568e-05</v>
       </c>
       <c r="U29" s="2">
         <f>IF(COUNT('Turns'!F111)=1,SUM('Turns'!F111),"Unknown")</f>
-        <v>2.88e-05</v>
+        <v>2.64e-05</v>
       </c>
       <c r="V29" s="2">
         <v>0</v>
@@ -6948,11 +6948,11 @@
       </c>
       <c r="Y29" s="2">
         <f>IF(COUNT('Turns'!E115)=1,SUM('Turns'!E115),"Unknown")</f>
-        <v>0.000119689164</v>
+        <v>0.00011951469</v>
       </c>
       <c r="Z29" s="2">
         <f>IF(COUNT('Turns'!F115)=1,SUM('Turns'!F115),"Unknown")</f>
-        <v>0.0001372</v>
+        <v>0.000137</v>
       </c>
       <c r="AA29" s="5">
         <f>IF(ISNUMBER(Y29),ROUND(Y29*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6966,7 +6966,7 @@
         <v>154</v>
       </c>
       <c r="AD29" s="1">
-        <v>861.476</v>
+        <v>1045.797</v>
       </c>
       <c r="AE29" s="1" t="s">
         <v>191</v>
@@ -6996,15 +6996,15 @@
       </c>
       <c r="J30" s="2">
         <f>IF(COUNT('Turns'!D119,'Turns'!D133,'Turns'!D149,'Turns'!D161)=4,SUM('Turns'!D119,'Turns'!D133,'Turns'!D149,'Turns'!D161),"Unknown")</f>
-        <v>1741.0</v>
+        <v>1763.0</v>
       </c>
       <c r="K30" s="2">
         <f>IF(COUNT('Turns'!E119,'Turns'!E133,'Turns'!E149,'Turns'!E161)=4,SUM('Turns'!E119,'Turns'!E133,'Turns'!E149,'Turns'!E161),"Unknown")</f>
-        <v>0.000303759234</v>
+        <v>0.000307597662</v>
       </c>
       <c r="L30" s="2">
         <f>IF(COUNT('Turns'!F119,'Turns'!F133,'Turns'!F149,'Turns'!F161)=4,SUM('Turns'!F119,'Turns'!F133,'Turns'!F149,'Turns'!F161),"Unknown")</f>
-        <v>0.0003482</v>
+        <v>0.0003526</v>
       </c>
       <c r="M30" s="2">
         <f>IF(COUNT('Turns'!D118,'Turns'!D148,'Turns'!D160)=3,SUM('Turns'!D118,'Turns'!D148,'Turns'!D160),"Unknown")</f>
@@ -7050,22 +7050,22 @@
       </c>
       <c r="Y30" s="2">
         <f>IF(COUNT('Turns'!E128,'Turns'!E143,'Turns'!E158,'Turns'!E170)=4,SUM('Turns'!E128,'Turns'!E143,'Turns'!E158,'Turns'!E170),"Unknown")</f>
-        <v>0.00046497321</v>
+        <v>0.000468811638</v>
       </c>
       <c r="Z30" s="2">
         <f>IF(COUNT('Turns'!F128,'Turns'!F143,'Turns'!F158,'Turns'!F170)=4,SUM('Turns'!F128,'Turns'!F143,'Turns'!F158,'Turns'!F170),"Unknown")</f>
-        <v>0.000533</v>
+        <v>0.0005374</v>
       </c>
       <c r="AA30" s="5">
         <f>IF(ISNUMBER(Y30),ROUND(Y30*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="AB30" s="5">
         <f>IF(ISNUMBER(Z30),ROUND(Z30*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="AD30" s="1">
-        <v>4203.898</v>
+        <v>6803.348</v>
       </c>
       <c r="AE30" s="1" t="s">
         <v>184</v>
@@ -7098,15 +7098,15 @@
       </c>
       <c r="J31" s="2">
         <f>IF(COUNT('Turns'!D119)=1,SUM('Turns'!D119),"Unknown")</f>
-        <v>581.0</v>
+        <v>590.0</v>
       </c>
       <c r="K31" s="2">
         <f>IF(COUNT('Turns'!E119)=1,SUM('Turns'!E119),"Unknown")</f>
-        <v>0.000101369394</v>
+        <v>0.00010293966</v>
       </c>
       <c r="L31" s="2">
         <f>IF(COUNT('Turns'!F119)=1,SUM('Turns'!F119),"Unknown")</f>
-        <v>0.0001162</v>
+        <v>0.000118</v>
       </c>
       <c r="M31" s="2">
         <f>IF(COUNT('Turns'!D118)=1,SUM('Turns'!D118),"Unknown")</f>
@@ -7131,15 +7131,15 @@
       </c>
       <c r="S31" s="2">
         <f>IF(COUNT('Turns'!D124)=1,SUM('Turns'!D124),"Unknown")</f>
-        <v>55.0</v>
+        <v>57.0</v>
       </c>
       <c r="T31" s="2">
         <f>IF(COUNT('Turns'!E124)=1,SUM('Turns'!E124),"Unknown")</f>
-        <v>5.757642e-05</v>
+        <v>5.9670108e-05</v>
       </c>
       <c r="U31" s="2">
         <f>IF(COUNT('Turns'!F124)=1,SUM('Turns'!F124),"Unknown")</f>
-        <v>6.6e-05</v>
+        <v>6.84e-05</v>
       </c>
       <c r="V31" s="2">
         <v>0</v>
@@ -7152,11 +7152,11 @@
       </c>
       <c r="Y31" s="2">
         <f>IF(COUNT('Turns'!E128)=1,SUM('Turns'!E128),"Unknown")</f>
-        <v>0.000158945814</v>
+        <v>0.000162609768</v>
       </c>
       <c r="Z31" s="2">
         <f>IF(COUNT('Turns'!F128)=1,SUM('Turns'!F128),"Unknown")</f>
-        <v>0.0001822</v>
+        <v>0.0001864</v>
       </c>
       <c r="AA31" s="5">
         <f>IF(ISNUMBER(Y31),ROUND(Y31*'Reference data'!$B$2,0),"Unknown")</f>
@@ -7164,10 +7164,10 @@
       </c>
       <c r="AB31" s="5">
         <f>IF(ISNUMBER(Z31),ROUND(Z31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="AD31" s="1">
-        <v>1091.588</v>
+        <v>2081.249</v>
       </c>
       <c r="AE31" s="1" t="s">
         <v>184</v>
@@ -7190,7 +7190,7 @@
         <v>110</v>
       </c>
       <c r="F32" s="1">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>190</v>
@@ -7203,15 +7203,15 @@
       </c>
       <c r="J32" s="2">
         <f>IF(COUNT('Turns'!D119)=1,SUM('Turns'!D119),"Unknown")</f>
-        <v>581.0</v>
+        <v>590.0</v>
       </c>
       <c r="K32" s="2">
         <f>IF(COUNT('Turns'!E119)=1,SUM('Turns'!E119),"Unknown")</f>
-        <v>0.000101369394</v>
+        <v>0.00010293966</v>
       </c>
       <c r="L32" s="2">
         <f>IF(COUNT('Turns'!F119)=1,SUM('Turns'!F119),"Unknown")</f>
-        <v>0.0001162</v>
+        <v>0.000118</v>
       </c>
       <c r="M32" s="2">
         <f>IF(COUNT('Turns'!D118)=1,SUM('Turns'!D118),"Unknown")</f>
@@ -7236,15 +7236,15 @@
       </c>
       <c r="S32" s="2">
         <f>IF(COUNT('Turns'!D124)=1,SUM('Turns'!D124),"Unknown")</f>
-        <v>55.0</v>
+        <v>57.0</v>
       </c>
       <c r="T32" s="2">
         <f>IF(COUNT('Turns'!E124)=1,SUM('Turns'!E124),"Unknown")</f>
-        <v>5.757642e-05</v>
+        <v>5.9670108e-05</v>
       </c>
       <c r="U32" s="2">
         <f>IF(COUNT('Turns'!F124)=1,SUM('Turns'!F124),"Unknown")</f>
-        <v>6.6e-05</v>
+        <v>6.84e-05</v>
       </c>
       <c r="V32" s="2">
         <v>0</v>
@@ -7257,11 +7257,11 @@
       </c>
       <c r="Y32" s="2">
         <f>IF(COUNT('Turns'!E128)=1,SUM('Turns'!E128),"Unknown")</f>
-        <v>0.000158945814</v>
+        <v>0.000162609768</v>
       </c>
       <c r="Z32" s="2">
         <f>IF(COUNT('Turns'!F128)=1,SUM('Turns'!F128),"Unknown")</f>
-        <v>0.0001822</v>
+        <v>0.0001864</v>
       </c>
       <c r="AA32" s="5">
         <f>IF(ISNUMBER(Y32),ROUND(Y32*'Reference data'!$B$2,0),"Unknown")</f>
@@ -7269,13 +7269,13 @@
       </c>
       <c r="AB32" s="5">
         <f>IF(ISNUMBER(Z32),ROUND(Z32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="AC32" s="1" t="s">
         <v>159</v>
       </c>
       <c r="AD32" s="1">
-        <v>1088.367</v>
+        <v>2079.88</v>
       </c>
       <c r="AE32" s="1" t="s">
         <v>191</v>
@@ -7308,15 +7308,15 @@
       </c>
       <c r="J33" s="2">
         <f>IF(COUNT('Turns'!D133,'Turns'!D149)=2,SUM('Turns'!D133,'Turns'!D149),"Unknown")</f>
-        <v>468.0</v>
+        <v>474.0</v>
       </c>
       <c r="K33" s="2">
         <f>IF(COUNT('Turns'!E133,'Turns'!E149)=2,SUM('Turns'!E133,'Turns'!E149),"Unknown")</f>
-        <v>8.1653832e-05</v>
+        <v>8.2700676e-05</v>
       </c>
       <c r="L33" s="2">
         <f>IF(COUNT('Turns'!F133,'Turns'!F149)=2,SUM('Turns'!F133,'Turns'!F149),"Unknown")</f>
-        <v>9.36e-05</v>
+        <v>9.48e-05</v>
       </c>
       <c r="M33" s="2">
         <f>IF(COUNT('Turns'!D148)=1,SUM('Turns'!D148),"Unknown")</f>
@@ -7341,15 +7341,15 @@
       </c>
       <c r="S33" s="2">
         <f>IF(COUNT('Turns'!D139,'Turns'!D154)=2,SUM('Turns'!D139,'Turns'!D154),"Unknown")</f>
-        <v>79.0</v>
+        <v>77.0</v>
       </c>
       <c r="T33" s="2">
         <f>IF(COUNT('Turns'!E139,'Turns'!E154)=2,SUM('Turns'!E139,'Turns'!E154),"Unknown")</f>
-        <v>8.2700676e-05</v>
+        <v>8.0606988e-05</v>
       </c>
       <c r="U33" s="2">
         <f>IF(COUNT('Turns'!F139,'Turns'!F154)=2,SUM('Turns'!F139,'Turns'!F154),"Unknown")</f>
-        <v>9.48e-05</v>
+        <v>9.24e-05</v>
       </c>
       <c r="V33" s="2">
         <v>0</v>
@@ -7362,11 +7362,11 @@
       </c>
       <c r="Y33" s="2">
         <f>IF(COUNT('Turns'!E143,'Turns'!E158)=2,SUM('Turns'!E143,'Turns'!E158),"Unknown")</f>
-        <v>0.000164354508</v>
+        <v>0.000163307664</v>
       </c>
       <c r="Z33" s="2">
         <f>IF(COUNT('Turns'!F143,'Turns'!F158)=2,SUM('Turns'!F143,'Turns'!F158),"Unknown")</f>
-        <v>0.0001884</v>
+        <v>0.0001872</v>
       </c>
       <c r="AA33" s="5">
         <f>IF(ISNUMBER(Y33),ROUND(Y33*'Reference data'!$B$2,0),"Unknown")</f>
@@ -7377,7 +7377,7 @@
         <v>19.0</v>
       </c>
       <c r="AD33" s="1">
-        <v>2198.23</v>
+        <v>2838.329</v>
       </c>
       <c r="AE33" s="1" t="s">
         <v>184</v>
@@ -7410,15 +7410,15 @@
       </c>
       <c r="J34" s="2">
         <f>IF(COUNT('Turns'!D133,'Turns'!D149)=2,SUM('Turns'!D133,'Turns'!D149),"Unknown")</f>
-        <v>468.0</v>
+        <v>474.0</v>
       </c>
       <c r="K34" s="2">
         <f>IF(COUNT('Turns'!E133,'Turns'!E149)=2,SUM('Turns'!E133,'Turns'!E149),"Unknown")</f>
-        <v>8.1653832e-05</v>
+        <v>8.2700676e-05</v>
       </c>
       <c r="L34" s="2">
         <f>IF(COUNT('Turns'!F133,'Turns'!F149)=2,SUM('Turns'!F133,'Turns'!F149),"Unknown")</f>
-        <v>9.36e-05</v>
+        <v>9.48e-05</v>
       </c>
       <c r="M34" s="2">
         <f>IF(COUNT('Turns'!D148)=1,SUM('Turns'!D148),"Unknown")</f>
@@ -7443,15 +7443,15 @@
       </c>
       <c r="S34" s="2">
         <f>IF(COUNT('Turns'!D139,'Turns'!D154)=2,SUM('Turns'!D139,'Turns'!D154),"Unknown")</f>
-        <v>79.0</v>
+        <v>77.0</v>
       </c>
       <c r="T34" s="2">
         <f>IF(COUNT('Turns'!E139,'Turns'!E154)=2,SUM('Turns'!E139,'Turns'!E154),"Unknown")</f>
-        <v>8.2700676e-05</v>
+        <v>8.0606988e-05</v>
       </c>
       <c r="U34" s="2">
         <f>IF(COUNT('Turns'!F139,'Turns'!F154)=2,SUM('Turns'!F139,'Turns'!F154),"Unknown")</f>
-        <v>9.48e-05</v>
+        <v>9.24e-05</v>
       </c>
       <c r="V34" s="2">
         <v>0</v>
@@ -7464,11 +7464,11 @@
       </c>
       <c r="Y34" s="2">
         <f>IF(COUNT('Turns'!E143,'Turns'!E158)=2,SUM('Turns'!E143,'Turns'!E158),"Unknown")</f>
-        <v>0.000164354508</v>
+        <v>0.000163307664</v>
       </c>
       <c r="Z34" s="2">
         <f>IF(COUNT('Turns'!F143,'Turns'!F158)=2,SUM('Turns'!F143,'Turns'!F158),"Unknown")</f>
-        <v>0.0001884</v>
+        <v>0.0001872</v>
       </c>
       <c r="AA34" s="5">
         <f>IF(ISNUMBER(Y34),ROUND(Y34*'Reference data'!$B$2,0),"Unknown")</f>
@@ -7479,7 +7479,7 @@
         <v>19.0</v>
       </c>
       <c r="AD34" s="1">
-        <v>2196.146</v>
+        <v>2837.225</v>
       </c>
       <c r="AE34" s="1" t="s">
         <v>184</v>
@@ -7512,15 +7512,15 @@
       </c>
       <c r="J35" s="2">
         <f>IF(COUNT('Turns'!D133,'Turns'!D149)=2,SUM('Turns'!D133,'Turns'!D149),"Unknown")</f>
-        <v>468.0</v>
+        <v>474.0</v>
       </c>
       <c r="K35" s="2">
         <f>IF(COUNT('Turns'!E133,'Turns'!E149)=2,SUM('Turns'!E133,'Turns'!E149),"Unknown")</f>
-        <v>8.1653832e-05</v>
+        <v>8.2700676e-05</v>
       </c>
       <c r="L35" s="2">
         <f>IF(COUNT('Turns'!F133,'Turns'!F149)=2,SUM('Turns'!F133,'Turns'!F149),"Unknown")</f>
-        <v>9.36e-05</v>
+        <v>9.48e-05</v>
       </c>
       <c r="M35" s="2">
         <f>IF(COUNT('Turns'!D148)=1,SUM('Turns'!D148),"Unknown")</f>
@@ -7545,15 +7545,15 @@
       </c>
       <c r="S35" s="2">
         <f>IF(COUNT('Turns'!D139,'Turns'!D154)=2,SUM('Turns'!D139,'Turns'!D154),"Unknown")</f>
-        <v>79.0</v>
+        <v>77.0</v>
       </c>
       <c r="T35" s="2">
         <f>IF(COUNT('Turns'!E139,'Turns'!E154)=2,SUM('Turns'!E139,'Turns'!E154),"Unknown")</f>
-        <v>8.2700676e-05</v>
+        <v>8.0606988e-05</v>
       </c>
       <c r="U35" s="2">
         <f>IF(COUNT('Turns'!F139,'Turns'!F154)=2,SUM('Turns'!F139,'Turns'!F154),"Unknown")</f>
-        <v>9.48e-05</v>
+        <v>9.24e-05</v>
       </c>
       <c r="V35" s="2">
         <v>0</v>
@@ -7566,11 +7566,11 @@
       </c>
       <c r="Y35" s="2">
         <f>IF(COUNT('Turns'!E143,'Turns'!E158)=2,SUM('Turns'!E143,'Turns'!E158),"Unknown")</f>
-        <v>0.000164354508</v>
+        <v>0.000163307664</v>
       </c>
       <c r="Z35" s="2">
         <f>IF(COUNT('Turns'!F143,'Turns'!F158)=2,SUM('Turns'!F143,'Turns'!F158),"Unknown")</f>
-        <v>0.0001884</v>
+        <v>0.0001872</v>
       </c>
       <c r="AA35" s="5">
         <f>IF(ISNUMBER(Y35),ROUND(Y35*'Reference data'!$B$2,0),"Unknown")</f>
@@ -7581,7 +7581,7 @@
         <v>19.0</v>
       </c>
       <c r="AD35" s="1">
-        <v>2194.073</v>
+        <v>2836.27</v>
       </c>
       <c r="AE35" s="1" t="s">
         <v>184</v>
@@ -7614,15 +7614,15 @@
       </c>
       <c r="J36" s="2">
         <f>IF(COUNT('Turns'!D133)=1,SUM('Turns'!D133),"Unknown")</f>
-        <v>187.0</v>
+        <v>189.0</v>
       </c>
       <c r="K36" s="2">
         <f>IF(COUNT('Turns'!E133)=1,SUM('Turns'!E133),"Unknown")</f>
-        <v>3.2626638e-05</v>
+        <v>3.2975586e-05</v>
       </c>
       <c r="L36" s="2">
         <f>IF(COUNT('Turns'!F133)=1,SUM('Turns'!F133),"Unknown")</f>
-        <v>3.74e-05</v>
+        <v>3.78e-05</v>
       </c>
       <c r="M36" s="2">
         <v>0</v>
@@ -7644,15 +7644,15 @@
       </c>
       <c r="S36" s="2">
         <f>IF(COUNT('Turns'!D139)=1,SUM('Turns'!D139),"Unknown")</f>
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
       <c r="T36" s="2">
         <f>IF(COUNT('Turns'!E139)=1,SUM('Turns'!E139),"Unknown")</f>
-        <v>3.0358476e-05</v>
+        <v>3.2452164e-05</v>
       </c>
       <c r="U36" s="2">
         <f>IF(COUNT('Turns'!F139)=1,SUM('Turns'!F139),"Unknown")</f>
-        <v>3.48e-05</v>
+        <v>3.72e-05</v>
       </c>
       <c r="V36" s="2">
         <v>0</v>
@@ -7665,22 +7665,22 @@
       </c>
       <c r="Y36" s="2">
         <f>IF(COUNT('Turns'!E143)=1,SUM('Turns'!E143),"Unknown")</f>
-        <v>6.2985114e-05</v>
+        <v>6.542775e-05</v>
       </c>
       <c r="Z36" s="2">
         <f>IF(COUNT('Turns'!F143)=1,SUM('Turns'!F143),"Unknown")</f>
-        <v>7.22e-05</v>
+        <v>7.5e-05</v>
       </c>
       <c r="AA36" s="5">
         <f>IF(ISNUMBER(Y36),ROUND(Y36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="AB36" s="5">
         <f>IF(ISNUMBER(Z36),ROUND(Z36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="AD36" s="1">
-        <v>1077.428</v>
+        <v>1329.595</v>
       </c>
       <c r="AE36" s="1" t="s">
         <v>184</v>
@@ -7703,7 +7703,7 @@
         <v>110</v>
       </c>
       <c r="F37" s="1">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>190</v>
@@ -7716,15 +7716,15 @@
       </c>
       <c r="J37" s="2">
         <f>IF(COUNT('Turns'!D133)=1,SUM('Turns'!D133),"Unknown")</f>
-        <v>187.0</v>
+        <v>189.0</v>
       </c>
       <c r="K37" s="2">
         <f>IF(COUNT('Turns'!E133)=1,SUM('Turns'!E133),"Unknown")</f>
-        <v>3.2626638e-05</v>
+        <v>3.2975586e-05</v>
       </c>
       <c r="L37" s="2">
         <f>IF(COUNT('Turns'!F133)=1,SUM('Turns'!F133),"Unknown")</f>
-        <v>3.74e-05</v>
+        <v>3.78e-05</v>
       </c>
       <c r="M37" s="2">
         <v>0</v>
@@ -7746,15 +7746,15 @@
       </c>
       <c r="S37" s="2">
         <f>IF(COUNT('Turns'!D139)=1,SUM('Turns'!D139),"Unknown")</f>
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
       <c r="T37" s="2">
         <f>IF(COUNT('Turns'!E139)=1,SUM('Turns'!E139),"Unknown")</f>
-        <v>3.0358476e-05</v>
+        <v>3.2452164e-05</v>
       </c>
       <c r="U37" s="2">
         <f>IF(COUNT('Turns'!F139)=1,SUM('Turns'!F139),"Unknown")</f>
-        <v>3.48e-05</v>
+        <v>3.72e-05</v>
       </c>
       <c r="V37" s="2">
         <v>0</v>
@@ -7767,25 +7767,25 @@
       </c>
       <c r="Y37" s="2">
         <f>IF(COUNT('Turns'!E143)=1,SUM('Turns'!E143),"Unknown")</f>
-        <v>6.2985114e-05</v>
+        <v>6.542775e-05</v>
       </c>
       <c r="Z37" s="2">
         <f>IF(COUNT('Turns'!F143)=1,SUM('Turns'!F143),"Unknown")</f>
-        <v>7.22e-05</v>
+        <v>7.5e-05</v>
       </c>
       <c r="AA37" s="5">
         <f>IF(ISNUMBER(Y37),ROUND(Y37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="AB37" s="5">
         <f>IF(ISNUMBER(Z37),ROUND(Z37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="AC37" s="1" t="s">
         <v>166</v>
       </c>
       <c r="AD37" s="1">
-        <v>1073.074</v>
+        <v>1326.951</v>
       </c>
       <c r="AE37" s="1" t="s">
         <v>191</v>
@@ -7817,7 +7817,7 @@
         <v>228</v>
       </c>
       <c r="AD38" s="1">
-        <v>1.531</v>
+        <v>1.558</v>
       </c>
       <c r="AE38" s="1" t="s">
         <v>206</v>
@@ -7849,7 +7849,7 @@
         <v>230</v>
       </c>
       <c r="AD39" s="1">
-        <v>0.522</v>
+        <v>0.506</v>
       </c>
       <c r="AE39" s="1" t="s">
         <v>206</v>
@@ -7882,15 +7882,15 @@
       </c>
       <c r="J40" s="2">
         <f>IF(COUNT('Turns'!D149)=1,SUM('Turns'!D149),"Unknown")</f>
-        <v>281.0</v>
+        <v>285.0</v>
       </c>
       <c r="K40" s="2">
         <f>IF(COUNT('Turns'!E149)=1,SUM('Turns'!E149),"Unknown")</f>
-        <v>4.9027194e-05</v>
+        <v>4.972509e-05</v>
       </c>
       <c r="L40" s="2">
         <f>IF(COUNT('Turns'!F149)=1,SUM('Turns'!F149),"Unknown")</f>
-        <v>5.62e-05</v>
+        <v>5.7e-05</v>
       </c>
       <c r="M40" s="2">
         <f>IF(COUNT('Turns'!D148)=1,SUM('Turns'!D148),"Unknown")</f>
@@ -7915,15 +7915,15 @@
       </c>
       <c r="S40" s="2">
         <f>IF(COUNT('Turns'!D154)=1,SUM('Turns'!D154),"Unknown")</f>
-        <v>50.0</v>
+        <v>46.0</v>
       </c>
       <c r="T40" s="2">
         <f>IF(COUNT('Turns'!E154)=1,SUM('Turns'!E154),"Unknown")</f>
-        <v>5.23422e-05</v>
+        <v>4.8154824e-05</v>
       </c>
       <c r="U40" s="2">
         <f>IF(COUNT('Turns'!F154)=1,SUM('Turns'!F154),"Unknown")</f>
-        <v>6e-05</v>
+        <v>5.52e-05</v>
       </c>
       <c r="V40" s="2">
         <v>0</v>
@@ -7936,11 +7936,11 @@
       </c>
       <c r="Y40" s="2">
         <f>IF(COUNT('Turns'!E158)=1,SUM('Turns'!E158),"Unknown")</f>
-        <v>0.000101369394</v>
+        <v>9.7879914e-05</v>
       </c>
       <c r="Z40" s="2">
         <f>IF(COUNT('Turns'!F158)=1,SUM('Turns'!F158),"Unknown")</f>
-        <v>0.0001162</v>
+        <v>0.0001122</v>
       </c>
       <c r="AA40" s="5">
         <f>IF(ISNUMBER(Y40),ROUND(Y40*'Reference data'!$B$2,0),"Unknown")</f>
@@ -7948,10 +7948,10 @@
       </c>
       <c r="AB40" s="5">
         <f>IF(ISNUMBER(Z40),ROUND(Z40*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="AD40" s="1">
-        <v>1110.847</v>
+        <v>1502.267</v>
       </c>
       <c r="AE40" s="1" t="s">
         <v>184</v>
@@ -7974,7 +7974,7 @@
         <v>110</v>
       </c>
       <c r="F41" s="1">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>190</v>
@@ -7987,15 +7987,15 @@
       </c>
       <c r="J41" s="2">
         <f>IF(COUNT('Turns'!D149)=1,SUM('Turns'!D149),"Unknown")</f>
-        <v>281.0</v>
+        <v>285.0</v>
       </c>
       <c r="K41" s="2">
         <f>IF(COUNT('Turns'!E149)=1,SUM('Turns'!E149),"Unknown")</f>
-        <v>4.9027194e-05</v>
+        <v>4.972509e-05</v>
       </c>
       <c r="L41" s="2">
         <f>IF(COUNT('Turns'!F149)=1,SUM('Turns'!F149),"Unknown")</f>
-        <v>5.62e-05</v>
+        <v>5.7e-05</v>
       </c>
       <c r="M41" s="2">
         <f>IF(COUNT('Turns'!D148)=1,SUM('Turns'!D148),"Unknown")</f>
@@ -8020,15 +8020,15 @@
       </c>
       <c r="S41" s="2">
         <f>IF(COUNT('Turns'!D154)=1,SUM('Turns'!D154),"Unknown")</f>
-        <v>50.0</v>
+        <v>46.0</v>
       </c>
       <c r="T41" s="2">
         <f>IF(COUNT('Turns'!E154)=1,SUM('Turns'!E154),"Unknown")</f>
-        <v>5.23422e-05</v>
+        <v>4.8154824e-05</v>
       </c>
       <c r="U41" s="2">
         <f>IF(COUNT('Turns'!F154)=1,SUM('Turns'!F154),"Unknown")</f>
-        <v>6e-05</v>
+        <v>5.52e-05</v>
       </c>
       <c r="V41" s="2">
         <v>0</v>
@@ -8041,11 +8041,11 @@
       </c>
       <c r="Y41" s="2">
         <f>IF(COUNT('Turns'!E158)=1,SUM('Turns'!E158),"Unknown")</f>
-        <v>0.000101369394</v>
+        <v>9.7879914e-05</v>
       </c>
       <c r="Z41" s="2">
         <f>IF(COUNT('Turns'!F158)=1,SUM('Turns'!F158),"Unknown")</f>
-        <v>0.0001162</v>
+        <v>0.0001122</v>
       </c>
       <c r="AA41" s="5">
         <f>IF(ISNUMBER(Y41),ROUND(Y41*'Reference data'!$B$2,0),"Unknown")</f>
@@ -8053,13 +8053,13 @@
       </c>
       <c r="AB41" s="5">
         <f>IF(ISNUMBER(Z41),ROUND(Z41*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="AC41" s="1" t="s">
         <v>174</v>
       </c>
       <c r="AD41" s="1">
-        <v>1109.252</v>
+        <v>1501.046</v>
       </c>
       <c r="AE41" s="1" t="s">
         <v>191</v>
@@ -8092,15 +8092,15 @@
       </c>
       <c r="J42" s="2">
         <f>IF(COUNT('Turns'!D161)=1,SUM('Turns'!D161),"Unknown")</f>
-        <v>692.0</v>
+        <v>699.0</v>
       </c>
       <c r="K42" s="2">
         <f>IF(COUNT('Turns'!E161)=1,SUM('Turns'!E161),"Unknown")</f>
-        <v>0.000120736008</v>
+        <v>0.000121957326</v>
       </c>
       <c r="L42" s="2">
         <f>IF(COUNT('Turns'!F161)=1,SUM('Turns'!F161),"Unknown")</f>
-        <v>0.0001384</v>
+        <v>0.0001398</v>
       </c>
       <c r="M42" s="2">
         <f>IF(COUNT('Turns'!D160)=1,SUM('Turns'!D160),"Unknown")</f>
@@ -8146,11 +8146,11 @@
       </c>
       <c r="Y42" s="2">
         <f>IF(COUNT('Turns'!E170)=1,SUM('Turns'!E170),"Unknown")</f>
-        <v>0.000141672888</v>
+        <v>0.000142894206</v>
       </c>
       <c r="Z42" s="2">
         <f>IF(COUNT('Turns'!F170)=1,SUM('Turns'!F170),"Unknown")</f>
-        <v>0.0001624</v>
+        <v>0.0001638</v>
       </c>
       <c r="AA42" s="5">
         <f>IF(ISNUMBER(Y42),ROUND(Y42*'Reference data'!$B$2,0),"Unknown")</f>
@@ -8161,7 +8161,7 @@
         <v>16.0</v>
       </c>
       <c r="AD42" s="1">
-        <v>909.125</v>
+        <v>1880.139</v>
       </c>
       <c r="AE42" s="1" t="s">
         <v>184</v>
@@ -8184,7 +8184,7 @@
         <v>110</v>
       </c>
       <c r="F43" s="1">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>190</v>
@@ -8197,15 +8197,15 @@
       </c>
       <c r="J43" s="2">
         <f>IF(COUNT('Turns'!D161)=1,SUM('Turns'!D161),"Unknown")</f>
-        <v>692.0</v>
+        <v>699.0</v>
       </c>
       <c r="K43" s="2">
         <f>IF(COUNT('Turns'!E161)=1,SUM('Turns'!E161),"Unknown")</f>
-        <v>0.000120736008</v>
+        <v>0.000121957326</v>
       </c>
       <c r="L43" s="2">
         <f>IF(COUNT('Turns'!F161)=1,SUM('Turns'!F161),"Unknown")</f>
-        <v>0.0001384</v>
+        <v>0.0001398</v>
       </c>
       <c r="M43" s="2">
         <f>IF(COUNT('Turns'!D160)=1,SUM('Turns'!D160),"Unknown")</f>
@@ -8251,11 +8251,11 @@
       </c>
       <c r="Y43" s="2">
         <f>IF(COUNT('Turns'!E170)=1,SUM('Turns'!E170),"Unknown")</f>
-        <v>0.000141672888</v>
+        <v>0.000142894206</v>
       </c>
       <c r="Z43" s="2">
         <f>IF(COUNT('Turns'!F170)=1,SUM('Turns'!F170),"Unknown")</f>
-        <v>0.0001624</v>
+        <v>0.0001638</v>
       </c>
       <c r="AA43" s="5">
         <f>IF(ISNUMBER(Y43),ROUND(Y43*'Reference data'!$B$2,0),"Unknown")</f>
@@ -8269,7 +8269,7 @@
         <v>177</v>
       </c>
       <c r="AD43" s="1">
-        <v>907.468</v>
+        <v>1878.597</v>
       </c>
       <c r="AE43" s="1" t="s">
         <v>191</v>

--- a/reports/expert_dispatch/report.xlsx
+++ b/reports/expert_dispatch/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="235">
   <si>
     <t>Request</t>
   </si>
@@ -75,13 +75,13 @@
     <t>Parent ID</t>
   </si>
   <si>
-    <t>Fresh input tokens</t>
-  </si>
-  <si>
-    <t>Fresh input EUR</t>
-  </si>
-  <si>
-    <t>Fresh input USD</t>
+    <t>Input at standard rate tokens</t>
+  </si>
+  <si>
+    <t>Input at standard rate EUR</t>
+  </si>
+  <si>
+    <t>Input at standard rate USD</t>
   </si>
   <si>
     <t>Cache read tokens</t>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cce0-6735-7753-8e79-ce7749b5311e</t>
+    <t>01a0d142-02ad-7f61-bee4-a7ae5c6e26f0</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-22</t>
+    <t>2026-09-23</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T06:06:28.037095Z</t>
+    <t>2026-09-24T02:09:35.117183Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,10 +306,10 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cce0-673b-7381-86bc-4c8b7a3b3cd2</t>
-  </si>
-  <si>
-    <t>Fresh input</t>
+    <t>01a0d142-02b1-76a3-b75e-9a60010f6341</t>
+  </si>
+  <si>
+    <t>Input at standard rate</t>
   </si>
   <si>
     <t xml:space="preserve">    Tool definitions</t>
@@ -342,8 +342,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"type": "function_call", "name": "task", "arguments": "{\"description\":\"Answer the movie question: Who directed the film Spirited Away? Provide the director's name and, if useful, the film's release year. Keep it concise and factually accurate.\",\"subagent_type\":\"movie_expert\"}", "call_id": "call_fQTXffX0DYMpQJyRpeeyO3l0", "id": "fc_01bfb711a688d9f4006ab36ca6b8a087d28630c7c7c85a76ab", "index": 0}]
-{"name": "task", "args": {"description": "Answer the movie question: Who directed the film Spirited Away? Provide the director's name and, if useful, the film's release year. Keep it concise and factually accurate.", "subagent_type": "movie_expert"}, "id": "call_fQTXffX0DYMpQJyRpeeyO3l0", "type": "tool_call"}</t>
+    <t>[{"type": "function_call", "name": "task", "arguments": "{\"description\":\"Answer the movie question: Who directed the animated film Spirited Away? Provide the director's name and, if useful, a brief identifying context. Be accurate and concise.\",\"subagent_type\":\"movie_expert\"}", "call_id": "call_PrxdCxR8ikTMeqXJV3eOGj8Y", "id": "fc_0fab2a2f54a70e43006ab48bc8645087d29e7fcc5c16d6e514", "index": 0}]
+{"name": "task", "args": {"description": "Answer the movie question: Who directed the animated film Spirited Away? Provide the director's name and, if useful, a brief identifying context. Be accurate and concise.", "subagent_type": "movie_expert"}, "id": "call_PrxdCxR8ikTMeqXJV3eOGj8Y", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -355,25 +355,25 @@
     <t>Tool · task</t>
   </si>
   <si>
-    <t>01a0cce0-6dfc-7842-8cb4-715f37153254</t>
+    <t>01a0d142-090f-7921-96c2-48e5b91aa36e</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
   </si>
   <si>
-    <t>{'description': "Answer the movie question: Who directed the film Spirited Away? Provide the director's name and, if useful, the film's release year. Keep it concise and factually accurate.", 'subagent_type': 'movie_expert'}</t>
+    <t>{'description': "Answer the movie question: Who directed the animated film Spirited Away? Provide the director's name and, if useful, a brief identifying context. Be accurate and concise.", 'subagent_type': 'movie_expert'}</t>
   </si>
   <si>
     <t xml:space="preserve">    Result</t>
   </si>
   <si>
-    <t>Command(update={'messages': [ToolMessage(content='*Spirited Away* was directed by **Hayao Miyazaki** and released in **2001**. [Source](https://www.ghibli.jp/works/)', tool_call_id='call_fQTXffX0DYMpQJyRpeeyO3l0')]})</t>
+    <t>Command(update={'messages': [ToolMessage(content='*Spirited Away* was directed by **Hayao Miyazaki**, the renowned Japanese animator and filmmaker. ([Studio Ghibli](https://www.ghibli.jp/works/))', tool_call_id='call_PrxdCxR8ikTMeqXJV3eOGj8Y')]})</t>
   </si>
   <si>
     <t>R2</t>
   </si>
   <si>
-    <t>01a0cce0-6dff-7d73-9fe8-97986ba55391</t>
+    <t>01a0d142-0912-7610-aad6-cb6582fa94f4</t>
   </si>
   <si>
     <t>You are the movies expert. Use search_movie_reference to retrieve evidence before answering the delegated question. Base factual claims on the returned passages and cite their source URLs. If no relevant evidence is found, explain the collection's limits instead of inventing an answer or claiming web research. Answer concisely. The collection is a small local teaching reference, not a complete or continually updated source.</t>
@@ -382,17 +382,17 @@
     <t>Reasoning</t>
   </si>
   <si>
-    <t>[{"id": "rs_05560943d4ef939e006ab36ca80f7087d2b77a5361027a4f7d", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2yoCWDDiimauxpzFQ3_EKiK2i4ZtYpreIsGTtbzvvccn0tikmQBA5BdXOgfuPey9o-Fa19HrzklfM1aNhvtqppUq9MAKm1VjbbpMiZIZ9J9jYtCKC2Bck6cKo2f8xP3c78-lekyMqgbOjY_aTXr6B_e07_jxW7BfGkkJ-mB4JYdoiMGXDOpdEXbd1CV6Bev9nZWM_tvMDsBik90qOLZ2DzbY5sQbZ5YP-ECyT18MFuEGaK7CW2a5MuyohCWH1sX2BEzqWImNZtg9D16r8UrW4Hbs8TXCKFQFzkuvuTd5DP1psbPO4aknZAhl00G-jnEFvnsIRQ7u2tnCOUGWc-hkEy-WDYdizSVXVcrXwy48ahi_WHTWf_3M_7KD0b7z7SYP-m0JO6qHv4QK5LvTEG1YxlZxnp6-6jVTr1_XyB84uJnifgDrp8l--KyjGSwxGIRW8WN-bx--XbhqvMfwl0u4yHPLEks9Gqbvc1J26G5Omkqi1gVBAooaF7D7hHlc89RG1-4mGyii6evIP3btjp2HzB0MAa3otZAPIzneOy__THa5_xce3SuEj19P_v7VpY4P9jxYyqIJAaBb6Cn-kdJjFPtMTPtVV7ZWLI3HJv9QzDsOJroXfgEGwOU2BBKNCY9egX2-FrFCnGy4n5b-sJ_hU7QFsNDAoECxnq0ZL0HeUsKqi9jp1uz_ER0mfm_if-dK2HofJlV0JlEvIKiZWIsDec2_1qaTi62kdIxFrE6qRmY7oe2vU-Z0X520kgTT8Z86jcUhDSRtlxgL_arRA1uF42bPT90krRliF_rbPZ4eN5BWVHVjYGHXepyMG0RvKxRGOVLCul1XDNTO6AIwc7bqSeoauN31i3nIsN1CrLy2ZGLVkws418C1jZRKT3YDMKH-JMr2oTNI7ou2bqDDPtJPVqsjdQJ7Mtkx4Diu01KmfVYmzYPCAMLij4FrmW41mTgsCizuaob4yCiae8uqBm9CKWNddudaWOGvUxLokHuXsTd26JUCJ_BQUqP8UX4wz-MmuwAISplsiYmKiFXnpwwo0SkRHT6NH8JERyoBE2ATtNH9hCU3ebrMTo-E_0Kd0R-r_MZf9p-BtPuuk6Yi3wop4miXwvoYpW4oVjCnsmeK6yqi5mEhrV9ioRzBJxh2z0pgKuWoxDvxJQVlJkklrtUWidgwHEXBBxidTXQMJZf2RxJt6ZqFaJH0xT0tO4XBx4Gi0ej"}, {"type": "function_call", "name": "search_movie_reference", "arguments": "{\"query\":\"Who directed the film Spirited Away? Include director and release year.\"}", "call_id": "call_eRwbrLBgu4XYeUicLddKy3yk", "id": "fc_05560943d4ef939e006ab36ca83a4c87d2acc0a6b30564a3f8", "index": 1}]
-{"name": "search_movie_reference", "args": {"query": "Who directed the film Spirited Away? Include director and release year."}, "id": "call_eRwbrLBgu4XYeUicLddKy3yk", "type": "tool_call"}</t>
+    <t>[{"id": "rs_00ccf8bc254a0520006ab48bc9c57c87d291ca3d74e17d1a70", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIvKo1mXpIa-e6G3aAzbB15xZGDlSbHtIBhe7vODm1fXSmH_42xCNb5w0GxeIcjbrw7egZcrTs-KVrQL2c6721N7H3BTs2JI6LKC-p595SBDGjBxLs-UbrS3BmYzrzBpeRx3G2PzKAgjttIlQg8md8YLLaDVecIoI_Tw22Y4-GFo3W6Y0Hlcvy4hyv1xF5qgicHOg7M1_jaMm8Bvap_pKa-zIJjeAI5SwsQs8lAFGUAeJNXgqhft1vcZ6WONkCh0as8dTzNAY6zez_OAh3sFbyixAxeN34Ield3l0r7WeqoFPDB_ZLyYHLcsi4sSxaKTJob9ocstLJLurP12UNSmL-8wJCPPAOtWm6LO4ds2_gQBaZYToLtPWy2QYV6g-tg6RcA8fJHtyUBLHcnO2N1_y7PX8Zr3n9wDlVmmTs2Ulo6N60GM9Aqn1BnJ171e4EIVv_pzhG_gCXCsK2jL0RRDszVbhIcgQN3FxiC2opAyQyAsq9o9SLcLc5UeLiNJ91CjUX9kK_Ty0KNBuaxMR2FSMJRbWyrFn7eYZgStIvMlBjmWeSNPQo4PZI-qBvXgLDUE5k0EurnDyE95rgMQY0a_M_JUMhDkLVn2_IT0Zvbeq2v49_xT_XKwoniZzbz2b1_a_Z0HmcQc4VMP9YhB7aDWK4d9E_6_d1eUNaII_65cegQaABcHHxT2GSasUjAv6Fy9p_bMLVgJ2dJe-xonMD_I1Tf_6VOycZzR2dinc-VYPna4TCn3v_cOzvstfo6JXFGNrDsisRfMonlUDlOv7ShJ7Ub9nYof1Y7q30F7LtpQaLBtdTESTjRth-tpfywJqrJaNffcvwJDjoDnI8R5X5JolYKNzHOsksSgJkB8nihm0NvTt-v5k5xcJNiulvvJOrQ_6FTjmYdiqfoZfDRsz7HaykzMX3E4XWMTHyuASXYSv6MUD7bx5SylI1ssEwLTEC_57wSA6Ug3m4EOI_GfgLQPwAQstpWVuxu6peFWJ00wXRSFgz6ccjVpnRLHfWWY8iPlzYJ-pVwJgcSE0RSry6P16RSPKBbXtzlMeOEpFAqtRgdGYt1DcvQfY0cqoAoadxrszRyzJK_iURZRkWeQugtPXjz59Y2elt77dvOC8Ih8XISGrKUk3Qc1Z_YEGocC-A7bHGpbgfgsqTMVfkyXQOGkF65Crcm0d9M60E_ARVzBKCMi0Sc="}, {"type": "function_call", "name": "search_movie_reference", "arguments": "{\"query\":\"Who directed the animated film Spirited Away? Director name and identifying context.\"}", "call_id": "call_UiDI8ksCWWneZfqDvCA3eZSj", "id": "fc_00ccf8bc254a0520006ab48bca03a887d2b9a29d4b0fe4ea65", "index": 1}]
+{"name": "search_movie_reference", "args": {"query": "Who directed the animated film Spirited Away? Director name and identifying context."}, "id": "call_UiDI8ksCWWneZfqDvCA3eZSj", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · search_movie_reference</t>
   </si>
   <si>
-    <t>01a0cce0-72b4-7021-80e5-546ed0198f9f</t>
-  </si>
-  <si>
-    <t>{'query': 'Who directed the film Spirited Away? Include director and release year.'}</t>
+    <t>01a0d142-0ec6-7ad3-b9c4-d5e03b83dcc8</t>
+  </si>
+  <si>
+    <t>{'query': 'Who directed the animated film Spirited Away? Director name and identifying context.'}</t>
   </si>
   <si>
     <t>Spirited Away
@@ -403,7 +403,7 @@
     <t>R3</t>
   </si>
   <si>
-    <t>01a0cce0-72b6-72b2-9083-549c77f57bca</t>
+    <t>01a0d142-0ecc-7b40-a02b-be7a4fb7f47a</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
@@ -412,19 +412,19 @@
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "*Spirited Away* was directed by **Hayao Miyazaki** and released in **2001**. [Source](https://www.ghibli.jp/works/)", "phase": "final_answer", "index": 0, "id": "msg_05560943d4ef939e006ab36ca9327887d2bd99ceacba810971"}]</t>
+    <t>[{"type": "text", "text": "*Spirited Away* was directed by **Hayao Miyazaki**, the renowned Japanese animator and filmmaker. ([Studio Ghibli](https://www.ghibli.jp/works/))", "phase": "final_answer", "index": 0, "id": "msg_00ccf8bc254a0520006ab48bcb49fc87d2b72a5db3da3143f7"}]</t>
   </si>
   <si>
     <t>R4</t>
   </si>
   <si>
-    <t>01a0cce0-76d3-7d11-997d-232ba008e854</t>
-  </si>
-  <si>
-    <t>*Spirited Away* was directed by **Hayao Miyazaki** and released in **2001**. [Source](https://www.ghibli.jp/works/)</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "*Spirited Away* was directed by **Hayao Miyazaki**.", "phase": "final_answer", "index": 0, "id": "msg_01bfb711a688d9f4006ab36caa2e8487d2989b20fb595cfbe3"}]</t>
+    <t>01a0d142-151d-7513-bc8f-bfaecf6b5347</t>
+  </si>
+  <si>
+    <t>*Spirited Away* was directed by **Hayao Miyazaki**, the renowned Japanese animator and filmmaker. ([Studio Ghibli](https://www.ghibli.jp/works/))</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "*Spirited Away* was directed by **Hayao Miyazaki**.", "phase": "final_answer", "index": 0, "id": "msg_0fab2a2f54a70e43006ab48bccb7c887d2990851df9b4a24e5"}]</t>
   </si>
   <si>
     <t>Turn 2</t>
@@ -433,45 +433,45 @@
     <t>R5</t>
   </si>
   <si>
-    <t>01a0cce0-7a25-7800-b4a8-95fea5aebf69</t>
+    <t>01a0d142-19b2-7110-83db-430607606dce</t>
   </si>
   <si>
     <t>How many players does a basketball team have on court?</t>
   </si>
   <si>
-    <t>[{"type": "function_call", "name": "task", "arguments": "{\"description\":\"Answer this sports rules question: How many players from one basketball team are on the court at a time during standard basketball play? Mention the usual five-player rule, and briefly note if relevant that rules can vary by format (such as 3x3). Keep it concise.\",\"subagent_type\":\"sports_expert\"}", "call_id": "call_kIUUc8kx5AP4y5q4UPHxCoDx", "id": "fc_01bfb711a688d9f4006ab36cab1b8487d29058068b0fc9517f", "index": 0}]
-{"name": "task", "args": {"description": "Answer this sports rules question: How many players from one basketball team are on the court at a time during standard basketball play? Mention the usual five-player rule, and briefly note if relevant that rules can vary by format (such as 3x3). Keep it concise.", "subagent_type": "sports_expert"}, "id": "call_kIUUc8kx5AP4y5q4UPHxCoDx", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0cce0-8083-70a2-8711-35071f6e667e</t>
-  </si>
-  <si>
-    <t>{'description': 'Answer this sports rules question: How many players from one basketball team are on the court at a time during standard basketball play? Mention the usual five-player rule, and briefly note if relevant that rules can vary by format (such as 3x3). Keep it concise.', 'subagent_type': 'sports_expert'}</t>
-  </si>
-  <si>
-    <t>Command(update={'messages': [ToolMessage(content='In standard basketball, **five players from each team** are on the court at a time. Other formats vary—for example, **3x3 basketball uses three players per team**. [FIBA](https://about.fiba.basketball/en/our-sport/basketball)', tool_call_id='call_kIUUc8kx5AP4y5q4UPHxCoDx')]})</t>
+    <t>[{"type": "function_call", "name": "task", "arguments": "{\"description\":\"Answer the sports question: How many players from one basketball team are on the court at a time? Mention the standard rule and briefly note any common variation only if relevant. Be concise.\",\"subagent_type\":\"sports_expert\"}", "call_id": "call_UI44fxbiLsncsRWgaCDVhjjn", "id": "fc_0fab2a2f54a70e43006ab48bcdf11887d2ae2f754130b987c0", "index": 0}]
+{"name": "task", "args": {"description": "Answer the sports question: How many players from one basketball team are on the court at a time? Mention the standard rule and briefly note any common variation only if relevant. Be concise.", "subagent_type": "sports_expert"}, "id": "call_UI44fxbiLsncsRWgaCDVhjjn", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0d142-1eb4-7932-bef7-c9981e3ce538</t>
+  </si>
+  <si>
+    <t>{'description': 'Answer the sports question: How many players from one basketball team are on the court at a time? Mention the standard rule and briefly note any common variation only if relevant. Be concise.', 'subagent_type': 'sports_expert'}</t>
+  </si>
+  <si>
+    <t>Command(update={'messages': [ToolMessage(content='In standard basketball, **five players from each team** are on the court at a time. (The separate 3x3 format uses three.)  \nSource: [FIBA](https://about.fiba.basketball/en/our-sport/basketball)', tool_call_id='call_UI44fxbiLsncsRWgaCDVhjjn')]})</t>
   </si>
   <si>
     <t>R6</t>
   </si>
   <si>
-    <t>01a0cce0-8086-79c3-b591-884905dd4c6f</t>
+    <t>01a0d142-1eba-75e1-a137-ed4f98e474a0</t>
   </si>
   <si>
     <t>You are the sports expert. Use search_sports_reference to retrieve evidence before answering the delegated question. Base factual claims on the returned passages and cite their source URLs. If no relevant evidence is found, explain the collection's limits instead of inventing an answer or claiming web research. Answer concisely. The collection is a small local teaching reference, not a complete or continually updated source.</t>
   </si>
   <si>
-    <t>[{"id": "rs_0cca63b5ce4951db006ab36cacc97c87d2a1d7ff9442a60a81", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2yt_WDtmOf5wmkhq2NJ_Kfc3fBkWEDuj7RSfCh3gR-eJod2QnBJqhztpWq02r2i9WJgAdL6J48m0B7KVC8MFDjij7hrblcjVYHrkBHoG34-Ah4XSmUkhkLKxz7PJPqEVHRxwqrFmefK6BmVkUBu0RUPluNFTslEH7WPNqb85shvflIR4G1yovujbEUuWBQqtWIBlq0Ap2-HDYzHiA-O_fo17F1tOAyrH_sU0bQj70bwL5x2FP6Fbv1XC-3FtRYavEnT2IkQD5ZPvKGH-4qO9GApElZgWR6vNG2q21GC1cHQzvmHR_JvekvJBtPsaaDgWGoVvyzhZfxCU3gQ667Ix960XIqBmAYIzpsZ9n6Rnu_Y3aTvQoE-lF8lDim3VLxKvEcpoGkOcn17dhNz7eXckjpLprjLgk8z-8tWvaSaKm0YO0DAPLW8YZZUIayS6SLi7DoOtmTNGv9xNXR78zs0xad_AkUVgvU6gULIBxYjt3gltf3U3WQeVBhcm4cLbF8wWP6V1CcdI7HLnSLHxjDxZnT2eHxtK8UltJ8LxBJoQlXcegQg3ki3TwtGFFVNzSgzPyJc6ajfMAZb7wOhtDBR2teHp_AjSJM9Skfp-_kx0AcX7fKLeOpXmFcr_beY2sIUbyvkS3_RyWhRgpnhJJP4HDfHOp5ZlArwIB3uOb4KO1W3dOVrdfLrD-9nlKDTVOBAScSlDY12g_IU4KpDhUXObJtBCo92bYxXnwOfWL6-ZkJ5rqBB6ngjwuMkiCT8XoImkj0dAVSMbGClPrqk21FwWE2Fh9oPWs2yAToN6OD-yyWn1iwYFOZeaqDK8kUuVVPhEkLAd5IH-gvIPGsKe36mb0GUHjXwiTARytNQVch_mmS7auKTIjIDhSMf_loisaYwUiuWSGiSGRhTehFnFTFMLKk-l7T5b7O--1HEKahJi1EQsbZ9wQY_l6nJQW7PJqpLhcdsRXZzjzoB_cuFAyZynPr-K55is0GzpEahoy5JjzyjesyspClmXrrBzSdq35rDhqpabD-tZOfvHKrhNFS9wsjFbrj6w52FICc7HMUThjpUZYdQOM28a9XkjUURbZwfE-pJPXBhAGr7fobzEOX9LCGFTf0AwkkM3HwpjyV5UgvrRriVMCcpTwAnCBAK4qCWu-Q0YnpNhWKiuGVGpei50io_l2lV9TKB5-a-k0rAPqGbpxXWHO7VEi9sE2dVPKmBdxGw"}, {"type": "function_call", "name": "search_sports_reference", "arguments": "{\"query\":\"How many players from one basketball team are on the court at a time during standard basketball play? usual five-player rule and 3x3 variation\"}", "call_id": "call_5P5x3EaI3rhJfUdzCFdKaUvL", "id": "fc_0cca63b5ce4951db006ab36cad032487d2b15ba2c6a7d077f6", "index": 1}]
-{"name": "search_sports_reference", "args": {"query": "How many players from one basketball team are on the court at a time during standard basketball play? usual five-player rule and 3x3 variation"}, "id": "call_5P5x3EaI3rhJfUdzCFdKaUvL", "type": "tool_call"}</t>
+    <t>[{"id": "rs_0ab3c6584ecff013006ab48bcf0de887d29cc4e8a2ef024907", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIvPTePCxs54MuFTbxQgTKto8PuyS_j01PkObHUa6pa2Otc3VEnKdGVi1ECoUTe9n4IGM46UGh9eGPSvqmra2dNab2S6cUC-j7-n_Ru4BMNPFvpHn23dkfqEyhK_x50NSxclzGytRH3-WWx-V9aL9KPxSR_siDz-lgZam09gqiwdR8iShN84H9JYJqXxhygiGHlnIhBHmDKo8klf3UxJ9CKmJ7BykduNo-K5Oez_ysnmxgjoiJRmpTQ3aZRwlQS_1KSsCdEo1bhGN6usPT2r0yAAqgekUQk7MDnQNzfTPodV3pk4UcOcRbcLSInbqQK_-EpfNNcfmOxVKDIm6vOi1eGNjBUCynmi-ha5huabNns1kntWEbiuFN2bEv51VgwPP7OHgZUuJfQnOVQLx03u4gE8sVu_dtfWXCqVkzfm_q-1sg4lJcAB0PZXq6UnJ80y_mIDwxwmMacXwK6-onGLT4rYAJLS53uW-OvW0fFJJY1FjjHpdxRYcJNaumLzkMXkrtfMnWJj3M-wd-WOn_KztT6xLQVfl6g_IDXGXBu4_H-5WaKrl_pbiCjRAPueNWtCD2LAWmcP8_LuVxay-Fj4xPkaZtuWJdurveNwVfFiWv6Q899OnxhIpqJcB9PuGtvHVqIuszRGlScM-jBUHnXuf9L065DxQewhT7MAXba7Gn1YoOIF918dfCXdSRWLYWQNmAma9izmMRLgPhPU636CyVGWy2GMM2pIhtq0dGbn6ceCxkuuxVqYL-rLVvDRel_wURurNQRK53gUyxVs-NeF77lV7WL-y0Y6YkggRwaBPwhz2Mw-HOWDnCKOFY6jes7E_Jg_FuduCKgXOKDIjPqvidcWRcm_gV6U-21x3o39q1D0LrG7jBq4CbLTt1RyT4TXB9DnCWNKRmkH74c22mvMjCnASTfA4c7aLaUFZ8T2etnkj-2gV-vupezWqQ8yVyBm6XyI1eD815zyZvtUDby6kGged_uenhC3zjAeAjLvSz67XVgJro6FFMaXJzhISR68yr2n5JM6_c29Vco52yarDRZsxpiULheepBaLcJ03JoueTPNXX7k3SDzCKrtBqvfHBFmwotVz6F3ZjQt0aLivAFiwnvgIjsiaPWikXmw8gVzFbvIcSZokwmyIwWt1lKuuJP_mHY2PK3t1fYla096iTMUBNf2Ng-EGGPrI_zyhwDNboF5gsdUwHocjYz4tP9vfcDMw"}, {"type": "function_call", "name": "search_sports_reference", "arguments": "{\"query\":\"How many players from one basketball team are on the court at a time? standard rule common variation\"}", "call_id": "call_AK913aOW2zvZsx5H1YHRHUP9", "id": "fc_0ab3c6584ecff013006ab48bcf370c87d2bcba8a5e2bd85a19", "index": 1}]
+{"name": "search_sports_reference", "args": {"query": "How many players from one basketball team are on the court at a time? standard rule common variation"}, "id": "call_AK913aOW2zvZsx5H1YHRHUP9", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · search_sports_reference</t>
   </si>
   <si>
-    <t>01a0cce0-86e8-7831-9f70-ab248e3fa642</t>
-  </si>
-  <si>
-    <t>{'query': 'How many players from one basketball team are on the court at a time during standard basketball play? usual five-player rule and 3x3 variation'}</t>
+    <t>01a0d142-233d-7433-b9a1-9d986a424ec7</t>
+  </si>
+  <si>
+    <t>{'query': 'How many players from one basketball team are on the court at a time? standard rule common variation'}</t>
   </si>
   <si>
     <t>Standard basketball teams
@@ -482,22 +482,23 @@
     <t>R7</t>
   </si>
   <si>
-    <t>01a0cce0-86ea-7592-b133-6c2752827ac5</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "In standard basketball, **five players from each team** are on the court at a time. Other formats vary\u2014for example, **3x3 basketball uses three players per team**. [FIBA](https://about.fiba.basketball/en/our-sport/basketball)", "phase": "final_answer", "index": 0, "id": "msg_0cca63b5ce4951db006ab36cae50e087d283ef0b2e43bd347a"}]</t>
+    <t>01a0d142-2342-7ca0-893a-2ef56c31a18c</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "In standard basketball, **five players from each team** are on the court at a time. (The separate 3x3 format uses three.)  \nSource: [FIBA](https://about.fiba.basketball/en/our-sport/basketball)", "phase": "final_answer", "index": 0, "id": "msg_0ab3c6584ecff013006ab48bd05ff887d2827deac2c998e246"}]</t>
   </si>
   <si>
     <t>R8</t>
   </si>
   <si>
-    <t>01a0cce0-8c38-7723-b72a-5b81b7556b81</t>
-  </si>
-  <si>
-    <t>In standard basketball, **five players from each team** are on the court at a time. Other formats vary—for example, **3x3 basketball uses three players per team**. [FIBA](https://about.fiba.basketball/en/our-sport/basketball)</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "In standard basketball, **five players per team** are on the court at a time.", "phase": "final_answer", "index": 0, "id": "msg_01bfb711a688d9f4006ab36cafcc9087d28a9f005ff4824f0b"}]</t>
+    <t>01a0d142-2817-72a1-8e99-22da4e6f8316</t>
+  </si>
+  <si>
+    <t>In standard basketball, **five players from each team** are on the court at a time. (The separate 3x3 format uses three.)  
+Source: [FIBA](https://about.fiba.basketball/en/our-sport/basketball)</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "In standard basketball, **five players from each team** are on the court at a time.", "phase": "final_answer", "index": 0, "id": "msg_0fab2a2f54a70e43006ab48bd1909c87d2a8a203290a1cf888"}]</t>
   </si>
   <si>
     <t>Turn 3</t>
@@ -506,45 +507,45 @@
     <t>R9</t>
   </si>
   <si>
-    <t>01a0cce0-9062-7552-9690-6278e93401d3</t>
+    <t>01a0d142-2bea-71b2-891f-ad6d2ad2d09c</t>
   </si>
   <si>
     <t>In which year did the Berlin Wall fall?</t>
   </si>
   <si>
-    <t>[{"type": "function_call", "name": "task", "arguments": "{\"description\":\"Answer this history question: In which year did the Berlin Wall fall? Give the year and, if useful, the date (9 November). Keep it concise and accurate.\",\"subagent_type\":\"history_expert\"}", "call_id": "call_gCytLnlCZd19JdIN3DhuOGoH", "id": "fc_01bfb711a688d9f4006ab36cb1638087d285e4d75556e6bfca", "index": 0}]
-{"name": "task", "args": {"description": "Answer this history question: In which year did the Berlin Wall fall? Give the year and, if useful, the date (9 November). Keep it concise and accurate.", "subagent_type": "history_expert"}, "id": "call_gCytLnlCZd19JdIN3DhuOGoH", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0cce0-9884-7282-9bd6-f28a2472d0cc</t>
-  </si>
-  <si>
-    <t>{'description': 'Answer this history question: In which year did the Berlin Wall fall? Give the year and, if useful, the date (9 November). Keep it concise and accurate.', 'subagent_type': 'history_expert'}</t>
-  </si>
-  <si>
-    <t>Command(update={'messages': [ToolMessage(content='The Berlin Wall fell in **1989**, on **9 November**. [Source](https://www.stiftung-berliner-mauer.de/de/ueber-uns/leichte-sprache/geschichte)', tool_call_id='call_gCytLnlCZd19JdIN3DhuOGoH')]})</t>
+    <t>[{"type": "function_call", "name": "task", "arguments": "{\"description\":\"Answer the history question: In which year did the Berlin Wall fall? Give the year and, if useful, the specific date. Be concise and accurate.\",\"subagent_type\":\"history_expert\"}", "call_id": "call_ACuuKSsbQFwmWbJCOqGwklB2", "id": "fc_0fab2a2f54a70e43006ab48bd2822487d287f0185a94c9f6a6", "index": 0}]
+{"name": "task", "args": {"description": "Answer the history question: In which year did the Berlin Wall fall? Give the year and, if useful, the specific date. Be concise and accurate.", "subagent_type": "history_expert"}, "id": "call_ACuuKSsbQFwmWbJCOqGwklB2", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0d142-303f-76a1-8184-b62ddbee2583</t>
+  </si>
+  <si>
+    <t>{'description': 'Answer the history question: In which year did the Berlin Wall fall? Give the year and, if useful, the specific date. Be concise and accurate.', 'subagent_type': 'history_expert'}</t>
+  </si>
+  <si>
+    <t>Command(update={'messages': [ToolMessage(content='The Berlin Wall fell in **1989**, opening on **9 November 1989**. Source: https://www.stiftung-berliner-mauer.de/de/ueber-uns/leichte-sprache/geschichte', tool_call_id='call_ACuuKSsbQFwmWbJCOqGwklB2')]})</t>
   </si>
   <si>
     <t>R10</t>
   </si>
   <si>
-    <t>01a0cce0-9887-7ea3-a249-4e2712e4b63b</t>
+    <t>01a0d142-3045-71f0-92a6-6ea718317cf6</t>
   </si>
   <si>
     <t>You are the history expert. Use search_history_reference to retrieve evidence before answering the delegated question. Base factual claims on the returned passages and cite their source URLs. If no relevant evidence is found, explain the collection's limits instead of inventing an answer or claiming web research. Answer concisely. The collection is a small local teaching reference, not a complete or continually updated source.</t>
   </si>
   <si>
-    <t>[{"type": "function_call", "name": "search_history_reference", "arguments": "{\"query\":\"In which year did the Berlin Wall fall? Date 9 November\"}", "call_id": "call_wwPYoEAWNebiCjRkOFUED6Hs", "id": "fc_0bd57306de4d18b3006ab36cb339dc87d2ae9562865cc15b62", "index": 0}]
-{"name": "search_history_reference", "args": {"query": "In which year did the Berlin Wall fall? Date 9 November"}, "id": "call_wwPYoEAWNebiCjRkOFUED6Hs", "type": "tool_call"}</t>
+    <t>[{"id": "rs_096f18f5a5025ecd006ab48bd3e61487d2975bc269cabc50cd", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIvUYWd_QcIDynGzoU260kn80ymQlb5wvpXRk8EOwIlaGvOOWv86XPqaw57qPz7n_1evVekYbLTH36SD0n6MrhOvJ7s_dbecib2F6rRM65mnVoShDwuG0A3-_RAWrTTCKLsE6lqA8KbgusTSn03CVozLbTBfJd3ZfYVYHaUEBxBZDeWIBB6SLITPXatLOy9MvaXl3Mwf6AWuT7DVs0X3GDV_1OJDECgcZIqd7_8D4O13SWtd1pd9yIRqHOwW4o0YUSZkz-ZjzYbE0x7DlMWk-Y9mrAV6j6Xe8WkST-6xvXS0M1FsvMh9ed-K6OiPe9IHdqhpZ2HOxGKmKWpcn23x2EjVoHjqgGbJrnGkZN3OCm_Rc1nU_31FD5A2gAdW5rENgHWI7foC_JnDXq9LOtjp0JL7mfjHNogPMOpEPVdoO57mwks73LGNIsi4kKCzKrk33NaeRoTkxePYciC0DZ5zGdrzG7LRElOFO3Cs7VQfoon8bdASYkp6Ctt_WQ23x1XZYFgrVbxA0l8qi6iAPuV4yVk5thWeaoL5C6mBt56GDV43bFi2nhaHw-y4QBF9GOhBdC6qEUkShRUgUQQ5-t-SfM_Ke9fpq5udU3hWlZ_zDUxlHQJXIWgGSwHERsa3uZVgNlc48z6kl4CEHJ4zSLX_QQdiBfXWDMwlHTxNjve40XpZil-JPR59YmorEe820hncCaFhfeQZ58s0Y1UYaFMgFS4xOi_5zWZeQzdYMdkzhBOhX3OZTjasrYjVct3pIF-acLv0Hw9J8JU9fz4wdqvehWQ7BitNvBeADKEnyyOSgJ8Jjf9aasPKRjDzVTH4K15BRfPvtMd-pQp314gVPpXM5Sk1btJH1NcQtKfeXLPezl5uQIOeak43Gb5Tj5dv-cfsWVCmcID5d7a7d3xaM_8F5xyn8JR1jGtwfskWjgSVP6sh8V3ronOy_HqKzv6yewg5CDMTcB3-LlbIE9p5RadDIuO2xztxVRapU2ExPtaq31gsUdB684OH3iFFjYQa6nnXI__pHqyZiCRzuC-rOOiuUTevWF_7lMhfBRuXVS8sEFqTKjRZ0DGTRYttybNqRDr3vtTmnbdUezR7Z1_tf3E2D9hwWnP9w0X6gU6DLD4KcDOXB6xiL4Gqb6dXDis7MUler6e4U2b3NrHrvioZtahaP3Q4BsclYyrVp28d8tUOs-cIP-byXUUXDYMNqyDGBY90A4p0"}, {"type": "function_call", "name": "search_history_reference", "arguments": "{\"query\":\"In which year did the Berlin Wall fall? specific date Berlin Wall opening/fall\"}", "call_id": "call_a6ujowYed8uba6tJS9HeXLdQ", "id": "fc_096f18f5a5025ecd006ab48bd412d087d29b6dcc2e31a3214a", "index": 1}]
+{"name": "search_history_reference", "args": {"query": "In which year did the Berlin Wall fall? specific date Berlin Wall opening/fall"}, "id": "call_a6ujowYed8uba6tJS9HeXLdQ", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · search_history_reference</t>
   </si>
   <si>
-    <t>01a0cce0-9db8-7c60-9777-e9b2ee77195c</t>
-  </si>
-  <si>
-    <t>{'query': 'In which year did the Berlin Wall fall? Date 9 November'}</t>
+    <t>01a0d142-3637-79f3-8638-4957b57fbed8</t>
+  </si>
+  <si>
+    <t>{'query': 'In which year did the Berlin Wall fall? specific date Berlin Wall opening/fall'}</t>
   </si>
   <si>
     <t>Opening of the Berlin Wall
@@ -555,22 +556,22 @@
     <t>R11</t>
   </si>
   <si>
-    <t>01a0cce0-9dba-7b73-a33b-1ac39dbf419b</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "The Berlin Wall fell in **1989**, on **9 November**. [Source](https://www.stiftung-berliner-mauer.de/de/ueber-uns/leichte-sprache/geschichte)", "phase": "final_answer", "index": 0, "id": "msg_0bd57306de4d18b3006ab36cb48a0887d2b1efd650f7edcbd4"}]</t>
+    <t>01a0d142-363c-78b2-9067-0b25a873d988</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "The Berlin Wall fell in **1989**, opening on **9 November 1989**. Source: https://www.stiftung-berliner-mauer.de/de/ueber-uns/leichte-sprache/geschichte", "phase": "final_answer", "index": 0, "id": "msg_096f18f5a5025ecd006ab48bd5496487d2bdf0847a52a902e6"}]</t>
   </si>
   <si>
     <t>R12</t>
   </si>
   <si>
-    <t>01a0cce0-a39b-7d32-b3a2-77bbfe691ac6</t>
-  </si>
-  <si>
-    <t>The Berlin Wall fell in **1989**, on **9 November**. [Source](https://www.stiftung-berliner-mauer.de/de/ueber-uns/leichte-sprache/geschichte)</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "The Berlin Wall fell in **1989**, on **November 9**.", "phase": "final_answer", "index": 0, "id": "msg_01bfb711a688d9f4006ab36cb6a54887d29d14193c12d4c596"}]</t>
+    <t>01a0d142-3b3a-7811-b96f-042b181f9566</t>
+  </si>
+  <si>
+    <t>The Berlin Wall fell in **1989**, opening on **9 November 1989**. Source: https://www.stiftung-berliner-mauer.de/de/ueber-uns/leichte-sprache/geschichte</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "The Berlin Wall fell in **1989**, on **November 9**.", "phase": "final_answer", "index": 0, "id": "msg_0fab2a2f54a70e43006ab48bd65fb887d29e213bf750b95115"}]</t>
   </si>
   <si>
     <t>dispatcher_agent</t>
@@ -591,7 +592,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0cce0-6739-77d0-8d8f-4f8e2b6b7f10</t>
+    <t>01a0d142-02b0-7d90-91fe-d26dd122ec25</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -612,7 +613,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0cce0-6dfb-7562-82c4-b07fd21efb11</t>
+    <t>01a0d142-090f-7921-96c2-48d48319afdd</t>
   </si>
   <si>
     <t xml:space="preserve">        task</t>
@@ -633,13 +634,13 @@
     <t>Execute the movie_expert workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cce0-6dfc-7842-8cb4-71621a174e6a</t>
+    <t>01a0d142-0910-76e0-9845-88307bc72b77</t>
   </si>
   <si>
     <t xml:space="preserve">                model</t>
   </si>
   <si>
-    <t>01a0cce0-6dfd-7931-a66d-651cb3e0966a</t>
+    <t>01a0d142-0911-7330-8c24-788afafb274a</t>
   </si>
   <si>
     <t xml:space="preserve">                    ChatOpenAI</t>
@@ -648,7 +649,7 @@
     <t xml:space="preserve">                tools</t>
   </si>
   <si>
-    <t>01a0cce0-72b3-7931-98fd-4ba3e0494b8c</t>
+    <t>01a0d142-0ec4-7860-8860-bac88f4e5142</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -660,19 +661,19 @@
     <t>Look up local movie evidence by phrase; return sources or an explicit miss.</t>
   </si>
   <si>
-    <t>01a0cce0-72b6-72b2-9083-5482a706f4e8</t>
-  </si>
-  <si>
-    <t>01a0cce0-76d2-71c0-997c-1ec4992f25c7</t>
-  </si>
-  <si>
-    <t>01a0cce0-7a23-7e50-bcc8-7c2011948a2c</t>
-  </si>
-  <si>
-    <t>01a0cce0-7a24-7381-be04-7ec2c9ebef39</t>
-  </si>
-  <si>
-    <t>01a0cce0-8083-70a2-8711-34fb64463027</t>
+    <t>01a0d142-0eca-75c0-a7de-f444541ea2f0</t>
+  </si>
+  <si>
+    <t>01a0d142-151b-7621-9aa8-b35f3b9c35dd</t>
+  </si>
+  <si>
+    <t>01a0d142-19b0-7fe3-b8f4-967da67c1906</t>
+  </si>
+  <si>
+    <t>01a0d142-19b1-74d3-a73a-2febdea8ec44</t>
+  </si>
+  <si>
+    <t>01a0d142-1eb3-74e2-be5f-312dde8a1b26</t>
   </si>
   <si>
     <t xml:space="preserve">            sports_expert</t>
@@ -681,13 +682,13 @@
     <t>Execute the sports_expert workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cce0-8084-73f0-b870-b04ca38304cb</t>
-  </si>
-  <si>
-    <t>01a0cce0-8084-73f0-b870-b053bae845f6</t>
-  </si>
-  <si>
-    <t>01a0cce0-86e7-76a0-b17a-ca6bcaafdbe2</t>
+    <t>01a0d142-1eb5-7591-85e4-ad1a06c05b6d</t>
+  </si>
+  <si>
+    <t>01a0d142-1eb7-76b0-9cd9-5bd041e9335a</t>
+  </si>
+  <si>
+    <t>01a0d142-233c-7841-a26a-6e40eb300a49</t>
   </si>
   <si>
     <t xml:space="preserve">                    search_sports_reference</t>
@@ -696,19 +697,19 @@
     <t>Look up local sports evidence by phrase; return sources or an explicit miss.</t>
   </si>
   <si>
-    <t>01a0cce0-86ea-7592-b133-6c1720ff69da</t>
-  </si>
-  <si>
-    <t>01a0cce0-8c37-7ac2-ab19-eed5a841abd9</t>
-  </si>
-  <si>
-    <t>01a0cce0-9060-7c82-8556-4973efb47cb5</t>
-  </si>
-  <si>
-    <t>01a0cce0-9061-7172-8e3c-18ba4ec467d2</t>
-  </si>
-  <si>
-    <t>01a0cce0-9883-7b02-9233-be303c155e86</t>
+    <t>01a0d142-2341-7bd2-9bd6-f88087b265db</t>
+  </si>
+  <si>
+    <t>01a0d142-2815-7653-ac6d-03d2d5b68a8c</t>
+  </si>
+  <si>
+    <t>01a0d142-2be6-72a2-a556-71d7de0cf5f8</t>
+  </si>
+  <si>
+    <t>01a0d142-2be9-74d2-a979-a9f9945e835c</t>
+  </si>
+  <si>
+    <t>01a0d142-303d-7191-978d-bd469225d8a0</t>
   </si>
   <si>
     <t xml:space="preserve">            history_expert</t>
@@ -717,13 +718,13 @@
     <t>Execute the history_expert workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cce0-9884-7282-9bd6-f290ab7207c2</t>
-  </si>
-  <si>
-    <t>01a0cce0-9885-7232-9d07-db0853895c8e</t>
-  </si>
-  <si>
-    <t>01a0cce0-9db7-7b81-a0c3-d6963e2eb0b3</t>
+    <t>01a0d142-3040-7f73-b8af-567a478a783b</t>
+  </si>
+  <si>
+    <t>01a0d142-3041-77e2-ae41-f8cc538e3bba</t>
+  </si>
+  <si>
+    <t>01a0d142-3636-7fe3-95b8-7fe311d9865d</t>
   </si>
   <si>
     <t xml:space="preserve">                    search_history_reference</t>
@@ -732,10 +733,10 @@
     <t>Look up local history evidence by phrase; return sources or an explicit miss.</t>
   </si>
   <si>
-    <t>01a0cce0-9dba-7b73-a33b-1ab1a49b11bc</t>
-  </si>
-  <si>
-    <t>01a0cce0-a39a-73b3-b565-26fe9f145163</t>
+    <t>01a0d142-363b-7142-9df8-f9ed1e347c19</t>
+  </si>
+  <si>
+    <t>01a0d142-3b38-78a2-a3dd-54d95d88d306</t>
   </si>
 </sst>
 </file>
@@ -1142,7 +1143,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M170"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1202,20 +1203,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59,'Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115,'Turns'!E128,'Turns'!E143,'Turns'!E158,'Turns'!E170)=12,SUM('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59,'Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115,'Turns'!E128,'Turns'!E143,'Turns'!E158,'Turns'!E170),"Unknown")</f>
-        <v>0.001329317406</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59,'Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115,'Turns'!E128,'Turns'!E144,'Turns'!E159,'Turns'!E171)=12,SUM('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59,'Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115,'Turns'!E128,'Turns'!E144,'Turns'!E159,'Turns'!E171),"Unknown")</f>
+        <v>0.00129734854</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59,'Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115,'Turns'!F128,'Turns'!F143,'Turns'!F158,'Turns'!F170)=12,SUM('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59,'Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115,'Turns'!F128,'Turns'!F143,'Turns'!F158,'Turns'!F170),"Unknown")</f>
-        <v>0.0015238</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59,'Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115,'Turns'!F128,'Turns'!F144,'Turns'!F159,'Turns'!F171)=12,SUM('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59,'Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115,'Turns'!F128,'Turns'!F144,'Turns'!F159,'Turns'!F171),"Unknown")</f>
+        <v>0.0014804</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>133.0</v>
+        <v>130.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>152.0</v>
+        <v>148.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1227,11 +1228,11 @@
       </c>
       <c r="E3" s="2">
         <f>IF(COUNT('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59)=4,SUM('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59),"Unknown")</f>
-        <v>0.000367442244</v>
+        <v>0.000368067</v>
       </c>
       <c r="F3" s="2">
         <f>IF(COUNT('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59)=4,SUM('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59),"Unknown")</f>
-        <v>0.0004212</v>
+        <v>0.00042</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1277,7 +1278,7 @@
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.5712188e-05</v>
+        <v>4.592074e-05</v>
       </c>
       <c r="F5" s="2">
         <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1364,7 +1365,7 @@
         <v>105</v>
       </c>
       <c r="D11" s="4">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
@@ -1378,15 +1379,15 @@
         <v>106</v>
       </c>
       <c r="D12" s="5">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E12" s="2">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.281064e-05</v>
+        <v>5.994234e-05</v>
       </c>
       <c r="F12" s="2">
         <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!E17),D12*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>7.2e-05</v>
+        <v>6.84e-05</v>
       </c>
       <c r="G12" s="5">
         <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1445,11 +1446,11 @@
       </c>
       <c r="E16" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E12)=2,SUM('Turns'!E5,'Turns'!E12),"Unknown")</f>
-        <v>0.000108522828</v>
+        <v>0.00010586308</v>
       </c>
       <c r="F16" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F12)=2,SUM('Turns'!F5,'Turns'!F12),"Unknown")</f>
-        <v>0.0001244</v>
+        <v>0.0001208</v>
       </c>
       <c r="G16" s="5">
         <f>IF(ISNUMBER(E16),ROUND(E16*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1510,7 +1511,7 @@
         <v>94</v>
       </c>
       <c r="D20" s="4">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>95</v>
@@ -1530,15 +1531,15 @@
         <v>97</v>
       </c>
       <c r="D21" s="5">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E21" s="2">
         <f>IF(AND(ISNUMBER(F21),ISNUMBER('Reference data'!$B$3)),F21*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.4371378e-05</v>
+        <v>3.400238e-05</v>
       </c>
       <c r="F21" s="2">
         <f>IF(D21=0,0,IF(ISNUMBER('Reference data'!B17),D21*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>3.94e-05</v>
+        <v>3.88e-05</v>
       </c>
       <c r="G21" s="5">
         <f>IF(ISNUMBER(E21),ROUND(E21*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1621,15 +1622,15 @@
         <v>120</v>
       </c>
       <c r="D27" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2">
         <f>IF(AND(ISNUMBER(F27),ISNUMBER('Reference data'!$B$3)),F27*'Reference data'!$B$3,"Unknown")</f>
-        <v>9.421596e-06</v>
+        <v>8.41296e-06</v>
       </c>
       <c r="F27" s="2">
         <f>IF(D27=0,0,IF(ISNUMBER('Reference data'!F17),D27*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>1.08e-05</v>
+        <v>9.6e-06</v>
       </c>
       <c r="G27" s="5">
         <f>IF(ISNUMBER(E27),ROUND(E27*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1651,15 +1652,15 @@
         <v>106</v>
       </c>
       <c r="D28" s="5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E28" s="2">
         <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.5592696e-05</v>
+        <v>3.68067e-05</v>
       </c>
       <c r="F28" s="2">
         <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!E17),D28*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>4.08e-05</v>
+        <v>4.2e-05</v>
       </c>
       <c r="G28" s="5">
         <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1718,11 +1719,11 @@
       </c>
       <c r="E32" s="2">
         <f>IF(COUNT('Turns'!E21,'Turns'!E27,'Turns'!E28)=3,SUM('Turns'!E21,'Turns'!E27,'Turns'!E28),"Unknown")</f>
-        <v>7.938567e-05</v>
+        <v>7.922204e-05</v>
       </c>
       <c r="F32" s="2">
         <f>IF(COUNT('Turns'!F21,'Turns'!F27,'Turns'!F28)=3,SUM('Turns'!F21,'Turns'!F27,'Turns'!F28),"Unknown")</f>
-        <v>9.1e-05</v>
+        <v>9.04e-05</v>
       </c>
       <c r="G32" s="5">
         <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1750,7 +1751,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="24" customHeight="1">
+    <row r="34" spans="1:13" ht="34" customHeight="1">
       <c r="B34">
         <v>1</v>
       </c>
@@ -1783,7 +1784,7 @@
         <v>94</v>
       </c>
       <c r="D36" s="4">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>95</v>
@@ -1833,15 +1834,15 @@
         <v>97</v>
       </c>
       <c r="D38" s="5">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E38" s="2">
         <f>IF(AND(ISNUMBER(F38),ISNUMBER('Reference data'!$B$3)),F38*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.0248512e-05</v>
+        <v>4.995195e-05</v>
       </c>
       <c r="F38" s="2">
         <f>IF(D38=0,0,IF(ISNUMBER('Reference data'!B17),D38*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>5.76e-05</v>
+        <v>5.7e-05</v>
       </c>
       <c r="G38" s="5">
         <f>IF(ISNUMBER(E38),ROUND(E38*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1899,7 +1900,7 @@
         <v>105</v>
       </c>
       <c r="D42" s="4">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="24" customHeight="1">
@@ -1913,26 +1914,26 @@
         <v>106</v>
       </c>
       <c r="D43" s="5">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E43" s="2">
         <f>IF(AND(ISNUMBER(F43),ISNUMBER('Reference data'!$B$3)),F43*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.2920604e-05</v>
+        <v>4.627128e-05</v>
       </c>
       <c r="F43" s="2">
         <f>IF(D43=0,0,IF(ISNUMBER('Reference data'!E17),D43*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>4.92e-05</v>
+        <v>5.28e-05</v>
       </c>
       <c r="G43" s="5">
         <f>IF(ISNUMBER(E43),ROUND(E43*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="H43" s="5">
         <f>IF(ISNUMBER(F43),ROUND(F43*'Reference data'!$B$2,0),"Unknown")</f>
         <v>5.0</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="47" customHeight="1">
+    <row r="44" spans="1:13" ht="60" customHeight="1">
       <c r="A44" t="s">
         <v>126</v>
       </c>
@@ -1980,15 +1981,15 @@
       </c>
       <c r="E47" s="2">
         <f>IF(COUNT('Turns'!E37,'Turns'!E38,'Turns'!E43)=3,SUM('Turns'!E37,'Turns'!E38,'Turns'!E43),"Unknown")</f>
-        <v>9.3169116e-05</v>
+        <v>9.622323e-05</v>
       </c>
       <c r="F47" s="2">
         <f>IF(COUNT('Turns'!F37,'Turns'!F38,'Turns'!F43)=3,SUM('Turns'!F37,'Turns'!F38,'Turns'!F43),"Unknown")</f>
-        <v>0.0001068</v>
+        <v>0.0001098</v>
       </c>
       <c r="G47" s="5">
         <f>IF(ISNUMBER(E47),ROUND(E47*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="H47" s="5">
         <f>IF(ISNUMBER(F47),ROUND(F47*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2063,7 +2064,7 @@
       </c>
       <c r="E50" s="2">
         <f>IF(AND(ISNUMBER(F50),ISNUMBER('Reference data'!$B$3)),F50*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.4380906e-05</v>
+        <v>6.467463e-05</v>
       </c>
       <c r="F50" s="2">
         <f>IF(D50=0,0,IF(ISNUMBER('Reference data'!B17),D50*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -2143,7 +2144,7 @@
       </c>
       <c r="E55" s="2">
         <f>IF(AND(ISNUMBER(F55),ISNUMBER('Reference data'!$B$3)),F55*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.1983724e-05</v>
+        <v>2.208402e-05</v>
       </c>
       <c r="F55" s="2">
         <f>IF(D55=0,0,IF(ISNUMBER('Reference data'!E17),D55*'Reference data'!E17/1000000,"Unknown"))</f>
@@ -2206,7 +2207,7 @@
       </c>
       <c r="E59" s="2">
         <f>IF(COUNT('Turns'!E49,'Turns'!E50,'Turns'!E55)=3,SUM('Turns'!E49,'Turns'!E50,'Turns'!E55),"Unknown")</f>
-        <v>8.636463e-05</v>
+        <v>8.675865e-05</v>
       </c>
       <c r="F59" s="2">
         <f>IF(COUNT('Turns'!F49,'Turns'!F50,'Turns'!F55)=3,SUM('Turns'!F49,'Turns'!F50,'Turns'!F55),"Unknown")</f>
@@ -2233,19 +2234,19 @@
       </c>
       <c r="E60" s="2">
         <f>IF(COUNT('Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115)=4,SUM('Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115),"Unknown")</f>
-        <v>0.000493063524</v>
+        <v>0.00045079444</v>
       </c>
       <c r="F60" s="2">
         <f>IF(COUNT('Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115)=4,SUM('Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115),"Unknown")</f>
-        <v>0.0005652</v>
+        <v>0.0005144</v>
       </c>
       <c r="G60" s="5">
         <f>IF(ISNUMBER(E60),ROUND(E60*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>49.0</v>
+        <v>45.0</v>
       </c>
       <c r="H60" s="5">
         <f>IF(ISNUMBER(F60),ROUND(F60*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>57.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="61" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -2313,7 +2314,7 @@
       </c>
       <c r="E63" s="2">
         <f>IF(AND(ISNUMBER(F63),ISNUMBER('Reference data'!$B$3)),F63*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.1010918e-05</v>
+        <v>7.133489e-05</v>
       </c>
       <c r="F63" s="2">
         <f>IF(D63=0,0,IF(ISNUMBER('Reference data'!B17),D63*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -2375,7 +2376,7 @@
         <v>105</v>
       </c>
       <c r="D67" s="4">
-        <v>78</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="24" customHeight="1">
@@ -2389,26 +2390,26 @@
         <v>106</v>
       </c>
       <c r="D68" s="5">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E68" s="2">
         <f>IF(AND(ISNUMBER(F68),ISNUMBER('Reference data'!$B$3)),F68*'Reference data'!$B$3,"Unknown")</f>
-        <v>8.1653832e-05</v>
+        <v>6.30972e-05</v>
       </c>
       <c r="F68" s="2">
         <f>IF(D68=0,0,IF(ISNUMBER('Reference data'!E17),D68*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>9.36e-05</v>
+        <v>7.2e-05</v>
       </c>
       <c r="G68" s="5">
         <f>IF(ISNUMBER(E68),ROUND(E68*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H68" s="5">
         <f>IF(ISNUMBER(F68),ROUND(F68*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="151" customHeight="1">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="125" customHeight="1">
       <c r="A69" t="s">
         <v>136</v>
       </c>
@@ -2456,19 +2457,19 @@
       </c>
       <c r="E72" s="2">
         <f>IF(COUNT('Turns'!E62,'Turns'!E63,'Turns'!E68)=3,SUM('Turns'!E62,'Turns'!E63,'Turns'!E68),"Unknown")</f>
-        <v>0.00015266475</v>
+        <v>0.00013443209</v>
       </c>
       <c r="F72" s="2">
         <f>IF(COUNT('Turns'!F62,'Turns'!F63,'Turns'!F68)=3,SUM('Turns'!F62,'Turns'!F63,'Turns'!F68),"Unknown")</f>
-        <v>0.000175</v>
+        <v>0.0001534</v>
       </c>
       <c r="G72" s="5">
         <f>IF(ISNUMBER(E72),ROUND(E72*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="H72" s="5">
         <f>IF(ISNUMBER(F72),ROUND(F72*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="K72" s="4" t="s">
         <v>110</v>
@@ -2488,7 +2489,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="60" customHeight="1">
+    <row r="74" spans="1:13" ht="47" customHeight="1">
       <c r="B74">
         <v>2</v>
       </c>
@@ -2521,7 +2522,7 @@
         <v>94</v>
       </c>
       <c r="D76" s="4">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>95</v>
@@ -2541,19 +2542,19 @@
         <v>97</v>
       </c>
       <c r="D77" s="5">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="E77" s="2">
         <f>IF(AND(ISNUMBER(F77),ISNUMBER('Reference data'!$B$3)),F77*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.6988488e-05</v>
+        <v>3.400238e-05</v>
       </c>
       <c r="F77" s="2">
         <f>IF(D77=0,0,IF(ISNUMBER('Reference data'!B17),D77*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>4.24e-05</v>
+        <v>3.88e-05</v>
       </c>
       <c r="G77" s="5">
         <f>IF(ISNUMBER(E77),ROUND(E77*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H77" s="5">
         <f>IF(ISNUMBER(F77),ROUND(F77*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2618,7 +2619,7 @@
         <v>105</v>
       </c>
       <c r="D82" s="4">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="24" customHeight="1">
@@ -2636,7 +2637,7 @@
       </c>
       <c r="E83" s="2">
         <f>IF(AND(ISNUMBER(F83),ISNUMBER('Reference data'!$B$3)),F83*'Reference data'!$B$3,"Unknown")</f>
-        <v>9.421596e-06</v>
+        <v>9.46458e-06</v>
       </c>
       <c r="F83" s="2">
         <f>IF(D83=0,0,IF(ISNUMBER('Reference data'!F17),D83*'Reference data'!F17/1000000,"Unknown"))</f>
@@ -2662,23 +2663,23 @@
         <v>106</v>
       </c>
       <c r="D84" s="5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E84" s="2">
         <f>IF(AND(ISNUMBER(F84),ISNUMBER('Reference data'!$B$3)),F84*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-05</v>
+        <v>4.20648e-05</v>
       </c>
       <c r="F84" s="2">
         <f>IF(D84=0,0,IF(ISNUMBER('Reference data'!E17),D84*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>6e-05</v>
+        <v>4.8e-05</v>
       </c>
       <c r="G84" s="5">
         <f>IF(ISNUMBER(E84),ROUND(E84*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="H84" s="5">
         <f>IF(ISNUMBER(F84),ROUND(F84*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="307" customHeight="1">
@@ -2729,19 +2730,19 @@
       </c>
       <c r="E88" s="2">
         <f>IF(COUNT('Turns'!E77,'Turns'!E83,'Turns'!E84)=3,SUM('Turns'!E77,'Turns'!E83,'Turns'!E84),"Unknown")</f>
-        <v>9.8752284e-05</v>
+        <v>8.553176e-05</v>
       </c>
       <c r="F88" s="2">
         <f>IF(COUNT('Turns'!F77,'Turns'!F83,'Turns'!F84)=3,SUM('Turns'!F77,'Turns'!F83,'Turns'!F84),"Unknown")</f>
-        <v>0.0001132</v>
+        <v>9.76e-05</v>
       </c>
       <c r="G88" s="5">
         <f>IF(ISNUMBER(E88),ROUND(E88*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="H88" s="5">
         <f>IF(ISNUMBER(F88),ROUND(F88*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>110</v>
@@ -2794,7 +2795,7 @@
         <v>94</v>
       </c>
       <c r="D92" s="4">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c r="J92" s="4" t="s">
         <v>95</v>
@@ -2844,23 +2845,23 @@
         <v>97</v>
       </c>
       <c r="D94" s="5">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c r="E94" s="2">
         <f>IF(AND(ISNUMBER(F94),ISNUMBER('Reference data'!$B$3)),F94*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.7227472e-05</v>
+        <v>5.2581e-05</v>
       </c>
       <c r="F94" s="2">
         <f>IF(D94=0,0,IF(ISNUMBER('Reference data'!B17),D94*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6.56e-05</v>
+        <v>6e-05</v>
       </c>
       <c r="G94" s="5">
         <f>IF(ISNUMBER(E94),ROUND(E94*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="H94" s="5">
         <f>IF(ISNUMBER(F94),ROUND(F94*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="60" customHeight="1">
@@ -2910,7 +2911,7 @@
         <v>105</v>
       </c>
       <c r="D98" s="4">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="24" customHeight="1">
@@ -2924,15 +2925,15 @@
         <v>106</v>
       </c>
       <c r="D99" s="5">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E99" s="2">
         <f>IF(AND(ISNUMBER(F99),ISNUMBER('Reference data'!$B$3)),F99*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.4904328e-05</v>
+        <v>6.099396e-05</v>
       </c>
       <c r="F99" s="2">
         <f>IF(D99=0,0,IF(ISNUMBER('Reference data'!E17),D99*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>7.44e-05</v>
+        <v>6.96e-05</v>
       </c>
       <c r="G99" s="5">
         <f>IF(ISNUMBER(E99),ROUND(E99*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2943,7 +2944,7 @@
         <v>7.0</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="73" customHeight="1">
+    <row r="100" spans="1:13" ht="60" customHeight="1">
       <c r="A100" t="s">
         <v>151</v>
       </c>
@@ -2991,19 +2992,19 @@
       </c>
       <c r="E103" s="2">
         <f>IF(COUNT('Turns'!E93,'Turns'!E94,'Turns'!E99)=3,SUM('Turns'!E93,'Turns'!E94,'Turns'!E99),"Unknown")</f>
-        <v>0.0001221318</v>
+        <v>0.00011357496</v>
       </c>
       <c r="F103" s="2">
         <f>IF(COUNT('Turns'!F93,'Turns'!F94,'Turns'!F99)=3,SUM('Turns'!F93,'Turns'!F94,'Turns'!F99),"Unknown")</f>
-        <v>0.00014</v>
+        <v>0.0001296</v>
       </c>
       <c r="G103" s="5">
         <f>IF(ISNUMBER(E103),ROUND(E103*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="H103" s="5">
         <f>IF(ISNUMBER(F103),ROUND(F103*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="K103" s="4" t="s">
         <v>110</v>
@@ -3020,7 +3021,7 @@
         <v>94</v>
       </c>
       <c r="D104" s="4">
-        <v>553</v>
+        <v>531</v>
       </c>
       <c r="J104" s="4" t="s">
         <v>95</v>
@@ -3070,19 +3071,19 @@
         <v>97</v>
       </c>
       <c r="D106" s="5">
-        <v>553</v>
+        <v>531</v>
       </c>
       <c r="E106" s="2">
         <f>IF(AND(ISNUMBER(F106),ISNUMBER('Reference data'!$B$3)),F106*'Reference data'!$B$3,"Unknown")</f>
-        <v>9.6484122e-05</v>
+        <v>9.306837e-05</v>
       </c>
       <c r="F106" s="2">
         <f>IF(D106=0,0,IF(ISNUMBER('Reference data'!B17),D106*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.0001106</v>
+        <v>0.0001062</v>
       </c>
       <c r="G106" s="5">
         <f>IF(ISNUMBER(E106),ROUND(E106*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="H106" s="5">
         <f>IF(ISNUMBER(F106),ROUND(F106*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3136,7 +3137,7 @@
         <v>105</v>
       </c>
       <c r="D110" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="24" customHeight="1">
@@ -3150,15 +3151,15 @@
         <v>106</v>
       </c>
       <c r="D111" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E111" s="2">
         <f>IF(AND(ISNUMBER(F111),ISNUMBER('Reference data'!$B$3)),F111*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.3030568e-05</v>
+        <v>2.418726e-05</v>
       </c>
       <c r="F111" s="2">
         <f>IF(D111=0,0,IF(ISNUMBER('Reference data'!E17),D111*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.64e-05</v>
+        <v>2.76e-05</v>
       </c>
       <c r="G111" s="5">
         <f>IF(ISNUMBER(E111),ROUND(E111*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3217,11 +3218,11 @@
       </c>
       <c r="E115" s="2">
         <f>IF(COUNT('Turns'!E105,'Turns'!E106,'Turns'!E111)=3,SUM('Turns'!E105,'Turns'!E106,'Turns'!E111),"Unknown")</f>
-        <v>0.00011951469</v>
+        <v>0.00011725563</v>
       </c>
       <c r="F115" s="2">
         <f>IF(COUNT('Turns'!F105,'Turns'!F106,'Turns'!F111)=3,SUM('Turns'!F105,'Turns'!F106,'Turns'!F111),"Unknown")</f>
-        <v>0.000137</v>
+        <v>0.0001338</v>
       </c>
       <c r="G115" s="5">
         <f>IF(ISNUMBER(E115),ROUND(E115*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3229,7 +3230,7 @@
       </c>
       <c r="H115" s="5">
         <f>IF(ISNUMBER(F115),ROUND(F115*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="K115" s="4" t="s">
         <v>110</v>
@@ -3243,20 +3244,20 @@
         <v>158</v>
       </c>
       <c r="E116" s="2">
-        <f>IF(COUNT('Turns'!E128,'Turns'!E143,'Turns'!E158,'Turns'!E170)=4,SUM('Turns'!E128,'Turns'!E143,'Turns'!E158,'Turns'!E170),"Unknown")</f>
-        <v>0.000468811638</v>
+        <f>IF(COUNT('Turns'!E128,'Turns'!E144,'Turns'!E159,'Turns'!E171)=4,SUM('Turns'!E128,'Turns'!E144,'Turns'!E159,'Turns'!E171),"Unknown")</f>
+        <v>0.0004784871</v>
       </c>
       <c r="F116" s="2">
-        <f>IF(COUNT('Turns'!F128,'Turns'!F143,'Turns'!F158,'Turns'!F170)=4,SUM('Turns'!F128,'Turns'!F143,'Turns'!F158,'Turns'!F170),"Unknown")</f>
-        <v>0.0005374</v>
+        <f>IF(COUNT('Turns'!F128,'Turns'!F144,'Turns'!F159,'Turns'!F171)=4,SUM('Turns'!F128,'Turns'!F144,'Turns'!F159,'Turns'!F171),"Unknown")</f>
+        <v>0.000546</v>
       </c>
       <c r="G116" s="5">
         <f>IF(ISNUMBER(E116),ROUND(E116*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="H116" s="5">
         <f>IF(ISNUMBER(F116),ROUND(F116*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="117" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -3270,7 +3271,7 @@
         <v>94</v>
       </c>
       <c r="D117" s="4">
-        <v>590</v>
+        <v>569</v>
       </c>
       <c r="J117" s="4" t="s">
         <v>95</v>
@@ -3320,15 +3321,15 @@
         <v>97</v>
       </c>
       <c r="D119" s="5">
-        <v>590</v>
+        <v>569</v>
       </c>
       <c r="E119" s="2">
         <f>IF(AND(ISNUMBER(F119),ISNUMBER('Reference data'!$B$3)),F119*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00010293966</v>
+        <v>9.972863e-05</v>
       </c>
       <c r="F119" s="2">
         <f>IF(D119=0,0,IF(ISNUMBER('Reference data'!B17),D119*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.000118</v>
+        <v>0.0001138</v>
       </c>
       <c r="G119" s="5">
         <f>IF(ISNUMBER(E119),ROUND(E119*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3336,7 +3337,7 @@
       </c>
       <c r="H119" s="5">
         <f>IF(ISNUMBER(F119),ROUND(F119*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="24" customHeight="1">
@@ -3386,7 +3387,7 @@
         <v>105</v>
       </c>
       <c r="D123" s="4">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="24" customHeight="1">
@@ -3400,15 +3401,15 @@
         <v>106</v>
       </c>
       <c r="D124" s="5">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E124" s="2">
         <f>IF(AND(ISNUMBER(F124),ISNUMBER('Reference data'!$B$3)),F124*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.9670108e-05</v>
+        <v>5.678748e-05</v>
       </c>
       <c r="F124" s="2">
         <f>IF(D124=0,0,IF(ISNUMBER('Reference data'!E17),D124*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>6.84e-05</v>
+        <v>6.48e-05</v>
       </c>
       <c r="G124" s="5">
         <f>IF(ISNUMBER(E124),ROUND(E124*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3416,7 +3417,7 @@
       </c>
       <c r="H124" s="5">
         <f>IF(ISNUMBER(F124),ROUND(F124*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="125" spans="1:13" ht="125" customHeight="1">
@@ -3467,11 +3468,11 @@
       </c>
       <c r="E128" s="2">
         <f>IF(COUNT('Turns'!E118,'Turns'!E119,'Turns'!E124)=3,SUM('Turns'!E118,'Turns'!E119,'Turns'!E124),"Unknown")</f>
-        <v>0.000162609768</v>
+        <v>0.00015651611</v>
       </c>
       <c r="F128" s="2">
         <f>IF(COUNT('Turns'!F118,'Turns'!F119,'Turns'!F124)=3,SUM('Turns'!F118,'Turns'!F119,'Turns'!F124),"Unknown")</f>
-        <v>0.0001864</v>
+        <v>0.0001786</v>
       </c>
       <c r="G128" s="5">
         <f>IF(ISNUMBER(E128),ROUND(E128*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3479,7 +3480,7 @@
       </c>
       <c r="H128" s="5">
         <f>IF(ISNUMBER(F128),ROUND(F128*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="K128" s="4" t="s">
         <v>110</v>
@@ -3532,7 +3533,7 @@
         <v>94</v>
       </c>
       <c r="D132" s="4">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J132" s="4" t="s">
         <v>95</v>
@@ -3552,15 +3553,15 @@
         <v>97</v>
       </c>
       <c r="D133" s="5">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E133" s="2">
         <f>IF(AND(ISNUMBER(F133),ISNUMBER('Reference data'!$B$3)),F133*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.2975586e-05</v>
+        <v>3.260022e-05</v>
       </c>
       <c r="F133" s="2">
         <f>IF(D133=0,0,IF(ISNUMBER('Reference data'!B17),D133*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>3.78e-05</v>
+        <v>3.72e-05</v>
       </c>
       <c r="G133" s="5">
         <f>IF(ISNUMBER(E133),ROUND(E133*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3629,7 +3630,7 @@
         <v>105</v>
       </c>
       <c r="D138" s="4">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="24" customHeight="1">
@@ -3640,29 +3641,29 @@
         <v>3</v>
       </c>
       <c r="C139" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="D139" s="5">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E139" s="2">
         <f>IF(AND(ISNUMBER(F139),ISNUMBER('Reference data'!$B$3)),F139*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.2452164e-05</v>
+        <v>9.46458e-06</v>
       </c>
       <c r="F139" s="2">
-        <f>IF(D139=0,0,IF(ISNUMBER('Reference data'!E17),D139*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>3.72e-05</v>
+        <f>IF(D139=0,0,IF(ISNUMBER('Reference data'!F17),D139*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>1.08e-05</v>
       </c>
       <c r="G139" s="5">
         <f>IF(ISNUMBER(E139),ROUND(E139*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H139" s="5">
         <f>IF(ISNUMBER(F139),ROUND(F139*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:13" ht="86" customHeight="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" ht="24" customHeight="1">
       <c r="A140" t="s">
         <v>166</v>
       </c>
@@ -3670,13 +3671,29 @@
         <v>3</v>
       </c>
       <c r="C140" t="s">
-        <v>107</v>
-      </c>
-      <c r="I140" s="6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="141" spans="1:13" ht="24" customHeight="1">
+        <v>106</v>
+      </c>
+      <c r="D140" s="5">
+        <v>36</v>
+      </c>
+      <c r="E140" s="2">
+        <f>IF(AND(ISNUMBER(F140),ISNUMBER('Reference data'!$B$3)),F140*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.785832e-05</v>
+      </c>
+      <c r="F140" s="2">
+        <f>IF(D140=0,0,IF(ISNUMBER('Reference data'!E17),D140*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>4.32e-05</v>
+      </c>
+      <c r="G140" s="5">
+        <f>IF(ISNUMBER(E140),ROUND(E140*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H140" s="5">
+        <f>IF(ISNUMBER(F140),ROUND(F140*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" ht="307" customHeight="1">
       <c r="A141" t="s">
         <v>166</v>
       </c>
@@ -3684,7 +3701,10 @@
         <v>3</v>
       </c>
       <c r="C141" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="I141" s="6" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="24" customHeight="1">
@@ -3695,123 +3715,104 @@
         <v>3</v>
       </c>
       <c r="C142" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" ht="24" customHeight="1">
+      <c r="A143" t="s">
+        <v>166</v>
+      </c>
+      <c r="B143">
+        <v>3</v>
+      </c>
+      <c r="C143" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="143" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A143" s="4" t="s">
+    <row r="144" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A144" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="B143" s="4">
-        <v>3</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E143" s="2">
-        <f>IF(COUNT('Turns'!E133,'Turns'!E139)=2,SUM('Turns'!E133,'Turns'!E139),"Unknown")</f>
-        <v>6.542775e-05</v>
-      </c>
-      <c r="F143" s="2">
-        <f>IF(COUNT('Turns'!F133,'Turns'!F139)=2,SUM('Turns'!F133,'Turns'!F139),"Unknown")</f>
-        <v>7.5e-05</v>
-      </c>
-      <c r="G143" s="5">
-        <f>IF(ISNUMBER(E143),ROUND(E143*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="H143" s="5">
-        <f>IF(ISNUMBER(F143),ROUND(F143*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
-      </c>
-      <c r="K143" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="B144" s="4">
         <v>3</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>170</v>
+        <v>109</v>
+      </c>
+      <c r="E144" s="2">
+        <f>IF(COUNT('Turns'!E133,'Turns'!E139,'Turns'!E140)=3,SUM('Turns'!E133,'Turns'!E139,'Turns'!E140),"Unknown")</f>
+        <v>7.992312e-05</v>
+      </c>
+      <c r="F144" s="2">
+        <f>IF(COUNT('Turns'!F133,'Turns'!F139,'Turns'!F140)=3,SUM('Turns'!F133,'Turns'!F139,'Turns'!F140),"Unknown")</f>
+        <v>9.12e-05</v>
+      </c>
+      <c r="G144" s="5">
+        <f>IF(ISNUMBER(E144),ROUND(E144*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="H144" s="5">
+        <f>IF(ISNUMBER(F144),ROUND(F144*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
       </c>
       <c r="K144" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="M144" s="4" t="s">
+    </row>
+    <row r="145" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B145" s="4">
+        <v>3</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K145" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="M145" s="4" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="24" customHeight="1">
-      <c r="B145">
-        <v>3</v>
-      </c>
-      <c r="C145" t="s">
-        <v>113</v>
-      </c>
-      <c r="I145" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="146" spans="1:13" ht="60" customHeight="1">
+    <row r="146" spans="1:13" ht="34" customHeight="1">
       <c r="B146">
         <v>3</v>
       </c>
       <c r="C146" t="s">
+        <v>113</v>
+      </c>
+      <c r="I146" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" ht="60" customHeight="1">
+      <c r="B147">
+        <v>3</v>
+      </c>
+      <c r="C147" t="s">
         <v>115</v>
       </c>
-      <c r="I146" s="6" t="s">
+      <c r="I147" s="6" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="147" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A147" s="4" t="s">
+    <row r="148" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A148" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="B147" s="4">
+      <c r="B148" s="4">
         <v>3</v>
       </c>
-      <c r="C147" s="4" t="s">
+      <c r="C148" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D147" s="4">
-        <v>285</v>
-      </c>
-      <c r="J147" s="4" t="s">
+      <c r="D148" s="4">
+        <v>296</v>
+      </c>
+      <c r="J148" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M147" s="4" t="s">
+      <c r="M148" s="4" t="s">
         <v>175</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13" ht="24" customHeight="1">
-      <c r="A148" t="s">
-        <v>174</v>
-      </c>
-      <c r="B148">
-        <v>3</v>
-      </c>
-      <c r="C148" t="s">
-        <v>128</v>
-      </c>
-      <c r="D148" s="5">
-        <v>0</v>
-      </c>
-      <c r="E148" s="2">
-        <f>IF(AND(ISNUMBER(F148),ISNUMBER('Reference data'!$B$3)),F148*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="F148" s="2">
-        <f>IF(D148=0,0,IF(ISNUMBER('Reference data'!C17),D148*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>0.0</v>
-      </c>
-      <c r="G148" s="5">
-        <f>IF(ISNUMBER(E148),ROUND(E148*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H148" s="5">
-        <f>IF(ISNUMBER(F148),ROUND(F148*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="24" customHeight="1">
@@ -3822,29 +3823,29 @@
         <v>3</v>
       </c>
       <c r="C149" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="D149" s="5">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="E149" s="2">
         <f>IF(AND(ISNUMBER(F149),ISNUMBER('Reference data'!$B$3)),F149*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.972509e-05</v>
+        <v>0.0</v>
       </c>
       <c r="F149" s="2">
-        <f>IF(D149=0,0,IF(ISNUMBER('Reference data'!B17),D149*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>5.7e-05</v>
+        <f>IF(D149=0,0,IF(ISNUMBER('Reference data'!C17),D149*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>0.0</v>
       </c>
       <c r="G149" s="5">
         <f>IF(ISNUMBER(E149),ROUND(E149*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H149" s="5">
         <f>IF(ISNUMBER(F149),ROUND(F149*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13" ht="60" customHeight="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" ht="24" customHeight="1">
       <c r="A150" t="s">
         <v>174</v>
       </c>
@@ -3852,13 +3853,29 @@
         <v>3</v>
       </c>
       <c r="C150" t="s">
-        <v>129</v>
-      </c>
-      <c r="I150" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13" ht="24" customHeight="1">
+        <v>97</v>
+      </c>
+      <c r="D150" s="5">
+        <v>296</v>
+      </c>
+      <c r="E150" s="2">
+        <f>IF(AND(ISNUMBER(F150),ISNUMBER('Reference data'!$B$3)),F150*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.187992e-05</v>
+      </c>
+      <c r="F150" s="2">
+        <f>IF(D150=0,0,IF(ISNUMBER('Reference data'!B17),D150*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>5.92e-05</v>
+      </c>
+      <c r="G150" s="5">
+        <f>IF(ISNUMBER(E150),ROUND(E150*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+      <c r="H150" s="5">
+        <f>IF(ISNUMBER(F150),ROUND(F150*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" ht="60" customHeight="1">
       <c r="A151" t="s">
         <v>174</v>
       </c>
@@ -3866,7 +3883,10 @@
         <v>3</v>
       </c>
       <c r="C151" t="s">
-        <v>103</v>
+        <v>129</v>
+      </c>
+      <c r="I151" s="6" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="24" customHeight="1">
@@ -3877,54 +3897,35 @@
         <v>3</v>
       </c>
       <c r="C152" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" ht="24" customHeight="1">
+      <c r="A153" t="s">
+        <v>174</v>
+      </c>
+      <c r="B153">
+        <v>3</v>
+      </c>
+      <c r="C153" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="153" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A153" s="4" t="s">
+    <row r="154" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A154" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="B153" s="4">
+      <c r="B154" s="4">
         <v>3</v>
       </c>
-      <c r="C153" s="4" t="s">
+      <c r="C154" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D153" s="4">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" ht="24" customHeight="1">
-      <c r="A154" t="s">
-        <v>174</v>
-      </c>
-      <c r="B154">
-        <v>3</v>
-      </c>
-      <c r="C154" t="s">
-        <v>106</v>
-      </c>
-      <c r="D154" s="5">
-        <v>46</v>
-      </c>
-      <c r="E154" s="2">
-        <f>IF(AND(ISNUMBER(F154),ISNUMBER('Reference data'!$B$3)),F154*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.8154824e-05</v>
-      </c>
-      <c r="F154" s="2">
-        <f>IF(D154=0,0,IF(ISNUMBER('Reference data'!E17),D154*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>5.52e-05</v>
-      </c>
-      <c r="G154" s="5">
-        <f>IF(ISNUMBER(E154),ROUND(E154*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-      <c r="H154" s="5">
-        <f>IF(ISNUMBER(F154),ROUND(F154*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13" ht="60" customHeight="1">
+      <c r="D154" s="4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" ht="24" customHeight="1">
       <c r="A155" t="s">
         <v>174</v>
       </c>
@@ -3932,13 +3933,29 @@
         <v>3</v>
       </c>
       <c r="C155" t="s">
-        <v>107</v>
-      </c>
-      <c r="I155" s="6" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13" ht="24" customHeight="1">
+        <v>106</v>
+      </c>
+      <c r="D155" s="5">
+        <v>48</v>
+      </c>
+      <c r="E155" s="2">
+        <f>IF(AND(ISNUMBER(F155),ISNUMBER('Reference data'!$B$3)),F155*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.047776e-05</v>
+      </c>
+      <c r="F155" s="2">
+        <f>IF(D155=0,0,IF(ISNUMBER('Reference data'!E17),D155*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>5.76e-05</v>
+      </c>
+      <c r="G155" s="5">
+        <f>IF(ISNUMBER(E155),ROUND(E155*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+      <c r="H155" s="5">
+        <f>IF(ISNUMBER(F155),ROUND(F155*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" ht="60" customHeight="1">
       <c r="A156" t="s">
         <v>174</v>
       </c>
@@ -3946,7 +3963,10 @@
         <v>3</v>
       </c>
       <c r="C156" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="I156" s="6" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="157" spans="1:13" ht="24" customHeight="1">
@@ -3957,87 +3977,68 @@
         <v>3</v>
       </c>
       <c r="C157" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" ht="24" customHeight="1">
+      <c r="A158" t="s">
+        <v>174</v>
+      </c>
+      <c r="B158">
+        <v>3</v>
+      </c>
+      <c r="C158" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="158" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A158" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B158" s="4">
-        <v>3</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E158" s="2">
-        <f>IF(COUNT('Turns'!E148,'Turns'!E149,'Turns'!E154)=3,SUM('Turns'!E148,'Turns'!E149,'Turns'!E154),"Unknown")</f>
-        <v>9.7879914e-05</v>
-      </c>
-      <c r="F158" s="2">
-        <f>IF(COUNT('Turns'!F148,'Turns'!F149,'Turns'!F154)=3,SUM('Turns'!F148,'Turns'!F149,'Turns'!F154),"Unknown")</f>
-        <v>0.0001122</v>
-      </c>
-      <c r="G158" s="5">
-        <f>IF(ISNUMBER(E158),ROUND(E158*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
-      </c>
-      <c r="H158" s="5">
-        <f>IF(ISNUMBER(F158),ROUND(F158*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
-      </c>
-      <c r="K158" s="4" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="159" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A159" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B159" s="4">
         <v>3</v>
       </c>
       <c r="C159" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E159" s="2">
+        <f>IF(COUNT('Turns'!E149,'Turns'!E150,'Turns'!E155)=3,SUM('Turns'!E149,'Turns'!E150,'Turns'!E155),"Unknown")</f>
+        <v>0.00010235768</v>
+      </c>
+      <c r="F159" s="2">
+        <f>IF(COUNT('Turns'!F149,'Turns'!F150,'Turns'!F155)=3,SUM('Turns'!F149,'Turns'!F150,'Turns'!F155),"Unknown")</f>
+        <v>0.0001168</v>
+      </c>
+      <c r="G159" s="5">
+        <f>IF(ISNUMBER(E159),ROUND(E159*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>10.0</v>
+      </c>
+      <c r="H159" s="5">
+        <f>IF(ISNUMBER(F159),ROUND(F159*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>12.0</v>
+      </c>
+      <c r="K159" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A160" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B160" s="4">
+        <v>3</v>
+      </c>
+      <c r="C160" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D159" s="4">
-        <v>699</v>
-      </c>
-      <c r="J159" s="4" t="s">
+      <c r="D160" s="4">
+        <v>677</v>
+      </c>
+      <c r="J160" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M159" s="4" t="s">
+      <c r="M160" s="4" t="s">
         <v>178</v>
-      </c>
-    </row>
-    <row r="160" spans="1:13" ht="24" customHeight="1">
-      <c r="A160" t="s">
-        <v>177</v>
-      </c>
-      <c r="B160">
-        <v>3</v>
-      </c>
-      <c r="C160" t="s">
-        <v>128</v>
-      </c>
-      <c r="D160" s="5">
-        <v>0</v>
-      </c>
-      <c r="E160" s="2">
-        <f>IF(AND(ISNUMBER(F160),ISNUMBER('Reference data'!$B$3)),F160*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="F160" s="2">
-        <f>IF(D160=0,0,IF(ISNUMBER('Reference data'!C17),D160*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>0.0</v>
-      </c>
-      <c r="G160" s="5">
-        <f>IF(ISNUMBER(E160),ROUND(E160*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H160" s="5">
-        <f>IF(ISNUMBER(F160),ROUND(F160*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
       </c>
     </row>
     <row r="161" spans="1:11" ht="24" customHeight="1">
@@ -4048,29 +4049,29 @@
         <v>3</v>
       </c>
       <c r="C161" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="D161" s="5">
-        <v>699</v>
+        <v>0</v>
       </c>
       <c r="E161" s="2">
         <f>IF(AND(ISNUMBER(F161),ISNUMBER('Reference data'!$B$3)),F161*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000121957326</v>
+        <v>0.0</v>
       </c>
       <c r="F161" s="2">
-        <f>IF(D161=0,0,IF(ISNUMBER('Reference data'!B17),D161*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.0001398</v>
+        <f>IF(D161=0,0,IF(ISNUMBER('Reference data'!C17),D161*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>0.0</v>
       </c>
       <c r="G161" s="5">
         <f>IF(ISNUMBER(E161),ROUND(E161*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="H161" s="5">
         <f>IF(ISNUMBER(F161),ROUND(F161*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:11" ht="34" customHeight="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" ht="24" customHeight="1">
       <c r="A162" t="s">
         <v>177</v>
       </c>
@@ -4078,13 +4079,29 @@
         <v>3</v>
       </c>
       <c r="C162" t="s">
-        <v>129</v>
-      </c>
-      <c r="I162" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11" ht="24" customHeight="1">
+        <v>97</v>
+      </c>
+      <c r="D162" s="5">
+        <v>677</v>
+      </c>
+      <c r="E162" s="2">
+        <f>IF(AND(ISNUMBER(F162),ISNUMBER('Reference data'!$B$3)),F162*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.00011865779</v>
+      </c>
+      <c r="F162" s="2">
+        <f>IF(D162=0,0,IF(ISNUMBER('Reference data'!B17),D162*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>0.0001354</v>
+      </c>
+      <c r="G162" s="5">
+        <f>IF(ISNUMBER(E162),ROUND(E162*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>12.0</v>
+      </c>
+      <c r="H162" s="5">
+        <f>IF(ISNUMBER(F162),ROUND(F162*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" ht="34" customHeight="1">
       <c r="A163" t="s">
         <v>177</v>
       </c>
@@ -4092,7 +4109,10 @@
         <v>3</v>
       </c>
       <c r="C163" t="s">
-        <v>103</v>
+        <v>129</v>
+      </c>
+      <c r="I163" s="6" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="164" spans="1:11" ht="24" customHeight="1">
@@ -4103,54 +4123,35 @@
         <v>3</v>
       </c>
       <c r="C164" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" ht="24" customHeight="1">
+      <c r="A165" t="s">
+        <v>177</v>
+      </c>
+      <c r="B165">
+        <v>3</v>
+      </c>
+      <c r="C165" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="165" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A165" s="4" t="s">
+    <row r="166" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A166" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B165" s="4">
+      <c r="B166" s="4">
         <v>3</v>
       </c>
-      <c r="C165" s="4" t="s">
+      <c r="C166" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D165" s="4">
+      <c r="D166" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="166" spans="1:11" ht="24" customHeight="1">
-      <c r="A166" t="s">
-        <v>177</v>
-      </c>
-      <c r="B166">
-        <v>3</v>
-      </c>
-      <c r="C166" t="s">
-        <v>106</v>
-      </c>
-      <c r="D166" s="5">
-        <v>20</v>
-      </c>
-      <c r="E166" s="2">
-        <f>IF(AND(ISNUMBER(F166),ISNUMBER('Reference data'!$B$3)),F166*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.093688e-05</v>
-      </c>
-      <c r="F166" s="2">
-        <f>IF(D166=0,0,IF(ISNUMBER('Reference data'!E17),D166*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.4e-05</v>
-      </c>
-      <c r="G166" s="5">
-        <f>IF(ISNUMBER(E166),ROUND(E166*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-      <c r="H166" s="5">
-        <f>IF(ISNUMBER(F166),ROUND(F166*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:11" ht="47" customHeight="1">
+    <row r="167" spans="1:11" ht="24" customHeight="1">
       <c r="A167" t="s">
         <v>177</v>
       </c>
@@ -4158,13 +4159,29 @@
         <v>3</v>
       </c>
       <c r="C167" t="s">
-        <v>107</v>
-      </c>
-      <c r="I167" s="6" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="168" spans="1:11" ht="24" customHeight="1">
+        <v>106</v>
+      </c>
+      <c r="D167" s="5">
+        <v>20</v>
+      </c>
+      <c r="E167" s="2">
+        <f>IF(AND(ISNUMBER(F167),ISNUMBER('Reference data'!$B$3)),F167*'Reference data'!$B$3,"Unknown")</f>
+        <v>2.10324e-05</v>
+      </c>
+      <c r="F167" s="2">
+        <f>IF(D167=0,0,IF(ISNUMBER('Reference data'!E17),D167*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>2.4e-05</v>
+      </c>
+      <c r="G167" s="5">
+        <f>IF(ISNUMBER(E167),ROUND(E167*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+      <c r="H167" s="5">
+        <f>IF(ISNUMBER(F167),ROUND(F167*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" ht="47" customHeight="1">
       <c r="A168" t="s">
         <v>177</v>
       </c>
@@ -4172,7 +4189,10 @@
         <v>3</v>
       </c>
       <c r="C168" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="I168" s="6" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="169" spans="1:11" ht="24" customHeight="1">
@@ -4183,41 +4203,52 @@
         <v>3</v>
       </c>
       <c r="C169" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" ht="24" customHeight="1">
+      <c r="A170" t="s">
+        <v>177</v>
+      </c>
+      <c r="B170">
+        <v>3</v>
+      </c>
+      <c r="C170" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="170" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A170" s="4" t="s">
+    <row r="171" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A171" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B170" s="4">
+      <c r="B171" s="4">
         <v>3</v>
       </c>
-      <c r="C170" s="4" t="s">
+      <c r="C171" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E170" s="2">
-        <f>IF(COUNT('Turns'!E160,'Turns'!E161,'Turns'!E166)=3,SUM('Turns'!E160,'Turns'!E161,'Turns'!E166),"Unknown")</f>
-        <v>0.000142894206</v>
-      </c>
-      <c r="F170" s="2">
-        <f>IF(COUNT('Turns'!F160,'Turns'!F161,'Turns'!F166)=3,SUM('Turns'!F160,'Turns'!F161,'Turns'!F166),"Unknown")</f>
-        <v>0.0001638</v>
-      </c>
-      <c r="G170" s="5">
-        <f>IF(ISNUMBER(E170),ROUND(E170*'Reference data'!$B$2,0),"Unknown")</f>
+      <c r="E171" s="2">
+        <f>IF(COUNT('Turns'!E161,'Turns'!E162,'Turns'!E167)=3,SUM('Turns'!E161,'Turns'!E162,'Turns'!E167),"Unknown")</f>
+        <v>0.00013969019</v>
+      </c>
+      <c r="F171" s="2">
+        <f>IF(COUNT('Turns'!F161,'Turns'!F162,'Turns'!F167)=3,SUM('Turns'!F161,'Turns'!F162,'Turns'!F167),"Unknown")</f>
+        <v>0.0001594</v>
+      </c>
+      <c r="G171" s="5">
+        <f>IF(ISNUMBER(E171),ROUND(E171*'Reference data'!$B$2,0),"Unknown")</f>
         <v>14.0</v>
       </c>
-      <c r="H170" s="5">
-        <f>IF(ISNUMBER(F170),ROUND(F170*'Reference data'!$B$2,0),"Unknown")</f>
+      <c r="H171" s="5">
+        <f>IF(ISNUMBER(F171),ROUND(F171*'Reference data'!$B$2,0),"Unknown")</f>
         <v>16.0</v>
       </c>
-      <c r="K170" s="4" t="s">
+      <c r="K171" s="4" t="s">
         <v>110</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE170">
+  <conditionalFormatting sqref="A2:AE171">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -4360,15 +4391,15 @@
       </c>
       <c r="J2" s="2">
         <f>IF(COUNT('Turns'!D5,'Turns'!D21,'Turns'!D38,'Turns'!D50)=4,SUM('Turns'!D5,'Turns'!D21,'Turns'!D38,'Turns'!D50),"Unknown")</f>
-        <v>1116.0</v>
+        <v>1110.0</v>
       </c>
       <c r="K2" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E21,'Turns'!E38,'Turns'!E50)=4,SUM('Turns'!E5,'Turns'!E21,'Turns'!E38,'Turns'!E50),"Unknown")</f>
-        <v>0.000194712984</v>
+        <v>0.0001945497</v>
       </c>
       <c r="L2" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F21,'Turns'!F38,'Turns'!F50)=4,SUM('Turns'!F5,'Turns'!F21,'Turns'!F38,'Turns'!F50),"Unknown")</f>
-        <v>0.0002232</v>
+        <v>0.000222</v>
       </c>
       <c r="M2" s="2">
         <f>IF(COUNT('Turns'!D37,'Turns'!D49)=2,SUM('Turns'!D37,'Turns'!D49),"Unknown")</f>
@@ -4393,35 +4424,35 @@
       </c>
       <c r="S2" s="2">
         <f>IF(COUNT('Turns'!D12,'Turns'!D28,'Turns'!D43,'Turns'!D55)=4,SUM('Turns'!D12,'Turns'!D28,'Turns'!D43,'Turns'!D55),"Unknown")</f>
-        <v>156.0</v>
+        <v>157.0</v>
       </c>
       <c r="T2" s="2">
         <f>IF(COUNT('Turns'!E12,'Turns'!E28,'Turns'!E43,'Turns'!E55)=4,SUM('Turns'!E12,'Turns'!E28,'Turns'!E43,'Turns'!E55),"Unknown")</f>
-        <v>0.000163307664</v>
+        <v>0.00016510434</v>
       </c>
       <c r="U2" s="2">
         <f>IF(COUNT('Turns'!F12,'Turns'!F28,'Turns'!F43,'Turns'!F55)=4,SUM('Turns'!F12,'Turns'!F28,'Turns'!F43,'Turns'!F55),"Unknown")</f>
-        <v>0.0001872</v>
+        <v>0.0001884</v>
       </c>
       <c r="V2" s="2">
         <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="W2" s="2">
         <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>9.421596e-06</v>
+        <v>8.41296e-06</v>
       </c>
       <c r="X2" s="2">
         <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>1.08e-05</v>
+        <v>9.6e-06</v>
       </c>
       <c r="Y2" s="2">
         <f>IF(COUNT('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59)=4,SUM('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59),"Unknown")</f>
-        <v>0.000367442244</v>
+        <v>0.000368067</v>
       </c>
       <c r="Z2" s="2">
         <f>IF(COUNT('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59)=4,SUM('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59),"Unknown")</f>
-        <v>0.0004212</v>
+        <v>0.00042</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4432,7 +4463,7 @@
         <v>42.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>4827.616</v>
+        <v>5851.253</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>184</v>
@@ -4469,7 +4500,7 @@
       </c>
       <c r="K3" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>4.5712188e-05</v>
+        <v>4.592074e-05</v>
       </c>
       <c r="L3" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -4495,15 +4526,15 @@
       </c>
       <c r="S3" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>60.0</v>
+        <v>57.0</v>
       </c>
       <c r="T3" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>6.281064e-05</v>
+        <v>5.994234e-05</v>
       </c>
       <c r="U3" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>7.2e-05</v>
+        <v>6.84e-05</v>
       </c>
       <c r="V3" s="2">
         <v>0</v>
@@ -4516,11 +4547,11 @@
       </c>
       <c r="Y3" s="2">
         <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
-        <v>0.000108522828</v>
+        <v>0.00010586308</v>
       </c>
       <c r="Z3" s="2">
         <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
-        <v>0.0001244</v>
+        <v>0.0001208</v>
       </c>
       <c r="AA3" s="5">
         <f>IF(ISNUMBER(Y3),ROUND(Y3*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4531,7 +4562,7 @@
         <v>12.0</v>
       </c>
       <c r="AD3" s="1">
-        <v>1728.893</v>
+        <v>1629.707</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>184</v>
@@ -4571,7 +4602,7 @@
       </c>
       <c r="K4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>4.5712188e-05</v>
+        <v>4.592074e-05</v>
       </c>
       <c r="L4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -4597,15 +4628,15 @@
       </c>
       <c r="S4" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>60.0</v>
+        <v>57.0</v>
       </c>
       <c r="T4" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>6.281064e-05</v>
+        <v>5.994234e-05</v>
       </c>
       <c r="U4" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>7.2e-05</v>
+        <v>6.84e-05</v>
       </c>
       <c r="V4" s="2">
         <v>0</v>
@@ -4618,11 +4649,11 @@
       </c>
       <c r="Y4" s="2">
         <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
-        <v>0.000108522828</v>
+        <v>0.00010586308</v>
       </c>
       <c r="Z4" s="2">
         <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
-        <v>0.0001244</v>
+        <v>0.0001208</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4636,7 +4667,7 @@
         <v>93</v>
       </c>
       <c r="AD4" s="1">
-        <v>1725.688</v>
+        <v>1627.239</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>191</v>
@@ -4669,15 +4700,15 @@
       </c>
       <c r="J5" s="2">
         <f>IF(COUNT('Turns'!D21,'Turns'!D38)=2,SUM('Turns'!D21,'Turns'!D38),"Unknown")</f>
-        <v>485.0</v>
+        <v>479.0</v>
       </c>
       <c r="K5" s="2">
         <f>IF(COUNT('Turns'!E21,'Turns'!E38)=2,SUM('Turns'!E21,'Turns'!E38),"Unknown")</f>
-        <v>8.461989e-05</v>
+        <v>8.395433e-05</v>
       </c>
       <c r="L5" s="2">
         <f>IF(COUNT('Turns'!F21,'Turns'!F38)=2,SUM('Turns'!F21,'Turns'!F38),"Unknown")</f>
-        <v>9.7e-05</v>
+        <v>9.58e-05</v>
       </c>
       <c r="M5" s="2">
         <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
@@ -4702,46 +4733,46 @@
       </c>
       <c r="S5" s="2">
         <f>IF(COUNT('Turns'!D28,'Turns'!D43)=2,SUM('Turns'!D28,'Turns'!D43),"Unknown")</f>
-        <v>75.0</v>
+        <v>79.0</v>
       </c>
       <c r="T5" s="2">
         <f>IF(COUNT('Turns'!E28,'Turns'!E43)=2,SUM('Turns'!E28,'Turns'!E43),"Unknown")</f>
-        <v>7.85133e-05</v>
+        <v>8.307798e-05</v>
       </c>
       <c r="U5" s="2">
         <f>IF(COUNT('Turns'!F28,'Turns'!F43)=2,SUM('Turns'!F28,'Turns'!F43),"Unknown")</f>
-        <v>9e-05</v>
+        <v>9.48e-05</v>
       </c>
       <c r="V5" s="2">
         <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="W5" s="2">
         <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>9.421596e-06</v>
+        <v>8.41296e-06</v>
       </c>
       <c r="X5" s="2">
         <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>1.08e-05</v>
+        <v>9.6e-06</v>
       </c>
       <c r="Y5" s="2">
         <f>IF(COUNT('Turns'!E32,'Turns'!E47)=2,SUM('Turns'!E32,'Turns'!E47),"Unknown")</f>
-        <v>0.000172554786</v>
+        <v>0.00017544527</v>
       </c>
       <c r="Z5" s="2">
         <f>IF(COUNT('Turns'!F32,'Turns'!F47)=2,SUM('Turns'!F32,'Turns'!F47),"Unknown")</f>
-        <v>0.0001978</v>
+        <v>0.0002002</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
         <v>20.0</v>
       </c>
       <c r="AD5" s="1">
-        <v>2261.826</v>
+        <v>3082.935</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>184</v>
@@ -4774,15 +4805,15 @@
       </c>
       <c r="J6" s="2">
         <f>IF(COUNT('Turns'!D21,'Turns'!D38)=2,SUM('Turns'!D21,'Turns'!D38),"Unknown")</f>
-        <v>485.0</v>
+        <v>479.0</v>
       </c>
       <c r="K6" s="2">
         <f>IF(COUNT('Turns'!E21,'Turns'!E38)=2,SUM('Turns'!E21,'Turns'!E38),"Unknown")</f>
-        <v>8.461989e-05</v>
+        <v>8.395433e-05</v>
       </c>
       <c r="L6" s="2">
         <f>IF(COUNT('Turns'!F21,'Turns'!F38)=2,SUM('Turns'!F21,'Turns'!F38),"Unknown")</f>
-        <v>9.7e-05</v>
+        <v>9.58e-05</v>
       </c>
       <c r="M6" s="2">
         <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
@@ -4807,46 +4838,46 @@
       </c>
       <c r="S6" s="2">
         <f>IF(COUNT('Turns'!D28,'Turns'!D43)=2,SUM('Turns'!D28,'Turns'!D43),"Unknown")</f>
-        <v>75.0</v>
+        <v>79.0</v>
       </c>
       <c r="T6" s="2">
         <f>IF(COUNT('Turns'!E28,'Turns'!E43)=2,SUM('Turns'!E28,'Turns'!E43),"Unknown")</f>
-        <v>7.85133e-05</v>
+        <v>8.307798e-05</v>
       </c>
       <c r="U6" s="2">
         <f>IF(COUNT('Turns'!F28,'Turns'!F43)=2,SUM('Turns'!F28,'Turns'!F43),"Unknown")</f>
-        <v>9e-05</v>
+        <v>9.48e-05</v>
       </c>
       <c r="V6" s="2">
         <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="W6" s="2">
         <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>9.421596e-06</v>
+        <v>8.41296e-06</v>
       </c>
       <c r="X6" s="2">
         <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>1.08e-05</v>
+        <v>9.6e-06</v>
       </c>
       <c r="Y6" s="2">
         <f>IF(COUNT('Turns'!E32,'Turns'!E47)=2,SUM('Turns'!E32,'Turns'!E47),"Unknown")</f>
-        <v>0.000172554786</v>
+        <v>0.00017544527</v>
       </c>
       <c r="Z6" s="2">
         <f>IF(COUNT('Turns'!F32,'Turns'!F47)=2,SUM('Turns'!F32,'Turns'!F47),"Unknown")</f>
-        <v>0.0001978</v>
+        <v>0.0002002</v>
       </c>
       <c r="AA6" s="5">
         <f>IF(ISNUMBER(Y6),ROUND(Y6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="AB6" s="5">
         <f>IF(ISNUMBER(Z6),ROUND(Z6*'Reference data'!$B$2,0),"Unknown")</f>
         <v>20.0</v>
       </c>
       <c r="AD6" s="1">
-        <v>2260.541</v>
+        <v>3081.093</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>184</v>
@@ -4879,15 +4910,15 @@
       </c>
       <c r="J7" s="2">
         <f>IF(COUNT('Turns'!D21,'Turns'!D38)=2,SUM('Turns'!D21,'Turns'!D38),"Unknown")</f>
-        <v>485.0</v>
+        <v>479.0</v>
       </c>
       <c r="K7" s="2">
         <f>IF(COUNT('Turns'!E21,'Turns'!E38)=2,SUM('Turns'!E21,'Turns'!E38),"Unknown")</f>
-        <v>8.461989e-05</v>
+        <v>8.395433e-05</v>
       </c>
       <c r="L7" s="2">
         <f>IF(COUNT('Turns'!F21,'Turns'!F38)=2,SUM('Turns'!F21,'Turns'!F38),"Unknown")</f>
-        <v>9.7e-05</v>
+        <v>9.58e-05</v>
       </c>
       <c r="M7" s="2">
         <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
@@ -4912,46 +4943,46 @@
       </c>
       <c r="S7" s="2">
         <f>IF(COUNT('Turns'!D28,'Turns'!D43)=2,SUM('Turns'!D28,'Turns'!D43),"Unknown")</f>
-        <v>75.0</v>
+        <v>79.0</v>
       </c>
       <c r="T7" s="2">
         <f>IF(COUNT('Turns'!E28,'Turns'!E43)=2,SUM('Turns'!E28,'Turns'!E43),"Unknown")</f>
-        <v>7.85133e-05</v>
+        <v>8.307798e-05</v>
       </c>
       <c r="U7" s="2">
         <f>IF(COUNT('Turns'!F28,'Turns'!F43)=2,SUM('Turns'!F28,'Turns'!F43),"Unknown")</f>
-        <v>9e-05</v>
+        <v>9.48e-05</v>
       </c>
       <c r="V7" s="2">
         <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="W7" s="2">
         <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>9.421596e-06</v>
+        <v>8.41296e-06</v>
       </c>
       <c r="X7" s="2">
         <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>1.08e-05</v>
+        <v>9.6e-06</v>
       </c>
       <c r="Y7" s="2">
         <f>IF(COUNT('Turns'!E32,'Turns'!E47)=2,SUM('Turns'!E32,'Turns'!E47),"Unknown")</f>
-        <v>0.000172554786</v>
+        <v>0.00017544527</v>
       </c>
       <c r="Z7" s="2">
         <f>IF(COUNT('Turns'!F32,'Turns'!F47)=2,SUM('Turns'!F32,'Turns'!F47),"Unknown")</f>
-        <v>0.0001978</v>
+        <v>0.0002002</v>
       </c>
       <c r="AA7" s="5">
         <f>IF(ISNUMBER(Y7),ROUND(Y7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="AB7" s="5">
         <f>IF(ISNUMBER(Z7),ROUND(Z7*'Reference data'!$B$2,0),"Unknown")</f>
         <v>20.0</v>
       </c>
       <c r="AD7" s="1">
-        <v>2259.592</v>
+        <v>3079.32</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>184</v>
@@ -4984,15 +5015,15 @@
       </c>
       <c r="J8" s="2">
         <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
-        <v>197.0</v>
+        <v>194.0</v>
       </c>
       <c r="K8" s="2">
         <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
-        <v>3.4371378e-05</v>
+        <v>3.400238e-05</v>
       </c>
       <c r="L8" s="2">
         <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
-        <v>3.94e-05</v>
+        <v>3.88e-05</v>
       </c>
       <c r="M8" s="2">
         <v>0</v>
@@ -5014,35 +5045,35 @@
       </c>
       <c r="S8" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="T8" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>3.5592696e-05</v>
+        <v>3.68067e-05</v>
       </c>
       <c r="U8" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>4.08e-05</v>
+        <v>4.2e-05</v>
       </c>
       <c r="V8" s="2">
         <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="W8" s="2">
         <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>9.421596e-06</v>
+        <v>8.41296e-06</v>
       </c>
       <c r="X8" s="2">
         <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>1.08e-05</v>
+        <v>9.6e-06</v>
       </c>
       <c r="Y8" s="2">
         <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>7.938567e-05</v>
+        <v>7.922204e-05</v>
       </c>
       <c r="Z8" s="2">
         <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>9.1e-05</v>
+        <v>9.04e-05</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5053,7 +5084,7 @@
         <v>9.0</v>
       </c>
       <c r="AD8" s="1">
-        <v>1205.046</v>
+        <v>1458.209</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>184</v>
@@ -5076,7 +5107,7 @@
         <v>110</v>
       </c>
       <c r="F9" s="1">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>190</v>
@@ -5089,15 +5120,15 @@
       </c>
       <c r="J9" s="2">
         <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
-        <v>197.0</v>
+        <v>194.0</v>
       </c>
       <c r="K9" s="2">
         <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
-        <v>3.4371378e-05</v>
+        <v>3.400238e-05</v>
       </c>
       <c r="L9" s="2">
         <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
-        <v>3.94e-05</v>
+        <v>3.88e-05</v>
       </c>
       <c r="M9" s="2">
         <v>0</v>
@@ -5119,35 +5150,35 @@
       </c>
       <c r="S9" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="T9" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>3.5592696e-05</v>
+        <v>3.68067e-05</v>
       </c>
       <c r="U9" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>4.08e-05</v>
+        <v>4.2e-05</v>
       </c>
       <c r="V9" s="2">
         <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="W9" s="2">
         <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>9.421596e-06</v>
+        <v>8.41296e-06</v>
       </c>
       <c r="X9" s="2">
         <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>1.08e-05</v>
+        <v>9.6e-06</v>
       </c>
       <c r="Y9" s="2">
         <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>7.938567e-05</v>
+        <v>7.922204e-05</v>
       </c>
       <c r="Z9" s="2">
         <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>9.1e-05</v>
+        <v>9.04e-05</v>
       </c>
       <c r="AA9" s="5">
         <f>IF(ISNUMBER(Y9),ROUND(Y9*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5161,7 +5192,7 @@
         <v>117</v>
       </c>
       <c r="AD9" s="1">
-        <v>1202.645</v>
+        <v>1454.898</v>
       </c>
       <c r="AE9" s="1" t="s">
         <v>191</v>
@@ -5193,7 +5224,7 @@
         <v>200</v>
       </c>
       <c r="AD10" s="1">
-        <v>1.987</v>
+        <v>4.528</v>
       </c>
       <c r="AE10" s="1" t="s">
         <v>206</v>
@@ -5225,7 +5256,7 @@
         <v>205</v>
       </c>
       <c r="AD11" s="1">
-        <v>0.622</v>
+        <v>1.505</v>
       </c>
       <c r="AE11" s="1" t="s">
         <v>206</v>
@@ -5258,15 +5289,15 @@
       </c>
       <c r="J12" s="2">
         <f>IF(COUNT('Turns'!D38)=1,SUM('Turns'!D38),"Unknown")</f>
-        <v>288.0</v>
+        <v>285.0</v>
       </c>
       <c r="K12" s="2">
         <f>IF(COUNT('Turns'!E38)=1,SUM('Turns'!E38),"Unknown")</f>
-        <v>5.0248512e-05</v>
+        <v>4.995195e-05</v>
       </c>
       <c r="L12" s="2">
         <f>IF(COUNT('Turns'!F38)=1,SUM('Turns'!F38),"Unknown")</f>
-        <v>5.76e-05</v>
+        <v>5.7e-05</v>
       </c>
       <c r="M12" s="2">
         <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
@@ -5291,15 +5322,15 @@
       </c>
       <c r="S12" s="2">
         <f>IF(COUNT('Turns'!D43)=1,SUM('Turns'!D43),"Unknown")</f>
-        <v>41.0</v>
+        <v>44.0</v>
       </c>
       <c r="T12" s="2">
         <f>IF(COUNT('Turns'!E43)=1,SUM('Turns'!E43),"Unknown")</f>
-        <v>4.2920604e-05</v>
+        <v>4.627128e-05</v>
       </c>
       <c r="U12" s="2">
         <f>IF(COUNT('Turns'!F43)=1,SUM('Turns'!F43),"Unknown")</f>
-        <v>4.92e-05</v>
+        <v>5.28e-05</v>
       </c>
       <c r="V12" s="2">
         <v>0</v>
@@ -5312,22 +5343,22 @@
       </c>
       <c r="Y12" s="2">
         <f>IF(COUNT('Turns'!E47)=1,SUM('Turns'!E47),"Unknown")</f>
-        <v>9.3169116e-05</v>
+        <v>9.622323e-05</v>
       </c>
       <c r="Z12" s="2">
         <f>IF(COUNT('Turns'!F47)=1,SUM('Turns'!F47),"Unknown")</f>
-        <v>0.0001068</v>
+        <v>0.0001098</v>
       </c>
       <c r="AA12" s="5">
         <f>IF(ISNUMBER(Y12),ROUND(Y12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="AB12" s="5">
         <f>IF(ISNUMBER(Z12),ROUND(Z12*'Reference data'!$B$2,0),"Unknown")</f>
         <v>11.0</v>
       </c>
       <c r="AD12" s="1">
-        <v>1049.556</v>
+        <v>1610.327</v>
       </c>
       <c r="AE12" s="1" t="s">
         <v>184</v>
@@ -5350,7 +5381,7 @@
         <v>110</v>
       </c>
       <c r="F13" s="1">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>190</v>
@@ -5363,15 +5394,15 @@
       </c>
       <c r="J13" s="2">
         <f>IF(COUNT('Turns'!D38)=1,SUM('Turns'!D38),"Unknown")</f>
-        <v>288.0</v>
+        <v>285.0</v>
       </c>
       <c r="K13" s="2">
         <f>IF(COUNT('Turns'!E38)=1,SUM('Turns'!E38),"Unknown")</f>
-        <v>5.0248512e-05</v>
+        <v>4.995195e-05</v>
       </c>
       <c r="L13" s="2">
         <f>IF(COUNT('Turns'!F38)=1,SUM('Turns'!F38),"Unknown")</f>
-        <v>5.76e-05</v>
+        <v>5.7e-05</v>
       </c>
       <c r="M13" s="2">
         <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
@@ -5396,15 +5427,15 @@
       </c>
       <c r="S13" s="2">
         <f>IF(COUNT('Turns'!D43)=1,SUM('Turns'!D43),"Unknown")</f>
-        <v>41.0</v>
+        <v>44.0</v>
       </c>
       <c r="T13" s="2">
         <f>IF(COUNT('Turns'!E43)=1,SUM('Turns'!E43),"Unknown")</f>
-        <v>4.2920604e-05</v>
+        <v>4.627128e-05</v>
       </c>
       <c r="U13" s="2">
         <f>IF(COUNT('Turns'!F43)=1,SUM('Turns'!F43),"Unknown")</f>
-        <v>4.92e-05</v>
+        <v>5.28e-05</v>
       </c>
       <c r="V13" s="2">
         <v>0</v>
@@ -5417,15 +5448,15 @@
       </c>
       <c r="Y13" s="2">
         <f>IF(COUNT('Turns'!E47)=1,SUM('Turns'!E47),"Unknown")</f>
-        <v>9.3169116e-05</v>
+        <v>9.622323e-05</v>
       </c>
       <c r="Z13" s="2">
         <f>IF(COUNT('Turns'!F47)=1,SUM('Turns'!F47),"Unknown")</f>
-        <v>0.0001068</v>
+        <v>0.0001098</v>
       </c>
       <c r="AA13" s="5">
         <f>IF(ISNUMBER(Y13),ROUND(Y13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="AB13" s="5">
         <f>IF(ISNUMBER(Z13),ROUND(Z13*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5435,7 +5466,7 @@
         <v>126</v>
       </c>
       <c r="AD13" s="1">
-        <v>1048.349</v>
+        <v>1607.712</v>
       </c>
       <c r="AE13" s="1" t="s">
         <v>191</v>
@@ -5472,7 +5503,7 @@
       </c>
       <c r="K14" s="2">
         <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>6.4380906e-05</v>
+        <v>6.467463e-05</v>
       </c>
       <c r="L14" s="2">
         <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
@@ -5505,7 +5536,7 @@
       </c>
       <c r="T14" s="2">
         <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
-        <v>2.1983724e-05</v>
+        <v>2.208402e-05</v>
       </c>
       <c r="U14" s="2">
         <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
@@ -5522,7 +5553,7 @@
       </c>
       <c r="Y14" s="2">
         <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
-        <v>8.636463e-05</v>
+        <v>8.675865e-05</v>
       </c>
       <c r="Z14" s="2">
         <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
@@ -5537,7 +5568,7 @@
         <v>10.0</v>
       </c>
       <c r="AD14" s="1">
-        <v>832.146</v>
+        <v>1131.682</v>
       </c>
       <c r="AE14" s="1" t="s">
         <v>184</v>
@@ -5577,7 +5608,7 @@
       </c>
       <c r="K15" s="2">
         <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>6.4380906e-05</v>
+        <v>6.467463e-05</v>
       </c>
       <c r="L15" s="2">
         <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
@@ -5610,7 +5641,7 @@
       </c>
       <c r="T15" s="2">
         <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
-        <v>2.1983724e-05</v>
+        <v>2.208402e-05</v>
       </c>
       <c r="U15" s="2">
         <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
@@ -5627,7 +5658,7 @@
       </c>
       <c r="Y15" s="2">
         <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
-        <v>8.636463e-05</v>
+        <v>8.675865e-05</v>
       </c>
       <c r="Z15" s="2">
         <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
@@ -5645,7 +5676,7 @@
         <v>131</v>
       </c>
       <c r="AD15" s="1">
-        <v>830.5549999999999</v>
+        <v>1128.269</v>
       </c>
       <c r="AE15" s="1" t="s">
         <v>191</v>
@@ -5675,15 +5706,15 @@
       </c>
       <c r="J16" s="2">
         <f>IF(COUNT('Turns'!D63,'Turns'!D77,'Turns'!D94,'Turns'!D106)=4,SUM('Turns'!D63,'Turns'!D77,'Turns'!D94,'Turns'!D106),"Unknown")</f>
-        <v>1500.0</v>
+        <v>1432.0</v>
       </c>
       <c r="K16" s="2">
         <f>IF(COUNT('Turns'!E63,'Turns'!E77,'Turns'!E94,'Turns'!E106)=4,SUM('Turns'!E63,'Turns'!E77,'Turns'!E94,'Turns'!E106),"Unknown")</f>
-        <v>0.000261711</v>
+        <v>0.00025098664</v>
       </c>
       <c r="L16" s="2">
         <f>IF(COUNT('Turns'!F63,'Turns'!F77,'Turns'!F94,'Turns'!F106)=4,SUM('Turns'!F63,'Turns'!F77,'Turns'!F94,'Turns'!F106),"Unknown")</f>
-        <v>0.0003</v>
+        <v>0.0002864</v>
       </c>
       <c r="M16" s="2">
         <f>IF(COUNT('Turns'!D62,'Turns'!D93,'Turns'!D105)=3,SUM('Turns'!D62,'Turns'!D93,'Turns'!D105),"Unknown")</f>
@@ -5708,15 +5739,15 @@
       </c>
       <c r="S16" s="2">
         <f>IF(COUNT('Turns'!D68,'Turns'!D84,'Turns'!D99,'Turns'!D111)=4,SUM('Turns'!D68,'Turns'!D84,'Turns'!D99,'Turns'!D111),"Unknown")</f>
-        <v>212.0</v>
+        <v>181.0</v>
       </c>
       <c r="T16" s="2">
         <f>IF(COUNT('Turns'!E68,'Turns'!E84,'Turns'!E99,'Turns'!E111)=4,SUM('Turns'!E68,'Turns'!E84,'Turns'!E99,'Turns'!E111),"Unknown")</f>
-        <v>0.000221930928</v>
+        <v>0.00019034322</v>
       </c>
       <c r="U16" s="2">
         <f>IF(COUNT('Turns'!F68,'Turns'!F84,'Turns'!F99,'Turns'!F111)=4,SUM('Turns'!F68,'Turns'!F84,'Turns'!F99,'Turns'!F111),"Unknown")</f>
-        <v>0.0002544</v>
+        <v>0.0002172</v>
       </c>
       <c r="V16" s="2">
         <f>IF(COUNT('Turns'!D83)=1,SUM('Turns'!D83),"Unknown")</f>
@@ -5724,7 +5755,7 @@
       </c>
       <c r="W16" s="2">
         <f>IF(COUNT('Turns'!E83)=1,SUM('Turns'!E83),"Unknown")</f>
-        <v>9.421596e-06</v>
+        <v>9.46458e-06</v>
       </c>
       <c r="X16" s="2">
         <f>IF(COUNT('Turns'!F83)=1,SUM('Turns'!F83),"Unknown")</f>
@@ -5732,22 +5763,22 @@
       </c>
       <c r="Y16" s="2">
         <f>IF(COUNT('Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115)=4,SUM('Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115),"Unknown")</f>
-        <v>0.000493063524</v>
+        <v>0.00045079444</v>
       </c>
       <c r="Z16" s="2">
         <f>IF(COUNT('Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115)=4,SUM('Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115),"Unknown")</f>
-        <v>0.0005652</v>
+        <v>0.0005144</v>
       </c>
       <c r="AA16" s="5">
         <f>IF(ISNUMBER(Y16),ROUND(Y16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>49.0</v>
+        <v>45.0</v>
       </c>
       <c r="AB16" s="5">
         <f>IF(ISNUMBER(Z16),ROUND(Z16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>57.0</v>
+        <v>51.0</v>
       </c>
       <c r="AD16" s="1">
-        <v>5675.891</v>
+        <v>4625.912</v>
       </c>
       <c r="AE16" s="1" t="s">
         <v>184</v>
@@ -5784,7 +5815,7 @@
       </c>
       <c r="K17" s="2">
         <f>IF(COUNT('Turns'!E63)=1,SUM('Turns'!E63),"Unknown")</f>
-        <v>7.1010918e-05</v>
+        <v>7.133489e-05</v>
       </c>
       <c r="L17" s="2">
         <f>IF(COUNT('Turns'!F63)=1,SUM('Turns'!F63),"Unknown")</f>
@@ -5813,15 +5844,15 @@
       </c>
       <c r="S17" s="2">
         <f>IF(COUNT('Turns'!D68)=1,SUM('Turns'!D68),"Unknown")</f>
-        <v>78.0</v>
+        <v>60.0</v>
       </c>
       <c r="T17" s="2">
         <f>IF(COUNT('Turns'!E68)=1,SUM('Turns'!E68),"Unknown")</f>
-        <v>8.1653832e-05</v>
+        <v>6.30972e-05</v>
       </c>
       <c r="U17" s="2">
         <f>IF(COUNT('Turns'!F68)=1,SUM('Turns'!F68),"Unknown")</f>
-        <v>9.36e-05</v>
+        <v>7.2e-05</v>
       </c>
       <c r="V17" s="2">
         <v>0</v>
@@ -5834,22 +5865,22 @@
       </c>
       <c r="Y17" s="2">
         <f>IF(COUNT('Turns'!E72)=1,SUM('Turns'!E72),"Unknown")</f>
-        <v>0.00015266475</v>
+        <v>0.00013443209</v>
       </c>
       <c r="Z17" s="2">
         <f>IF(COUNT('Turns'!F72)=1,SUM('Turns'!F72),"Unknown")</f>
-        <v>0.000175</v>
+        <v>0.0001534</v>
       </c>
       <c r="AA17" s="5">
         <f>IF(ISNUMBER(Y17),ROUND(Y17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="AB17" s="5">
         <f>IF(ISNUMBER(Z17),ROUND(Z17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="AD17" s="1">
-        <v>1629.667</v>
+        <v>1279.76</v>
       </c>
       <c r="AE17" s="1" t="s">
         <v>184</v>
@@ -5889,7 +5920,7 @@
       </c>
       <c r="K18" s="2">
         <f>IF(COUNT('Turns'!E63)=1,SUM('Turns'!E63),"Unknown")</f>
-        <v>7.1010918e-05</v>
+        <v>7.133489e-05</v>
       </c>
       <c r="L18" s="2">
         <f>IF(COUNT('Turns'!F63)=1,SUM('Turns'!F63),"Unknown")</f>
@@ -5918,15 +5949,15 @@
       </c>
       <c r="S18" s="2">
         <f>IF(COUNT('Turns'!D68)=1,SUM('Turns'!D68),"Unknown")</f>
-        <v>78.0</v>
+        <v>60.0</v>
       </c>
       <c r="T18" s="2">
         <f>IF(COUNT('Turns'!E68)=1,SUM('Turns'!E68),"Unknown")</f>
-        <v>8.1653832e-05</v>
+        <v>6.30972e-05</v>
       </c>
       <c r="U18" s="2">
         <f>IF(COUNT('Turns'!F68)=1,SUM('Turns'!F68),"Unknown")</f>
-        <v>9.36e-05</v>
+        <v>7.2e-05</v>
       </c>
       <c r="V18" s="2">
         <v>0</v>
@@ -5939,25 +5970,25 @@
       </c>
       <c r="Y18" s="2">
         <f>IF(COUNT('Turns'!E72)=1,SUM('Turns'!E72),"Unknown")</f>
-        <v>0.00015266475</v>
+        <v>0.00013443209</v>
       </c>
       <c r="Z18" s="2">
         <f>IF(COUNT('Turns'!F72)=1,SUM('Turns'!F72),"Unknown")</f>
-        <v>0.000175</v>
+        <v>0.0001534</v>
       </c>
       <c r="AA18" s="5">
         <f>IF(ISNUMBER(Y18),ROUND(Y18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="AB18" s="5">
         <f>IF(ISNUMBER(Z18),ROUND(Z18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="AC18" s="1" t="s">
         <v>136</v>
       </c>
       <c r="AD18" s="1">
-        <v>1628.302</v>
+        <v>1277.459</v>
       </c>
       <c r="AE18" s="1" t="s">
         <v>191</v>
@@ -5990,15 +6021,15 @@
       </c>
       <c r="J19" s="2">
         <f>IF(COUNT('Turns'!D77,'Turns'!D94)=2,SUM('Turns'!D77,'Turns'!D94),"Unknown")</f>
-        <v>540.0</v>
+        <v>494.0</v>
       </c>
       <c r="K19" s="2">
         <f>IF(COUNT('Turns'!E77,'Turns'!E94)=2,SUM('Turns'!E77,'Turns'!E94),"Unknown")</f>
-        <v>9.421596e-05</v>
+        <v>8.658338e-05</v>
       </c>
       <c r="L19" s="2">
         <f>IF(COUNT('Turns'!F77,'Turns'!F94)=2,SUM('Turns'!F77,'Turns'!F94),"Unknown")</f>
-        <v>0.000108</v>
+        <v>9.88e-05</v>
       </c>
       <c r="M19" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -6023,15 +6054,15 @@
       </c>
       <c r="S19" s="2">
         <f>IF(COUNT('Turns'!D84,'Turns'!D99)=2,SUM('Turns'!D84,'Turns'!D99),"Unknown")</f>
-        <v>112.0</v>
+        <v>98.0</v>
       </c>
       <c r="T19" s="2">
         <f>IF(COUNT('Turns'!E84,'Turns'!E99)=2,SUM('Turns'!E84,'Turns'!E99),"Unknown")</f>
-        <v>0.000117246528</v>
+        <v>0.00010305876</v>
       </c>
       <c r="U19" s="2">
         <f>IF(COUNT('Turns'!F84,'Turns'!F99)=2,SUM('Turns'!F84,'Turns'!F99),"Unknown")</f>
-        <v>0.0001344</v>
+        <v>0.0001176</v>
       </c>
       <c r="V19" s="2">
         <f>IF(COUNT('Turns'!D83)=1,SUM('Turns'!D83),"Unknown")</f>
@@ -6039,7 +6070,7 @@
       </c>
       <c r="W19" s="2">
         <f>IF(COUNT('Turns'!E83)=1,SUM('Turns'!E83),"Unknown")</f>
-        <v>9.421596e-06</v>
+        <v>9.46458e-06</v>
       </c>
       <c r="X19" s="2">
         <f>IF(COUNT('Turns'!F83)=1,SUM('Turns'!F83),"Unknown")</f>
@@ -6047,22 +6078,22 @@
       </c>
       <c r="Y19" s="2">
         <f>IF(COUNT('Turns'!E88,'Turns'!E103)=2,SUM('Turns'!E88,'Turns'!E103),"Unknown")</f>
-        <v>0.000220884084</v>
+        <v>0.00019910672</v>
       </c>
       <c r="Z19" s="2">
         <f>IF(COUNT('Turns'!F88,'Turns'!F103)=2,SUM('Turns'!F88,'Turns'!F103),"Unknown")</f>
-        <v>0.0002532</v>
+        <v>0.0002272</v>
       </c>
       <c r="AA19" s="5">
         <f>IF(ISNUMBER(Y19),ROUND(Y19*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="AB19" s="5">
         <f>IF(ISNUMBER(Z19),ROUND(Z19*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
       <c r="AD19" s="1">
-        <v>2995.943</v>
+        <v>2400.625</v>
       </c>
       <c r="AE19" s="1" t="s">
         <v>184</v>
@@ -6095,15 +6126,15 @@
       </c>
       <c r="J20" s="2">
         <f>IF(COUNT('Turns'!D77,'Turns'!D94)=2,SUM('Turns'!D77,'Turns'!D94),"Unknown")</f>
-        <v>540.0</v>
+        <v>494.0</v>
       </c>
       <c r="K20" s="2">
         <f>IF(COUNT('Turns'!E77,'Turns'!E94)=2,SUM('Turns'!E77,'Turns'!E94),"Unknown")</f>
-        <v>9.421596e-05</v>
+        <v>8.658338e-05</v>
       </c>
       <c r="L20" s="2">
         <f>IF(COUNT('Turns'!F77,'Turns'!F94)=2,SUM('Turns'!F77,'Turns'!F94),"Unknown")</f>
-        <v>0.000108</v>
+        <v>9.88e-05</v>
       </c>
       <c r="M20" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -6128,15 +6159,15 @@
       </c>
       <c r="S20" s="2">
         <f>IF(COUNT('Turns'!D84,'Turns'!D99)=2,SUM('Turns'!D84,'Turns'!D99),"Unknown")</f>
-        <v>112.0</v>
+        <v>98.0</v>
       </c>
       <c r="T20" s="2">
         <f>IF(COUNT('Turns'!E84,'Turns'!E99)=2,SUM('Turns'!E84,'Turns'!E99),"Unknown")</f>
-        <v>0.000117246528</v>
+        <v>0.00010305876</v>
       </c>
       <c r="U20" s="2">
         <f>IF(COUNT('Turns'!F84,'Turns'!F99)=2,SUM('Turns'!F84,'Turns'!F99),"Unknown")</f>
-        <v>0.0001344</v>
+        <v>0.0001176</v>
       </c>
       <c r="V20" s="2">
         <f>IF(COUNT('Turns'!D83)=1,SUM('Turns'!D83),"Unknown")</f>
@@ -6144,7 +6175,7 @@
       </c>
       <c r="W20" s="2">
         <f>IF(COUNT('Turns'!E83)=1,SUM('Turns'!E83),"Unknown")</f>
-        <v>9.421596e-06</v>
+        <v>9.46458e-06</v>
       </c>
       <c r="X20" s="2">
         <f>IF(COUNT('Turns'!F83)=1,SUM('Turns'!F83),"Unknown")</f>
@@ -6152,22 +6183,22 @@
       </c>
       <c r="Y20" s="2">
         <f>IF(COUNT('Turns'!E88,'Turns'!E103)=2,SUM('Turns'!E88,'Turns'!E103),"Unknown")</f>
-        <v>0.000220884084</v>
+        <v>0.00019910672</v>
       </c>
       <c r="Z20" s="2">
         <f>IF(COUNT('Turns'!F88,'Turns'!F103)=2,SUM('Turns'!F88,'Turns'!F103),"Unknown")</f>
-        <v>0.0002532</v>
+        <v>0.0002272</v>
       </c>
       <c r="AA20" s="5">
         <f>IF(ISNUMBER(Y20),ROUND(Y20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="AB20" s="5">
         <f>IF(ISNUMBER(Z20),ROUND(Z20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
       <c r="AD20" s="1">
-        <v>2995.011</v>
+        <v>2398.465</v>
       </c>
       <c r="AE20" s="1" t="s">
         <v>184</v>
@@ -6200,15 +6231,15 @@
       </c>
       <c r="J21" s="2">
         <f>IF(COUNT('Turns'!D77,'Turns'!D94)=2,SUM('Turns'!D77,'Turns'!D94),"Unknown")</f>
-        <v>540.0</v>
+        <v>494.0</v>
       </c>
       <c r="K21" s="2">
         <f>IF(COUNT('Turns'!E77,'Turns'!E94)=2,SUM('Turns'!E77,'Turns'!E94),"Unknown")</f>
-        <v>9.421596e-05</v>
+        <v>8.658338e-05</v>
       </c>
       <c r="L21" s="2">
         <f>IF(COUNT('Turns'!F77,'Turns'!F94)=2,SUM('Turns'!F77,'Turns'!F94),"Unknown")</f>
-        <v>0.000108</v>
+        <v>9.88e-05</v>
       </c>
       <c r="M21" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -6233,15 +6264,15 @@
       </c>
       <c r="S21" s="2">
         <f>IF(COUNT('Turns'!D84,'Turns'!D99)=2,SUM('Turns'!D84,'Turns'!D99),"Unknown")</f>
-        <v>112.0</v>
+        <v>98.0</v>
       </c>
       <c r="T21" s="2">
         <f>IF(COUNT('Turns'!E84,'Turns'!E99)=2,SUM('Turns'!E84,'Turns'!E99),"Unknown")</f>
-        <v>0.000117246528</v>
+        <v>0.00010305876</v>
       </c>
       <c r="U21" s="2">
         <f>IF(COUNT('Turns'!F84,'Turns'!F99)=2,SUM('Turns'!F84,'Turns'!F99),"Unknown")</f>
-        <v>0.0001344</v>
+        <v>0.0001176</v>
       </c>
       <c r="V21" s="2">
         <f>IF(COUNT('Turns'!D83)=1,SUM('Turns'!D83),"Unknown")</f>
@@ -6249,7 +6280,7 @@
       </c>
       <c r="W21" s="2">
         <f>IF(COUNT('Turns'!E83)=1,SUM('Turns'!E83),"Unknown")</f>
-        <v>9.421596e-06</v>
+        <v>9.46458e-06</v>
       </c>
       <c r="X21" s="2">
         <f>IF(COUNT('Turns'!F83)=1,SUM('Turns'!F83),"Unknown")</f>
@@ -6257,22 +6288,22 @@
       </c>
       <c r="Y21" s="2">
         <f>IF(COUNT('Turns'!E88,'Turns'!E103)=2,SUM('Turns'!E88,'Turns'!E103),"Unknown")</f>
-        <v>0.000220884084</v>
+        <v>0.00019910672</v>
       </c>
       <c r="Z21" s="2">
         <f>IF(COUNT('Turns'!F88,'Turns'!F103)=2,SUM('Turns'!F88,'Turns'!F103),"Unknown")</f>
-        <v>0.0002532</v>
+        <v>0.0002272</v>
       </c>
       <c r="AA21" s="5">
         <f>IF(ISNUMBER(Y21),ROUND(Y21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="AB21" s="5">
         <f>IF(ISNUMBER(Z21),ROUND(Z21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
       <c r="AD21" s="1">
-        <v>2994.071</v>
+        <v>2396.452</v>
       </c>
       <c r="AE21" s="1" t="s">
         <v>184</v>
@@ -6305,15 +6336,15 @@
       </c>
       <c r="J22" s="2">
         <f>IF(COUNT('Turns'!D77)=1,SUM('Turns'!D77),"Unknown")</f>
-        <v>212.0</v>
+        <v>194.0</v>
       </c>
       <c r="K22" s="2">
         <f>IF(COUNT('Turns'!E77)=1,SUM('Turns'!E77),"Unknown")</f>
-        <v>3.6988488e-05</v>
+        <v>3.400238e-05</v>
       </c>
       <c r="L22" s="2">
         <f>IF(COUNT('Turns'!F77)=1,SUM('Turns'!F77),"Unknown")</f>
-        <v>4.24e-05</v>
+        <v>3.88e-05</v>
       </c>
       <c r="M22" s="2">
         <v>0</v>
@@ -6335,15 +6366,15 @@
       </c>
       <c r="S22" s="2">
         <f>IF(COUNT('Turns'!D84)=1,SUM('Turns'!D84),"Unknown")</f>
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="T22" s="2">
         <f>IF(COUNT('Turns'!E84)=1,SUM('Turns'!E84),"Unknown")</f>
-        <v>5.23422e-05</v>
+        <v>4.20648e-05</v>
       </c>
       <c r="U22" s="2">
         <f>IF(COUNT('Turns'!F84)=1,SUM('Turns'!F84),"Unknown")</f>
-        <v>6e-05</v>
+        <v>4.8e-05</v>
       </c>
       <c r="V22" s="2">
         <f>IF(COUNT('Turns'!D83)=1,SUM('Turns'!D83),"Unknown")</f>
@@ -6351,7 +6382,7 @@
       </c>
       <c r="W22" s="2">
         <f>IF(COUNT('Turns'!E83)=1,SUM('Turns'!E83),"Unknown")</f>
-        <v>9.421596e-06</v>
+        <v>9.46458e-06</v>
       </c>
       <c r="X22" s="2">
         <f>IF(COUNT('Turns'!F83)=1,SUM('Turns'!F83),"Unknown")</f>
@@ -6359,22 +6390,22 @@
       </c>
       <c r="Y22" s="2">
         <f>IF(COUNT('Turns'!E88)=1,SUM('Turns'!E88),"Unknown")</f>
-        <v>9.8752284e-05</v>
+        <v>8.553176e-05</v>
       </c>
       <c r="Z22" s="2">
         <f>IF(COUNT('Turns'!F88)=1,SUM('Turns'!F88),"Unknown")</f>
-        <v>0.0001132</v>
+        <v>9.76e-05</v>
       </c>
       <c r="AA22" s="5">
         <f>IF(ISNUMBER(Y22),ROUND(Y22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="AB22" s="5">
         <f>IF(ISNUMBER(Z22),ROUND(Z22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="AD22" s="1">
-        <v>1634.397</v>
+        <v>1155.481</v>
       </c>
       <c r="AE22" s="1" t="s">
         <v>184</v>
@@ -6397,7 +6428,7 @@
         <v>110</v>
       </c>
       <c r="F23" s="1">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>190</v>
@@ -6410,15 +6441,15 @@
       </c>
       <c r="J23" s="2">
         <f>IF(COUNT('Turns'!D77)=1,SUM('Turns'!D77),"Unknown")</f>
-        <v>212.0</v>
+        <v>194.0</v>
       </c>
       <c r="K23" s="2">
         <f>IF(COUNT('Turns'!E77)=1,SUM('Turns'!E77),"Unknown")</f>
-        <v>3.6988488e-05</v>
+        <v>3.400238e-05</v>
       </c>
       <c r="L23" s="2">
         <f>IF(COUNT('Turns'!F77)=1,SUM('Turns'!F77),"Unknown")</f>
-        <v>4.24e-05</v>
+        <v>3.88e-05</v>
       </c>
       <c r="M23" s="2">
         <v>0</v>
@@ -6440,15 +6471,15 @@
       </c>
       <c r="S23" s="2">
         <f>IF(COUNT('Turns'!D84)=1,SUM('Turns'!D84),"Unknown")</f>
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="T23" s="2">
         <f>IF(COUNT('Turns'!E84)=1,SUM('Turns'!E84),"Unknown")</f>
-        <v>5.23422e-05</v>
+        <v>4.20648e-05</v>
       </c>
       <c r="U23" s="2">
         <f>IF(COUNT('Turns'!F84)=1,SUM('Turns'!F84),"Unknown")</f>
-        <v>6e-05</v>
+        <v>4.8e-05</v>
       </c>
       <c r="V23" s="2">
         <f>IF(COUNT('Turns'!D83)=1,SUM('Turns'!D83),"Unknown")</f>
@@ -6456,7 +6487,7 @@
       </c>
       <c r="W23" s="2">
         <f>IF(COUNT('Turns'!E83)=1,SUM('Turns'!E83),"Unknown")</f>
-        <v>9.421596e-06</v>
+        <v>9.46458e-06</v>
       </c>
       <c r="X23" s="2">
         <f>IF(COUNT('Turns'!F83)=1,SUM('Turns'!F83),"Unknown")</f>
@@ -6464,25 +6495,25 @@
       </c>
       <c r="Y23" s="2">
         <f>IF(COUNT('Turns'!E88)=1,SUM('Turns'!E88),"Unknown")</f>
-        <v>9.8752284e-05</v>
+        <v>8.553176e-05</v>
       </c>
       <c r="Z23" s="2">
         <f>IF(COUNT('Turns'!F88)=1,SUM('Turns'!F88),"Unknown")</f>
-        <v>0.0001132</v>
+        <v>9.76e-05</v>
       </c>
       <c r="AA23" s="5">
         <f>IF(ISNUMBER(Y23),ROUND(Y23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="AB23" s="5">
         <f>IF(ISNUMBER(Z23),ROUND(Z23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="AC23" s="1" t="s">
         <v>143</v>
       </c>
       <c r="AD23" s="1">
-        <v>1631.824</v>
+        <v>1150.346</v>
       </c>
       <c r="AE23" s="1" t="s">
         <v>191</v>
@@ -6514,7 +6545,7 @@
         <v>216</v>
       </c>
       <c r="AD24" s="1">
-        <v>1.546</v>
+        <v>3.775</v>
       </c>
       <c r="AE24" s="1" t="s">
         <v>206</v>
@@ -6546,7 +6577,7 @@
         <v>218</v>
       </c>
       <c r="AD25" s="1">
-        <v>0.423</v>
+        <v>1.128</v>
       </c>
       <c r="AE25" s="1" t="s">
         <v>206</v>
@@ -6579,15 +6610,15 @@
       </c>
       <c r="J26" s="2">
         <f>IF(COUNT('Turns'!D94)=1,SUM('Turns'!D94),"Unknown")</f>
-        <v>328.0</v>
+        <v>300.0</v>
       </c>
       <c r="K26" s="2">
         <f>IF(COUNT('Turns'!E94)=1,SUM('Turns'!E94),"Unknown")</f>
-        <v>5.7227472e-05</v>
+        <v>5.2581e-05</v>
       </c>
       <c r="L26" s="2">
         <f>IF(COUNT('Turns'!F94)=1,SUM('Turns'!F94),"Unknown")</f>
-        <v>6.56e-05</v>
+        <v>6e-05</v>
       </c>
       <c r="M26" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -6612,15 +6643,15 @@
       </c>
       <c r="S26" s="2">
         <f>IF(COUNT('Turns'!D99)=1,SUM('Turns'!D99),"Unknown")</f>
-        <v>62.0</v>
+        <v>58.0</v>
       </c>
       <c r="T26" s="2">
         <f>IF(COUNT('Turns'!E99)=1,SUM('Turns'!E99),"Unknown")</f>
-        <v>6.4904328e-05</v>
+        <v>6.099396e-05</v>
       </c>
       <c r="U26" s="2">
         <f>IF(COUNT('Turns'!F99)=1,SUM('Turns'!F99),"Unknown")</f>
-        <v>7.44e-05</v>
+        <v>6.96e-05</v>
       </c>
       <c r="V26" s="2">
         <v>0</v>
@@ -6633,22 +6664,22 @@
       </c>
       <c r="Y26" s="2">
         <f>IF(COUNT('Turns'!E103)=1,SUM('Turns'!E103),"Unknown")</f>
-        <v>0.0001221318</v>
+        <v>0.00011357496</v>
       </c>
       <c r="Z26" s="2">
         <f>IF(COUNT('Turns'!F103)=1,SUM('Turns'!F103),"Unknown")</f>
-        <v>0.00014</v>
+        <v>0.0001296</v>
       </c>
       <c r="AA26" s="5">
         <f>IF(ISNUMBER(Y26),ROUND(Y26*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="AB26" s="5">
         <f>IF(ISNUMBER(Z26),ROUND(Z26*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="AD26" s="1">
-        <v>1355.38</v>
+        <v>1231.425</v>
       </c>
       <c r="AE26" s="1" t="s">
         <v>184</v>
@@ -6671,7 +6702,7 @@
         <v>110</v>
       </c>
       <c r="F27" s="1">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>190</v>
@@ -6684,15 +6715,15 @@
       </c>
       <c r="J27" s="2">
         <f>IF(COUNT('Turns'!D94)=1,SUM('Turns'!D94),"Unknown")</f>
-        <v>328.0</v>
+        <v>300.0</v>
       </c>
       <c r="K27" s="2">
         <f>IF(COUNT('Turns'!E94)=1,SUM('Turns'!E94),"Unknown")</f>
-        <v>5.7227472e-05</v>
+        <v>5.2581e-05</v>
       </c>
       <c r="L27" s="2">
         <f>IF(COUNT('Turns'!F94)=1,SUM('Turns'!F94),"Unknown")</f>
-        <v>6.56e-05</v>
+        <v>6e-05</v>
       </c>
       <c r="M27" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -6717,15 +6748,15 @@
       </c>
       <c r="S27" s="2">
         <f>IF(COUNT('Turns'!D99)=1,SUM('Turns'!D99),"Unknown")</f>
-        <v>62.0</v>
+        <v>58.0</v>
       </c>
       <c r="T27" s="2">
         <f>IF(COUNT('Turns'!E99)=1,SUM('Turns'!E99),"Unknown")</f>
-        <v>6.4904328e-05</v>
+        <v>6.099396e-05</v>
       </c>
       <c r="U27" s="2">
         <f>IF(COUNT('Turns'!F99)=1,SUM('Turns'!F99),"Unknown")</f>
-        <v>7.44e-05</v>
+        <v>6.96e-05</v>
       </c>
       <c r="V27" s="2">
         <v>0</v>
@@ -6738,25 +6769,25 @@
       </c>
       <c r="Y27" s="2">
         <f>IF(COUNT('Turns'!E103)=1,SUM('Turns'!E103),"Unknown")</f>
-        <v>0.0001221318</v>
+        <v>0.00011357496</v>
       </c>
       <c r="Z27" s="2">
         <f>IF(COUNT('Turns'!F103)=1,SUM('Turns'!F103),"Unknown")</f>
-        <v>0.00014</v>
+        <v>0.0001296</v>
       </c>
       <c r="AA27" s="5">
         <f>IF(ISNUMBER(Y27),ROUND(Y27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="AB27" s="5">
         <f>IF(ISNUMBER(Z27),ROUND(Z27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="AC27" s="1" t="s">
         <v>151</v>
       </c>
       <c r="AD27" s="1">
-        <v>1353.89</v>
+        <v>1229.024</v>
       </c>
       <c r="AE27" s="1" t="s">
         <v>191</v>
@@ -6789,15 +6820,15 @@
       </c>
       <c r="J28" s="2">
         <f>IF(COUNT('Turns'!D106)=1,SUM('Turns'!D106),"Unknown")</f>
-        <v>553.0</v>
+        <v>531.0</v>
       </c>
       <c r="K28" s="2">
         <f>IF(COUNT('Turns'!E106)=1,SUM('Turns'!E106),"Unknown")</f>
-        <v>9.6484122e-05</v>
+        <v>9.306837e-05</v>
       </c>
       <c r="L28" s="2">
         <f>IF(COUNT('Turns'!F106)=1,SUM('Turns'!F106),"Unknown")</f>
-        <v>0.0001106</v>
+        <v>0.0001062</v>
       </c>
       <c r="M28" s="2">
         <f>IF(COUNT('Turns'!D105)=1,SUM('Turns'!D105),"Unknown")</f>
@@ -6822,15 +6853,15 @@
       </c>
       <c r="S28" s="2">
         <f>IF(COUNT('Turns'!D111)=1,SUM('Turns'!D111),"Unknown")</f>
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="T28" s="2">
         <f>IF(COUNT('Turns'!E111)=1,SUM('Turns'!E111),"Unknown")</f>
-        <v>2.3030568e-05</v>
+        <v>2.418726e-05</v>
       </c>
       <c r="U28" s="2">
         <f>IF(COUNT('Turns'!F111)=1,SUM('Turns'!F111),"Unknown")</f>
-        <v>2.64e-05</v>
+        <v>2.76e-05</v>
       </c>
       <c r="V28" s="2">
         <v>0</v>
@@ -6843,11 +6874,11 @@
       </c>
       <c r="Y28" s="2">
         <f>IF(COUNT('Turns'!E115)=1,SUM('Turns'!E115),"Unknown")</f>
-        <v>0.00011951469</v>
+        <v>0.00011725563</v>
       </c>
       <c r="Z28" s="2">
         <f>IF(COUNT('Turns'!F115)=1,SUM('Turns'!F115),"Unknown")</f>
-        <v>0.000137</v>
+        <v>0.0001338</v>
       </c>
       <c r="AA28" s="5">
         <f>IF(ISNUMBER(Y28),ROUND(Y28*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6855,10 +6886,10 @@
       </c>
       <c r="AB28" s="5">
         <f>IF(ISNUMBER(Z28),ROUND(Z28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="AD28" s="1">
-        <v>1047.086</v>
+        <v>937.609</v>
       </c>
       <c r="AE28" s="1" t="s">
         <v>184</v>
@@ -6881,7 +6912,7 @@
         <v>110</v>
       </c>
       <c r="F29" s="1">
-        <v>553</v>
+        <v>531</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>190</v>
@@ -6894,15 +6925,15 @@
       </c>
       <c r="J29" s="2">
         <f>IF(COUNT('Turns'!D106)=1,SUM('Turns'!D106),"Unknown")</f>
-        <v>553.0</v>
+        <v>531.0</v>
       </c>
       <c r="K29" s="2">
         <f>IF(COUNT('Turns'!E106)=1,SUM('Turns'!E106),"Unknown")</f>
-        <v>9.6484122e-05</v>
+        <v>9.306837e-05</v>
       </c>
       <c r="L29" s="2">
         <f>IF(COUNT('Turns'!F106)=1,SUM('Turns'!F106),"Unknown")</f>
-        <v>0.0001106</v>
+        <v>0.0001062</v>
       </c>
       <c r="M29" s="2">
         <f>IF(COUNT('Turns'!D105)=1,SUM('Turns'!D105),"Unknown")</f>
@@ -6927,15 +6958,15 @@
       </c>
       <c r="S29" s="2">
         <f>IF(COUNT('Turns'!D111)=1,SUM('Turns'!D111),"Unknown")</f>
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="T29" s="2">
         <f>IF(COUNT('Turns'!E111)=1,SUM('Turns'!E111),"Unknown")</f>
-        <v>2.3030568e-05</v>
+        <v>2.418726e-05</v>
       </c>
       <c r="U29" s="2">
         <f>IF(COUNT('Turns'!F111)=1,SUM('Turns'!F111),"Unknown")</f>
-        <v>2.64e-05</v>
+        <v>2.76e-05</v>
       </c>
       <c r="V29" s="2">
         <v>0</v>
@@ -6948,11 +6979,11 @@
       </c>
       <c r="Y29" s="2">
         <f>IF(COUNT('Turns'!E115)=1,SUM('Turns'!E115),"Unknown")</f>
-        <v>0.00011951469</v>
+        <v>0.00011725563</v>
       </c>
       <c r="Z29" s="2">
         <f>IF(COUNT('Turns'!F115)=1,SUM('Turns'!F115),"Unknown")</f>
-        <v>0.000137</v>
+        <v>0.0001338</v>
       </c>
       <c r="AA29" s="5">
         <f>IF(ISNUMBER(Y29),ROUND(Y29*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6960,13 +6991,13 @@
       </c>
       <c r="AB29" s="5">
         <f>IF(ISNUMBER(Z29),ROUND(Z29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="AC29" s="1" t="s">
         <v>154</v>
       </c>
       <c r="AD29" s="1">
-        <v>1045.797</v>
+        <v>934.571</v>
       </c>
       <c r="AE29" s="1" t="s">
         <v>191</v>
@@ -6995,27 +7026,27 @@
         <v>223</v>
       </c>
       <c r="J30" s="2">
-        <f>IF(COUNT('Turns'!D119,'Turns'!D133,'Turns'!D149,'Turns'!D161)=4,SUM('Turns'!D119,'Turns'!D133,'Turns'!D149,'Turns'!D161),"Unknown")</f>
-        <v>1763.0</v>
+        <f>IF(COUNT('Turns'!D119,'Turns'!D133,'Turns'!D150,'Turns'!D162)=4,SUM('Turns'!D119,'Turns'!D133,'Turns'!D150,'Turns'!D162),"Unknown")</f>
+        <v>1728.0</v>
       </c>
       <c r="K30" s="2">
-        <f>IF(COUNT('Turns'!E119,'Turns'!E133,'Turns'!E149,'Turns'!E161)=4,SUM('Turns'!E119,'Turns'!E133,'Turns'!E149,'Turns'!E161),"Unknown")</f>
-        <v>0.000307597662</v>
+        <f>IF(COUNT('Turns'!E119,'Turns'!E133,'Turns'!E150,'Turns'!E162)=4,SUM('Turns'!E119,'Turns'!E133,'Turns'!E150,'Turns'!E162),"Unknown")</f>
+        <v>0.00030286656</v>
       </c>
       <c r="L30" s="2">
-        <f>IF(COUNT('Turns'!F119,'Turns'!F133,'Turns'!F149,'Turns'!F161)=4,SUM('Turns'!F119,'Turns'!F133,'Turns'!F149,'Turns'!F161),"Unknown")</f>
-        <v>0.0003526</v>
+        <f>IF(COUNT('Turns'!F119,'Turns'!F133,'Turns'!F150,'Turns'!F162)=4,SUM('Turns'!F119,'Turns'!F133,'Turns'!F150,'Turns'!F162),"Unknown")</f>
+        <v>0.0003456</v>
       </c>
       <c r="M30" s="2">
-        <f>IF(COUNT('Turns'!D118,'Turns'!D148,'Turns'!D160)=3,SUM('Turns'!D118,'Turns'!D148,'Turns'!D160),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D118,'Turns'!D149,'Turns'!D161)=3,SUM('Turns'!D118,'Turns'!D149,'Turns'!D161),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N30" s="2">
-        <f>IF(COUNT('Turns'!E118,'Turns'!E148,'Turns'!E160)=3,SUM('Turns'!E118,'Turns'!E148,'Turns'!E160),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E118,'Turns'!E149,'Turns'!E161)=3,SUM('Turns'!E118,'Turns'!E149,'Turns'!E161),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O30" s="2">
-        <f>IF(COUNT('Turns'!F118,'Turns'!F148,'Turns'!F160)=3,SUM('Turns'!F118,'Turns'!F148,'Turns'!F160),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F118,'Turns'!F149,'Turns'!F161)=3,SUM('Turns'!F118,'Turns'!F149,'Turns'!F161),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P30" s="2">
@@ -7028,44 +7059,47 @@
         <v>0</v>
       </c>
       <c r="S30" s="2">
-        <f>IF(COUNT('Turns'!D124,'Turns'!D139,'Turns'!D154,'Turns'!D166)=4,SUM('Turns'!D124,'Turns'!D139,'Turns'!D154,'Turns'!D166),"Unknown")</f>
-        <v>154.0</v>
+        <f>IF(COUNT('Turns'!D124,'Turns'!D140,'Turns'!D155,'Turns'!D167)=4,SUM('Turns'!D124,'Turns'!D140,'Turns'!D155,'Turns'!D167),"Unknown")</f>
+        <v>158.0</v>
       </c>
       <c r="T30" s="2">
-        <f>IF(COUNT('Turns'!E124,'Turns'!E139,'Turns'!E154,'Turns'!E166)=4,SUM('Turns'!E124,'Turns'!E139,'Turns'!E154,'Turns'!E166),"Unknown")</f>
-        <v>0.000161213976</v>
+        <f>IF(COUNT('Turns'!E124,'Turns'!E140,'Turns'!E155,'Turns'!E167)=4,SUM('Turns'!E124,'Turns'!E140,'Turns'!E155,'Turns'!E167),"Unknown")</f>
+        <v>0.00016615596</v>
       </c>
       <c r="U30" s="2">
-        <f>IF(COUNT('Turns'!F124,'Turns'!F139,'Turns'!F154,'Turns'!F166)=4,SUM('Turns'!F124,'Turns'!F139,'Turns'!F154,'Turns'!F166),"Unknown")</f>
-        <v>0.0001848</v>
+        <f>IF(COUNT('Turns'!F124,'Turns'!F140,'Turns'!F155,'Turns'!F167)=4,SUM('Turns'!F124,'Turns'!F140,'Turns'!F155,'Turns'!F167),"Unknown")</f>
+        <v>0.0001896</v>
       </c>
       <c r="V30" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D139)=1,SUM('Turns'!D139),"Unknown")</f>
+        <v>9.0</v>
       </c>
       <c r="W30" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E139)=1,SUM('Turns'!E139),"Unknown")</f>
+        <v>9.46458e-06</v>
       </c>
       <c r="X30" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F139)=1,SUM('Turns'!F139),"Unknown")</f>
+        <v>1.08e-05</v>
       </c>
       <c r="Y30" s="2">
-        <f>IF(COUNT('Turns'!E128,'Turns'!E143,'Turns'!E158,'Turns'!E170)=4,SUM('Turns'!E128,'Turns'!E143,'Turns'!E158,'Turns'!E170),"Unknown")</f>
-        <v>0.000468811638</v>
+        <f>IF(COUNT('Turns'!E128,'Turns'!E144,'Turns'!E159,'Turns'!E171)=4,SUM('Turns'!E128,'Turns'!E144,'Turns'!E159,'Turns'!E171),"Unknown")</f>
+        <v>0.0004784871</v>
       </c>
       <c r="Z30" s="2">
-        <f>IF(COUNT('Turns'!F128,'Turns'!F143,'Turns'!F158,'Turns'!F170)=4,SUM('Turns'!F128,'Turns'!F143,'Turns'!F158,'Turns'!F170),"Unknown")</f>
-        <v>0.0005374</v>
+        <f>IF(COUNT('Turns'!F128,'Turns'!F144,'Turns'!F159,'Turns'!F171)=4,SUM('Turns'!F128,'Turns'!F144,'Turns'!F159,'Turns'!F171),"Unknown")</f>
+        <v>0.000546</v>
       </c>
       <c r="AA30" s="5">
         <f>IF(ISNUMBER(Y30),ROUND(Y30*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="AB30" s="5">
         <f>IF(ISNUMBER(Z30),ROUND(Z30*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="AD30" s="1">
-        <v>6803.348</v>
+        <v>4756.339</v>
       </c>
       <c r="AE30" s="1" t="s">
         <v>184</v>
@@ -7098,15 +7132,15 @@
       </c>
       <c r="J31" s="2">
         <f>IF(COUNT('Turns'!D119)=1,SUM('Turns'!D119),"Unknown")</f>
-        <v>590.0</v>
+        <v>569.0</v>
       </c>
       <c r="K31" s="2">
         <f>IF(COUNT('Turns'!E119)=1,SUM('Turns'!E119),"Unknown")</f>
-        <v>0.00010293966</v>
+        <v>9.972863e-05</v>
       </c>
       <c r="L31" s="2">
         <f>IF(COUNT('Turns'!F119)=1,SUM('Turns'!F119),"Unknown")</f>
-        <v>0.000118</v>
+        <v>0.0001138</v>
       </c>
       <c r="M31" s="2">
         <f>IF(COUNT('Turns'!D118)=1,SUM('Turns'!D118),"Unknown")</f>
@@ -7131,15 +7165,15 @@
       </c>
       <c r="S31" s="2">
         <f>IF(COUNT('Turns'!D124)=1,SUM('Turns'!D124),"Unknown")</f>
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
       <c r="T31" s="2">
         <f>IF(COUNT('Turns'!E124)=1,SUM('Turns'!E124),"Unknown")</f>
-        <v>5.9670108e-05</v>
+        <v>5.678748e-05</v>
       </c>
       <c r="U31" s="2">
         <f>IF(COUNT('Turns'!F124)=1,SUM('Turns'!F124),"Unknown")</f>
-        <v>6.84e-05</v>
+        <v>6.48e-05</v>
       </c>
       <c r="V31" s="2">
         <v>0</v>
@@ -7152,11 +7186,11 @@
       </c>
       <c r="Y31" s="2">
         <f>IF(COUNT('Turns'!E128)=1,SUM('Turns'!E128),"Unknown")</f>
-        <v>0.000162609768</v>
+        <v>0.00015651611</v>
       </c>
       <c r="Z31" s="2">
         <f>IF(COUNT('Turns'!F128)=1,SUM('Turns'!F128),"Unknown")</f>
-        <v>0.0001864</v>
+        <v>0.0001786</v>
       </c>
       <c r="AA31" s="5">
         <f>IF(ISNUMBER(Y31),ROUND(Y31*'Reference data'!$B$2,0),"Unknown")</f>
@@ -7164,10 +7198,10 @@
       </c>
       <c r="AB31" s="5">
         <f>IF(ISNUMBER(Z31),ROUND(Z31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="AD31" s="1">
-        <v>2081.249</v>
+        <v>1106.929</v>
       </c>
       <c r="AE31" s="1" t="s">
         <v>184</v>
@@ -7190,7 +7224,7 @@
         <v>110</v>
       </c>
       <c r="F32" s="1">
-        <v>590</v>
+        <v>569</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>190</v>
@@ -7203,15 +7237,15 @@
       </c>
       <c r="J32" s="2">
         <f>IF(COUNT('Turns'!D119)=1,SUM('Turns'!D119),"Unknown")</f>
-        <v>590.0</v>
+        <v>569.0</v>
       </c>
       <c r="K32" s="2">
         <f>IF(COUNT('Turns'!E119)=1,SUM('Turns'!E119),"Unknown")</f>
-        <v>0.00010293966</v>
+        <v>9.972863e-05</v>
       </c>
       <c r="L32" s="2">
         <f>IF(COUNT('Turns'!F119)=1,SUM('Turns'!F119),"Unknown")</f>
-        <v>0.000118</v>
+        <v>0.0001138</v>
       </c>
       <c r="M32" s="2">
         <f>IF(COUNT('Turns'!D118)=1,SUM('Turns'!D118),"Unknown")</f>
@@ -7236,15 +7270,15 @@
       </c>
       <c r="S32" s="2">
         <f>IF(COUNT('Turns'!D124)=1,SUM('Turns'!D124),"Unknown")</f>
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
       <c r="T32" s="2">
         <f>IF(COUNT('Turns'!E124)=1,SUM('Turns'!E124),"Unknown")</f>
-        <v>5.9670108e-05</v>
+        <v>5.678748e-05</v>
       </c>
       <c r="U32" s="2">
         <f>IF(COUNT('Turns'!F124)=1,SUM('Turns'!F124),"Unknown")</f>
-        <v>6.84e-05</v>
+        <v>6.48e-05</v>
       </c>
       <c r="V32" s="2">
         <v>0</v>
@@ -7257,11 +7291,11 @@
       </c>
       <c r="Y32" s="2">
         <f>IF(COUNT('Turns'!E128)=1,SUM('Turns'!E128),"Unknown")</f>
-        <v>0.000162609768</v>
+        <v>0.00015651611</v>
       </c>
       <c r="Z32" s="2">
         <f>IF(COUNT('Turns'!F128)=1,SUM('Turns'!F128),"Unknown")</f>
-        <v>0.0001864</v>
+        <v>0.0001786</v>
       </c>
       <c r="AA32" s="5">
         <f>IF(ISNUMBER(Y32),ROUND(Y32*'Reference data'!$B$2,0),"Unknown")</f>
@@ -7269,13 +7303,13 @@
       </c>
       <c r="AB32" s="5">
         <f>IF(ISNUMBER(Z32),ROUND(Z32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="AC32" s="1" t="s">
         <v>159</v>
       </c>
       <c r="AD32" s="1">
-        <v>2079.88</v>
+        <v>1104.188</v>
       </c>
       <c r="AE32" s="1" t="s">
         <v>191</v>
@@ -7307,27 +7341,27 @@
         <v>223</v>
       </c>
       <c r="J33" s="2">
-        <f>IF(COUNT('Turns'!D133,'Turns'!D149)=2,SUM('Turns'!D133,'Turns'!D149),"Unknown")</f>
-        <v>474.0</v>
+        <f>IF(COUNT('Turns'!D133,'Turns'!D150)=2,SUM('Turns'!D133,'Turns'!D150),"Unknown")</f>
+        <v>482.0</v>
       </c>
       <c r="K33" s="2">
-        <f>IF(COUNT('Turns'!E133,'Turns'!E149)=2,SUM('Turns'!E133,'Turns'!E149),"Unknown")</f>
-        <v>8.2700676e-05</v>
+        <f>IF(COUNT('Turns'!E133,'Turns'!E150)=2,SUM('Turns'!E133,'Turns'!E150),"Unknown")</f>
+        <v>8.448014e-05</v>
       </c>
       <c r="L33" s="2">
-        <f>IF(COUNT('Turns'!F133,'Turns'!F149)=2,SUM('Turns'!F133,'Turns'!F149),"Unknown")</f>
-        <v>9.48e-05</v>
+        <f>IF(COUNT('Turns'!F133,'Turns'!F150)=2,SUM('Turns'!F133,'Turns'!F150),"Unknown")</f>
+        <v>9.64e-05</v>
       </c>
       <c r="M33" s="2">
-        <f>IF(COUNT('Turns'!D148)=1,SUM('Turns'!D148),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D149)=1,SUM('Turns'!D149),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N33" s="2">
-        <f>IF(COUNT('Turns'!E148)=1,SUM('Turns'!E148),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E149)=1,SUM('Turns'!E149),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O33" s="2">
-        <f>IF(COUNT('Turns'!F148)=1,SUM('Turns'!F148),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F149)=1,SUM('Turns'!F149),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P33" s="2">
@@ -7340,44 +7374,47 @@
         <v>0</v>
       </c>
       <c r="S33" s="2">
-        <f>IF(COUNT('Turns'!D139,'Turns'!D154)=2,SUM('Turns'!D139,'Turns'!D154),"Unknown")</f>
-        <v>77.0</v>
+        <f>IF(COUNT('Turns'!D140,'Turns'!D155)=2,SUM('Turns'!D140,'Turns'!D155),"Unknown")</f>
+        <v>84.0</v>
       </c>
       <c r="T33" s="2">
-        <f>IF(COUNT('Turns'!E139,'Turns'!E154)=2,SUM('Turns'!E139,'Turns'!E154),"Unknown")</f>
-        <v>8.0606988e-05</v>
+        <f>IF(COUNT('Turns'!E140,'Turns'!E155)=2,SUM('Turns'!E140,'Turns'!E155),"Unknown")</f>
+        <v>8.833608e-05</v>
       </c>
       <c r="U33" s="2">
-        <f>IF(COUNT('Turns'!F139,'Turns'!F154)=2,SUM('Turns'!F139,'Turns'!F154),"Unknown")</f>
-        <v>9.24e-05</v>
+        <f>IF(COUNT('Turns'!F140,'Turns'!F155)=2,SUM('Turns'!F140,'Turns'!F155),"Unknown")</f>
+        <v>0.0001008</v>
       </c>
       <c r="V33" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D139)=1,SUM('Turns'!D139),"Unknown")</f>
+        <v>9.0</v>
       </c>
       <c r="W33" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E139)=1,SUM('Turns'!E139),"Unknown")</f>
+        <v>9.46458e-06</v>
       </c>
       <c r="X33" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F139)=1,SUM('Turns'!F139),"Unknown")</f>
+        <v>1.08e-05</v>
       </c>
       <c r="Y33" s="2">
-        <f>IF(COUNT('Turns'!E143,'Turns'!E158)=2,SUM('Turns'!E143,'Turns'!E158),"Unknown")</f>
-        <v>0.000163307664</v>
+        <f>IF(COUNT('Turns'!E144,'Turns'!E159)=2,SUM('Turns'!E144,'Turns'!E159),"Unknown")</f>
+        <v>0.0001822808</v>
       </c>
       <c r="Z33" s="2">
-        <f>IF(COUNT('Turns'!F143,'Turns'!F158)=2,SUM('Turns'!F143,'Turns'!F158),"Unknown")</f>
-        <v>0.0001872</v>
+        <f>IF(COUNT('Turns'!F144,'Turns'!F159)=2,SUM('Turns'!F144,'Turns'!F159),"Unknown")</f>
+        <v>0.000208</v>
       </c>
       <c r="AA33" s="5">
         <f>IF(ISNUMBER(Y33),ROUND(Y33*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="AB33" s="5">
         <f>IF(ISNUMBER(Z33),ROUND(Z33*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="AD33" s="1">
-        <v>2838.329</v>
+        <v>2809.288</v>
       </c>
       <c r="AE33" s="1" t="s">
         <v>184</v>
@@ -7409,27 +7446,27 @@
         <v>225</v>
       </c>
       <c r="J34" s="2">
-        <f>IF(COUNT('Turns'!D133,'Turns'!D149)=2,SUM('Turns'!D133,'Turns'!D149),"Unknown")</f>
-        <v>474.0</v>
+        <f>IF(COUNT('Turns'!D133,'Turns'!D150)=2,SUM('Turns'!D133,'Turns'!D150),"Unknown")</f>
+        <v>482.0</v>
       </c>
       <c r="K34" s="2">
-        <f>IF(COUNT('Turns'!E133,'Turns'!E149)=2,SUM('Turns'!E133,'Turns'!E149),"Unknown")</f>
-        <v>8.2700676e-05</v>
+        <f>IF(COUNT('Turns'!E133,'Turns'!E150)=2,SUM('Turns'!E133,'Turns'!E150),"Unknown")</f>
+        <v>8.448014e-05</v>
       </c>
       <c r="L34" s="2">
-        <f>IF(COUNT('Turns'!F133,'Turns'!F149)=2,SUM('Turns'!F133,'Turns'!F149),"Unknown")</f>
-        <v>9.48e-05</v>
+        <f>IF(COUNT('Turns'!F133,'Turns'!F150)=2,SUM('Turns'!F133,'Turns'!F150),"Unknown")</f>
+        <v>9.64e-05</v>
       </c>
       <c r="M34" s="2">
-        <f>IF(COUNT('Turns'!D148)=1,SUM('Turns'!D148),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D149)=1,SUM('Turns'!D149),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N34" s="2">
-        <f>IF(COUNT('Turns'!E148)=1,SUM('Turns'!E148),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E149)=1,SUM('Turns'!E149),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O34" s="2">
-        <f>IF(COUNT('Turns'!F148)=1,SUM('Turns'!F148),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F149)=1,SUM('Turns'!F149),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P34" s="2">
@@ -7442,44 +7479,47 @@
         <v>0</v>
       </c>
       <c r="S34" s="2">
-        <f>IF(COUNT('Turns'!D139,'Turns'!D154)=2,SUM('Turns'!D139,'Turns'!D154),"Unknown")</f>
-        <v>77.0</v>
+        <f>IF(COUNT('Turns'!D140,'Turns'!D155)=2,SUM('Turns'!D140,'Turns'!D155),"Unknown")</f>
+        <v>84.0</v>
       </c>
       <c r="T34" s="2">
-        <f>IF(COUNT('Turns'!E139,'Turns'!E154)=2,SUM('Turns'!E139,'Turns'!E154),"Unknown")</f>
-        <v>8.0606988e-05</v>
+        <f>IF(COUNT('Turns'!E140,'Turns'!E155)=2,SUM('Turns'!E140,'Turns'!E155),"Unknown")</f>
+        <v>8.833608e-05</v>
       </c>
       <c r="U34" s="2">
-        <f>IF(COUNT('Turns'!F139,'Turns'!F154)=2,SUM('Turns'!F139,'Turns'!F154),"Unknown")</f>
-        <v>9.24e-05</v>
+        <f>IF(COUNT('Turns'!F140,'Turns'!F155)=2,SUM('Turns'!F140,'Turns'!F155),"Unknown")</f>
+        <v>0.0001008</v>
       </c>
       <c r="V34" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D139)=1,SUM('Turns'!D139),"Unknown")</f>
+        <v>9.0</v>
       </c>
       <c r="W34" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E139)=1,SUM('Turns'!E139),"Unknown")</f>
+        <v>9.46458e-06</v>
       </c>
       <c r="X34" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F139)=1,SUM('Turns'!F139),"Unknown")</f>
+        <v>1.08e-05</v>
       </c>
       <c r="Y34" s="2">
-        <f>IF(COUNT('Turns'!E143,'Turns'!E158)=2,SUM('Turns'!E143,'Turns'!E158),"Unknown")</f>
-        <v>0.000163307664</v>
+        <f>IF(COUNT('Turns'!E144,'Turns'!E159)=2,SUM('Turns'!E144,'Turns'!E159),"Unknown")</f>
+        <v>0.0001822808</v>
       </c>
       <c r="Z34" s="2">
-        <f>IF(COUNT('Turns'!F143,'Turns'!F158)=2,SUM('Turns'!F143,'Turns'!F158),"Unknown")</f>
-        <v>0.0001872</v>
+        <f>IF(COUNT('Turns'!F144,'Turns'!F159)=2,SUM('Turns'!F144,'Turns'!F159),"Unknown")</f>
+        <v>0.000208</v>
       </c>
       <c r="AA34" s="5">
         <f>IF(ISNUMBER(Y34),ROUND(Y34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="AB34" s="5">
         <f>IF(ISNUMBER(Z34),ROUND(Z34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="AD34" s="1">
-        <v>2837.225</v>
+        <v>2807.139</v>
       </c>
       <c r="AE34" s="1" t="s">
         <v>184</v>
@@ -7511,27 +7551,27 @@
         <v>163</v>
       </c>
       <c r="J35" s="2">
-        <f>IF(COUNT('Turns'!D133,'Turns'!D149)=2,SUM('Turns'!D133,'Turns'!D149),"Unknown")</f>
-        <v>474.0</v>
+        <f>IF(COUNT('Turns'!D133,'Turns'!D150)=2,SUM('Turns'!D133,'Turns'!D150),"Unknown")</f>
+        <v>482.0</v>
       </c>
       <c r="K35" s="2">
-        <f>IF(COUNT('Turns'!E133,'Turns'!E149)=2,SUM('Turns'!E133,'Turns'!E149),"Unknown")</f>
-        <v>8.2700676e-05</v>
+        <f>IF(COUNT('Turns'!E133,'Turns'!E150)=2,SUM('Turns'!E133,'Turns'!E150),"Unknown")</f>
+        <v>8.448014e-05</v>
       </c>
       <c r="L35" s="2">
-        <f>IF(COUNT('Turns'!F133,'Turns'!F149)=2,SUM('Turns'!F133,'Turns'!F149),"Unknown")</f>
-        <v>9.48e-05</v>
+        <f>IF(COUNT('Turns'!F133,'Turns'!F150)=2,SUM('Turns'!F133,'Turns'!F150),"Unknown")</f>
+        <v>9.64e-05</v>
       </c>
       <c r="M35" s="2">
-        <f>IF(COUNT('Turns'!D148)=1,SUM('Turns'!D148),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D149)=1,SUM('Turns'!D149),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N35" s="2">
-        <f>IF(COUNT('Turns'!E148)=1,SUM('Turns'!E148),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E149)=1,SUM('Turns'!E149),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O35" s="2">
-        <f>IF(COUNT('Turns'!F148)=1,SUM('Turns'!F148),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F149)=1,SUM('Turns'!F149),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P35" s="2">
@@ -7544,44 +7584,47 @@
         <v>0</v>
       </c>
       <c r="S35" s="2">
-        <f>IF(COUNT('Turns'!D139,'Turns'!D154)=2,SUM('Turns'!D139,'Turns'!D154),"Unknown")</f>
-        <v>77.0</v>
+        <f>IF(COUNT('Turns'!D140,'Turns'!D155)=2,SUM('Turns'!D140,'Turns'!D155),"Unknown")</f>
+        <v>84.0</v>
       </c>
       <c r="T35" s="2">
-        <f>IF(COUNT('Turns'!E139,'Turns'!E154)=2,SUM('Turns'!E139,'Turns'!E154),"Unknown")</f>
-        <v>8.0606988e-05</v>
+        <f>IF(COUNT('Turns'!E140,'Turns'!E155)=2,SUM('Turns'!E140,'Turns'!E155),"Unknown")</f>
+        <v>8.833608e-05</v>
       </c>
       <c r="U35" s="2">
-        <f>IF(COUNT('Turns'!F139,'Turns'!F154)=2,SUM('Turns'!F139,'Turns'!F154),"Unknown")</f>
-        <v>9.24e-05</v>
+        <f>IF(COUNT('Turns'!F140,'Turns'!F155)=2,SUM('Turns'!F140,'Turns'!F155),"Unknown")</f>
+        <v>0.0001008</v>
       </c>
       <c r="V35" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D139)=1,SUM('Turns'!D139),"Unknown")</f>
+        <v>9.0</v>
       </c>
       <c r="W35" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E139)=1,SUM('Turns'!E139),"Unknown")</f>
+        <v>9.46458e-06</v>
       </c>
       <c r="X35" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F139)=1,SUM('Turns'!F139),"Unknown")</f>
+        <v>1.08e-05</v>
       </c>
       <c r="Y35" s="2">
-        <f>IF(COUNT('Turns'!E143,'Turns'!E158)=2,SUM('Turns'!E143,'Turns'!E158),"Unknown")</f>
-        <v>0.000163307664</v>
+        <f>IF(COUNT('Turns'!E144,'Turns'!E159)=2,SUM('Turns'!E144,'Turns'!E159),"Unknown")</f>
+        <v>0.0001822808</v>
       </c>
       <c r="Z35" s="2">
-        <f>IF(COUNT('Turns'!F143,'Turns'!F158)=2,SUM('Turns'!F143,'Turns'!F158),"Unknown")</f>
-        <v>0.0001872</v>
+        <f>IF(COUNT('Turns'!F144,'Turns'!F159)=2,SUM('Turns'!F144,'Turns'!F159),"Unknown")</f>
+        <v>0.000208</v>
       </c>
       <c r="AA35" s="5">
         <f>IF(ISNUMBER(Y35),ROUND(Y35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="AB35" s="5">
         <f>IF(ISNUMBER(Z35),ROUND(Z35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="AD35" s="1">
-        <v>2836.27</v>
+        <v>2805.076</v>
       </c>
       <c r="AE35" s="1" t="s">
         <v>184</v>
@@ -7614,15 +7657,15 @@
       </c>
       <c r="J36" s="2">
         <f>IF(COUNT('Turns'!D133)=1,SUM('Turns'!D133),"Unknown")</f>
-        <v>189.0</v>
+        <v>186.0</v>
       </c>
       <c r="K36" s="2">
         <f>IF(COUNT('Turns'!E133)=1,SUM('Turns'!E133),"Unknown")</f>
-        <v>3.2975586e-05</v>
+        <v>3.260022e-05</v>
       </c>
       <c r="L36" s="2">
         <f>IF(COUNT('Turns'!F133)=1,SUM('Turns'!F133),"Unknown")</f>
-        <v>3.78e-05</v>
+        <v>3.72e-05</v>
       </c>
       <c r="M36" s="2">
         <v>0</v>
@@ -7643,44 +7686,47 @@
         <v>0</v>
       </c>
       <c r="S36" s="2">
+        <f>IF(COUNT('Turns'!D140)=1,SUM('Turns'!D140),"Unknown")</f>
+        <v>36.0</v>
+      </c>
+      <c r="T36" s="2">
+        <f>IF(COUNT('Turns'!E140)=1,SUM('Turns'!E140),"Unknown")</f>
+        <v>3.785832e-05</v>
+      </c>
+      <c r="U36" s="2">
+        <f>IF(COUNT('Turns'!F140)=1,SUM('Turns'!F140),"Unknown")</f>
+        <v>4.32e-05</v>
+      </c>
+      <c r="V36" s="2">
         <f>IF(COUNT('Turns'!D139)=1,SUM('Turns'!D139),"Unknown")</f>
-        <v>31.0</v>
-      </c>
-      <c r="T36" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="W36" s="2">
         <f>IF(COUNT('Turns'!E139)=1,SUM('Turns'!E139),"Unknown")</f>
-        <v>3.2452164e-05</v>
-      </c>
-      <c r="U36" s="2">
+        <v>9.46458e-06</v>
+      </c>
+      <c r="X36" s="2">
         <f>IF(COUNT('Turns'!F139)=1,SUM('Turns'!F139),"Unknown")</f>
-        <v>3.72e-05</v>
-      </c>
-      <c r="V36" s="2">
-        <v>0</v>
-      </c>
-      <c r="W36" s="2">
-        <v>0</v>
-      </c>
-      <c r="X36" s="2">
-        <v>0</v>
+        <v>1.08e-05</v>
       </c>
       <c r="Y36" s="2">
-        <f>IF(COUNT('Turns'!E143)=1,SUM('Turns'!E143),"Unknown")</f>
-        <v>6.542775e-05</v>
+        <f>IF(COUNT('Turns'!E144)=1,SUM('Turns'!E144),"Unknown")</f>
+        <v>7.992312e-05</v>
       </c>
       <c r="Z36" s="2">
-        <f>IF(COUNT('Turns'!F143)=1,SUM('Turns'!F143),"Unknown")</f>
-        <v>7.5e-05</v>
+        <f>IF(COUNT('Turns'!F144)=1,SUM('Turns'!F144),"Unknown")</f>
+        <v>9.12e-05</v>
       </c>
       <c r="AA36" s="5">
         <f>IF(ISNUMBER(Y36),ROUND(Y36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="AB36" s="5">
         <f>IF(ISNUMBER(Z36),ROUND(Z36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="AD36" s="1">
-        <v>1329.595</v>
+        <v>1523.87</v>
       </c>
       <c r="AE36" s="1" t="s">
         <v>184</v>
@@ -7703,7 +7749,7 @@
         <v>110</v>
       </c>
       <c r="F37" s="1">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>190</v>
@@ -7716,15 +7762,15 @@
       </c>
       <c r="J37" s="2">
         <f>IF(COUNT('Turns'!D133)=1,SUM('Turns'!D133),"Unknown")</f>
-        <v>189.0</v>
+        <v>186.0</v>
       </c>
       <c r="K37" s="2">
         <f>IF(COUNT('Turns'!E133)=1,SUM('Turns'!E133),"Unknown")</f>
-        <v>3.2975586e-05</v>
+        <v>3.260022e-05</v>
       </c>
       <c r="L37" s="2">
         <f>IF(COUNT('Turns'!F133)=1,SUM('Turns'!F133),"Unknown")</f>
-        <v>3.78e-05</v>
+        <v>3.72e-05</v>
       </c>
       <c r="M37" s="2">
         <v>0</v>
@@ -7745,47 +7791,50 @@
         <v>0</v>
       </c>
       <c r="S37" s="2">
+        <f>IF(COUNT('Turns'!D140)=1,SUM('Turns'!D140),"Unknown")</f>
+        <v>36.0</v>
+      </c>
+      <c r="T37" s="2">
+        <f>IF(COUNT('Turns'!E140)=1,SUM('Turns'!E140),"Unknown")</f>
+        <v>3.785832e-05</v>
+      </c>
+      <c r="U37" s="2">
+        <f>IF(COUNT('Turns'!F140)=1,SUM('Turns'!F140),"Unknown")</f>
+        <v>4.32e-05</v>
+      </c>
+      <c r="V37" s="2">
         <f>IF(COUNT('Turns'!D139)=1,SUM('Turns'!D139),"Unknown")</f>
-        <v>31.0</v>
-      </c>
-      <c r="T37" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="W37" s="2">
         <f>IF(COUNT('Turns'!E139)=1,SUM('Turns'!E139),"Unknown")</f>
-        <v>3.2452164e-05</v>
-      </c>
-      <c r="U37" s="2">
+        <v>9.46458e-06</v>
+      </c>
+      <c r="X37" s="2">
         <f>IF(COUNT('Turns'!F139)=1,SUM('Turns'!F139),"Unknown")</f>
-        <v>3.72e-05</v>
-      </c>
-      <c r="V37" s="2">
-        <v>0</v>
-      </c>
-      <c r="W37" s="2">
-        <v>0</v>
-      </c>
-      <c r="X37" s="2">
-        <v>0</v>
+        <v>1.08e-05</v>
       </c>
       <c r="Y37" s="2">
-        <f>IF(COUNT('Turns'!E143)=1,SUM('Turns'!E143),"Unknown")</f>
-        <v>6.542775e-05</v>
+        <f>IF(COUNT('Turns'!E144)=1,SUM('Turns'!E144),"Unknown")</f>
+        <v>7.992312e-05</v>
       </c>
       <c r="Z37" s="2">
-        <f>IF(COUNT('Turns'!F143)=1,SUM('Turns'!F143),"Unknown")</f>
-        <v>7.5e-05</v>
+        <f>IF(COUNT('Turns'!F144)=1,SUM('Turns'!F144),"Unknown")</f>
+        <v>9.12e-05</v>
       </c>
       <c r="AA37" s="5">
         <f>IF(ISNUMBER(Y37),ROUND(Y37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="AB37" s="5">
         <f>IF(ISNUMBER(Z37),ROUND(Z37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="AC37" s="1" t="s">
         <v>166</v>
       </c>
       <c r="AD37" s="1">
-        <v>1326.951</v>
+        <v>1519.66</v>
       </c>
       <c r="AE37" s="1" t="s">
         <v>191</v>
@@ -7817,7 +7866,7 @@
         <v>228</v>
       </c>
       <c r="AD38" s="1">
-        <v>1.558</v>
+        <v>3.392</v>
       </c>
       <c r="AE38" s="1" t="s">
         <v>206</v>
@@ -7849,7 +7898,7 @@
         <v>230</v>
       </c>
       <c r="AD39" s="1">
-        <v>0.506</v>
+        <v>1.148</v>
       </c>
       <c r="AE39" s="1" t="s">
         <v>206</v>
@@ -7881,27 +7930,27 @@
         <v>228</v>
       </c>
       <c r="J40" s="2">
+        <f>IF(COUNT('Turns'!D150)=1,SUM('Turns'!D150),"Unknown")</f>
+        <v>296.0</v>
+      </c>
+      <c r="K40" s="2">
+        <f>IF(COUNT('Turns'!E150)=1,SUM('Turns'!E150),"Unknown")</f>
+        <v>5.187992e-05</v>
+      </c>
+      <c r="L40" s="2">
+        <f>IF(COUNT('Turns'!F150)=1,SUM('Turns'!F150),"Unknown")</f>
+        <v>5.92e-05</v>
+      </c>
+      <c r="M40" s="2">
         <f>IF(COUNT('Turns'!D149)=1,SUM('Turns'!D149),"Unknown")</f>
-        <v>285.0</v>
-      </c>
-      <c r="K40" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N40" s="2">
         <f>IF(COUNT('Turns'!E149)=1,SUM('Turns'!E149),"Unknown")</f>
-        <v>4.972509e-05</v>
-      </c>
-      <c r="L40" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="O40" s="2">
         <f>IF(COUNT('Turns'!F149)=1,SUM('Turns'!F149),"Unknown")</f>
-        <v>5.7e-05</v>
-      </c>
-      <c r="M40" s="2">
-        <f>IF(COUNT('Turns'!D148)=1,SUM('Turns'!D148),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="N40" s="2">
-        <f>IF(COUNT('Turns'!E148)=1,SUM('Turns'!E148),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="O40" s="2">
-        <f>IF(COUNT('Turns'!F148)=1,SUM('Turns'!F148),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P40" s="2">
@@ -7914,16 +7963,16 @@
         <v>0</v>
       </c>
       <c r="S40" s="2">
-        <f>IF(COUNT('Turns'!D154)=1,SUM('Turns'!D154),"Unknown")</f>
-        <v>46.0</v>
+        <f>IF(COUNT('Turns'!D155)=1,SUM('Turns'!D155),"Unknown")</f>
+        <v>48.0</v>
       </c>
       <c r="T40" s="2">
-        <f>IF(COUNT('Turns'!E154)=1,SUM('Turns'!E154),"Unknown")</f>
-        <v>4.8154824e-05</v>
+        <f>IF(COUNT('Turns'!E155)=1,SUM('Turns'!E155),"Unknown")</f>
+        <v>5.047776e-05</v>
       </c>
       <c r="U40" s="2">
-        <f>IF(COUNT('Turns'!F154)=1,SUM('Turns'!F154),"Unknown")</f>
-        <v>5.52e-05</v>
+        <f>IF(COUNT('Turns'!F155)=1,SUM('Turns'!F155),"Unknown")</f>
+        <v>5.76e-05</v>
       </c>
       <c r="V40" s="2">
         <v>0</v>
@@ -7935,12 +7984,12 @@
         <v>0</v>
       </c>
       <c r="Y40" s="2">
-        <f>IF(COUNT('Turns'!E158)=1,SUM('Turns'!E158),"Unknown")</f>
-        <v>9.7879914e-05</v>
+        <f>IF(COUNT('Turns'!E159)=1,SUM('Turns'!E159),"Unknown")</f>
+        <v>0.00010235768</v>
       </c>
       <c r="Z40" s="2">
-        <f>IF(COUNT('Turns'!F158)=1,SUM('Turns'!F158),"Unknown")</f>
-        <v>0.0001122</v>
+        <f>IF(COUNT('Turns'!F159)=1,SUM('Turns'!F159),"Unknown")</f>
+        <v>0.0001168</v>
       </c>
       <c r="AA40" s="5">
         <f>IF(ISNUMBER(Y40),ROUND(Y40*'Reference data'!$B$2,0),"Unknown")</f>
@@ -7948,10 +7997,10 @@
       </c>
       <c r="AB40" s="5">
         <f>IF(ISNUMBER(Z40),ROUND(Z40*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="AD40" s="1">
-        <v>1502.267</v>
+        <v>1272.585</v>
       </c>
       <c r="AE40" s="1" t="s">
         <v>184</v>
@@ -7974,7 +8023,7 @@
         <v>110</v>
       </c>
       <c r="F41" s="1">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>190</v>
@@ -7986,27 +8035,27 @@
         <v>233</v>
       </c>
       <c r="J41" s="2">
+        <f>IF(COUNT('Turns'!D150)=1,SUM('Turns'!D150),"Unknown")</f>
+        <v>296.0</v>
+      </c>
+      <c r="K41" s="2">
+        <f>IF(COUNT('Turns'!E150)=1,SUM('Turns'!E150),"Unknown")</f>
+        <v>5.187992e-05</v>
+      </c>
+      <c r="L41" s="2">
+        <f>IF(COUNT('Turns'!F150)=1,SUM('Turns'!F150),"Unknown")</f>
+        <v>5.92e-05</v>
+      </c>
+      <c r="M41" s="2">
         <f>IF(COUNT('Turns'!D149)=1,SUM('Turns'!D149),"Unknown")</f>
-        <v>285.0</v>
-      </c>
-      <c r="K41" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N41" s="2">
         <f>IF(COUNT('Turns'!E149)=1,SUM('Turns'!E149),"Unknown")</f>
-        <v>4.972509e-05</v>
-      </c>
-      <c r="L41" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="O41" s="2">
         <f>IF(COUNT('Turns'!F149)=1,SUM('Turns'!F149),"Unknown")</f>
-        <v>5.7e-05</v>
-      </c>
-      <c r="M41" s="2">
-        <f>IF(COUNT('Turns'!D148)=1,SUM('Turns'!D148),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="N41" s="2">
-        <f>IF(COUNT('Turns'!E148)=1,SUM('Turns'!E148),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="O41" s="2">
-        <f>IF(COUNT('Turns'!F148)=1,SUM('Turns'!F148),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P41" s="2">
@@ -8019,16 +8068,16 @@
         <v>0</v>
       </c>
       <c r="S41" s="2">
-        <f>IF(COUNT('Turns'!D154)=1,SUM('Turns'!D154),"Unknown")</f>
-        <v>46.0</v>
+        <f>IF(COUNT('Turns'!D155)=1,SUM('Turns'!D155),"Unknown")</f>
+        <v>48.0</v>
       </c>
       <c r="T41" s="2">
-        <f>IF(COUNT('Turns'!E154)=1,SUM('Turns'!E154),"Unknown")</f>
-        <v>4.8154824e-05</v>
+        <f>IF(COUNT('Turns'!E155)=1,SUM('Turns'!E155),"Unknown")</f>
+        <v>5.047776e-05</v>
       </c>
       <c r="U41" s="2">
-        <f>IF(COUNT('Turns'!F154)=1,SUM('Turns'!F154),"Unknown")</f>
-        <v>5.52e-05</v>
+        <f>IF(COUNT('Turns'!F155)=1,SUM('Turns'!F155),"Unknown")</f>
+        <v>5.76e-05</v>
       </c>
       <c r="V41" s="2">
         <v>0</v>
@@ -8040,12 +8089,12 @@
         <v>0</v>
       </c>
       <c r="Y41" s="2">
-        <f>IF(COUNT('Turns'!E158)=1,SUM('Turns'!E158),"Unknown")</f>
-        <v>9.7879914e-05</v>
+        <f>IF(COUNT('Turns'!E159)=1,SUM('Turns'!E159),"Unknown")</f>
+        <v>0.00010235768</v>
       </c>
       <c r="Z41" s="2">
-        <f>IF(COUNT('Turns'!F158)=1,SUM('Turns'!F158),"Unknown")</f>
-        <v>0.0001122</v>
+        <f>IF(COUNT('Turns'!F159)=1,SUM('Turns'!F159),"Unknown")</f>
+        <v>0.0001168</v>
       </c>
       <c r="AA41" s="5">
         <f>IF(ISNUMBER(Y41),ROUND(Y41*'Reference data'!$B$2,0),"Unknown")</f>
@@ -8053,13 +8102,13 @@
       </c>
       <c r="AB41" s="5">
         <f>IF(ISNUMBER(Z41),ROUND(Z41*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="AC41" s="1" t="s">
         <v>174</v>
       </c>
       <c r="AD41" s="1">
-        <v>1501.046</v>
+        <v>1270.302</v>
       </c>
       <c r="AE41" s="1" t="s">
         <v>191</v>
@@ -8091,27 +8140,27 @@
         <v>223</v>
       </c>
       <c r="J42" s="2">
+        <f>IF(COUNT('Turns'!D162)=1,SUM('Turns'!D162),"Unknown")</f>
+        <v>677.0</v>
+      </c>
+      <c r="K42" s="2">
+        <f>IF(COUNT('Turns'!E162)=1,SUM('Turns'!E162),"Unknown")</f>
+        <v>0.00011865779</v>
+      </c>
+      <c r="L42" s="2">
+        <f>IF(COUNT('Turns'!F162)=1,SUM('Turns'!F162),"Unknown")</f>
+        <v>0.0001354</v>
+      </c>
+      <c r="M42" s="2">
         <f>IF(COUNT('Turns'!D161)=1,SUM('Turns'!D161),"Unknown")</f>
-        <v>699.0</v>
-      </c>
-      <c r="K42" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N42" s="2">
         <f>IF(COUNT('Turns'!E161)=1,SUM('Turns'!E161),"Unknown")</f>
-        <v>0.000121957326</v>
-      </c>
-      <c r="L42" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="O42" s="2">
         <f>IF(COUNT('Turns'!F161)=1,SUM('Turns'!F161),"Unknown")</f>
-        <v>0.0001398</v>
-      </c>
-      <c r="M42" s="2">
-        <f>IF(COUNT('Turns'!D160)=1,SUM('Turns'!D160),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="N42" s="2">
-        <f>IF(COUNT('Turns'!E160)=1,SUM('Turns'!E160),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="O42" s="2">
-        <f>IF(COUNT('Turns'!F160)=1,SUM('Turns'!F160),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P42" s="2">
@@ -8124,15 +8173,15 @@
         <v>0</v>
       </c>
       <c r="S42" s="2">
-        <f>IF(COUNT('Turns'!D166)=1,SUM('Turns'!D166),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D167)=1,SUM('Turns'!D167),"Unknown")</f>
         <v>20.0</v>
       </c>
       <c r="T42" s="2">
-        <f>IF(COUNT('Turns'!E166)=1,SUM('Turns'!E166),"Unknown")</f>
-        <v>2.093688e-05</v>
+        <f>IF(COUNT('Turns'!E167)=1,SUM('Turns'!E167),"Unknown")</f>
+        <v>2.10324e-05</v>
       </c>
       <c r="U42" s="2">
-        <f>IF(COUNT('Turns'!F166)=1,SUM('Turns'!F166),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F167)=1,SUM('Turns'!F167),"Unknown")</f>
         <v>2.4e-05</v>
       </c>
       <c r="V42" s="2">
@@ -8145,12 +8194,12 @@
         <v>0</v>
       </c>
       <c r="Y42" s="2">
-        <f>IF(COUNT('Turns'!E170)=1,SUM('Turns'!E170),"Unknown")</f>
-        <v>0.000142894206</v>
+        <f>IF(COUNT('Turns'!E171)=1,SUM('Turns'!E171),"Unknown")</f>
+        <v>0.00013969019</v>
       </c>
       <c r="Z42" s="2">
-        <f>IF(COUNT('Turns'!F170)=1,SUM('Turns'!F170),"Unknown")</f>
-        <v>0.0001638</v>
+        <f>IF(COUNT('Turns'!F171)=1,SUM('Turns'!F171),"Unknown")</f>
+        <v>0.0001594</v>
       </c>
       <c r="AA42" s="5">
         <f>IF(ISNUMBER(Y42),ROUND(Y42*'Reference data'!$B$2,0),"Unknown")</f>
@@ -8161,7 +8210,7 @@
         <v>16.0</v>
       </c>
       <c r="AD42" s="1">
-        <v>1880.139</v>
+        <v>832.677</v>
       </c>
       <c r="AE42" s="1" t="s">
         <v>184</v>
@@ -8184,7 +8233,7 @@
         <v>110</v>
       </c>
       <c r="F43" s="1">
-        <v>699</v>
+        <v>677</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>190</v>
@@ -8196,27 +8245,27 @@
         <v>234</v>
       </c>
       <c r="J43" s="2">
+        <f>IF(COUNT('Turns'!D162)=1,SUM('Turns'!D162),"Unknown")</f>
+        <v>677.0</v>
+      </c>
+      <c r="K43" s="2">
+        <f>IF(COUNT('Turns'!E162)=1,SUM('Turns'!E162),"Unknown")</f>
+        <v>0.00011865779</v>
+      </c>
+      <c r="L43" s="2">
+        <f>IF(COUNT('Turns'!F162)=1,SUM('Turns'!F162),"Unknown")</f>
+        <v>0.0001354</v>
+      </c>
+      <c r="M43" s="2">
         <f>IF(COUNT('Turns'!D161)=1,SUM('Turns'!D161),"Unknown")</f>
-        <v>699.0</v>
-      </c>
-      <c r="K43" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N43" s="2">
         <f>IF(COUNT('Turns'!E161)=1,SUM('Turns'!E161),"Unknown")</f>
-        <v>0.000121957326</v>
-      </c>
-      <c r="L43" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="O43" s="2">
         <f>IF(COUNT('Turns'!F161)=1,SUM('Turns'!F161),"Unknown")</f>
-        <v>0.0001398</v>
-      </c>
-      <c r="M43" s="2">
-        <f>IF(COUNT('Turns'!D160)=1,SUM('Turns'!D160),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="N43" s="2">
-        <f>IF(COUNT('Turns'!E160)=1,SUM('Turns'!E160),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="O43" s="2">
-        <f>IF(COUNT('Turns'!F160)=1,SUM('Turns'!F160),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P43" s="2">
@@ -8229,15 +8278,15 @@
         <v>0</v>
       </c>
       <c r="S43" s="2">
-        <f>IF(COUNT('Turns'!D166)=1,SUM('Turns'!D166),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D167)=1,SUM('Turns'!D167),"Unknown")</f>
         <v>20.0</v>
       </c>
       <c r="T43" s="2">
-        <f>IF(COUNT('Turns'!E166)=1,SUM('Turns'!E166),"Unknown")</f>
-        <v>2.093688e-05</v>
+        <f>IF(COUNT('Turns'!E167)=1,SUM('Turns'!E167),"Unknown")</f>
+        <v>2.10324e-05</v>
       </c>
       <c r="U43" s="2">
-        <f>IF(COUNT('Turns'!F166)=1,SUM('Turns'!F166),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F167)=1,SUM('Turns'!F167),"Unknown")</f>
         <v>2.4e-05</v>
       </c>
       <c r="V43" s="2">
@@ -8250,12 +8299,12 @@
         <v>0</v>
       </c>
       <c r="Y43" s="2">
-        <f>IF(COUNT('Turns'!E170)=1,SUM('Turns'!E170),"Unknown")</f>
-        <v>0.000142894206</v>
+        <f>IF(COUNT('Turns'!E171)=1,SUM('Turns'!E171),"Unknown")</f>
+        <v>0.00013969019</v>
       </c>
       <c r="Z43" s="2">
-        <f>IF(COUNT('Turns'!F170)=1,SUM('Turns'!F170),"Unknown")</f>
-        <v>0.0001638</v>
+        <f>IF(COUNT('Turns'!F171)=1,SUM('Turns'!F171),"Unknown")</f>
+        <v>0.0001594</v>
       </c>
       <c r="AA43" s="5">
         <f>IF(ISNUMBER(Y43),ROUND(Y43*'Reference data'!$B$2,0),"Unknown")</f>
@@ -8269,7 +8318,7 @@
         <v>177</v>
       </c>
       <c r="AD43" s="1">
-        <v>1878.597</v>
+        <v>829.279</v>
       </c>
       <c r="AE43" s="1" t="s">
         <v>191</v>
@@ -8327,7 +8376,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87237</v>
+        <v>0.87635</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>

--- a/reports/expert_dispatch/report.xlsx
+++ b/reports/expert_dispatch/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="235">
   <si>
     <t>Request</t>
   </si>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0d142-02ad-7f61-bee4-a7ae5c6e26f0</t>
+    <t>01a0d584-431a-7670-a84d-31f4a317f39c</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-23</t>
+    <t>2026-09-24</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-24T02:09:35.117183Z</t>
+    <t>2026-09-24T22:21:31.719587Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,7 +306,7 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0d142-02b1-76a3-b75e-9a60010f6341</t>
+    <t>01a0d584-431e-7ec2-a707-25d39b0d3bb6</t>
   </si>
   <si>
     <t>Input at standard rate</t>
@@ -342,8 +342,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"type": "function_call", "name": "task", "arguments": "{\"description\":\"Answer the movie question: Who directed the animated film Spirited Away? Provide the director's name and, if useful, a brief identifying context. Be accurate and concise.\",\"subagent_type\":\"movie_expert\"}", "call_id": "call_PrxdCxR8ikTMeqXJV3eOGj8Y", "id": "fc_0fab2a2f54a70e43006ab48bc8645087d29e7fcc5c16d6e514", "index": 0}]
-{"name": "task", "args": {"description": "Answer the movie question: Who directed the animated film Spirited Away? Provide the director's name and, if useful, a brief identifying context. Be accurate and concise.", "subagent_type": "movie_expert"}, "id": "call_PrxdCxR8ikTMeqXJV3eOGj8Y", "type": "tool_call"}</t>
+    <t>[{"type": "function_call", "name": "task", "arguments": "{\"description\":\"Answer the movie question: Who directed the film Spirited Away? Provide the director's name and, if useful, a brief identifying detail. Be accurate and concise.\",\"subagent_type\":\"movie_expert\"}", "call_id": "call_vwmI5a38fUZInRHJUPZSkwga", "id": "fc_0ca30177df7fe36f006ab5a2e2f28087d2b80b1536d128db5c", "index": 0}]
+{"name": "task", "args": {"description": "Answer the movie question: Who directed the film Spirited Away? Provide the director's name and, if useful, a brief identifying detail. Be accurate and concise.", "subagent_type": "movie_expert"}, "id": "call_vwmI5a38fUZInRHJUPZSkwga", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -355,44 +355,41 @@
     <t>Tool · task</t>
   </si>
   <si>
-    <t>01a0d142-090f-7921-96c2-48e5b91aa36e</t>
+    <t>01a0d584-48a6-7703-97a7-b1ecc8438e8d</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
   </si>
   <si>
-    <t>{'description': "Answer the movie question: Who directed the animated film Spirited Away? Provide the director's name and, if useful, a brief identifying context. Be accurate and concise.", 'subagent_type': 'movie_expert'}</t>
+    <t>{'description': "Answer the movie question: Who directed the film Spirited Away? Provide the director's name and, if useful, a brief identifying detail. Be accurate and concise.", 'subagent_type': 'movie_expert'}</t>
   </si>
   <si>
     <t xml:space="preserve">    Result</t>
   </si>
   <si>
-    <t>Command(update={'messages': [ToolMessage(content='*Spirited Away* was directed by **Hayao Miyazaki**, the renowned Japanese animator and filmmaker. ([Studio Ghibli](https://www.ghibli.jp/works/))', tool_call_id='call_PrxdCxR8ikTMeqXJV3eOGj8Y')]})</t>
+    <t>Command(update={'messages': [ToolMessage(content='*Spirited Away* was directed by **Hayao Miyazaki**, the acclaimed Studio Ghibli filmmaker. Source: https://www.ghibli.jp/works/', tool_call_id='call_vwmI5a38fUZInRHJUPZSkwga')]})</t>
   </si>
   <si>
     <t>R2</t>
   </si>
   <si>
-    <t>01a0d142-0912-7610-aad6-cb6582fa94f4</t>
+    <t>01a0d584-48a9-76d2-b472-9ff9ea6c4ec1</t>
   </si>
   <si>
     <t>You are the movies expert. Use search_movie_reference to retrieve evidence before answering the delegated question. Base factual claims on the returned passages and cite their source URLs. If no relevant evidence is found, explain the collection's limits instead of inventing an answer or claiming web research. Answer concisely. The collection is a small local teaching reference, not a complete or continually updated source.</t>
   </si>
   <si>
-    <t>Reasoning</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_00ccf8bc254a0520006ab48bc9c57c87d291ca3d74e17d1a70", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIvKo1mXpIa-e6G3aAzbB15xZGDlSbHtIBhe7vODm1fXSmH_42xCNb5w0GxeIcjbrw7egZcrTs-KVrQL2c6721N7H3BTs2JI6LKC-p595SBDGjBxLs-UbrS3BmYzrzBpeRx3G2PzKAgjttIlQg8md8YLLaDVecIoI_Tw22Y4-GFo3W6Y0Hlcvy4hyv1xF5qgicHOg7M1_jaMm8Bvap_pKa-zIJjeAI5SwsQs8lAFGUAeJNXgqhft1vcZ6WONkCh0as8dTzNAY6zez_OAh3sFbyixAxeN34Ield3l0r7WeqoFPDB_ZLyYHLcsi4sSxaKTJob9ocstLJLurP12UNSmL-8wJCPPAOtWm6LO4ds2_gQBaZYToLtPWy2QYV6g-tg6RcA8fJHtyUBLHcnO2N1_y7PX8Zr3n9wDlVmmTs2Ulo6N60GM9Aqn1BnJ171e4EIVv_pzhG_gCXCsK2jL0RRDszVbhIcgQN3FxiC2opAyQyAsq9o9SLcLc5UeLiNJ91CjUX9kK_Ty0KNBuaxMR2FSMJRbWyrFn7eYZgStIvMlBjmWeSNPQo4PZI-qBvXgLDUE5k0EurnDyE95rgMQY0a_M_JUMhDkLVn2_IT0Zvbeq2v49_xT_XKwoniZzbz2b1_a_Z0HmcQc4VMP9YhB7aDWK4d9E_6_d1eUNaII_65cegQaABcHHxT2GSasUjAv6Fy9p_bMLVgJ2dJe-xonMD_I1Tf_6VOycZzR2dinc-VYPna4TCn3v_cOzvstfo6JXFGNrDsisRfMonlUDlOv7ShJ7Ub9nYof1Y7q30F7LtpQaLBtdTESTjRth-tpfywJqrJaNffcvwJDjoDnI8R5X5JolYKNzHOsksSgJkB8nihm0NvTt-v5k5xcJNiulvvJOrQ_6FTjmYdiqfoZfDRsz7HaykzMX3E4XWMTHyuASXYSv6MUD7bx5SylI1ssEwLTEC_57wSA6Ug3m4EOI_GfgLQPwAQstpWVuxu6peFWJ00wXRSFgz6ccjVpnRLHfWWY8iPlzYJ-pVwJgcSE0RSry6P16RSPKBbXtzlMeOEpFAqtRgdGYt1DcvQfY0cqoAoadxrszRyzJK_iURZRkWeQugtPXjz59Y2elt77dvOC8Ih8XISGrKUk3Qc1Z_YEGocC-A7bHGpbgfgsqTMVfkyXQOGkF65Crcm0d9M60E_ARVzBKCMi0Sc="}, {"type": "function_call", "name": "search_movie_reference", "arguments": "{\"query\":\"Who directed the animated film Spirited Away? Director name and identifying context.\"}", "call_id": "call_UiDI8ksCWWneZfqDvCA3eZSj", "id": "fc_00ccf8bc254a0520006ab48bca03a887d2b9a29d4b0fe4ea65", "index": 1}]
-{"name": "search_movie_reference", "args": {"query": "Who directed the animated film Spirited Away? Director name and identifying context."}, "id": "call_UiDI8ksCWWneZfqDvCA3eZSj", "type": "tool_call"}</t>
+    <t>[{"type": "function_call", "name": "search_movie_reference", "arguments": "{\"query\":\"Who directed the film Spirited Away?\"}", "call_id": "call_xhvlnQehC2OlrK6VrpCAqeqz", "id": "fc_0a6acba15b3aeb56006ab5a2e41f1887d2b2ccf86031e8e199", "index": 0}]
+{"name": "search_movie_reference", "args": {"query": "Who directed the film Spirited Away?"}, "id": "call_xhvlnQehC2OlrK6VrpCAqeqz", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · search_movie_reference</t>
   </si>
   <si>
-    <t>01a0d142-0ec6-7ad3-b9c4-d5e03b83dcc8</t>
-  </si>
-  <si>
-    <t>{'query': 'Who directed the animated film Spirited Away? Director name and identifying context.'}</t>
+    <t>01a0d584-4c3c-75b1-afe4-cb1749286f01</t>
+  </si>
+  <si>
+    <t>{'query': 'Who directed the film Spirited Away?'}</t>
   </si>
   <si>
     <t>Spirited Away
@@ -403,7 +400,7 @@
     <t>R3</t>
   </si>
   <si>
-    <t>01a0d142-0ecc-7b40-a02b-be7a4fb7f47a</t>
+    <t>01a0d584-4c3e-7600-812e-65a9a52d2618</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
@@ -412,19 +409,19 @@
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "*Spirited Away* was directed by **Hayao Miyazaki**, the renowned Japanese animator and filmmaker. ([Studio Ghibli](https://www.ghibli.jp/works/))", "phase": "final_answer", "index": 0, "id": "msg_00ccf8bc254a0520006ab48bcb49fc87d2b72a5db3da3143f7"}]</t>
+    <t>[{"type": "text", "text": "*Spirited Away* was directed by **Hayao Miyazaki**, the acclaimed Studio Ghibli filmmaker. Source: https://www.ghibli.jp/works/", "phase": "final_answer", "index": 0, "id": "msg_0a6acba15b3aeb56006ab5a2e4f0d087d2a575de53a8913080"}]</t>
   </si>
   <si>
     <t>R4</t>
   </si>
   <si>
-    <t>01a0d142-151d-7513-bc8f-bfaecf6b5347</t>
-  </si>
-  <si>
-    <t>*Spirited Away* was directed by **Hayao Miyazaki**, the renowned Japanese animator and filmmaker. ([Studio Ghibli](https://www.ghibli.jp/works/))</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "*Spirited Away* was directed by **Hayao Miyazaki**.", "phase": "final_answer", "index": 0, "id": "msg_0fab2a2f54a70e43006ab48bccb7c887d2990851df9b4a24e5"}]</t>
+    <t>01a0d584-4fc3-7821-a7ce-caccaba0de5b</t>
+  </si>
+  <si>
+    <t>*Spirited Away* was directed by **Hayao Miyazaki**, the acclaimed Studio Ghibli filmmaker. Source: https://www.ghibli.jp/works/</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "*Spirited Away* was directed by **Hayao Miyazaki**.", "phase": "final_answer", "index": 0, "id": "msg_0ca30177df7fe36f006ab5a2e5f29887d2b5e554fe93999e0d"}]</t>
   </si>
   <si>
     <t>Turn 2</t>
@@ -433,45 +430,45 @@
     <t>R5</t>
   </si>
   <si>
-    <t>01a0d142-19b2-7110-83db-430607606dce</t>
+    <t>01a0d584-5369-7f42-a5cf-bbb41a706ecd</t>
   </si>
   <si>
     <t>How many players does a basketball team have on court?</t>
   </si>
   <si>
-    <t>[{"type": "function_call", "name": "task", "arguments": "{\"description\":\"Answer the sports question: How many players from one basketball team are on the court at a time? Mention the standard rule and briefly note any common variation only if relevant. Be concise.\",\"subagent_type\":\"sports_expert\"}", "call_id": "call_UI44fxbiLsncsRWgaCDVhjjn", "id": "fc_0fab2a2f54a70e43006ab48bcdf11887d2ae2f754130b987c0", "index": 0}]
-{"name": "task", "args": {"description": "Answer the sports question: How many players from one basketball team are on the court at a time? Mention the standard rule and briefly note any common variation only if relevant. Be concise.", "subagent_type": "sports_expert"}, "id": "call_UI44fxbiLsncsRWgaCDVhjjn", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0d142-1eb4-7932-bef7-c9981e3ce538</t>
-  </si>
-  <si>
-    <t>{'description': 'Answer the sports question: How many players from one basketball team are on the court at a time? Mention the standard rule and briefly note any common variation only if relevant. Be concise.', 'subagent_type': 'sports_expert'}</t>
-  </si>
-  <si>
-    <t>Command(update={'messages': [ToolMessage(content='In standard basketball, **five players from each team** are on the court at a time. (The separate 3x3 format uses three.)  \nSource: [FIBA](https://about.fiba.basketball/en/our-sport/basketball)', tool_call_id='call_UI44fxbiLsncsRWgaCDVhjjn')]})</t>
+    <t>[{"type": "function_call", "name": "task", "arguments": "{\"description\":\"Answer this sports rules question: How many players from one basketball team are on the court at a time during standard basketball play? Mention the standard number and briefly note any common variation only if relevant. Be concise and accurate.\",\"subagent_type\":\"sports_expert\"}", "call_id": "call_dgUD2BUQrltDmZK9vlEAIBuk", "id": "fc_0ca30177df7fe36f006ab5a2e6da8487d299d75f592af663b2", "index": 0}]
+{"name": "task", "args": {"description": "Answer this sports rules question: How many players from one basketball team are on the court at a time during standard basketball play? Mention the standard number and briefly note any common variation only if relevant. Be concise and accurate.", "subagent_type": "sports_expert"}, "id": "call_dgUD2BUQrltDmZK9vlEAIBuk", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0d584-5885-7831-97cc-894aa3f1fa9d</t>
+  </si>
+  <si>
+    <t>{'description': 'Answer this sports rules question: How many players from one basketball team are on the court at a time during standard basketball play? Mention the standard number and briefly note any common variation only if relevant. Be concise and accurate.', 'subagent_type': 'sports_expert'}</t>
+  </si>
+  <si>
+    <t>Command(update={'messages': [ToolMessage(content='In standard basketball, **five players from each team** are on the court at a time. This differs from **3x3 basketball**, which has three players per team. ([FIBA](https://about.fiba.basketball/en/our-sport/basketball))', tool_call_id='call_dgUD2BUQrltDmZK9vlEAIBuk')]})</t>
   </si>
   <si>
     <t>R6</t>
   </si>
   <si>
-    <t>01a0d142-1eba-75e1-a137-ed4f98e474a0</t>
+    <t>01a0d584-5889-77d1-806c-33b1e32f9fc9</t>
   </si>
   <si>
     <t>You are the sports expert. Use search_sports_reference to retrieve evidence before answering the delegated question. Base factual claims on the returned passages and cite their source URLs. If no relevant evidence is found, explain the collection's limits instead of inventing an answer or claiming web research. Answer concisely. The collection is a small local teaching reference, not a complete or continually updated source.</t>
   </si>
   <si>
-    <t>[{"id": "rs_0ab3c6584ecff013006ab48bcf0de887d29cc4e8a2ef024907", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIvPTePCxs54MuFTbxQgTKto8PuyS_j01PkObHUa6pa2Otc3VEnKdGVi1ECoUTe9n4IGM46UGh9eGPSvqmra2dNab2S6cUC-j7-n_Ru4BMNPFvpHn23dkfqEyhK_x50NSxclzGytRH3-WWx-V9aL9KPxSR_siDz-lgZam09gqiwdR8iShN84H9JYJqXxhygiGHlnIhBHmDKo8klf3UxJ9CKmJ7BykduNo-K5Oez_ysnmxgjoiJRmpTQ3aZRwlQS_1KSsCdEo1bhGN6usPT2r0yAAqgekUQk7MDnQNzfTPodV3pk4UcOcRbcLSInbqQK_-EpfNNcfmOxVKDIm6vOi1eGNjBUCynmi-ha5huabNns1kntWEbiuFN2bEv51VgwPP7OHgZUuJfQnOVQLx03u4gE8sVu_dtfWXCqVkzfm_q-1sg4lJcAB0PZXq6UnJ80y_mIDwxwmMacXwK6-onGLT4rYAJLS53uW-OvW0fFJJY1FjjHpdxRYcJNaumLzkMXkrtfMnWJj3M-wd-WOn_KztT6xLQVfl6g_IDXGXBu4_H-5WaKrl_pbiCjRAPueNWtCD2LAWmcP8_LuVxay-Fj4xPkaZtuWJdurveNwVfFiWv6Q899OnxhIpqJcB9PuGtvHVqIuszRGlScM-jBUHnXuf9L065DxQewhT7MAXba7Gn1YoOIF918dfCXdSRWLYWQNmAma9izmMRLgPhPU636CyVGWy2GMM2pIhtq0dGbn6ceCxkuuxVqYL-rLVvDRel_wURurNQRK53gUyxVs-NeF77lV7WL-y0Y6YkggRwaBPwhz2Mw-HOWDnCKOFY6jes7E_Jg_FuduCKgXOKDIjPqvidcWRcm_gV6U-21x3o39q1D0LrG7jBq4CbLTt1RyT4TXB9DnCWNKRmkH74c22mvMjCnASTfA4c7aLaUFZ8T2etnkj-2gV-vupezWqQ8yVyBm6XyI1eD815zyZvtUDby6kGged_uenhC3zjAeAjLvSz67XVgJro6FFMaXJzhISR68yr2n5JM6_c29Vco52yarDRZsxpiULheepBaLcJ03JoueTPNXX7k3SDzCKrtBqvfHBFmwotVz6F3ZjQt0aLivAFiwnvgIjsiaPWikXmw8gVzFbvIcSZokwmyIwWt1lKuuJP_mHY2PK3t1fYla096iTMUBNf2Ng-EGGPrI_zyhwDNboF5gsdUwHocjYz4tP9vfcDMw"}, {"type": "function_call", "name": "search_sports_reference", "arguments": "{\"query\":\"How many players from one basketball team are on the court at a time? standard rule common variation\"}", "call_id": "call_AK913aOW2zvZsx5H1YHRHUP9", "id": "fc_0ab3c6584ecff013006ab48bcf370c87d2bcba8a5e2bd85a19", "index": 1}]
-{"name": "search_sports_reference", "args": {"query": "How many players from one basketball team are on the court at a time? standard rule common variation"}, "id": "call_AK913aOW2zvZsx5H1YHRHUP9", "type": "tool_call"}</t>
+    <t>[{"type": "function_call", "name": "search_sports_reference", "arguments": "{\"query\":\"How many players from one basketball team are on the court at a time during standard basketball play? standard number common variation\"}", "call_id": "call_xRvbzoPLIFPiYYipYNQMIoKS", "id": "fc_045902d56d72c85c006ab5a2e8bd8887d28bf0d44510198c30", "index": 0}]
+{"name": "search_sports_reference", "args": {"query": "How many players from one basketball team are on the court at a time during standard basketball play? standard number common variation"}, "id": "call_xRvbzoPLIFPiYYipYNQMIoKS", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · search_sports_reference</t>
   </si>
   <si>
-    <t>01a0d142-233d-7433-b9a1-9d986a424ec7</t>
-  </si>
-  <si>
-    <t>{'query': 'How many players from one basketball team are on the court at a time? standard rule common variation'}</t>
+    <t>01a0d584-62c8-7bb0-922c-d4f92038f303</t>
+  </si>
+  <si>
+    <t>{'query': 'How many players from one basketball team are on the court at a time during standard basketball play? standard number common variation'}</t>
   </si>
   <si>
     <t>Standard basketball teams
@@ -482,23 +479,22 @@
     <t>R7</t>
   </si>
   <si>
-    <t>01a0d142-2342-7ca0-893a-2ef56c31a18c</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "In standard basketball, **five players from each team** are on the court at a time. (The separate 3x3 format uses three.)  \nSource: [FIBA](https://about.fiba.basketball/en/our-sport/basketball)", "phase": "final_answer", "index": 0, "id": "msg_0ab3c6584ecff013006ab48bd05ff887d2827deac2c998e246"}]</t>
+    <t>01a0d584-62cb-7a93-87b1-bc6515c5634f</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "In standard basketball, **five players from each team** are on the court at a time. This differs from **3x3 basketball**, which has three players per team. ([FIBA](https://about.fiba.basketball/en/our-sport/basketball))", "phase": "final_answer", "index": 0, "id": "msg_045902d56d72c85c006ab5a2eaba3887d2a79652ca4c1efa03"}]</t>
   </si>
   <si>
     <t>R8</t>
   </si>
   <si>
-    <t>01a0d142-2817-72a1-8e99-22da4e6f8316</t>
-  </si>
-  <si>
-    <t>In standard basketball, **five players from each team** are on the court at a time. (The separate 3x3 format uses three.)  
-Source: [FIBA](https://about.fiba.basketball/en/our-sport/basketball)</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "In standard basketball, **five players from each team** are on the court at a time.", "phase": "final_answer", "index": 0, "id": "msg_0fab2a2f54a70e43006ab48bd1909c87d2a8a203290a1cf888"}]</t>
+    <t>01a0d584-6730-71c2-9a2f-74de4fbbbee0</t>
+  </si>
+  <si>
+    <t>In standard basketball, **five players from each team** are on the court at a time. This differs from **3x3 basketball**, which has three players per team. ([FIBA](https://about.fiba.basketball/en/our-sport/basketball))</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "A basketball team has **five players on the court** at a time.", "phase": "final_answer", "index": 0, "id": "msg_0ca30177df7fe36f006ab5a2ebf12087d28bc49e9d6a9f3b67"}]</t>
   </si>
   <si>
     <t>Turn 3</t>
@@ -507,45 +503,48 @@
     <t>R9</t>
   </si>
   <si>
-    <t>01a0d142-2bea-71b2-891f-ad6d2ad2d09c</t>
+    <t>01a0d584-6b03-7ab2-ad42-ef88e2862f3a</t>
   </si>
   <si>
     <t>In which year did the Berlin Wall fall?</t>
   </si>
   <si>
-    <t>[{"type": "function_call", "name": "task", "arguments": "{\"description\":\"Answer the history question: In which year did the Berlin Wall fall? Give the year and, if useful, the specific date. Be concise and accurate.\",\"subagent_type\":\"history_expert\"}", "call_id": "call_ACuuKSsbQFwmWbJCOqGwklB2", "id": "fc_0fab2a2f54a70e43006ab48bd2822487d287f0185a94c9f6a6", "index": 0}]
-{"name": "task", "args": {"description": "Answer the history question: In which year did the Berlin Wall fall? Give the year and, if useful, the specific date. Be concise and accurate.", "subagent_type": "history_expert"}, "id": "call_ACuuKSsbQFwmWbJCOqGwklB2", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>01a0d142-303f-76a1-8184-b62ddbee2583</t>
-  </si>
-  <si>
-    <t>{'description': 'Answer the history question: In which year did the Berlin Wall fall? Give the year and, if useful, the specific date. Be concise and accurate.', 'subagent_type': 'history_expert'}</t>
-  </si>
-  <si>
-    <t>Command(update={'messages': [ToolMessage(content='The Berlin Wall fell in **1989**, opening on **9 November 1989**. Source: https://www.stiftung-berliner-mauer.de/de/ueber-uns/leichte-sprache/geschichte', tool_call_id='call_ACuuKSsbQFwmWbJCOqGwklB2')]})</t>
+    <t>[{"type": "function_call", "name": "task", "arguments": "{\"description\":\"Answer the history question: In which year did the Berlin Wall fall? Give the year and optionally the exact date for clarity. Be concise and accurate.\",\"subagent_type\":\"history_expert\"}", "call_id": "call_CzRHVsSMUBPtrOG3PRCUJ0sD", "id": "fc_0ca30177df7fe36f006ab5a2ecff2c87d28da612262dda4490", "index": 0}]
+{"name": "task", "args": {"description": "Answer the history question: In which year did the Berlin Wall fall? Give the year and optionally the exact date for clarity. Be concise and accurate.", "subagent_type": "history_expert"}, "id": "call_CzRHVsSMUBPtrOG3PRCUJ0sD", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>01a0d584-7004-7a50-8b49-905e97f10c0c</t>
+  </si>
+  <si>
+    <t>{'description': 'Answer the history question: In which year did the Berlin Wall fall? Give the year and optionally the exact date for clarity. Be concise and accurate.', 'subagent_type': 'history_expert'}</t>
+  </si>
+  <si>
+    <t>Command(update={'messages': [ToolMessage(content='The Berlin Wall fell in **1989**, opening on **9 November 1989**. ([Source](https://www.stiftung-berliner-mauer.de/de/ueber-uns/leichte-sprache/geschichte))', tool_call_id='call_CzRHVsSMUBPtrOG3PRCUJ0sD')]})</t>
   </si>
   <si>
     <t>R10</t>
   </si>
   <si>
-    <t>01a0d142-3045-71f0-92a6-6ea718317cf6</t>
+    <t>01a0d584-700a-7741-9922-a5ace39be30c</t>
   </si>
   <si>
     <t>You are the history expert. Use search_history_reference to retrieve evidence before answering the delegated question. Base factual claims on the returned passages and cite their source URLs. If no relevant evidence is found, explain the collection's limits instead of inventing an answer or claiming web research. Answer concisely. The collection is a small local teaching reference, not a complete or continually updated source.</t>
   </si>
   <si>
-    <t>[{"id": "rs_096f18f5a5025ecd006ab48bd3e61487d2975bc269cabc50cd", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIvUYWd_QcIDynGzoU260kn80ymQlb5wvpXRk8EOwIlaGvOOWv86XPqaw57qPz7n_1evVekYbLTH36SD0n6MrhOvJ7s_dbecib2F6rRM65mnVoShDwuG0A3-_RAWrTTCKLsE6lqA8KbgusTSn03CVozLbTBfJd3ZfYVYHaUEBxBZDeWIBB6SLITPXatLOy9MvaXl3Mwf6AWuT7DVs0X3GDV_1OJDECgcZIqd7_8D4O13SWtd1pd9yIRqHOwW4o0YUSZkz-ZjzYbE0x7DlMWk-Y9mrAV6j6Xe8WkST-6xvXS0M1FsvMh9ed-K6OiPe9IHdqhpZ2HOxGKmKWpcn23x2EjVoHjqgGbJrnGkZN3OCm_Rc1nU_31FD5A2gAdW5rENgHWI7foC_JnDXq9LOtjp0JL7mfjHNogPMOpEPVdoO57mwks73LGNIsi4kKCzKrk33NaeRoTkxePYciC0DZ5zGdrzG7LRElOFO3Cs7VQfoon8bdASYkp6Ctt_WQ23x1XZYFgrVbxA0l8qi6iAPuV4yVk5thWeaoL5C6mBt56GDV43bFi2nhaHw-y4QBF9GOhBdC6qEUkShRUgUQQ5-t-SfM_Ke9fpq5udU3hWlZ_zDUxlHQJXIWgGSwHERsa3uZVgNlc48z6kl4CEHJ4zSLX_QQdiBfXWDMwlHTxNjve40XpZil-JPR59YmorEe820hncCaFhfeQZ58s0Y1UYaFMgFS4xOi_5zWZeQzdYMdkzhBOhX3OZTjasrYjVct3pIF-acLv0Hw9J8JU9fz4wdqvehWQ7BitNvBeADKEnyyOSgJ8Jjf9aasPKRjDzVTH4K15BRfPvtMd-pQp314gVPpXM5Sk1btJH1NcQtKfeXLPezl5uQIOeak43Gb5Tj5dv-cfsWVCmcID5d7a7d3xaM_8F5xyn8JR1jGtwfskWjgSVP6sh8V3ronOy_HqKzv6yewg5CDMTcB3-LlbIE9p5RadDIuO2xztxVRapU2ExPtaq31gsUdB684OH3iFFjYQa6nnXI__pHqyZiCRzuC-rOOiuUTevWF_7lMhfBRuXVS8sEFqTKjRZ0DGTRYttybNqRDr3vtTmnbdUezR7Z1_tf3E2D9hwWnP9w0X6gU6DLD4KcDOXB6xiL4Gqb6dXDis7MUler6e4U2b3NrHrvioZtahaP3Q4BsclYyrVp28d8tUOs-cIP-byXUUXDYMNqyDGBY90A4p0"}, {"type": "function_call", "name": "search_history_reference", "arguments": "{\"query\":\"In which year did the Berlin Wall fall? specific date Berlin Wall opening/fall\"}", "call_id": "call_a6ujowYed8uba6tJS9HeXLdQ", "id": "fc_096f18f5a5025ecd006ab48bd412d087d29b6dcc2e31a3214a", "index": 1}]
-{"name": "search_history_reference", "args": {"query": "In which year did the Berlin Wall fall? specific date Berlin Wall opening/fall"}, "id": "call_a6ujowYed8uba6tJS9HeXLdQ", "type": "tool_call"}</t>
+    <t>Reasoning</t>
+  </si>
+  <si>
+    <t>[{"id": "rs_04f9fec6b68d93e9006ab5a2ee229887d2bae66b992da4e61a", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaLunQCPJJ3BHzgb_ykdLRQ7CjXe3trLWCU8Cf0a6_TgDH6aZMKwb41tdbabKpOUHgI2-dEq0x7XP5Km4d8uy09SEEOeJlmzz686VGLrTC-dTUEs2-zJMC6qbYWiVF_Z1tqRjOwsuCiNr_OAJKYdJcLJeZJNEaN-zWUXqZGledVR5YfTHt73SWtORxJKTCtsBZrXVuixWmkuzH7FCy_G1kLfqfHUTMlvzvLR0hXA44O843lxKQ6EfAqnppJKa4h1TZf6srCUXVT6lYl0b4HneS1vQd_j9yORpV2i2Pony92DhjAS8DWH4HFu67EKlkM6Hhg49EyOXHQPDUfBK9vicBQHd3ons6uG1axLB0eKkPnvOXwOrPp2uwzmC4Kjl5Mgvx-Xbn94Z9J-N1_VKNfJiyLSkZNwJL99RsyO3NGxUcBXwOJYLhzsXOZ1q6cU4h03GybXGfmqWoEHKqliBw2zqc-XXCOU03YDT43IlHPNvUzy9fHZ4yMF0_FTOMVhHESZyeeAwqz8K1WDpVeadvWZUIsUOj7a_WS7b-rU_C_ZKZBYsK7VEWg7eZvTwkPZGrl6i0dfdQ8mYONUDh5R_rieSyqEz-_9Ou6NQyPDi5Yapxf9BUl9PD6fPNFpmCjJQEegNC977_tQ4zWBqDoOy7ALPaQVWbozPCYPcJjf7XQNHHFyk7eVE_XY1MOLB2X0YfKMrGIEMI8twamNoD1pNcxRco442jc5pegir-A4_5M0X0rF6t3BJc7oOJhANYy7zNnNM3jfoCzmJUpzmGrdCCo5lm83omHEE1a2fOasdjKeRnlcKzZi3HGbbXuhG8rczOuCeiIsv0gOK_RrcsoBu09xX6_jW6N7GqERrhsiQDUVKPjqId8-s-7lJ4NV5iVSVjOdBUhjJYIqvMtuuGHnH8KGzfT77JYsooJIBK02tkNKFSow3y8kmOb0oJ9f_cHDjo7kbFVq2kzL23SPYROw4ytk88PPLoAFKV0Zxo2-0hybrkRsctpa0sVdEMTL5pvx8ZACasICbGBR5vXWMUYB8mNISinIjKI1NjD9JnvBXJYyFf3Q84C5jFUJ8rIwAmAbuA6slEnzSMZq3n0VTW9Bph928lxz887F4NlchTGpzVWoE_KA6rFLimz76GuyNbk4frrW-t1HFGwLY9brMJME2JcT4VvIy6YnEfpY07UUer0UVZVc8PL7prGcjGhg1mOCiobJTF6h"}, {"type": "function_call", "name": "search_history_reference", "arguments": "{\"query\":\"In which year did the Berlin Wall fall? exact date opening\"}", "call_id": "call_Lq6Mb9NjmvsndcGaLWulQdK9", "id": "fc_04f9fec6b68d93e9006ab5a2ee516887d2aca7eb53a9aeb4d8", "index": 1}]
+{"name": "search_history_reference", "args": {"query": "In which year did the Berlin Wall fall? exact date opening"}, "id": "call_Lq6Mb9NjmvsndcGaLWulQdK9", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · search_history_reference</t>
   </si>
   <si>
-    <t>01a0d142-3637-79f3-8638-4957b57fbed8</t>
-  </si>
-  <si>
-    <t>{'query': 'In which year did the Berlin Wall fall? specific date Berlin Wall opening/fall'}</t>
+    <t>01a0d584-7415-77d0-9667-00eea0564495</t>
+  </si>
+  <si>
+    <t>{'query': 'In which year did the Berlin Wall fall? exact date opening'}</t>
   </si>
   <si>
     <t>Opening of the Berlin Wall
@@ -556,22 +555,22 @@
     <t>R11</t>
   </si>
   <si>
-    <t>01a0d142-363c-78b2-9067-0b25a873d988</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "The Berlin Wall fell in **1989**, opening on **9 November 1989**. Source: https://www.stiftung-berliner-mauer.de/de/ueber-uns/leichte-sprache/geschichte", "phase": "final_answer", "index": 0, "id": "msg_096f18f5a5025ecd006ab48bd5496487d2bdf0847a52a902e6"}]</t>
+    <t>01a0d584-7418-7603-88b5-ac0fa2ad565e</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "The Berlin Wall fell in **1989**, opening on **9 November 1989**. ([Source](https://www.stiftung-berliner-mauer.de/de/ueber-uns/leichte-sprache/geschichte))", "phase": "final_answer", "index": 0, "id": "msg_04f9fec6b68d93e9006ab5a2ef9b9087d2b6f59f2643a5e527"}]</t>
   </si>
   <si>
     <t>R12</t>
   </si>
   <si>
-    <t>01a0d142-3b3a-7811-b96f-042b181f9566</t>
-  </si>
-  <si>
-    <t>The Berlin Wall fell in **1989**, opening on **9 November 1989**. Source: https://www.stiftung-berliner-mauer.de/de/ueber-uns/leichte-sprache/geschichte</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "The Berlin Wall fell in **1989**, on **November 9**.", "phase": "final_answer", "index": 0, "id": "msg_0fab2a2f54a70e43006ab48bd65fb887d29e213bf750b95115"}]</t>
+    <t>01a0d584-7b59-7bc0-95af-6068128398e5</t>
+  </si>
+  <si>
+    <t>The Berlin Wall fell in **1989**, opening on **9 November 1989**. ([Source](https://www.stiftung-berliner-mauer.de/de/ueber-uns/leichte-sprache/geschichte))</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "The Berlin Wall fell in **1989**, on **November 9**.", "phase": "final_answer", "index": 0, "id": "msg_0ca30177df7fe36f006ab5a2f125e887d29c3efb054573f91b"}]</t>
   </si>
   <si>
     <t>dispatcher_agent</t>
@@ -592,7 +591,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0d142-02b0-7d90-91fe-d26dd122ec25</t>
+    <t>01a0d584-431c-7523-a2f9-580d9ae4b19b</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -613,7 +612,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0d142-090f-7921-96c2-48d48319afdd</t>
+    <t>01a0d584-48a6-7703-97a7-b1d84542a380</t>
   </si>
   <si>
     <t xml:space="preserve">        task</t>
@@ -634,13 +633,13 @@
     <t>Execute the movie_expert workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0d142-0910-76e0-9845-88307bc72b77</t>
+    <t>01a0d584-48a7-7f42-b873-60570a34271d</t>
   </si>
   <si>
     <t xml:space="preserve">                model</t>
   </si>
   <si>
-    <t>01a0d142-0911-7330-8c24-788afafb274a</t>
+    <t>01a0d584-48a8-79f3-95db-05e3a18e1c6f</t>
   </si>
   <si>
     <t xml:space="preserve">                    ChatOpenAI</t>
@@ -649,7 +648,7 @@
     <t xml:space="preserve">                tools</t>
   </si>
   <si>
-    <t>01a0d142-0ec4-7860-8860-bac88f4e5142</t>
+    <t>01a0d584-4c3b-7992-bc25-64c9a339e3b1</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -661,19 +660,19 @@
     <t>Look up local movie evidence by phrase; return sources or an explicit miss.</t>
   </si>
   <si>
-    <t>01a0d142-0eca-75c0-a7de-f444541ea2f0</t>
-  </si>
-  <si>
-    <t>01a0d142-151b-7621-9aa8-b35f3b9c35dd</t>
-  </si>
-  <si>
-    <t>01a0d142-19b0-7fe3-b8f4-967da67c1906</t>
-  </si>
-  <si>
-    <t>01a0d142-19b1-74d3-a73a-2febdea8ec44</t>
-  </si>
-  <si>
-    <t>01a0d142-1eb3-74e2-be5f-312dde8a1b26</t>
+    <t>01a0d584-4c3e-7600-812e-6594ab68b287</t>
+  </si>
+  <si>
+    <t>01a0d584-4fc2-7693-8ae6-2fd09c6b62e0</t>
+  </si>
+  <si>
+    <t>01a0d584-5367-7a81-9ff9-6737e767749f</t>
+  </si>
+  <si>
+    <t>01a0d584-5368-7600-9dfb-6896090920dc</t>
+  </si>
+  <si>
+    <t>01a0d584-5885-7831-97cc-893cdbadd6ff</t>
   </si>
   <si>
     <t xml:space="preserve">            sports_expert</t>
@@ -682,13 +681,13 @@
     <t>Execute the sports_expert workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0d142-1eb5-7591-85e4-ad1a06c05b6d</t>
-  </si>
-  <si>
-    <t>01a0d142-1eb7-76b0-9cd9-5bd041e9335a</t>
-  </si>
-  <si>
-    <t>01a0d142-233c-7841-a26a-6e40eb300a49</t>
+    <t>01a0d584-5886-77c1-93ee-351efe9d2977</t>
+  </si>
+  <si>
+    <t>01a0d584-5887-7330-82e0-d67124af98e7</t>
+  </si>
+  <si>
+    <t>01a0d584-62c8-7bb0-922c-d4ebdbdf4e52</t>
   </si>
   <si>
     <t xml:space="preserve">                    search_sports_reference</t>
@@ -697,19 +696,19 @@
     <t>Look up local sports evidence by phrase; return sources or an explicit miss.</t>
   </si>
   <si>
-    <t>01a0d142-2341-7bd2-9bd6-f88087b265db</t>
-  </si>
-  <si>
-    <t>01a0d142-2815-7653-ac6d-03d2d5b68a8c</t>
-  </si>
-  <si>
-    <t>01a0d142-2be6-72a2-a556-71d7de0cf5f8</t>
-  </si>
-  <si>
-    <t>01a0d142-2be9-74d2-a979-a9f9945e835c</t>
-  </si>
-  <si>
-    <t>01a0d142-303d-7191-978d-bd469225d8a0</t>
+    <t>01a0d584-62ca-7361-9d0e-96e6d3fea86c</t>
+  </si>
+  <si>
+    <t>01a0d584-6730-71c2-9a2f-74c86b7fc06a</t>
+  </si>
+  <si>
+    <t>01a0d584-6b02-76f1-bfa4-ae1854b0704d</t>
+  </si>
+  <si>
+    <t>01a0d584-6b03-7ab2-ad42-ef710ce199c3</t>
+  </si>
+  <si>
+    <t>01a0d584-7003-79f0-8039-7980c3124a33</t>
   </si>
   <si>
     <t xml:space="preserve">            history_expert</t>
@@ -718,13 +717,13 @@
     <t>Execute the history_expert workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0d142-3040-7f73-b8af-567a478a783b</t>
-  </si>
-  <si>
-    <t>01a0d142-3041-77e2-ae41-f8cc538e3bba</t>
-  </si>
-  <si>
-    <t>01a0d142-3636-7fe3-95b8-7fe311d9865d</t>
+    <t>01a0d584-7005-7fc2-b972-df0f7950ab0a</t>
+  </si>
+  <si>
+    <t>01a0d584-7007-79f3-9822-9d6684519fcc</t>
+  </si>
+  <si>
+    <t>01a0d584-7415-77d0-9667-00d19d31064e</t>
   </si>
   <si>
     <t xml:space="preserve">                    search_history_reference</t>
@@ -733,10 +732,10 @@
     <t>Look up local history evidence by phrase; return sources or an explicit miss.</t>
   </si>
   <si>
-    <t>01a0d142-363b-7142-9df8-f9ed1e347c19</t>
-  </si>
-  <si>
-    <t>01a0d142-3b38-78a2-a3dd-54d95d88d306</t>
+    <t>01a0d584-7418-7603-88b5-abf1d3f2c57a</t>
+  </si>
+  <si>
+    <t>01a0d584-7b59-7bc0-95af-605f917dda7d</t>
   </si>
 </sst>
 </file>
@@ -1143,7 +1142,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M171"/>
+  <dimension ref="A1:M169"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1203,20 +1202,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59,'Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115,'Turns'!E128,'Turns'!E144,'Turns'!E159,'Turns'!E171)=12,SUM('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59,'Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115,'Turns'!E128,'Turns'!E144,'Turns'!E159,'Turns'!E171),"Unknown")</f>
-        <v>0.00129734854</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E31,'Turns'!E46,'Turns'!E58,'Turns'!E71,'Turns'!E86,'Turns'!E101,'Turns'!E113,'Turns'!E126,'Turns'!E142,'Turns'!E157,'Turns'!E169)=12,SUM('Turns'!E16,'Turns'!E31,'Turns'!E46,'Turns'!E58,'Turns'!E71,'Turns'!E86,'Turns'!E101,'Turns'!E113,'Turns'!E126,'Turns'!E142,'Turns'!E157,'Turns'!E169),"Unknown")</f>
+        <v>0.001269816716</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59,'Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115,'Turns'!F128,'Turns'!F144,'Turns'!F159,'Turns'!F171)=12,SUM('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59,'Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115,'Turns'!F128,'Turns'!F144,'Turns'!F159,'Turns'!F171),"Unknown")</f>
-        <v>0.0014804</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F31,'Turns'!F46,'Turns'!F58,'Turns'!F71,'Turns'!F86,'Turns'!F101,'Turns'!F113,'Turns'!F126,'Turns'!F142,'Turns'!F157,'Turns'!F169)=12,SUM('Turns'!F16,'Turns'!F31,'Turns'!F46,'Turns'!F58,'Turns'!F71,'Turns'!F86,'Turns'!F101,'Turns'!F113,'Turns'!F126,'Turns'!F142,'Turns'!F157,'Turns'!F169),"Unknown")</f>
+        <v>0.0014434</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>130.0</v>
+        <v>127.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>148.0</v>
+        <v>144.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1227,20 +1226,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59)=4,SUM('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59),"Unknown")</f>
-        <v>0.000368067</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E31,'Turns'!E46,'Turns'!E58)=4,SUM('Turns'!E16,'Turns'!E31,'Turns'!E46,'Turns'!E58),"Unknown")</f>
+        <v>0.000342042912</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59)=4,SUM('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59),"Unknown")</f>
-        <v>0.00042</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F31,'Turns'!F46,'Turns'!F58)=4,SUM('Turns'!F16,'Turns'!F31,'Turns'!F46,'Turns'!F58),"Unknown")</f>
+        <v>0.0003888</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>37.0</v>
+        <v>34.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>42.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1278,7 +1277,7 @@
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.592074e-05</v>
+        <v>4.6098376e-05</v>
       </c>
       <c r="F5" s="2">
         <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1365,7 +1364,7 @@
         <v>105</v>
       </c>
       <c r="D11" s="4">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
@@ -1379,15 +1378,15 @@
         <v>106</v>
       </c>
       <c r="D12" s="5">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" s="2">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.994234e-05</v>
+        <v>5.9118528e-05</v>
       </c>
       <c r="F12" s="2">
         <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!E17),D12*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>6.84e-05</v>
+        <v>6.72e-05</v>
       </c>
       <c r="G12" s="5">
         <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1446,11 +1445,11 @@
       </c>
       <c r="E16" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E12)=2,SUM('Turns'!E5,'Turns'!E12),"Unknown")</f>
-        <v>0.00010586308</v>
+        <v>0.000105216904</v>
       </c>
       <c r="F16" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F12)=2,SUM('Turns'!F5,'Turns'!F12),"Unknown")</f>
-        <v>0.0001208</v>
+        <v>0.0001196</v>
       </c>
       <c r="G16" s="5">
         <f>IF(ISNUMBER(E16),ROUND(E16*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1511,7 +1510,7 @@
         <v>94</v>
       </c>
       <c r="D20" s="4">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>95</v>
@@ -1531,15 +1530,15 @@
         <v>97</v>
       </c>
       <c r="D21" s="5">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E21" s="2">
         <f>IF(AND(ISNUMBER(F21),ISNUMBER('Reference data'!$B$3)),F21*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.400238e-05</v>
+        <v>3.3957964e-05</v>
       </c>
       <c r="F21" s="2">
         <f>IF(D21=0,0,IF(ISNUMBER('Reference data'!B17),D21*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>3.88e-05</v>
+        <v>3.86e-05</v>
       </c>
       <c r="G21" s="5">
         <f>IF(ISNUMBER(E21),ROUND(E21*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1608,7 +1607,7 @@
         <v>105</v>
       </c>
       <c r="D26" s="4">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="24" customHeight="1">
@@ -1619,29 +1618,29 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="D27" s="5">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E27" s="2">
         <f>IF(AND(ISNUMBER(F27),ISNUMBER('Reference data'!$B$3)),F27*'Reference data'!$B$3,"Unknown")</f>
-        <v>8.41296e-06</v>
+        <v>2.7447888e-05</v>
       </c>
       <c r="F27" s="2">
-        <f>IF(D27=0,0,IF(ISNUMBER('Reference data'!F17),D27*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>9.6e-06</v>
+        <f>IF(D27=0,0,IF(ISNUMBER('Reference data'!E17),D27*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>3.12e-05</v>
       </c>
       <c r="G27" s="5">
         <f>IF(ISNUMBER(E27),ROUND(E27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H27" s="5">
         <f>IF(ISNUMBER(F27),ROUND(F27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="24" customHeight="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="73" customHeight="1">
       <c r="A28" t="s">
         <v>117</v>
       </c>
@@ -1649,29 +1648,13 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" s="5">
-        <v>35</v>
-      </c>
-      <c r="E28" s="2">
-        <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.68067e-05</v>
-      </c>
-      <c r="F28" s="2">
-        <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!E17),D28*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>4.2e-05</v>
-      </c>
-      <c r="G28" s="5">
-        <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H28" s="5">
-        <f>IF(ISNUMBER(F28),ROUND(F28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="294" customHeight="1">
+        <v>107</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="24" customHeight="1">
       <c r="A29" t="s">
         <v>117</v>
       </c>
@@ -1679,10 +1662,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1">
@@ -1693,1120 +1673,1139 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="24" customHeight="1">
-      <c r="A31" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A31" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="4">
         <v>1</v>
       </c>
-      <c r="C31" t="s">
-        <v>104</v>
+      <c r="C31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" s="2">
+        <f>IF(COUNT('Turns'!E21,'Turns'!E27)=2,SUM('Turns'!E21,'Turns'!E27),"Unknown")</f>
+        <v>6.1405852e-05</v>
+      </c>
+      <c r="F31" s="2">
+        <f>IF(COUNT('Turns'!F21,'Turns'!F27)=2,SUM('Turns'!F21,'Turns'!F27),"Unknown")</f>
+        <v>6.98e-05</v>
+      </c>
+      <c r="G31" s="5">
+        <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="H31" s="5">
+        <f>IF(ISNUMBER(F31),ROUND(F31*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A32" s="4" t="s">
-        <v>117</v>
-      </c>
       <c r="B32" s="4">
         <v>1</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E32" s="2">
-        <f>IF(COUNT('Turns'!E21,'Turns'!E27,'Turns'!E28)=3,SUM('Turns'!E21,'Turns'!E27,'Turns'!E28),"Unknown")</f>
-        <v>7.922204e-05</v>
-      </c>
-      <c r="F32" s="2">
-        <f>IF(COUNT('Turns'!F21,'Turns'!F27,'Turns'!F28)=3,SUM('Turns'!F21,'Turns'!F27,'Turns'!F28),"Unknown")</f>
-        <v>9.04e-05</v>
-      </c>
-      <c r="G32" s="5">
-        <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
-      </c>
-      <c r="H32" s="5">
-        <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>121</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B33" s="4">
+      <c r="M32" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="24" customHeight="1">
+      <c r="B33">
         <v>1</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="M33" s="4" t="s">
+      <c r="C33" t="s">
+        <v>113</v>
+      </c>
+      <c r="I33" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="34" customHeight="1">
+    <row r="34" spans="1:13" ht="47" customHeight="1">
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="47" customHeight="1">
-      <c r="B35">
+    <row r="35" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A35" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" s="4">
         <v>1</v>
       </c>
-      <c r="C35" t="s">
-        <v>115</v>
-      </c>
-      <c r="I35" s="6" t="s">
+      <c r="C35" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D35" s="4">
+        <v>267</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="24" customHeight="1">
+      <c r="A36" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A36" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B36" s="4">
+      <c r="B36">
         <v>1</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" s="4">
-        <v>285</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M36" s="4" t="s">
+      <c r="C36" t="s">
         <v>127</v>
+      </c>
+      <c r="D36" s="5">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <f>IF(AND(ISNUMBER(F36),ISNUMBER('Reference data'!$B$3)),F36*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="F36" s="2">
+        <f>IF(D36=0,0,IF(ISNUMBER('Reference data'!C17),D36*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G36" s="5">
+        <f>IF(ISNUMBER(E36),ROUND(E36*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H36" s="5">
+        <f>IF(ISNUMBER(F36),ROUND(F36*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="24" customHeight="1">
       <c r="A37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="D37" s="5">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="E37" s="2">
         <f>IF(AND(ISNUMBER(F37),ISNUMBER('Reference data'!$B$3)),F37*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0</v>
+        <v>4.6978116e-05</v>
       </c>
       <c r="F37" s="2">
-        <f>IF(D37=0,0,IF(ISNUMBER('Reference data'!C17),D37*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>0.0</v>
+        <f>IF(D37=0,0,IF(ISNUMBER('Reference data'!B17),D37*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>5.34e-05</v>
       </c>
       <c r="G37" s="5">
         <f>IF(ISNUMBER(E37),ROUND(E37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H37" s="5">
         <f>IF(ISNUMBER(F37),ROUND(F37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="24" customHeight="1">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="47" customHeight="1">
       <c r="A38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>97</v>
-      </c>
-      <c r="D38" s="5">
-        <v>285</v>
-      </c>
-      <c r="E38" s="2">
-        <f>IF(AND(ISNUMBER(F38),ISNUMBER('Reference data'!$B$3)),F38*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.995195e-05</v>
-      </c>
-      <c r="F38" s="2">
-        <f>IF(D38=0,0,IF(ISNUMBER('Reference data'!B17),D38*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>5.7e-05</v>
-      </c>
-      <c r="G38" s="5">
-        <f>IF(ISNUMBER(E38),ROUND(E38*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-      <c r="H38" s="5">
-        <f>IF(ISNUMBER(F38),ROUND(F38*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="47" customHeight="1">
+        <v>128</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="24" customHeight="1">
       <c r="A39" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>129</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="24" customHeight="1">
       <c r="A40" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="24" customHeight="1">
-      <c r="A41" t="s">
-        <v>126</v>
-      </c>
-      <c r="B41">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A41" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B41" s="4">
         <v>1</v>
       </c>
-      <c r="C41" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A42" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B42" s="4">
+      <c r="C41" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D41" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="24" customHeight="1">
+      <c r="A42" t="s">
+        <v>125</v>
+      </c>
+      <c r="B42">
         <v>1</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D42" s="4">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="24" customHeight="1">
+      <c r="C42" t="s">
+        <v>106</v>
+      </c>
+      <c r="D42" s="5">
+        <v>40</v>
+      </c>
+      <c r="E42" s="2">
+        <f>IF(AND(ISNUMBER(F42),ISNUMBER('Reference data'!$B$3)),F42*'Reference data'!$B$3,"Unknown")</f>
+        <v>4.222752e-05</v>
+      </c>
+      <c r="F42" s="2">
+        <f>IF(D42=0,0,IF(ISNUMBER('Reference data'!E17),D42*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>4.8e-05</v>
+      </c>
+      <c r="G42" s="5">
+        <f>IF(ISNUMBER(E42),ROUND(E42*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H42" s="5">
+        <f>IF(ISNUMBER(F42),ROUND(F42*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="47" customHeight="1">
       <c r="A43" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>106</v>
-      </c>
-      <c r="D43" s="5">
-        <v>44</v>
-      </c>
-      <c r="E43" s="2">
-        <f>IF(AND(ISNUMBER(F43),ISNUMBER('Reference data'!$B$3)),F43*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.627128e-05</v>
-      </c>
-      <c r="F43" s="2">
-        <f>IF(D43=0,0,IF(ISNUMBER('Reference data'!E17),D43*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>5.28e-05</v>
-      </c>
-      <c r="G43" s="5">
-        <f>IF(ISNUMBER(E43),ROUND(E43*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-      <c r="H43" s="5">
-        <f>IF(ISNUMBER(F43),ROUND(F43*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="60" customHeight="1">
+        <v>107</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="24" customHeight="1">
       <c r="A44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>107</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="24" customHeight="1">
       <c r="A45" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="24" customHeight="1">
-      <c r="A46" t="s">
-        <v>126</v>
-      </c>
-      <c r="B46">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A46" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B46" s="4">
         <v>1</v>
       </c>
-      <c r="C46" t="s">
-        <v>104</v>
+      <c r="C46" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E46" s="2">
+        <f>IF(COUNT('Turns'!E36,'Turns'!E37,'Turns'!E42)=3,SUM('Turns'!E36,'Turns'!E37,'Turns'!E42),"Unknown")</f>
+        <v>8.9205636e-05</v>
+      </c>
+      <c r="F46" s="2">
+        <f>IF(COUNT('Turns'!F36,'Turns'!F37,'Turns'!F42)=3,SUM('Turns'!F36,'Turns'!F37,'Turns'!F42),"Unknown")</f>
+        <v>0.0001014</v>
+      </c>
+      <c r="G46" s="5">
+        <f>IF(ISNUMBER(E46),ROUND(E46*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+      <c r="H46" s="5">
+        <f>IF(ISNUMBER(F46),ROUND(F46*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>10.0</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B47" s="4">
         <v>1</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E47" s="2">
-        <f>IF(COUNT('Turns'!E37,'Turns'!E38,'Turns'!E43)=3,SUM('Turns'!E37,'Turns'!E38,'Turns'!E43),"Unknown")</f>
-        <v>9.622323e-05</v>
-      </c>
-      <c r="F47" s="2">
-        <f>IF(COUNT('Turns'!F37,'Turns'!F38,'Turns'!F43)=3,SUM('Turns'!F37,'Turns'!F38,'Turns'!F43),"Unknown")</f>
-        <v>0.0001098</v>
-      </c>
-      <c r="G47" s="5">
-        <f>IF(ISNUMBER(E47),ROUND(E47*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
-      </c>
-      <c r="H47" s="5">
-        <f>IF(ISNUMBER(F47),ROUND(F47*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A48" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D47" s="4">
+        <v>364</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M47" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B48" s="4">
+    </row>
+    <row r="48" spans="1:13" ht="24" customHeight="1">
+      <c r="A48" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48">
         <v>1</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D48" s="4">
-        <v>369</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M48" s="4" t="s">
-        <v>132</v>
+      <c r="C48" t="s">
+        <v>127</v>
+      </c>
+      <c r="D48" s="5">
+        <v>0</v>
+      </c>
+      <c r="E48" s="2">
+        <f>IF(AND(ISNUMBER(F48),ISNUMBER('Reference data'!$B$3)),F48*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="F48" s="2">
+        <f>IF(D48=0,0,IF(ISNUMBER('Reference data'!C17),D48*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G48" s="5">
+        <f>IF(ISNUMBER(E48),ROUND(E48*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H48" s="5">
+        <f>IF(ISNUMBER(F48),ROUND(F48*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="24" customHeight="1">
       <c r="A49" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="D49" s="5">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="E49" s="2">
         <f>IF(AND(ISNUMBER(F49),ISNUMBER('Reference data'!$B$3)),F49*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0</v>
+        <v>6.4045072e-05</v>
       </c>
       <c r="F49" s="2">
-        <f>IF(D49=0,0,IF(ISNUMBER('Reference data'!C17),D49*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>0.0</v>
+        <f>IF(D49=0,0,IF(ISNUMBER('Reference data'!B17),D49*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>7.28e-05</v>
       </c>
       <c r="G49" s="5">
         <f>IF(ISNUMBER(E49),ROUND(E49*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H49" s="5">
         <f>IF(ISNUMBER(F49),ROUND(F49*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="24" customHeight="1">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="34" customHeight="1">
       <c r="A50" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
-      </c>
-      <c r="D50" s="5">
-        <v>369</v>
-      </c>
-      <c r="E50" s="2">
-        <f>IF(AND(ISNUMBER(F50),ISNUMBER('Reference data'!$B$3)),F50*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.467463e-05</v>
-      </c>
-      <c r="F50" s="2">
-        <f>IF(D50=0,0,IF(ISNUMBER('Reference data'!B17),D50*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>7.38e-05</v>
-      </c>
-      <c r="G50" s="5">
-        <f>IF(ISNUMBER(E50),ROUND(E50*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="H50" s="5">
-        <f>IF(ISNUMBER(F50),ROUND(F50*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="34" customHeight="1">
+        <v>128</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="24" customHeight="1">
       <c r="A51" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B51">
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>129</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="24" customHeight="1">
       <c r="A52" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="24" customHeight="1">
-      <c r="A53" t="s">
-        <v>131</v>
-      </c>
-      <c r="B53">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A53" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B53" s="4">
         <v>1</v>
       </c>
-      <c r="C53" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A54" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B54" s="4">
+      <c r="C53" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D53" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="24" customHeight="1">
+      <c r="A54" t="s">
+        <v>130</v>
+      </c>
+      <c r="B54">
         <v>1</v>
       </c>
-      <c r="C54" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D54" s="4">
+      <c r="C54" t="s">
+        <v>106</v>
+      </c>
+      <c r="D54" s="5">
         <v>21</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" ht="24" customHeight="1">
+      <c r="E54" s="2">
+        <f>IF(AND(ISNUMBER(F54),ISNUMBER('Reference data'!$B$3)),F54*'Reference data'!$B$3,"Unknown")</f>
+        <v>2.2169448e-05</v>
+      </c>
+      <c r="F54" s="2">
+        <f>IF(D54=0,0,IF(ISNUMBER('Reference data'!E17),D54*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>2.52e-05</v>
+      </c>
+      <c r="G54" s="5">
+        <f>IF(ISNUMBER(E54),ROUND(E54*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+      <c r="H54" s="5">
+        <f>IF(ISNUMBER(F54),ROUND(F54*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="47" customHeight="1">
       <c r="A55" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>106</v>
-      </c>
-      <c r="D55" s="5">
-        <v>21</v>
-      </c>
-      <c r="E55" s="2">
-        <f>IF(AND(ISNUMBER(F55),ISNUMBER('Reference data'!$B$3)),F55*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.208402e-05</v>
-      </c>
-      <c r="F55" s="2">
-        <f>IF(D55=0,0,IF(ISNUMBER('Reference data'!E17),D55*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.52e-05</v>
-      </c>
-      <c r="G55" s="5">
-        <f>IF(ISNUMBER(E55),ROUND(E55*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-      <c r="H55" s="5">
-        <f>IF(ISNUMBER(F55),ROUND(F55*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="47" customHeight="1">
+        <v>107</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="24" customHeight="1">
       <c r="A56" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>107</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="24" customHeight="1">
       <c r="A57" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="24" customHeight="1">
-      <c r="A58" t="s">
-        <v>131</v>
-      </c>
-      <c r="B58">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A58" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B58" s="4">
         <v>1</v>
       </c>
-      <c r="C58" t="s">
-        <v>104</v>
+      <c r="C58" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E58" s="2">
+        <f>IF(COUNT('Turns'!E48,'Turns'!E49,'Turns'!E54)=3,SUM('Turns'!E48,'Turns'!E49,'Turns'!E54),"Unknown")</f>
+        <v>8.621452e-05</v>
+      </c>
+      <c r="F58" s="2">
+        <f>IF(COUNT('Turns'!F48,'Turns'!F49,'Turns'!F54)=3,SUM('Turns'!F48,'Turns'!F49,'Turns'!F54),"Unknown")</f>
+        <v>9.8e-05</v>
+      </c>
+      <c r="G58" s="5">
+        <f>IF(ISNUMBER(E58),ROUND(E58*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+      <c r="H58" s="5">
+        <f>IF(ISNUMBER(F58),ROUND(F58*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>10.0</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A59" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="B59" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="E59" s="2">
-        <f>IF(COUNT('Turns'!E49,'Turns'!E50,'Turns'!E55)=3,SUM('Turns'!E49,'Turns'!E50,'Turns'!E55),"Unknown")</f>
-        <v>8.675865e-05</v>
+        <f>IF(COUNT('Turns'!E71,'Turns'!E86,'Turns'!E101,'Turns'!E113)=4,SUM('Turns'!E71,'Turns'!E86,'Turns'!E101,'Turns'!E113),"Unknown")</f>
+        <v>0.000451482568</v>
       </c>
       <c r="F59" s="2">
-        <f>IF(COUNT('Turns'!F49,'Turns'!F50,'Turns'!F55)=3,SUM('Turns'!F49,'Turns'!F50,'Turns'!F55),"Unknown")</f>
-        <v>9.9e-05</v>
+        <f>IF(COUNT('Turns'!F71,'Turns'!F86,'Turns'!F101,'Turns'!F113)=4,SUM('Turns'!F71,'Turns'!F86,'Turns'!F101,'Turns'!F113),"Unknown")</f>
+        <v>0.0005132</v>
       </c>
       <c r="G59" s="5">
         <f>IF(ISNUMBER(E59),ROUND(E59*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>45.0</v>
       </c>
       <c r="H59" s="5">
         <f>IF(ISNUMBER(F59),ROUND(F59*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
-      </c>
-      <c r="K59" s="4" t="s">
-        <v>110</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="60" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A60" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="B60" s="4">
         <v>2</v>
       </c>
       <c r="C60" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D60" s="4">
+        <v>402</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M60" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="24" customHeight="1">
+      <c r="A61" t="s">
         <v>135</v>
       </c>
-      <c r="E60" s="2">
-        <f>IF(COUNT('Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115)=4,SUM('Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115),"Unknown")</f>
-        <v>0.00045079444</v>
-      </c>
-      <c r="F60" s="2">
-        <f>IF(COUNT('Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115)=4,SUM('Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115),"Unknown")</f>
-        <v>0.0005144</v>
-      </c>
-      <c r="G60" s="5">
-        <f>IF(ISNUMBER(E60),ROUND(E60*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>45.0</v>
-      </c>
-      <c r="H60" s="5">
-        <f>IF(ISNUMBER(F60),ROUND(F60*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>51.0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A61" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B61" s="4">
+      <c r="B61">
         <v>2</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D61" s="4">
-        <v>407</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M61" s="4" t="s">
-        <v>137</v>
+      <c r="C61" t="s">
+        <v>127</v>
+      </c>
+      <c r="D61" s="5">
+        <v>0</v>
+      </c>
+      <c r="E61" s="2">
+        <f>IF(AND(ISNUMBER(F61),ISNUMBER('Reference data'!$B$3)),F61*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="F61" s="2">
+        <f>IF(D61=0,0,IF(ISNUMBER('Reference data'!C17),D61*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G61" s="5">
+        <f>IF(ISNUMBER(E61),ROUND(E61*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H61" s="5">
+        <f>IF(ISNUMBER(F61),ROUND(F61*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="24" customHeight="1">
       <c r="A62" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="D62" s="5">
-        <v>0</v>
+        <v>402</v>
       </c>
       <c r="E62" s="2">
         <f>IF(AND(ISNUMBER(F62),ISNUMBER('Reference data'!$B$3)),F62*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0</v>
+        <v>7.0731096e-05</v>
       </c>
       <c r="F62" s="2">
-        <f>IF(D62=0,0,IF(ISNUMBER('Reference data'!C17),D62*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>0.0</v>
+        <f>IF(D62=0,0,IF(ISNUMBER('Reference data'!B17),D62*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>8.04e-05</v>
       </c>
       <c r="G62" s="5">
         <f>IF(ISNUMBER(E62),ROUND(E62*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H62" s="5">
         <f>IF(ISNUMBER(F62),ROUND(F62*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="24" customHeight="1">
       <c r="A63" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>97</v>
-      </c>
-      <c r="D63" s="5">
-        <v>407</v>
-      </c>
-      <c r="E63" s="2">
-        <f>IF(AND(ISNUMBER(F63),ISNUMBER('Reference data'!$B$3)),F63*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.133489e-05</v>
-      </c>
-      <c r="F63" s="2">
-        <f>IF(D63=0,0,IF(ISNUMBER('Reference data'!B17),D63*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>8.14e-05</v>
-      </c>
-      <c r="G63" s="5">
-        <f>IF(ISNUMBER(E63),ROUND(E63*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="H63" s="5">
-        <f>IF(ISNUMBER(F63),ROUND(F63*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>101</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="24" customHeight="1">
       <c r="A64" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>101</v>
-      </c>
-      <c r="I64" s="6" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="24" customHeight="1">
       <c r="A65" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="24" customHeight="1">
-      <c r="A66" t="s">
-        <v>136</v>
-      </c>
-      <c r="B66">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A66" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B66" s="4">
         <v>2</v>
       </c>
-      <c r="C66" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A67" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B67" s="4">
+      <c r="C66" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D66" s="4">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="24" customHeight="1">
+      <c r="A67" t="s">
+        <v>135</v>
+      </c>
+      <c r="B67">
         <v>2</v>
       </c>
-      <c r="C67" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D67" s="4">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="24" customHeight="1">
+      <c r="C67" t="s">
+        <v>106</v>
+      </c>
+      <c r="D67" s="5">
+        <v>67</v>
+      </c>
+      <c r="E67" s="2">
+        <f>IF(AND(ISNUMBER(F67),ISNUMBER('Reference data'!$B$3)),F67*'Reference data'!$B$3,"Unknown")</f>
+        <v>7.0731096e-05</v>
+      </c>
+      <c r="F67" s="2">
+        <f>IF(D67=0,0,IF(ISNUMBER('Reference data'!E17),D67*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>8.04e-05</v>
+      </c>
+      <c r="G67" s="5">
+        <f>IF(ISNUMBER(E67),ROUND(E67*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="H67" s="5">
+        <f>IF(ISNUMBER(F67),ROUND(F67*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="151" customHeight="1">
       <c r="A68" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B68">
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>106</v>
-      </c>
-      <c r="D68" s="5">
-        <v>60</v>
-      </c>
-      <c r="E68" s="2">
-        <f>IF(AND(ISNUMBER(F68),ISNUMBER('Reference data'!$B$3)),F68*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.30972e-05</v>
-      </c>
-      <c r="F68" s="2">
-        <f>IF(D68=0,0,IF(ISNUMBER('Reference data'!E17),D68*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>7.2e-05</v>
-      </c>
-      <c r="G68" s="5">
-        <f>IF(ISNUMBER(E68),ROUND(E68*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="H68" s="5">
-        <f>IF(ISNUMBER(F68),ROUND(F68*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="125" customHeight="1">
+        <v>107</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="24" customHeight="1">
       <c r="A69" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>107</v>
-      </c>
-      <c r="I69" s="6" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="24" customHeight="1">
       <c r="A70" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B70">
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="24" customHeight="1">
-      <c r="A71" t="s">
-        <v>136</v>
-      </c>
-      <c r="B71">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A71" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B71" s="4">
         <v>2</v>
       </c>
-      <c r="C71" t="s">
-        <v>104</v>
+      <c r="C71" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E71" s="2">
+        <f>IF(COUNT('Turns'!E61,'Turns'!E62,'Turns'!E67)=3,SUM('Turns'!E61,'Turns'!E62,'Turns'!E67),"Unknown")</f>
+        <v>0.000141462192</v>
+      </c>
+      <c r="F71" s="2">
+        <f>IF(COUNT('Turns'!F61,'Turns'!F62,'Turns'!F67)=3,SUM('Turns'!F61,'Turns'!F62,'Turns'!F67),"Unknown")</f>
+        <v>0.0001608</v>
+      </c>
+      <c r="G71" s="5">
+        <f>IF(ISNUMBER(E71),ROUND(E71*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>14.0</v>
+      </c>
+      <c r="H71" s="5">
+        <f>IF(ISNUMBER(F71),ROUND(F71*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>16.0</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="72" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A72" s="4" t="s">
-        <v>136</v>
-      </c>
       <c r="B72" s="4">
         <v>2</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E72" s="2">
-        <f>IF(COUNT('Turns'!E62,'Turns'!E63,'Turns'!E68)=3,SUM('Turns'!E62,'Turns'!E63,'Turns'!E68),"Unknown")</f>
-        <v>0.00013443209</v>
-      </c>
-      <c r="F72" s="2">
-        <f>IF(COUNT('Turns'!F62,'Turns'!F63,'Turns'!F68)=3,SUM('Turns'!F62,'Turns'!F63,'Turns'!F68),"Unknown")</f>
-        <v>0.0001534</v>
-      </c>
-      <c r="G72" s="5">
-        <f>IF(ISNUMBER(E72),ROUND(E72*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
-      </c>
-      <c r="H72" s="5">
-        <f>IF(ISNUMBER(F72),ROUND(F72*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>111</v>
       </c>
       <c r="K72" s="4" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="73" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B73" s="4">
+      <c r="M72" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="60" customHeight="1">
+      <c r="B73">
         <v>2</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="K73" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="M73" s="4" t="s">
+      <c r="C73" t="s">
+        <v>113</v>
+      </c>
+      <c r="I73" s="6" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="47" customHeight="1">
+    <row r="74" spans="1:13" ht="60" customHeight="1">
       <c r="B74">
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I74" s="6" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="60" customHeight="1">
-      <c r="B75">
+    <row r="75" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A75" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B75" s="4">
         <v>2</v>
       </c>
-      <c r="C75" t="s">
-        <v>115</v>
-      </c>
-      <c r="I75" s="6" t="s">
+      <c r="C75" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D75" s="4">
+        <v>201</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M75" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="24" customHeight="1">
+      <c r="A76" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="76" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A76" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B76" s="4">
+      <c r="B76">
         <v>2</v>
       </c>
-      <c r="C76" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D76" s="4">
-        <v>194</v>
-      </c>
-      <c r="J76" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M76" s="4" t="s">
-        <v>144</v>
+      <c r="C76" t="s">
+        <v>97</v>
+      </c>
+      <c r="D76" s="5">
+        <v>201</v>
+      </c>
+      <c r="E76" s="2">
+        <f>IF(AND(ISNUMBER(F76),ISNUMBER('Reference data'!$B$3)),F76*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.5365548e-05</v>
+      </c>
+      <c r="F76" s="2">
+        <f>IF(D76=0,0,IF(ISNUMBER('Reference data'!B17),D76*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>4.02e-05</v>
+      </c>
+      <c r="G76" s="5">
+        <f>IF(ISNUMBER(E76),ROUND(E76*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H76" s="5">
+        <f>IF(ISNUMBER(F76),ROUND(F76*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="24" customHeight="1">
       <c r="A77" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B77">
         <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>97</v>
-      </c>
-      <c r="D77" s="5">
-        <v>194</v>
-      </c>
-      <c r="E77" s="2">
-        <f>IF(AND(ISNUMBER(F77),ISNUMBER('Reference data'!$B$3)),F77*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.400238e-05</v>
-      </c>
-      <c r="F77" s="2">
-        <f>IF(D77=0,0,IF(ISNUMBER('Reference data'!B17),D77*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>3.88e-05</v>
-      </c>
-      <c r="G77" s="5">
-        <f>IF(ISNUMBER(E77),ROUND(E77*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H77" s="5">
-        <f>IF(ISNUMBER(F77),ROUND(F77*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="24" customHeight="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="73" customHeight="1">
       <c r="A78" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="73" customHeight="1">
+        <v>99</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="24" customHeight="1">
       <c r="A79" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B79">
         <v>2</v>
       </c>
       <c r="C79" t="s">
-        <v>99</v>
-      </c>
-      <c r="I79" s="6" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="24" customHeight="1">
       <c r="A80" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B80">
         <v>2</v>
       </c>
       <c r="C80" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" ht="24" customHeight="1">
-      <c r="A81" t="s">
-        <v>143</v>
-      </c>
-      <c r="B81">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A81" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B81" s="4">
         <v>2</v>
       </c>
-      <c r="C81" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A82" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B82" s="4">
+      <c r="C81" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D81" s="4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="24" customHeight="1">
+      <c r="A82" t="s">
+        <v>142</v>
+      </c>
+      <c r="B82">
         <v>2</v>
       </c>
-      <c r="C82" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D82" s="4">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="24" customHeight="1">
+      <c r="C82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D82" s="5">
+        <v>42</v>
+      </c>
+      <c r="E82" s="2">
+        <f>IF(AND(ISNUMBER(F82),ISNUMBER('Reference data'!$B$3)),F82*'Reference data'!$B$3,"Unknown")</f>
+        <v>4.4338896e-05</v>
+      </c>
+      <c r="F82" s="2">
+        <f>IF(D82=0,0,IF(ISNUMBER('Reference data'!E17),D82*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>5.04e-05</v>
+      </c>
+      <c r="G82" s="5">
+        <f>IF(ISNUMBER(E82),ROUND(E82*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H82" s="5">
+        <f>IF(ISNUMBER(F82),ROUND(F82*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="99" customHeight="1">
       <c r="A83" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B83">
         <v>2</v>
       </c>
       <c r="C83" t="s">
-        <v>120</v>
-      </c>
-      <c r="D83" s="5">
-        <v>9</v>
-      </c>
-      <c r="E83" s="2">
-        <f>IF(AND(ISNUMBER(F83),ISNUMBER('Reference data'!$B$3)),F83*'Reference data'!$B$3,"Unknown")</f>
-        <v>9.46458e-06</v>
-      </c>
-      <c r="F83" s="2">
-        <f>IF(D83=0,0,IF(ISNUMBER('Reference data'!F17),D83*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>1.08e-05</v>
-      </c>
-      <c r="G83" s="5">
-        <f>IF(ISNUMBER(E83),ROUND(E83*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-      <c r="H83" s="5">
-        <f>IF(ISNUMBER(F83),ROUND(F83*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
+        <v>107</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="24" customHeight="1">
       <c r="A84" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B84">
         <v>2</v>
       </c>
       <c r="C84" t="s">
-        <v>106</v>
-      </c>
-      <c r="D84" s="5">
-        <v>40</v>
-      </c>
-      <c r="E84" s="2">
-        <f>IF(AND(ISNUMBER(F84),ISNUMBER('Reference data'!$B$3)),F84*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.20648e-05</v>
-      </c>
-      <c r="F84" s="2">
-        <f>IF(D84=0,0,IF(ISNUMBER('Reference data'!E17),D84*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>4.8e-05</v>
-      </c>
-      <c r="G84" s="5">
-        <f>IF(ISNUMBER(E84),ROUND(E84*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H84" s="5">
-        <f>IF(ISNUMBER(F84),ROUND(F84*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="307" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="24" customHeight="1">
       <c r="A85" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B85">
         <v>2</v>
       </c>
       <c r="C85" t="s">
-        <v>107</v>
-      </c>
-      <c r="I85" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A86" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B86" s="4">
+        <v>2</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E86" s="2">
+        <f>IF(COUNT('Turns'!E76,'Turns'!E82)=2,SUM('Turns'!E76,'Turns'!E82),"Unknown")</f>
+        <v>7.9704444e-05</v>
+      </c>
+      <c r="F86" s="2">
+        <f>IF(COUNT('Turns'!F76,'Turns'!F82)=2,SUM('Turns'!F76,'Turns'!F82),"Unknown")</f>
+        <v>9.06e-05</v>
+      </c>
+      <c r="G86" s="5">
+        <f>IF(ISNUMBER(E86),ROUND(E86*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="H86" s="5">
+        <f>IF(ISNUMBER(F86),ROUND(F86*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B87" s="4">
+        <v>2</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="86" spans="1:13" ht="24" customHeight="1">
-      <c r="A86" t="s">
-        <v>143</v>
-      </c>
-      <c r="B86">
+      <c r="K87" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="M87" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="34" customHeight="1">
+      <c r="B88">
         <v>2</v>
       </c>
-      <c r="C86" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" ht="24" customHeight="1">
-      <c r="A87" t="s">
-        <v>143</v>
-      </c>
-      <c r="B87">
+      <c r="C88" t="s">
+        <v>113</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="60" customHeight="1">
+      <c r="B89">
         <v>2</v>
       </c>
-      <c r="C87" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A88" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B88" s="4">
+      <c r="C89" t="s">
+        <v>115</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A90" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B90" s="4">
         <v>2</v>
       </c>
-      <c r="C88" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E88" s="2">
-        <f>IF(COUNT('Turns'!E77,'Turns'!E83,'Turns'!E84)=3,SUM('Turns'!E77,'Turns'!E83,'Turns'!E84),"Unknown")</f>
-        <v>8.553176e-05</v>
-      </c>
-      <c r="F88" s="2">
-        <f>IF(COUNT('Turns'!F77,'Turns'!F83,'Turns'!F84)=3,SUM('Turns'!F77,'Turns'!F83,'Turns'!F84),"Unknown")</f>
-        <v>9.76e-05</v>
-      </c>
-      <c r="G88" s="5">
-        <f>IF(ISNUMBER(E88),ROUND(E88*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
-      </c>
-      <c r="H88" s="5">
-        <f>IF(ISNUMBER(F88),ROUND(F88*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
-      </c>
-      <c r="K88" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B89" s="4">
-        <v>2</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="K89" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="M89" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" ht="34" customHeight="1">
-      <c r="B90">
-        <v>2</v>
-      </c>
-      <c r="C90" t="s">
-        <v>113</v>
-      </c>
-      <c r="I90" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" ht="60" customHeight="1">
+      <c r="C90" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D90" s="4">
+        <v>300</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M90" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="24" customHeight="1">
+      <c r="A91" t="s">
+        <v>150</v>
+      </c>
       <c r="B91">
         <v>2</v>
       </c>
       <c r="C91" t="s">
-        <v>115</v>
-      </c>
-      <c r="I91" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D91" s="5">
+        <v>0</v>
+      </c>
+      <c r="E91" s="2">
+        <f>IF(AND(ISNUMBER(F91),ISNUMBER('Reference data'!$B$3)),F91*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="F91" s="2">
+        <f>IF(D91=0,0,IF(ISNUMBER('Reference data'!C17),D91*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G91" s="5">
+        <f>IF(ISNUMBER(E91),ROUND(E91*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H91" s="5">
+        <f>IF(ISNUMBER(F91),ROUND(F91*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="24" customHeight="1">
+      <c r="A92" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="92" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A92" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B92" s="4">
+      <c r="B92">
         <v>2</v>
       </c>
-      <c r="C92" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D92" s="4">
+      <c r="C92" t="s">
+        <v>97</v>
+      </c>
+      <c r="D92" s="5">
         <v>300</v>
       </c>
-      <c r="J92" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M92" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" ht="24" customHeight="1">
+      <c r="E92" s="2">
+        <f>IF(AND(ISNUMBER(F92),ISNUMBER('Reference data'!$B$3)),F92*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.27844e-05</v>
+      </c>
+      <c r="F92" s="2">
+        <f>IF(D92=0,0,IF(ISNUMBER('Reference data'!B17),D92*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-05</v>
+      </c>
+      <c r="G92" s="5">
+        <f>IF(ISNUMBER(E92),ROUND(E92*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+      <c r="H92" s="5">
+        <f>IF(ISNUMBER(F92),ROUND(F92*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="60" customHeight="1">
       <c r="A93" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -2814,225 +2813,225 @@
       <c r="C93" t="s">
         <v>128</v>
       </c>
-      <c r="D93" s="5">
-        <v>0</v>
-      </c>
-      <c r="E93" s="2">
-        <f>IF(AND(ISNUMBER(F93),ISNUMBER('Reference data'!$B$3)),F93*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="F93" s="2">
-        <f>IF(D93=0,0,IF(ISNUMBER('Reference data'!C17),D93*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>0.0</v>
-      </c>
-      <c r="G93" s="5">
-        <f>IF(ISNUMBER(E93),ROUND(E93*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H93" s="5">
-        <f>IF(ISNUMBER(F93),ROUND(F93*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+      <c r="I93" s="6" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="24" customHeight="1">
       <c r="A94" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B94">
         <v>2</v>
       </c>
       <c r="C94" t="s">
-        <v>97</v>
-      </c>
-      <c r="D94" s="5">
-        <v>300</v>
-      </c>
-      <c r="E94" s="2">
-        <f>IF(AND(ISNUMBER(F94),ISNUMBER('Reference data'!$B$3)),F94*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-05</v>
-      </c>
-      <c r="F94" s="2">
-        <f>IF(D94=0,0,IF(ISNUMBER('Reference data'!B17),D94*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-05</v>
-      </c>
-      <c r="G94" s="5">
-        <f>IF(ISNUMBER(E94),ROUND(E94*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-      <c r="H94" s="5">
-        <f>IF(ISNUMBER(F94),ROUND(F94*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" ht="60" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="24" customHeight="1">
       <c r="A95" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B95">
         <v>2</v>
       </c>
       <c r="C95" t="s">
-        <v>129</v>
-      </c>
-      <c r="I95" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A96" s="4" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="96" spans="1:13" ht="24" customHeight="1">
-      <c r="A96" t="s">
-        <v>151</v>
-      </c>
-      <c r="B96">
+      <c r="B96" s="4">
         <v>2</v>
       </c>
-      <c r="C96" t="s">
-        <v>103</v>
+      <c r="C96" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D96" s="4">
+        <v>60</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="24" customHeight="1">
       <c r="A97" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B97">
         <v>2</v>
       </c>
       <c r="C97" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A98" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B98" s="4">
+        <v>106</v>
+      </c>
+      <c r="D97" s="5">
+        <v>60</v>
+      </c>
+      <c r="E97" s="2">
+        <f>IF(AND(ISNUMBER(F97),ISNUMBER('Reference data'!$B$3)),F97*'Reference data'!$B$3,"Unknown")</f>
+        <v>6.334128e-05</v>
+      </c>
+      <c r="F97" s="2">
+        <f>IF(D97=0,0,IF(ISNUMBER('Reference data'!E17),D97*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>7.2e-05</v>
+      </c>
+      <c r="G97" s="5">
+        <f>IF(ISNUMBER(E97),ROUND(E97*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="H97" s="5">
+        <f>IF(ISNUMBER(F97),ROUND(F97*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="60" customHeight="1">
+      <c r="A98" t="s">
+        <v>150</v>
+      </c>
+      <c r="B98">
         <v>2</v>
       </c>
-      <c r="C98" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D98" s="4">
-        <v>58</v>
+      <c r="C98" t="s">
+        <v>107</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="24" customHeight="1">
       <c r="A99" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B99">
         <v>2</v>
       </c>
       <c r="C99" t="s">
-        <v>106</v>
-      </c>
-      <c r="D99" s="5">
-        <v>58</v>
-      </c>
-      <c r="E99" s="2">
-        <f>IF(AND(ISNUMBER(F99),ISNUMBER('Reference data'!$B$3)),F99*'Reference data'!$B$3,"Unknown")</f>
-        <v>6.099396e-05</v>
-      </c>
-      <c r="F99" s="2">
-        <f>IF(D99=0,0,IF(ISNUMBER('Reference data'!E17),D99*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>6.96e-05</v>
-      </c>
-      <c r="G99" s="5">
-        <f>IF(ISNUMBER(E99),ROUND(E99*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="H99" s="5">
-        <f>IF(ISNUMBER(F99),ROUND(F99*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" ht="60" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="24" customHeight="1">
       <c r="A100" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B100">
         <v>2</v>
       </c>
       <c r="C100" t="s">
-        <v>107</v>
-      </c>
-      <c r="I100" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A101" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B101" s="4">
+        <v>2</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E101" s="2">
+        <f>IF(COUNT('Turns'!E91,'Turns'!E92,'Turns'!E97)=3,SUM('Turns'!E91,'Turns'!E92,'Turns'!E97),"Unknown")</f>
+        <v>0.00011612568</v>
+      </c>
+      <c r="F101" s="2">
+        <f>IF(COUNT('Turns'!F91,'Turns'!F92,'Turns'!F97)=3,SUM('Turns'!F91,'Turns'!F92,'Turns'!F97),"Unknown")</f>
+        <v>0.000132</v>
+      </c>
+      <c r="G101" s="5">
+        <f>IF(ISNUMBER(E101),ROUND(E101*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>12.0</v>
+      </c>
+      <c r="H101" s="5">
+        <f>IF(ISNUMBER(F101),ROUND(F101*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>13.0</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A102" s="4" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="101" spans="1:13" ht="24" customHeight="1">
-      <c r="A101" t="s">
-        <v>151</v>
-      </c>
-      <c r="B101">
+      <c r="B102" s="4">
         <v>2</v>
       </c>
-      <c r="C101" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" ht="24" customHeight="1">
-      <c r="A102" t="s">
-        <v>151</v>
-      </c>
-      <c r="B102">
+      <c r="C102" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D102" s="4">
+        <v>535</v>
+      </c>
+      <c r="J102" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M102" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" ht="24" customHeight="1">
+      <c r="A103" t="s">
+        <v>153</v>
+      </c>
+      <c r="B103">
         <v>2</v>
       </c>
-      <c r="C102" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A103" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B103" s="4">
-        <v>2</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>109</v>
+      <c r="C103" t="s">
+        <v>127</v>
+      </c>
+      <c r="D103" s="5">
+        <v>0</v>
       </c>
       <c r="E103" s="2">
-        <f>IF(COUNT('Turns'!E93,'Turns'!E94,'Turns'!E99)=3,SUM('Turns'!E93,'Turns'!E94,'Turns'!E99),"Unknown")</f>
-        <v>0.00011357496</v>
+        <f>IF(AND(ISNUMBER(F103),ISNUMBER('Reference data'!$B$3)),F103*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.0</v>
       </c>
       <c r="F103" s="2">
-        <f>IF(COUNT('Turns'!F93,'Turns'!F94,'Turns'!F99)=3,SUM('Turns'!F93,'Turns'!F94,'Turns'!F99),"Unknown")</f>
-        <v>0.0001296</v>
+        <f>IF(D103=0,0,IF(ISNUMBER('Reference data'!C17),D103*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>0.0</v>
       </c>
       <c r="G103" s="5">
         <f>IF(ISNUMBER(E103),ROUND(E103*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="H103" s="5">
         <f>IF(ISNUMBER(F103),ROUND(F103*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
-      </c>
-      <c r="K103" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A104" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B104" s="4">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" ht="24" customHeight="1">
+      <c r="A104" t="s">
+        <v>153</v>
+      </c>
+      <c r="B104">
         <v>2</v>
       </c>
-      <c r="C104" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D104" s="4">
-        <v>531</v>
-      </c>
-      <c r="J104" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M104" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" ht="24" customHeight="1">
+      <c r="C104" t="s">
+        <v>97</v>
+      </c>
+      <c r="D104" s="5">
+        <v>535</v>
+      </c>
+      <c r="E104" s="2">
+        <f>IF(AND(ISNUMBER(F104),ISNUMBER('Reference data'!$B$3)),F104*'Reference data'!$B$3,"Unknown")</f>
+        <v>9.413218e-05</v>
+      </c>
+      <c r="F104" s="2">
+        <f>IF(D104=0,0,IF(ISNUMBER('Reference data'!B17),D104*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>0.000107</v>
+      </c>
+      <c r="G104" s="5">
+        <f>IF(ISNUMBER(E104),ROUND(E104*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+      <c r="H104" s="5">
+        <f>IF(ISNUMBER(F104),ROUND(F104*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" ht="47" customHeight="1">
       <c r="A105" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B105">
         <v>2</v>
@@ -3040,782 +3039,782 @@
       <c r="C105" t="s">
         <v>128</v>
       </c>
-      <c r="D105" s="5">
-        <v>0</v>
-      </c>
-      <c r="E105" s="2">
-        <f>IF(AND(ISNUMBER(F105),ISNUMBER('Reference data'!$B$3)),F105*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="F105" s="2">
-        <f>IF(D105=0,0,IF(ISNUMBER('Reference data'!C17),D105*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>0.0</v>
-      </c>
-      <c r="G105" s="5">
-        <f>IF(ISNUMBER(E105),ROUND(E105*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H105" s="5">
-        <f>IF(ISNUMBER(F105),ROUND(F105*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+      <c r="I105" s="6" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="24" customHeight="1">
       <c r="A106" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B106">
         <v>2</v>
       </c>
       <c r="C106" t="s">
-        <v>97</v>
-      </c>
-      <c r="D106" s="5">
-        <v>531</v>
-      </c>
-      <c r="E106" s="2">
-        <f>IF(AND(ISNUMBER(F106),ISNUMBER('Reference data'!$B$3)),F106*'Reference data'!$B$3,"Unknown")</f>
-        <v>9.306837e-05</v>
-      </c>
-      <c r="F106" s="2">
-        <f>IF(D106=0,0,IF(ISNUMBER('Reference data'!B17),D106*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.0001062</v>
-      </c>
-      <c r="G106" s="5">
-        <f>IF(ISNUMBER(E106),ROUND(E106*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
-      </c>
-      <c r="H106" s="5">
-        <f>IF(ISNUMBER(F106),ROUND(F106*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13" ht="47" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" ht="24" customHeight="1">
       <c r="A107" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B107">
         <v>2</v>
       </c>
       <c r="C107" t="s">
-        <v>129</v>
-      </c>
-      <c r="I107" s="6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" ht="24" customHeight="1">
-      <c r="A108" t="s">
-        <v>154</v>
-      </c>
-      <c r="B108">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A108" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B108" s="4">
         <v>2</v>
       </c>
-      <c r="C108" t="s">
-        <v>103</v>
+      <c r="C108" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D108" s="4">
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="24" customHeight="1">
       <c r="A109" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B109">
         <v>2</v>
       </c>
       <c r="C109" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A110" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B110" s="4">
+        <v>106</v>
+      </c>
+      <c r="D109" s="5">
+        <v>19</v>
+      </c>
+      <c r="E109" s="2">
+        <f>IF(AND(ISNUMBER(F109),ISNUMBER('Reference data'!$B$3)),F109*'Reference data'!$B$3,"Unknown")</f>
+        <v>2.0058072e-05</v>
+      </c>
+      <c r="F109" s="2">
+        <f>IF(D109=0,0,IF(ISNUMBER('Reference data'!E17),D109*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>2.28e-05</v>
+      </c>
+      <c r="G109" s="5">
+        <f>IF(ISNUMBER(E109),ROUND(E109*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+      <c r="H109" s="5">
+        <f>IF(ISNUMBER(F109),ROUND(F109*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" ht="47" customHeight="1">
+      <c r="A110" t="s">
+        <v>153</v>
+      </c>
+      <c r="B110">
         <v>2</v>
       </c>
-      <c r="C110" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D110" s="4">
-        <v>23</v>
+      <c r="C110" t="s">
+        <v>107</v>
+      </c>
+      <c r="I110" s="6" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="24" customHeight="1">
       <c r="A111" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B111">
         <v>2</v>
       </c>
       <c r="C111" t="s">
-        <v>106</v>
-      </c>
-      <c r="D111" s="5">
-        <v>23</v>
-      </c>
-      <c r="E111" s="2">
-        <f>IF(AND(ISNUMBER(F111),ISNUMBER('Reference data'!$B$3)),F111*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.418726e-05</v>
-      </c>
-      <c r="F111" s="2">
-        <f>IF(D111=0,0,IF(ISNUMBER('Reference data'!E17),D111*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.76e-05</v>
-      </c>
-      <c r="G111" s="5">
-        <f>IF(ISNUMBER(E111),ROUND(E111*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-      <c r="H111" s="5">
-        <f>IF(ISNUMBER(F111),ROUND(F111*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13" ht="47" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" ht="24" customHeight="1">
       <c r="A112" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B112">
         <v>2</v>
       </c>
       <c r="C112" t="s">
-        <v>107</v>
-      </c>
-      <c r="I112" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A113" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B113" s="4">
+        <v>2</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E113" s="2">
+        <f>IF(COUNT('Turns'!E103,'Turns'!E104,'Turns'!E109)=3,SUM('Turns'!E103,'Turns'!E104,'Turns'!E109),"Unknown")</f>
+        <v>0.000114190252</v>
+      </c>
+      <c r="F113" s="2">
+        <f>IF(COUNT('Turns'!F103,'Turns'!F104,'Turns'!F109)=3,SUM('Turns'!F103,'Turns'!F104,'Turns'!F109),"Unknown")</f>
+        <v>0.0001298</v>
+      </c>
+      <c r="G113" s="5">
+        <f>IF(ISNUMBER(E113),ROUND(E113*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>11.0</v>
+      </c>
+      <c r="H113" s="5">
+        <f>IF(ISNUMBER(F113),ROUND(F113*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>13.0</v>
+      </c>
+      <c r="K113" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B114" s="4">
+        <v>3</v>
+      </c>
+      <c r="C114" s="4" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="113" spans="1:13" ht="24" customHeight="1">
-      <c r="A113" t="s">
-        <v>154</v>
-      </c>
-      <c r="B113">
-        <v>2</v>
-      </c>
-      <c r="C113" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" ht="24" customHeight="1">
-      <c r="A114" t="s">
-        <v>154</v>
-      </c>
-      <c r="B114">
-        <v>2</v>
-      </c>
-      <c r="C114" t="s">
-        <v>104</v>
+      <c r="E114" s="2">
+        <f>IF(COUNT('Turns'!E126,'Turns'!E142,'Turns'!E157,'Turns'!E169)=4,SUM('Turns'!E126,'Turns'!E142,'Turns'!E157,'Turns'!E169),"Unknown")</f>
+        <v>0.000476291236</v>
+      </c>
+      <c r="F114" s="2">
+        <f>IF(COUNT('Turns'!F126,'Turns'!F142,'Turns'!F157,'Turns'!F169)=4,SUM('Turns'!F126,'Turns'!F142,'Turns'!F157,'Turns'!F169),"Unknown")</f>
+        <v>0.0005414</v>
+      </c>
+      <c r="G114" s="5">
+        <f>IF(ISNUMBER(E114),ROUND(E114*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>48.0</v>
+      </c>
+      <c r="H114" s="5">
+        <f>IF(ISNUMBER(F114),ROUND(F114*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>54.0</v>
       </c>
     </row>
     <row r="115" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A115" s="4" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B115" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E115" s="2">
-        <f>IF(COUNT('Turns'!E105,'Turns'!E106,'Turns'!E111)=3,SUM('Turns'!E105,'Turns'!E106,'Turns'!E111),"Unknown")</f>
-        <v>0.00011725563</v>
-      </c>
-      <c r="F115" s="2">
-        <f>IF(COUNT('Turns'!F105,'Turns'!F106,'Turns'!F111)=3,SUM('Turns'!F105,'Turns'!F106,'Turns'!F111),"Unknown")</f>
-        <v>0.0001338</v>
-      </c>
-      <c r="G115" s="5">
-        <f>IF(ISNUMBER(E115),ROUND(E115*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
-      </c>
-      <c r="H115" s="5">
-        <f>IF(ISNUMBER(F115),ROUND(F115*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
-      </c>
-      <c r="K115" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B116" s="4">
+        <v>94</v>
+      </c>
+      <c r="D115" s="4">
+        <v>569</v>
+      </c>
+      <c r="J115" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M115" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" ht="24" customHeight="1">
+      <c r="A116" t="s">
+        <v>158</v>
+      </c>
+      <c r="B116">
         <v>3</v>
       </c>
-      <c r="C116" s="4" t="s">
-        <v>158</v>
+      <c r="C116" t="s">
+        <v>127</v>
+      </c>
+      <c r="D116" s="5">
+        <v>0</v>
       </c>
       <c r="E116" s="2">
-        <f>IF(COUNT('Turns'!E128,'Turns'!E144,'Turns'!E159,'Turns'!E171)=4,SUM('Turns'!E128,'Turns'!E144,'Turns'!E159,'Turns'!E171),"Unknown")</f>
-        <v>0.0004784871</v>
+        <f>IF(AND(ISNUMBER(F116),ISNUMBER('Reference data'!$B$3)),F116*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.0</v>
       </c>
       <c r="F116" s="2">
-        <f>IF(COUNT('Turns'!F128,'Turns'!F144,'Turns'!F159,'Turns'!F171)=4,SUM('Turns'!F128,'Turns'!F144,'Turns'!F159,'Turns'!F171),"Unknown")</f>
-        <v>0.000546</v>
+        <f>IF(D116=0,0,IF(ISNUMBER('Reference data'!C17),D116*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>0.0</v>
       </c>
       <c r="G116" s="5">
         <f>IF(ISNUMBER(E116),ROUND(E116*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>48.0</v>
+        <v>0.0</v>
       </c>
       <c r="H116" s="5">
         <f>IF(ISNUMBER(F116),ROUND(F116*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>55.0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A117" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B117" s="4">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" ht="24" customHeight="1">
+      <c r="A117" t="s">
+        <v>158</v>
+      </c>
+      <c r="B117">
         <v>3</v>
       </c>
-      <c r="C117" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D117" s="4">
+      <c r="C117" t="s">
+        <v>97</v>
+      </c>
+      <c r="D117" s="5">
         <v>569</v>
       </c>
-      <c r="J117" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M117" s="4" t="s">
-        <v>160</v>
+      <c r="E117" s="2">
+        <f>IF(AND(ISNUMBER(F117),ISNUMBER('Reference data'!$B$3)),F117*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.000100114412</v>
+      </c>
+      <c r="F117" s="2">
+        <f>IF(D117=0,0,IF(ISNUMBER('Reference data'!B17),D117*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>0.0001138</v>
+      </c>
+      <c r="G117" s="5">
+        <f>IF(ISNUMBER(E117),ROUND(E117*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>10.0</v>
+      </c>
+      <c r="H117" s="5">
+        <f>IF(ISNUMBER(F117),ROUND(F117*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>11.0</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="24" customHeight="1">
       <c r="A118" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B118">
         <v>3</v>
       </c>
       <c r="C118" t="s">
-        <v>128</v>
-      </c>
-      <c r="D118" s="5">
-        <v>0</v>
-      </c>
-      <c r="E118" s="2">
-        <f>IF(AND(ISNUMBER(F118),ISNUMBER('Reference data'!$B$3)),F118*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="F118" s="2">
-        <f>IF(D118=0,0,IF(ISNUMBER('Reference data'!C17),D118*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>0.0</v>
-      </c>
-      <c r="G118" s="5">
-        <f>IF(ISNUMBER(E118),ROUND(E118*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H118" s="5">
-        <f>IF(ISNUMBER(F118),ROUND(F118*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>101</v>
+      </c>
+      <c r="I118" s="6" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="119" spans="1:13" ht="24" customHeight="1">
       <c r="A119" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B119">
         <v>3</v>
       </c>
       <c r="C119" t="s">
-        <v>97</v>
-      </c>
-      <c r="D119" s="5">
-        <v>569</v>
-      </c>
-      <c r="E119" s="2">
-        <f>IF(AND(ISNUMBER(F119),ISNUMBER('Reference data'!$B$3)),F119*'Reference data'!$B$3,"Unknown")</f>
-        <v>9.972863e-05</v>
-      </c>
-      <c r="F119" s="2">
-        <f>IF(D119=0,0,IF(ISNUMBER('Reference data'!B17),D119*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.0001138</v>
-      </c>
-      <c r="G119" s="5">
-        <f>IF(ISNUMBER(E119),ROUND(E119*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
-      </c>
-      <c r="H119" s="5">
-        <f>IF(ISNUMBER(F119),ROUND(F119*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>103</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="24" customHeight="1">
       <c r="A120" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B120">
         <v>3</v>
       </c>
       <c r="C120" t="s">
-        <v>101</v>
-      </c>
-      <c r="I120" s="6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13" ht="24" customHeight="1">
-      <c r="A121" t="s">
-        <v>159</v>
-      </c>
-      <c r="B121">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A121" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B121" s="4">
         <v>3</v>
       </c>
-      <c r="C121" t="s">
-        <v>103</v>
+      <c r="C121" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D121" s="4">
+        <v>53</v>
       </c>
     </row>
     <row r="122" spans="1:13" ht="24" customHeight="1">
       <c r="A122" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B122">
         <v>3</v>
       </c>
       <c r="C122" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="123" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A123" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B123" s="4">
+        <v>106</v>
+      </c>
+      <c r="D122" s="5">
+        <v>53</v>
+      </c>
+      <c r="E122" s="2">
+        <f>IF(AND(ISNUMBER(F122),ISNUMBER('Reference data'!$B$3)),F122*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.5951464e-05</v>
+      </c>
+      <c r="F122" s="2">
+        <f>IF(D122=0,0,IF(ISNUMBER('Reference data'!E17),D122*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>6.36e-05</v>
+      </c>
+      <c r="G122" s="5">
+        <f>IF(ISNUMBER(E122),ROUND(E122*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="H122" s="5">
+        <f>IF(ISNUMBER(F122),ROUND(F122*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" ht="125" customHeight="1">
+      <c r="A123" t="s">
+        <v>158</v>
+      </c>
+      <c r="B123">
         <v>3</v>
       </c>
-      <c r="C123" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D123" s="4">
-        <v>54</v>
+      <c r="C123" t="s">
+        <v>107</v>
+      </c>
+      <c r="I123" s="6" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="24" customHeight="1">
       <c r="A124" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B124">
         <v>3</v>
       </c>
       <c r="C124" t="s">
-        <v>106</v>
-      </c>
-      <c r="D124" s="5">
-        <v>54</v>
-      </c>
-      <c r="E124" s="2">
-        <f>IF(AND(ISNUMBER(F124),ISNUMBER('Reference data'!$B$3)),F124*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.678748e-05</v>
-      </c>
-      <c r="F124" s="2">
-        <f>IF(D124=0,0,IF(ISNUMBER('Reference data'!E17),D124*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>6.48e-05</v>
-      </c>
-      <c r="G124" s="5">
-        <f>IF(ISNUMBER(E124),ROUND(E124*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="H124" s="5">
-        <f>IF(ISNUMBER(F124),ROUND(F124*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13" ht="125" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" ht="24" customHeight="1">
       <c r="A125" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B125">
         <v>3</v>
       </c>
       <c r="C125" t="s">
-        <v>107</v>
-      </c>
-      <c r="I125" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A126" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B126" s="4">
+        <v>3</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E126" s="2">
+        <f>IF(COUNT('Turns'!E116,'Turns'!E117,'Turns'!E122)=3,SUM('Turns'!E116,'Turns'!E117,'Turns'!E122),"Unknown")</f>
+        <v>0.000156065876</v>
+      </c>
+      <c r="F126" s="2">
+        <f>IF(COUNT('Turns'!F116,'Turns'!F117,'Turns'!F122)=3,SUM('Turns'!F116,'Turns'!F117,'Turns'!F122),"Unknown")</f>
+        <v>0.0001774</v>
+      </c>
+      <c r="G126" s="5">
+        <f>IF(ISNUMBER(E126),ROUND(E126*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>16.0</v>
+      </c>
+      <c r="H126" s="5">
+        <f>IF(ISNUMBER(F126),ROUND(F126*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>18.0</v>
+      </c>
+      <c r="K126" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B127" s="4">
+        <v>3</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="K127" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="M127" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="24" customHeight="1">
-      <c r="A126" t="s">
-        <v>159</v>
-      </c>
-      <c r="B126">
+    <row r="128" spans="1:13" ht="47" customHeight="1">
+      <c r="B128">
         <v>3</v>
       </c>
-      <c r="C126" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="127" spans="1:13" ht="24" customHeight="1">
-      <c r="A127" t="s">
-        <v>159</v>
-      </c>
-      <c r="B127">
+      <c r="C128" t="s">
+        <v>113</v>
+      </c>
+      <c r="I128" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" ht="47" customHeight="1">
+      <c r="B129">
         <v>3</v>
       </c>
-      <c r="C127" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="128" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A128" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B128" s="4">
+      <c r="C129" t="s">
+        <v>115</v>
+      </c>
+      <c r="I129" s="6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A130" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B130" s="4">
         <v>3</v>
       </c>
-      <c r="C128" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E128" s="2">
-        <f>IF(COUNT('Turns'!E118,'Turns'!E119,'Turns'!E124)=3,SUM('Turns'!E118,'Turns'!E119,'Turns'!E124),"Unknown")</f>
-        <v>0.00015651611</v>
-      </c>
-      <c r="F128" s="2">
-        <f>IF(COUNT('Turns'!F118,'Turns'!F119,'Turns'!F124)=3,SUM('Turns'!F118,'Turns'!F119,'Turns'!F124),"Unknown")</f>
-        <v>0.0001786</v>
-      </c>
-      <c r="G128" s="5">
-        <f>IF(ISNUMBER(E128),ROUND(E128*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
-      </c>
-      <c r="H128" s="5">
-        <f>IF(ISNUMBER(F128),ROUND(F128*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
-      </c>
-      <c r="K128" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B129" s="4">
-        <v>3</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="K129" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="M129" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="130" spans="1:13" ht="47" customHeight="1">
-      <c r="B130">
-        <v>3</v>
-      </c>
-      <c r="C130" t="s">
-        <v>113</v>
-      </c>
-      <c r="I130" s="6" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13" ht="47" customHeight="1">
+      <c r="C130" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D130" s="4">
+        <v>185</v>
+      </c>
+      <c r="J130" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M130" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" ht="24" customHeight="1">
+      <c r="A131" t="s">
+        <v>165</v>
+      </c>
       <c r="B131">
         <v>3</v>
       </c>
       <c r="C131" t="s">
-        <v>115</v>
-      </c>
-      <c r="I131" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D131" s="5">
+        <v>185</v>
+      </c>
+      <c r="E131" s="2">
+        <f>IF(AND(ISNUMBER(F131),ISNUMBER('Reference data'!$B$3)),F131*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.255038e-05</v>
+      </c>
+      <c r="F131" s="2">
+        <f>IF(D131=0,0,IF(ISNUMBER('Reference data'!B17),D131*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>3.7e-05</v>
+      </c>
+      <c r="G131" s="5">
+        <f>IF(ISNUMBER(E131),ROUND(E131*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H131" s="5">
+        <f>IF(ISNUMBER(F131),ROUND(F131*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" ht="24" customHeight="1">
+      <c r="A132" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="132" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A132" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B132" s="4">
+      <c r="B132">
         <v>3</v>
       </c>
-      <c r="C132" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D132" s="4">
-        <v>186</v>
-      </c>
-      <c r="J132" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M132" s="4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="133" spans="1:13" ht="24" customHeight="1">
+      <c r="C132" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" ht="73" customHeight="1">
       <c r="A133" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B133">
         <v>3</v>
       </c>
       <c r="C133" t="s">
-        <v>97</v>
-      </c>
-      <c r="D133" s="5">
-        <v>186</v>
-      </c>
-      <c r="E133" s="2">
-        <f>IF(AND(ISNUMBER(F133),ISNUMBER('Reference data'!$B$3)),F133*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.260022e-05</v>
-      </c>
-      <c r="F133" s="2">
-        <f>IF(D133=0,0,IF(ISNUMBER('Reference data'!B17),D133*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>3.72e-05</v>
-      </c>
-      <c r="G133" s="5">
-        <f>IF(ISNUMBER(E133),ROUND(E133*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H133" s="5">
-        <f>IF(ISNUMBER(F133),ROUND(F133*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>99</v>
+      </c>
+      <c r="I133" s="6" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="134" spans="1:13" ht="24" customHeight="1">
       <c r="A134" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B134">
         <v>3</v>
       </c>
       <c r="C134" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="135" spans="1:13" ht="73" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" ht="24" customHeight="1">
       <c r="A135" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B135">
         <v>3</v>
       </c>
       <c r="C135" t="s">
-        <v>99</v>
-      </c>
-      <c r="I135" s="6" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="136" spans="1:13" ht="24" customHeight="1">
-      <c r="A136" t="s">
-        <v>166</v>
-      </c>
-      <c r="B136">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A136" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B136" s="4">
         <v>3</v>
       </c>
-      <c r="C136" t="s">
-        <v>103</v>
+      <c r="C136" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D136" s="4">
+        <v>41</v>
       </c>
     </row>
     <row r="137" spans="1:13" ht="24" customHeight="1">
       <c r="A137" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B137">
         <v>3</v>
       </c>
       <c r="C137" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="138" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A138" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B138" s="4">
+        <v>168</v>
+      </c>
+      <c r="D137" s="5">
+        <v>9</v>
+      </c>
+      <c r="E137" s="2">
+        <f>IF(AND(ISNUMBER(F137),ISNUMBER('Reference data'!$B$3)),F137*'Reference data'!$B$3,"Unknown")</f>
+        <v>9.501192e-06</v>
+      </c>
+      <c r="F137" s="2">
+        <f>IF(D137=0,0,IF(ISNUMBER('Reference data'!F17),D137*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>1.08e-05</v>
+      </c>
+      <c r="G137" s="5">
+        <f>IF(ISNUMBER(E137),ROUND(E137*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H137" s="5">
+        <f>IF(ISNUMBER(F137),ROUND(F137*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" ht="24" customHeight="1">
+      <c r="A138" t="s">
+        <v>165</v>
+      </c>
+      <c r="B138">
         <v>3</v>
       </c>
-      <c r="C138" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D138" s="4">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="139" spans="1:13" ht="24" customHeight="1">
+      <c r="C138" t="s">
+        <v>106</v>
+      </c>
+      <c r="D138" s="5">
+        <v>32</v>
+      </c>
+      <c r="E138" s="2">
+        <f>IF(AND(ISNUMBER(F138),ISNUMBER('Reference data'!$B$3)),F138*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.3782016e-05</v>
+      </c>
+      <c r="F138" s="2">
+        <f>IF(D138=0,0,IF(ISNUMBER('Reference data'!E17),D138*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>3.84e-05</v>
+      </c>
+      <c r="G138" s="5">
+        <f>IF(ISNUMBER(E138),ROUND(E138*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H138" s="5">
+        <f>IF(ISNUMBER(F138),ROUND(F138*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" ht="294" customHeight="1">
       <c r="A139" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B139">
         <v>3</v>
       </c>
       <c r="C139" t="s">
-        <v>120</v>
-      </c>
-      <c r="D139" s="5">
-        <v>9</v>
-      </c>
-      <c r="E139" s="2">
-        <f>IF(AND(ISNUMBER(F139),ISNUMBER('Reference data'!$B$3)),F139*'Reference data'!$B$3,"Unknown")</f>
-        <v>9.46458e-06</v>
-      </c>
-      <c r="F139" s="2">
-        <f>IF(D139=0,0,IF(ISNUMBER('Reference data'!F17),D139*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>1.08e-05</v>
-      </c>
-      <c r="G139" s="5">
-        <f>IF(ISNUMBER(E139),ROUND(E139*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-      <c r="H139" s="5">
-        <f>IF(ISNUMBER(F139),ROUND(F139*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
+        <v>107</v>
+      </c>
+      <c r="I139" s="6" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="140" spans="1:13" ht="24" customHeight="1">
       <c r="A140" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B140">
         <v>3</v>
       </c>
       <c r="C140" t="s">
-        <v>106</v>
-      </c>
-      <c r="D140" s="5">
-        <v>36</v>
-      </c>
-      <c r="E140" s="2">
-        <f>IF(AND(ISNUMBER(F140),ISNUMBER('Reference data'!$B$3)),F140*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.785832e-05</v>
-      </c>
-      <c r="F140" s="2">
-        <f>IF(D140=0,0,IF(ISNUMBER('Reference data'!E17),D140*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>4.32e-05</v>
-      </c>
-      <c r="G140" s="5">
-        <f>IF(ISNUMBER(E140),ROUND(E140*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H140" s="5">
-        <f>IF(ISNUMBER(F140),ROUND(F140*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:13" ht="307" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" ht="24" customHeight="1">
       <c r="A141" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B141">
         <v>3</v>
       </c>
       <c r="C141" t="s">
-        <v>107</v>
-      </c>
-      <c r="I141" s="6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="142" spans="1:13" ht="24" customHeight="1">
-      <c r="A142" t="s">
-        <v>166</v>
-      </c>
-      <c r="B142">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A142" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B142" s="4">
         <v>3</v>
       </c>
-      <c r="C142" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="143" spans="1:13" ht="24" customHeight="1">
-      <c r="A143" t="s">
-        <v>166</v>
-      </c>
-      <c r="B143">
+      <c r="C142" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E142" s="2">
+        <f>IF(COUNT('Turns'!E131,'Turns'!E137,'Turns'!E138)=3,SUM('Turns'!E131,'Turns'!E137,'Turns'!E138),"Unknown")</f>
+        <v>7.5833588e-05</v>
+      </c>
+      <c r="F142" s="2">
+        <f>IF(COUNT('Turns'!F131,'Turns'!F137,'Turns'!F138)=3,SUM('Turns'!F131,'Turns'!F137,'Turns'!F138),"Unknown")</f>
+        <v>8.62e-05</v>
+      </c>
+      <c r="G142" s="5">
+        <f>IF(ISNUMBER(E142),ROUND(E142*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="H142" s="5">
+        <f>IF(ISNUMBER(F142),ROUND(F142*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+      <c r="K142" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B143" s="4">
         <v>3</v>
       </c>
-      <c r="C143" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A144" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B144" s="4">
+      <c r="C143" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K143" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="M143" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" ht="24" customHeight="1">
+      <c r="B144">
         <v>3</v>
       </c>
-      <c r="C144" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E144" s="2">
-        <f>IF(COUNT('Turns'!E133,'Turns'!E139,'Turns'!E140)=3,SUM('Turns'!E133,'Turns'!E139,'Turns'!E140),"Unknown")</f>
-        <v>7.992312e-05</v>
-      </c>
-      <c r="F144" s="2">
-        <f>IF(COUNT('Turns'!F133,'Turns'!F139,'Turns'!F140)=3,SUM('Turns'!F133,'Turns'!F139,'Turns'!F140),"Unknown")</f>
-        <v>9.12e-05</v>
-      </c>
-      <c r="G144" s="5">
-        <f>IF(ISNUMBER(E144),ROUND(E144*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
-      </c>
-      <c r="H144" s="5">
-        <f>IF(ISNUMBER(F144),ROUND(F144*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
-      </c>
-      <c r="K144" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B145" s="4">
+      <c r="C144" t="s">
+        <v>113</v>
+      </c>
+      <c r="I144" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" ht="60" customHeight="1">
+      <c r="B145">
         <v>3</v>
       </c>
-      <c r="C145" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="K145" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="M145" s="4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="146" spans="1:13" ht="34" customHeight="1">
-      <c r="B146">
+      <c r="C145" t="s">
+        <v>115</v>
+      </c>
+      <c r="I145" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A146" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B146" s="4">
         <v>3</v>
       </c>
-      <c r="C146" t="s">
-        <v>113</v>
-      </c>
-      <c r="I146" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="147" spans="1:13" ht="60" customHeight="1">
+      <c r="C146" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D146" s="4">
+        <v>291</v>
+      </c>
+      <c r="J146" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M146" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" ht="24" customHeight="1">
+      <c r="A147" t="s">
+        <v>174</v>
+      </c>
       <c r="B147">
         <v>3</v>
       </c>
       <c r="C147" t="s">
-        <v>115</v>
-      </c>
-      <c r="I147" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A148" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D147" s="5">
+        <v>0</v>
+      </c>
+      <c r="E147" s="2">
+        <f>IF(AND(ISNUMBER(F147),ISNUMBER('Reference data'!$B$3)),F147*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="F147" s="2">
+        <f>IF(D147=0,0,IF(ISNUMBER('Reference data'!C17),D147*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>0.0</v>
+      </c>
+      <c r="G147" s="5">
+        <f>IF(ISNUMBER(E147),ROUND(E147*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H147" s="5">
+        <f>IF(ISNUMBER(F147),ROUND(F147*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" ht="24" customHeight="1">
+      <c r="A148" t="s">
         <v>174</v>
       </c>
-      <c r="B148" s="4">
+      <c r="B148">
         <v>3</v>
       </c>
-      <c r="C148" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D148" s="4">
-        <v>296</v>
-      </c>
-      <c r="J148" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M148" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="149" spans="1:13" ht="24" customHeight="1">
+      <c r="C148" t="s">
+        <v>97</v>
+      </c>
+      <c r="D148" s="5">
+        <v>291</v>
+      </c>
+      <c r="E148" s="2">
+        <f>IF(AND(ISNUMBER(F148),ISNUMBER('Reference data'!$B$3)),F148*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.1200868e-05</v>
+      </c>
+      <c r="F148" s="2">
+        <f>IF(D148=0,0,IF(ISNUMBER('Reference data'!B17),D148*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>5.82e-05</v>
+      </c>
+      <c r="G148" s="5">
+        <f>IF(ISNUMBER(E148),ROUND(E148*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+      <c r="H148" s="5">
+        <f>IF(ISNUMBER(F148),ROUND(F148*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" ht="60" customHeight="1">
       <c r="A149" t="s">
         <v>174</v>
       </c>
@@ -3825,24 +3824,8 @@
       <c r="C149" t="s">
         <v>128</v>
       </c>
-      <c r="D149" s="5">
-        <v>0</v>
-      </c>
-      <c r="E149" s="2">
-        <f>IF(AND(ISNUMBER(F149),ISNUMBER('Reference data'!$B$3)),F149*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="F149" s="2">
-        <f>IF(D149=0,0,IF(ISNUMBER('Reference data'!C17),D149*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>0.0</v>
-      </c>
-      <c r="G149" s="5">
-        <f>IF(ISNUMBER(E149),ROUND(E149*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H149" s="5">
-        <f>IF(ISNUMBER(F149),ROUND(F149*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+      <c r="I149" s="6" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="24" customHeight="1">
@@ -3853,29 +3836,10 @@
         <v>3</v>
       </c>
       <c r="C150" t="s">
-        <v>97</v>
-      </c>
-      <c r="D150" s="5">
-        <v>296</v>
-      </c>
-      <c r="E150" s="2">
-        <f>IF(AND(ISNUMBER(F150),ISNUMBER('Reference data'!$B$3)),F150*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.187992e-05</v>
-      </c>
-      <c r="F150" s="2">
-        <f>IF(D150=0,0,IF(ISNUMBER('Reference data'!B17),D150*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>5.92e-05</v>
-      </c>
-      <c r="G150" s="5">
-        <f>IF(ISNUMBER(E150),ROUND(E150*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-      <c r="H150" s="5">
-        <f>IF(ISNUMBER(F150),ROUND(F150*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13" ht="60" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" ht="24" customHeight="1">
       <c r="A151" t="s">
         <v>174</v>
       </c>
@@ -3883,21 +3847,21 @@
         <v>3</v>
       </c>
       <c r="C151" t="s">
-        <v>129</v>
-      </c>
-      <c r="I151" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13" ht="24" customHeight="1">
-      <c r="A152" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A152" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="B152">
+      <c r="B152" s="4">
         <v>3</v>
       </c>
-      <c r="C152" t="s">
-        <v>103</v>
+      <c r="C152" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D152" s="4">
+        <v>50</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="24" customHeight="1">
@@ -3908,21 +3872,40 @@
         <v>3</v>
       </c>
       <c r="C153" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A154" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D153" s="5">
+        <v>50</v>
+      </c>
+      <c r="E153" s="2">
+        <f>IF(AND(ISNUMBER(F153),ISNUMBER('Reference data'!$B$3)),F153*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.27844e-05</v>
+      </c>
+      <c r="F153" s="2">
+        <f>IF(D153=0,0,IF(ISNUMBER('Reference data'!E17),D153*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>6e-05</v>
+      </c>
+      <c r="G153" s="5">
+        <f>IF(ISNUMBER(E153),ROUND(E153*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+      <c r="H153" s="5">
+        <f>IF(ISNUMBER(F153),ROUND(F153*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" ht="60" customHeight="1">
+      <c r="A154" t="s">
         <v>174</v>
       </c>
-      <c r="B154" s="4">
+      <c r="B154">
         <v>3</v>
       </c>
-      <c r="C154" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D154" s="4">
-        <v>48</v>
+      <c r="C154" t="s">
+        <v>107</v>
+      </c>
+      <c r="I154" s="6" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="155" spans="1:13" ht="24" customHeight="1">
@@ -3933,29 +3916,10 @@
         <v>3</v>
       </c>
       <c r="C155" t="s">
-        <v>106</v>
-      </c>
-      <c r="D155" s="5">
-        <v>48</v>
-      </c>
-      <c r="E155" s="2">
-        <f>IF(AND(ISNUMBER(F155),ISNUMBER('Reference data'!$B$3)),F155*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.047776e-05</v>
-      </c>
-      <c r="F155" s="2">
-        <f>IF(D155=0,0,IF(ISNUMBER('Reference data'!E17),D155*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>5.76e-05</v>
-      </c>
-      <c r="G155" s="5">
-        <f>IF(ISNUMBER(E155),ROUND(E155*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-      <c r="H155" s="5">
-        <f>IF(ISNUMBER(F155),ROUND(F155*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13" ht="60" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" ht="24" customHeight="1">
       <c r="A156" t="s">
         <v>174</v>
       </c>
@@ -3963,85 +3927,120 @@
         <v>3</v>
       </c>
       <c r="C156" t="s">
-        <v>107</v>
-      </c>
-      <c r="I156" s="6" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="157" spans="1:13" ht="24" customHeight="1">
-      <c r="A157" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A157" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="B157">
+      <c r="B157" s="4">
         <v>3</v>
       </c>
-      <c r="C157" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="158" spans="1:13" ht="24" customHeight="1">
-      <c r="A158" t="s">
-        <v>174</v>
-      </c>
-      <c r="B158">
+      <c r="C157" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E157" s="2">
+        <f>IF(COUNT('Turns'!E147,'Turns'!E148,'Turns'!E153)=3,SUM('Turns'!E147,'Turns'!E148,'Turns'!E153),"Unknown")</f>
+        <v>0.000103985268</v>
+      </c>
+      <c r="F157" s="2">
+        <f>IF(COUNT('Turns'!F147,'Turns'!F148,'Turns'!F153)=3,SUM('Turns'!F147,'Turns'!F148,'Turns'!F153),"Unknown")</f>
+        <v>0.0001182</v>
+      </c>
+      <c r="G157" s="5">
+        <f>IF(ISNUMBER(E157),ROUND(E157*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>10.0</v>
+      </c>
+      <c r="H157" s="5">
+        <f>IF(ISNUMBER(F157),ROUND(F157*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>12.0</v>
+      </c>
+      <c r="K157" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A158" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B158" s="4">
         <v>3</v>
       </c>
-      <c r="C158" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="159" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A159" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B159" s="4">
+      <c r="C158" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D158" s="4">
+        <v>678</v>
+      </c>
+      <c r="J158" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M158" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" ht="24" customHeight="1">
+      <c r="A159" t="s">
+        <v>177</v>
+      </c>
+      <c r="B159">
         <v>3</v>
       </c>
-      <c r="C159" s="4" t="s">
-        <v>109</v>
+      <c r="C159" t="s">
+        <v>127</v>
+      </c>
+      <c r="D159" s="5">
+        <v>0</v>
       </c>
       <c r="E159" s="2">
-        <f>IF(COUNT('Turns'!E149,'Turns'!E150,'Turns'!E155)=3,SUM('Turns'!E149,'Turns'!E150,'Turns'!E155),"Unknown")</f>
-        <v>0.00010235768</v>
+        <f>IF(AND(ISNUMBER(F159),ISNUMBER('Reference data'!$B$3)),F159*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.0</v>
       </c>
       <c r="F159" s="2">
-        <f>IF(COUNT('Turns'!F149,'Turns'!F150,'Turns'!F155)=3,SUM('Turns'!F149,'Turns'!F150,'Turns'!F155),"Unknown")</f>
-        <v>0.0001168</v>
+        <f>IF(D159=0,0,IF(ISNUMBER('Reference data'!C17),D159*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>0.0</v>
       </c>
       <c r="G159" s="5">
         <f>IF(ISNUMBER(E159),ROUND(E159*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H159" s="5">
         <f>IF(ISNUMBER(F159),ROUND(F159*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" ht="24" customHeight="1">
+      <c r="A160" t="s">
+        <v>177</v>
+      </c>
+      <c r="B160">
+        <v>3</v>
+      </c>
+      <c r="C160" t="s">
+        <v>97</v>
+      </c>
+      <c r="D160" s="5">
+        <v>678</v>
+      </c>
+      <c r="E160" s="2">
+        <f>IF(AND(ISNUMBER(F160),ISNUMBER('Reference data'!$B$3)),F160*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.000119292744</v>
+      </c>
+      <c r="F160" s="2">
+        <f>IF(D160=0,0,IF(ISNUMBER('Reference data'!B17),D160*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>0.0001356</v>
+      </c>
+      <c r="G160" s="5">
+        <f>IF(ISNUMBER(E160),ROUND(E160*'Reference data'!$B$2,0),"Unknown")</f>
         <v>12.0</v>
       </c>
-      <c r="K159" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="160" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A160" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B160" s="4">
-        <v>3</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D160" s="4">
-        <v>677</v>
-      </c>
-      <c r="J160" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M160" s="4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="161" spans="1:11" ht="24" customHeight="1">
+      <c r="H160" s="5">
+        <f>IF(ISNUMBER(F160),ROUND(F160*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" ht="34" customHeight="1">
       <c r="A161" t="s">
         <v>177</v>
       </c>
@@ -4051,24 +4050,8 @@
       <c r="C161" t="s">
         <v>128</v>
       </c>
-      <c r="D161" s="5">
-        <v>0</v>
-      </c>
-      <c r="E161" s="2">
-        <f>IF(AND(ISNUMBER(F161),ISNUMBER('Reference data'!$B$3)),F161*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="F161" s="2">
-        <f>IF(D161=0,0,IF(ISNUMBER('Reference data'!C17),D161*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>0.0</v>
-      </c>
-      <c r="G161" s="5">
-        <f>IF(ISNUMBER(E161),ROUND(E161*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H161" s="5">
-        <f>IF(ISNUMBER(F161),ROUND(F161*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+      <c r="I161" s="6" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="162" spans="1:11" ht="24" customHeight="1">
@@ -4079,29 +4062,10 @@
         <v>3</v>
       </c>
       <c r="C162" t="s">
-        <v>97</v>
-      </c>
-      <c r="D162" s="5">
-        <v>677</v>
-      </c>
-      <c r="E162" s="2">
-        <f>IF(AND(ISNUMBER(F162),ISNUMBER('Reference data'!$B$3)),F162*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00011865779</v>
-      </c>
-      <c r="F162" s="2">
-        <f>IF(D162=0,0,IF(ISNUMBER('Reference data'!B17),D162*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.0001354</v>
-      </c>
-      <c r="G162" s="5">
-        <f>IF(ISNUMBER(E162),ROUND(E162*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
-      </c>
-      <c r="H162" s="5">
-        <f>IF(ISNUMBER(F162),ROUND(F162*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11" ht="34" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" ht="24" customHeight="1">
       <c r="A163" t="s">
         <v>177</v>
       </c>
@@ -4109,21 +4073,21 @@
         <v>3</v>
       </c>
       <c r="C163" t="s">
-        <v>129</v>
-      </c>
-      <c r="I163" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11" ht="24" customHeight="1">
-      <c r="A164" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A164" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B164">
+      <c r="B164" s="4">
         <v>3</v>
       </c>
-      <c r="C164" t="s">
-        <v>103</v>
+      <c r="C164" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D164" s="4">
+        <v>20</v>
       </c>
     </row>
     <row r="165" spans="1:11" ht="24" customHeight="1">
@@ -4134,21 +4098,40 @@
         <v>3</v>
       </c>
       <c r="C165" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A166" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D165" s="5">
+        <v>20</v>
+      </c>
+      <c r="E165" s="2">
+        <f>IF(AND(ISNUMBER(F165),ISNUMBER('Reference data'!$B$3)),F165*'Reference data'!$B$3,"Unknown")</f>
+        <v>2.111376e-05</v>
+      </c>
+      <c r="F165" s="2">
+        <f>IF(D165=0,0,IF(ISNUMBER('Reference data'!E17),D165*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>2.4e-05</v>
+      </c>
+      <c r="G165" s="5">
+        <f>IF(ISNUMBER(E165),ROUND(E165*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+      <c r="H165" s="5">
+        <f>IF(ISNUMBER(F165),ROUND(F165*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" ht="47" customHeight="1">
+      <c r="A166" t="s">
         <v>177</v>
       </c>
-      <c r="B166" s="4">
+      <c r="B166">
         <v>3</v>
       </c>
-      <c r="C166" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D166" s="4">
-        <v>20</v>
+      <c r="C166" t="s">
+        <v>107</v>
+      </c>
+      <c r="I166" s="6" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="167" spans="1:11" ht="24" customHeight="1">
@@ -4159,29 +4142,10 @@
         <v>3</v>
       </c>
       <c r="C167" t="s">
-        <v>106</v>
-      </c>
-      <c r="D167" s="5">
-        <v>20</v>
-      </c>
-      <c r="E167" s="2">
-        <f>IF(AND(ISNUMBER(F167),ISNUMBER('Reference data'!$B$3)),F167*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.10324e-05</v>
-      </c>
-      <c r="F167" s="2">
-        <f>IF(D167=0,0,IF(ISNUMBER('Reference data'!E17),D167*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.4e-05</v>
-      </c>
-      <c r="G167" s="5">
-        <f>IF(ISNUMBER(E167),ROUND(E167*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-      <c r="H167" s="5">
-        <f>IF(ISNUMBER(F167),ROUND(F167*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:11" ht="47" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" ht="24" customHeight="1">
       <c r="A168" t="s">
         <v>177</v>
       </c>
@@ -4189,66 +4153,41 @@
         <v>3</v>
       </c>
       <c r="C168" t="s">
-        <v>107</v>
-      </c>
-      <c r="I168" s="6" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="169" spans="1:11" ht="24" customHeight="1">
-      <c r="A169" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A169" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B169">
+      <c r="B169" s="4">
         <v>3</v>
       </c>
-      <c r="C169" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="170" spans="1:11" ht="24" customHeight="1">
-      <c r="A170" t="s">
-        <v>177</v>
-      </c>
-      <c r="B170">
-        <v>3</v>
-      </c>
-      <c r="C170" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="171" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A171" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B171" s="4">
-        <v>3</v>
-      </c>
-      <c r="C171" s="4" t="s">
+      <c r="C169" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E171" s="2">
-        <f>IF(COUNT('Turns'!E161,'Turns'!E162,'Turns'!E167)=3,SUM('Turns'!E161,'Turns'!E162,'Turns'!E167),"Unknown")</f>
-        <v>0.00013969019</v>
-      </c>
-      <c r="F171" s="2">
-        <f>IF(COUNT('Turns'!F161,'Turns'!F162,'Turns'!F167)=3,SUM('Turns'!F161,'Turns'!F162,'Turns'!F167),"Unknown")</f>
-        <v>0.0001594</v>
-      </c>
-      <c r="G171" s="5">
-        <f>IF(ISNUMBER(E171),ROUND(E171*'Reference data'!$B$2,0),"Unknown")</f>
+      <c r="E169" s="2">
+        <f>IF(COUNT('Turns'!E159,'Turns'!E160,'Turns'!E165)=3,SUM('Turns'!E159,'Turns'!E160,'Turns'!E165),"Unknown")</f>
+        <v>0.000140406504</v>
+      </c>
+      <c r="F169" s="2">
+        <f>IF(COUNT('Turns'!F159,'Turns'!F160,'Turns'!F165)=3,SUM('Turns'!F159,'Turns'!F160,'Turns'!F165),"Unknown")</f>
+        <v>0.0001596</v>
+      </c>
+      <c r="G169" s="5">
+        <f>IF(ISNUMBER(E169),ROUND(E169*'Reference data'!$B$2,0),"Unknown")</f>
         <v>14.0</v>
       </c>
-      <c r="H171" s="5">
-        <f>IF(ISNUMBER(F171),ROUND(F171*'Reference data'!$B$2,0),"Unknown")</f>
+      <c r="H169" s="5">
+        <f>IF(ISNUMBER(F169),ROUND(F169*'Reference data'!$B$2,0),"Unknown")</f>
         <v>16.0</v>
       </c>
-      <c r="K171" s="4" t="s">
+      <c r="K169" s="4" t="s">
         <v>110</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE171">
+  <conditionalFormatting sqref="A2:AE169">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -4390,27 +4329,27 @@
         <v>49</v>
       </c>
       <c r="J2" s="2">
-        <f>IF(COUNT('Turns'!D5,'Turns'!D21,'Turns'!D38,'Turns'!D50)=4,SUM('Turns'!D5,'Turns'!D21,'Turns'!D38,'Turns'!D50),"Unknown")</f>
-        <v>1110.0</v>
+        <f>IF(COUNT('Turns'!D5,'Turns'!D21,'Turns'!D37,'Turns'!D49)=4,SUM('Turns'!D5,'Turns'!D21,'Turns'!D37,'Turns'!D49),"Unknown")</f>
+        <v>1086.0</v>
       </c>
       <c r="K2" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E21,'Turns'!E38,'Turns'!E50)=4,SUM('Turns'!E5,'Turns'!E21,'Turns'!E38,'Turns'!E50),"Unknown")</f>
-        <v>0.0001945497</v>
+        <f>IF(COUNT('Turns'!E5,'Turns'!E21,'Turns'!E37,'Turns'!E49)=4,SUM('Turns'!E5,'Turns'!E21,'Turns'!E37,'Turns'!E49),"Unknown")</f>
+        <v>0.000191079528</v>
       </c>
       <c r="L2" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F21,'Turns'!F38,'Turns'!F50)=4,SUM('Turns'!F5,'Turns'!F21,'Turns'!F38,'Turns'!F50),"Unknown")</f>
-        <v>0.000222</v>
+        <f>IF(COUNT('Turns'!F5,'Turns'!F21,'Turns'!F37,'Turns'!F49)=4,SUM('Turns'!F5,'Turns'!F21,'Turns'!F37,'Turns'!F49),"Unknown")</f>
+        <v>0.0002172</v>
       </c>
       <c r="M2" s="2">
-        <f>IF(COUNT('Turns'!D37,'Turns'!D49)=2,SUM('Turns'!D37,'Turns'!D49),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D36,'Turns'!D48)=2,SUM('Turns'!D36,'Turns'!D48),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N2" s="2">
-        <f>IF(COUNT('Turns'!E37,'Turns'!E49)=2,SUM('Turns'!E37,'Turns'!E49),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E36,'Turns'!E48)=2,SUM('Turns'!E36,'Turns'!E48),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O2" s="2">
-        <f>IF(COUNT('Turns'!F37,'Turns'!F49)=2,SUM('Turns'!F37,'Turns'!F49),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F36,'Turns'!F48)=2,SUM('Turns'!F36,'Turns'!F48),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P2" s="2">
@@ -4423,47 +4362,44 @@
         <v>0</v>
       </c>
       <c r="S2" s="2">
-        <f>IF(COUNT('Turns'!D12,'Turns'!D28,'Turns'!D43,'Turns'!D55)=4,SUM('Turns'!D12,'Turns'!D28,'Turns'!D43,'Turns'!D55),"Unknown")</f>
-        <v>157.0</v>
+        <f>IF(COUNT('Turns'!D12,'Turns'!D27,'Turns'!D42,'Turns'!D54)=4,SUM('Turns'!D12,'Turns'!D27,'Turns'!D42,'Turns'!D54),"Unknown")</f>
+        <v>143.0</v>
       </c>
       <c r="T2" s="2">
-        <f>IF(COUNT('Turns'!E12,'Turns'!E28,'Turns'!E43,'Turns'!E55)=4,SUM('Turns'!E12,'Turns'!E28,'Turns'!E43,'Turns'!E55),"Unknown")</f>
-        <v>0.00016510434</v>
+        <f>IF(COUNT('Turns'!E12,'Turns'!E27,'Turns'!E42,'Turns'!E54)=4,SUM('Turns'!E12,'Turns'!E27,'Turns'!E42,'Turns'!E54),"Unknown")</f>
+        <v>0.000150963384</v>
       </c>
       <c r="U2" s="2">
-        <f>IF(COUNT('Turns'!F12,'Turns'!F28,'Turns'!F43,'Turns'!F55)=4,SUM('Turns'!F12,'Turns'!F28,'Turns'!F43,'Turns'!F55),"Unknown")</f>
-        <v>0.0001884</v>
+        <f>IF(COUNT('Turns'!F12,'Turns'!F27,'Turns'!F42,'Turns'!F54)=4,SUM('Turns'!F12,'Turns'!F27,'Turns'!F42,'Turns'!F54),"Unknown")</f>
+        <v>0.0001716</v>
       </c>
       <c r="V2" s="2">
-        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>8.0</v>
+        <v>0</v>
       </c>
       <c r="W2" s="2">
-        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>8.41296e-06</v>
+        <v>0</v>
       </c>
       <c r="X2" s="2">
-        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>9.6e-06</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59)=4,SUM('Turns'!E16,'Turns'!E32,'Turns'!E47,'Turns'!E59),"Unknown")</f>
-        <v>0.000368067</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E31,'Turns'!E46,'Turns'!E58)=4,SUM('Turns'!E16,'Turns'!E31,'Turns'!E46,'Turns'!E58),"Unknown")</f>
+        <v>0.000342042912</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59)=4,SUM('Turns'!F16,'Turns'!F32,'Turns'!F47,'Turns'!F59),"Unknown")</f>
-        <v>0.00042</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F31,'Turns'!F46,'Turns'!F58)=4,SUM('Turns'!F16,'Turns'!F31,'Turns'!F46,'Turns'!F58),"Unknown")</f>
+        <v>0.0003888</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>37.0</v>
+        <v>34.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>42.0</v>
+        <v>39.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>5851.253</v>
+        <v>4155.05</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>184</v>
@@ -4500,7 +4436,7 @@
       </c>
       <c r="K3" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>4.592074e-05</v>
+        <v>4.6098376e-05</v>
       </c>
       <c r="L3" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -4526,15 +4462,15 @@
       </c>
       <c r="S3" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>57.0</v>
+        <v>56.0</v>
       </c>
       <c r="T3" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>5.994234e-05</v>
+        <v>5.9118528e-05</v>
       </c>
       <c r="U3" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>6.84e-05</v>
+        <v>6.72e-05</v>
       </c>
       <c r="V3" s="2">
         <v>0</v>
@@ -4547,11 +4483,11 @@
       </c>
       <c r="Y3" s="2">
         <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
-        <v>0.00010586308</v>
+        <v>0.000105216904</v>
       </c>
       <c r="Z3" s="2">
         <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
-        <v>0.0001208</v>
+        <v>0.0001196</v>
       </c>
       <c r="AA3" s="5">
         <f>IF(ISNUMBER(Y3),ROUND(Y3*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4562,7 +4498,7 @@
         <v>12.0</v>
       </c>
       <c r="AD3" s="1">
-        <v>1629.707</v>
+        <v>1416.21</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>184</v>
@@ -4602,7 +4538,7 @@
       </c>
       <c r="K4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>4.592074e-05</v>
+        <v>4.6098376e-05</v>
       </c>
       <c r="L4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -4628,15 +4564,15 @@
       </c>
       <c r="S4" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>57.0</v>
+        <v>56.0</v>
       </c>
       <c r="T4" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>5.994234e-05</v>
+        <v>5.9118528e-05</v>
       </c>
       <c r="U4" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>6.84e-05</v>
+        <v>6.72e-05</v>
       </c>
       <c r="V4" s="2">
         <v>0</v>
@@ -4649,11 +4585,11 @@
       </c>
       <c r="Y4" s="2">
         <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
-        <v>0.00010586308</v>
+        <v>0.000105216904</v>
       </c>
       <c r="Z4" s="2">
         <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
-        <v>0.0001208</v>
+        <v>0.0001196</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4667,7 +4603,7 @@
         <v>93</v>
       </c>
       <c r="AD4" s="1">
-        <v>1627.239</v>
+        <v>1413.068</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>191</v>
@@ -4699,27 +4635,27 @@
         <v>49</v>
       </c>
       <c r="J5" s="2">
-        <f>IF(COUNT('Turns'!D21,'Turns'!D38)=2,SUM('Turns'!D21,'Turns'!D38),"Unknown")</f>
-        <v>479.0</v>
+        <f>IF(COUNT('Turns'!D21,'Turns'!D37)=2,SUM('Turns'!D21,'Turns'!D37),"Unknown")</f>
+        <v>460.0</v>
       </c>
       <c r="K5" s="2">
-        <f>IF(COUNT('Turns'!E21,'Turns'!E38)=2,SUM('Turns'!E21,'Turns'!E38),"Unknown")</f>
-        <v>8.395433e-05</v>
+        <f>IF(COUNT('Turns'!E21,'Turns'!E37)=2,SUM('Turns'!E21,'Turns'!E37),"Unknown")</f>
+        <v>8.093608e-05</v>
       </c>
       <c r="L5" s="2">
-        <f>IF(COUNT('Turns'!F21,'Turns'!F38)=2,SUM('Turns'!F21,'Turns'!F38),"Unknown")</f>
-        <v>9.58e-05</v>
+        <f>IF(COUNT('Turns'!F21,'Turns'!F37)=2,SUM('Turns'!F21,'Turns'!F37),"Unknown")</f>
+        <v>9.2e-05</v>
       </c>
       <c r="M5" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N5" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O5" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P5" s="2">
@@ -4732,47 +4668,44 @@
         <v>0</v>
       </c>
       <c r="S5" s="2">
-        <f>IF(COUNT('Turns'!D28,'Turns'!D43)=2,SUM('Turns'!D28,'Turns'!D43),"Unknown")</f>
-        <v>79.0</v>
+        <f>IF(COUNT('Turns'!D27,'Turns'!D42)=2,SUM('Turns'!D27,'Turns'!D42),"Unknown")</f>
+        <v>66.0</v>
       </c>
       <c r="T5" s="2">
-        <f>IF(COUNT('Turns'!E28,'Turns'!E43)=2,SUM('Turns'!E28,'Turns'!E43),"Unknown")</f>
-        <v>8.307798e-05</v>
+        <f>IF(COUNT('Turns'!E27,'Turns'!E42)=2,SUM('Turns'!E27,'Turns'!E42),"Unknown")</f>
+        <v>6.9675408e-05</v>
       </c>
       <c r="U5" s="2">
-        <f>IF(COUNT('Turns'!F28,'Turns'!F43)=2,SUM('Turns'!F28,'Turns'!F43),"Unknown")</f>
-        <v>9.48e-05</v>
+        <f>IF(COUNT('Turns'!F27,'Turns'!F42)=2,SUM('Turns'!F27,'Turns'!F42),"Unknown")</f>
+        <v>7.92e-05</v>
       </c>
       <c r="V5" s="2">
-        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>8.0</v>
+        <v>0</v>
       </c>
       <c r="W5" s="2">
-        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>8.41296e-06</v>
+        <v>0</v>
       </c>
       <c r="X5" s="2">
-        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>9.6e-06</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="2">
-        <f>IF(COUNT('Turns'!E32,'Turns'!E47)=2,SUM('Turns'!E32,'Turns'!E47),"Unknown")</f>
-        <v>0.00017544527</v>
+        <f>IF(COUNT('Turns'!E31,'Turns'!E46)=2,SUM('Turns'!E31,'Turns'!E46),"Unknown")</f>
+        <v>0.000150611488</v>
       </c>
       <c r="Z5" s="2">
-        <f>IF(COUNT('Turns'!F32,'Turns'!F47)=2,SUM('Turns'!F32,'Turns'!F47),"Unknown")</f>
-        <v>0.0002002</v>
+        <f>IF(COUNT('Turns'!F31,'Turns'!F46)=2,SUM('Turns'!F31,'Turns'!F46),"Unknown")</f>
+        <v>0.0001712</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>17.0</v>
       </c>
       <c r="AD5" s="1">
-        <v>3082.935</v>
+        <v>1819.893</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>184</v>
@@ -4804,27 +4737,27 @@
         <v>194</v>
       </c>
       <c r="J6" s="2">
-        <f>IF(COUNT('Turns'!D21,'Turns'!D38)=2,SUM('Turns'!D21,'Turns'!D38),"Unknown")</f>
-        <v>479.0</v>
+        <f>IF(COUNT('Turns'!D21,'Turns'!D37)=2,SUM('Turns'!D21,'Turns'!D37),"Unknown")</f>
+        <v>460.0</v>
       </c>
       <c r="K6" s="2">
-        <f>IF(COUNT('Turns'!E21,'Turns'!E38)=2,SUM('Turns'!E21,'Turns'!E38),"Unknown")</f>
-        <v>8.395433e-05</v>
+        <f>IF(COUNT('Turns'!E21,'Turns'!E37)=2,SUM('Turns'!E21,'Turns'!E37),"Unknown")</f>
+        <v>8.093608e-05</v>
       </c>
       <c r="L6" s="2">
-        <f>IF(COUNT('Turns'!F21,'Turns'!F38)=2,SUM('Turns'!F21,'Turns'!F38),"Unknown")</f>
-        <v>9.58e-05</v>
+        <f>IF(COUNT('Turns'!F21,'Turns'!F37)=2,SUM('Turns'!F21,'Turns'!F37),"Unknown")</f>
+        <v>9.2e-05</v>
       </c>
       <c r="M6" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N6" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O6" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P6" s="2">
@@ -4837,47 +4770,44 @@
         <v>0</v>
       </c>
       <c r="S6" s="2">
-        <f>IF(COUNT('Turns'!D28,'Turns'!D43)=2,SUM('Turns'!D28,'Turns'!D43),"Unknown")</f>
-        <v>79.0</v>
+        <f>IF(COUNT('Turns'!D27,'Turns'!D42)=2,SUM('Turns'!D27,'Turns'!D42),"Unknown")</f>
+        <v>66.0</v>
       </c>
       <c r="T6" s="2">
-        <f>IF(COUNT('Turns'!E28,'Turns'!E43)=2,SUM('Turns'!E28,'Turns'!E43),"Unknown")</f>
-        <v>8.307798e-05</v>
+        <f>IF(COUNT('Turns'!E27,'Turns'!E42)=2,SUM('Turns'!E27,'Turns'!E42),"Unknown")</f>
+        <v>6.9675408e-05</v>
       </c>
       <c r="U6" s="2">
-        <f>IF(COUNT('Turns'!F28,'Turns'!F43)=2,SUM('Turns'!F28,'Turns'!F43),"Unknown")</f>
-        <v>9.48e-05</v>
+        <f>IF(COUNT('Turns'!F27,'Turns'!F42)=2,SUM('Turns'!F27,'Turns'!F42),"Unknown")</f>
+        <v>7.92e-05</v>
       </c>
       <c r="V6" s="2">
-        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>8.0</v>
+        <v>0</v>
       </c>
       <c r="W6" s="2">
-        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>8.41296e-06</v>
+        <v>0</v>
       </c>
       <c r="X6" s="2">
-        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>9.6e-06</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="2">
-        <f>IF(COUNT('Turns'!E32,'Turns'!E47)=2,SUM('Turns'!E32,'Turns'!E47),"Unknown")</f>
-        <v>0.00017544527</v>
+        <f>IF(COUNT('Turns'!E31,'Turns'!E46)=2,SUM('Turns'!E31,'Turns'!E46),"Unknown")</f>
+        <v>0.000150611488</v>
       </c>
       <c r="Z6" s="2">
-        <f>IF(COUNT('Turns'!F32,'Turns'!F47)=2,SUM('Turns'!F32,'Turns'!F47),"Unknown")</f>
-        <v>0.0002002</v>
+        <f>IF(COUNT('Turns'!F31,'Turns'!F46)=2,SUM('Turns'!F31,'Turns'!F46),"Unknown")</f>
+        <v>0.0001712</v>
       </c>
       <c r="AA6" s="5">
         <f>IF(ISNUMBER(Y6),ROUND(Y6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="AB6" s="5">
         <f>IF(ISNUMBER(Z6),ROUND(Z6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>17.0</v>
       </c>
       <c r="AD6" s="1">
-        <v>3081.093</v>
+        <v>1818.657</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>184</v>
@@ -4909,27 +4839,27 @@
         <v>112</v>
       </c>
       <c r="J7" s="2">
-        <f>IF(COUNT('Turns'!D21,'Turns'!D38)=2,SUM('Turns'!D21,'Turns'!D38),"Unknown")</f>
-        <v>479.0</v>
+        <f>IF(COUNT('Turns'!D21,'Turns'!D37)=2,SUM('Turns'!D21,'Turns'!D37),"Unknown")</f>
+        <v>460.0</v>
       </c>
       <c r="K7" s="2">
-        <f>IF(COUNT('Turns'!E21,'Turns'!E38)=2,SUM('Turns'!E21,'Turns'!E38),"Unknown")</f>
-        <v>8.395433e-05</v>
+        <f>IF(COUNT('Turns'!E21,'Turns'!E37)=2,SUM('Turns'!E21,'Turns'!E37),"Unknown")</f>
+        <v>8.093608e-05</v>
       </c>
       <c r="L7" s="2">
-        <f>IF(COUNT('Turns'!F21,'Turns'!F38)=2,SUM('Turns'!F21,'Turns'!F38),"Unknown")</f>
-        <v>9.58e-05</v>
+        <f>IF(COUNT('Turns'!F21,'Turns'!F37)=2,SUM('Turns'!F21,'Turns'!F37),"Unknown")</f>
+        <v>9.2e-05</v>
       </c>
       <c r="M7" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N7" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O7" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P7" s="2">
@@ -4942,47 +4872,44 @@
         <v>0</v>
       </c>
       <c r="S7" s="2">
-        <f>IF(COUNT('Turns'!D28,'Turns'!D43)=2,SUM('Turns'!D28,'Turns'!D43),"Unknown")</f>
-        <v>79.0</v>
+        <f>IF(COUNT('Turns'!D27,'Turns'!D42)=2,SUM('Turns'!D27,'Turns'!D42),"Unknown")</f>
+        <v>66.0</v>
       </c>
       <c r="T7" s="2">
-        <f>IF(COUNT('Turns'!E28,'Turns'!E43)=2,SUM('Turns'!E28,'Turns'!E43),"Unknown")</f>
-        <v>8.307798e-05</v>
+        <f>IF(COUNT('Turns'!E27,'Turns'!E42)=2,SUM('Turns'!E27,'Turns'!E42),"Unknown")</f>
+        <v>6.9675408e-05</v>
       </c>
       <c r="U7" s="2">
-        <f>IF(COUNT('Turns'!F28,'Turns'!F43)=2,SUM('Turns'!F28,'Turns'!F43),"Unknown")</f>
-        <v>9.48e-05</v>
+        <f>IF(COUNT('Turns'!F27,'Turns'!F42)=2,SUM('Turns'!F27,'Turns'!F42),"Unknown")</f>
+        <v>7.92e-05</v>
       </c>
       <c r="V7" s="2">
-        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>8.0</v>
+        <v>0</v>
       </c>
       <c r="W7" s="2">
-        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>8.41296e-06</v>
+        <v>0</v>
       </c>
       <c r="X7" s="2">
-        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>9.6e-06</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="2">
-        <f>IF(COUNT('Turns'!E32,'Turns'!E47)=2,SUM('Turns'!E32,'Turns'!E47),"Unknown")</f>
-        <v>0.00017544527</v>
+        <f>IF(COUNT('Turns'!E31,'Turns'!E46)=2,SUM('Turns'!E31,'Turns'!E46),"Unknown")</f>
+        <v>0.000150611488</v>
       </c>
       <c r="Z7" s="2">
-        <f>IF(COUNT('Turns'!F32,'Turns'!F47)=2,SUM('Turns'!F32,'Turns'!F47),"Unknown")</f>
-        <v>0.0002002</v>
+        <f>IF(COUNT('Turns'!F31,'Turns'!F46)=2,SUM('Turns'!F31,'Turns'!F46),"Unknown")</f>
+        <v>0.0001712</v>
       </c>
       <c r="AA7" s="5">
         <f>IF(ISNUMBER(Y7),ROUND(Y7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="AB7" s="5">
         <f>IF(ISNUMBER(Z7),ROUND(Z7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>17.0</v>
       </c>
       <c r="AD7" s="1">
-        <v>3079.32</v>
+        <v>1817.685</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>184</v>
@@ -5015,15 +4942,15 @@
       </c>
       <c r="J8" s="2">
         <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
-        <v>194.0</v>
+        <v>193.0</v>
       </c>
       <c r="K8" s="2">
         <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
-        <v>3.400238e-05</v>
+        <v>3.3957964e-05</v>
       </c>
       <c r="L8" s="2">
         <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
-        <v>3.88e-05</v>
+        <v>3.86e-05</v>
       </c>
       <c r="M8" s="2">
         <v>0</v>
@@ -5044,47 +4971,44 @@
         <v>0</v>
       </c>
       <c r="S8" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>35.0</v>
+        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
+        <v>26.0</v>
       </c>
       <c r="T8" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>3.68067e-05</v>
+        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
+        <v>2.7447888e-05</v>
       </c>
       <c r="U8" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>4.2e-05</v>
+        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
+        <v>3.12e-05</v>
       </c>
       <c r="V8" s="2">
-        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>8.0</v>
+        <v>0</v>
       </c>
       <c r="W8" s="2">
-        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>8.41296e-06</v>
+        <v>0</v>
       </c>
       <c r="X8" s="2">
-        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>9.6e-06</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>7.922204e-05</v>
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>6.1405852e-05</v>
       </c>
       <c r="Z8" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>9.04e-05</v>
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>6.98e-05</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="AD8" s="1">
-        <v>1458.209</v>
+        <v>914.684</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>184</v>
@@ -5107,7 +5031,7 @@
         <v>110</v>
       </c>
       <c r="F9" s="1">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>190</v>
@@ -5120,15 +5044,15 @@
       </c>
       <c r="J9" s="2">
         <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
-        <v>194.0</v>
+        <v>193.0</v>
       </c>
       <c r="K9" s="2">
         <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
-        <v>3.400238e-05</v>
+        <v>3.3957964e-05</v>
       </c>
       <c r="L9" s="2">
         <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
-        <v>3.88e-05</v>
+        <v>3.86e-05</v>
       </c>
       <c r="M9" s="2">
         <v>0</v>
@@ -5149,50 +5073,47 @@
         <v>0</v>
       </c>
       <c r="S9" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>35.0</v>
+        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
+        <v>26.0</v>
       </c>
       <c r="T9" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>3.68067e-05</v>
+        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
+        <v>2.7447888e-05</v>
       </c>
       <c r="U9" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>4.2e-05</v>
+        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
+        <v>3.12e-05</v>
       </c>
       <c r="V9" s="2">
-        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>8.0</v>
+        <v>0</v>
       </c>
       <c r="W9" s="2">
-        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>8.41296e-06</v>
+        <v>0</v>
       </c>
       <c r="X9" s="2">
-        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>9.6e-06</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>7.922204e-05</v>
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>6.1405852e-05</v>
       </c>
       <c r="Z9" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>9.04e-05</v>
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>6.98e-05</v>
       </c>
       <c r="AA9" s="5">
         <f>IF(ISNUMBER(Y9),ROUND(Y9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="AB9" s="5">
         <f>IF(ISNUMBER(Z9),ROUND(Z9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="AC9" s="1" t="s">
         <v>117</v>
       </c>
       <c r="AD9" s="1">
-        <v>1454.898</v>
+        <v>911.932</v>
       </c>
       <c r="AE9" s="1" t="s">
         <v>191</v>
@@ -5224,7 +5145,7 @@
         <v>200</v>
       </c>
       <c r="AD10" s="1">
-        <v>4.528</v>
+        <v>1.782</v>
       </c>
       <c r="AE10" s="1" t="s">
         <v>206</v>
@@ -5250,13 +5171,13 @@
         <v>208</v>
       </c>
       <c r="H11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I11" t="s">
         <v>205</v>
       </c>
       <c r="AD11" s="1">
-        <v>1.505</v>
+        <v>0.517</v>
       </c>
       <c r="AE11" s="1" t="s">
         <v>206</v>
@@ -5288,27 +5209,27 @@
         <v>200</v>
       </c>
       <c r="J12" s="2">
-        <f>IF(COUNT('Turns'!D38)=1,SUM('Turns'!D38),"Unknown")</f>
-        <v>285.0</v>
+        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <v>267.0</v>
       </c>
       <c r="K12" s="2">
-        <f>IF(COUNT('Turns'!E38)=1,SUM('Turns'!E38),"Unknown")</f>
-        <v>4.995195e-05</v>
+        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <v>4.6978116e-05</v>
       </c>
       <c r="L12" s="2">
-        <f>IF(COUNT('Turns'!F38)=1,SUM('Turns'!F38),"Unknown")</f>
-        <v>5.7e-05</v>
+        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <v>5.34e-05</v>
       </c>
       <c r="M12" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N12" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O12" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P12" s="2">
@@ -5321,16 +5242,16 @@
         <v>0</v>
       </c>
       <c r="S12" s="2">
-        <f>IF(COUNT('Turns'!D43)=1,SUM('Turns'!D43),"Unknown")</f>
-        <v>44.0</v>
+        <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
+        <v>40.0</v>
       </c>
       <c r="T12" s="2">
-        <f>IF(COUNT('Turns'!E43)=1,SUM('Turns'!E43),"Unknown")</f>
-        <v>4.627128e-05</v>
+        <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
+        <v>4.222752e-05</v>
       </c>
       <c r="U12" s="2">
-        <f>IF(COUNT('Turns'!F43)=1,SUM('Turns'!F43),"Unknown")</f>
-        <v>5.28e-05</v>
+        <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
+        <v>4.8e-05</v>
       </c>
       <c r="V12" s="2">
         <v>0</v>
@@ -5342,23 +5263,23 @@
         <v>0</v>
       </c>
       <c r="Y12" s="2">
-        <f>IF(COUNT('Turns'!E47)=1,SUM('Turns'!E47),"Unknown")</f>
-        <v>9.622323e-05</v>
+        <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
+        <v>8.9205636e-05</v>
       </c>
       <c r="Z12" s="2">
-        <f>IF(COUNT('Turns'!F47)=1,SUM('Turns'!F47),"Unknown")</f>
-        <v>0.0001098</v>
+        <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
+        <v>0.0001014</v>
       </c>
       <c r="AA12" s="5">
         <f>IF(ISNUMBER(Y12),ROUND(Y12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="AB12" s="5">
         <f>IF(ISNUMBER(Z12),ROUND(Z12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="AD12" s="1">
-        <v>1610.327</v>
+        <v>898.388</v>
       </c>
       <c r="AE12" s="1" t="s">
         <v>184</v>
@@ -5381,39 +5302,39 @@
         <v>110</v>
       </c>
       <c r="F13" s="1">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>190</v>
       </c>
       <c r="H13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I13" t="s">
         <v>209</v>
       </c>
       <c r="J13" s="2">
-        <f>IF(COUNT('Turns'!D38)=1,SUM('Turns'!D38),"Unknown")</f>
-        <v>285.0</v>
+        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <v>267.0</v>
       </c>
       <c r="K13" s="2">
-        <f>IF(COUNT('Turns'!E38)=1,SUM('Turns'!E38),"Unknown")</f>
-        <v>4.995195e-05</v>
+        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <v>4.6978116e-05</v>
       </c>
       <c r="L13" s="2">
-        <f>IF(COUNT('Turns'!F38)=1,SUM('Turns'!F38),"Unknown")</f>
-        <v>5.7e-05</v>
+        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <v>5.34e-05</v>
       </c>
       <c r="M13" s="2">
-        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N13" s="2">
-        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O13" s="2">
-        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P13" s="2">
@@ -5426,16 +5347,16 @@
         <v>0</v>
       </c>
       <c r="S13" s="2">
-        <f>IF(COUNT('Turns'!D43)=1,SUM('Turns'!D43),"Unknown")</f>
-        <v>44.0</v>
+        <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
+        <v>40.0</v>
       </c>
       <c r="T13" s="2">
-        <f>IF(COUNT('Turns'!E43)=1,SUM('Turns'!E43),"Unknown")</f>
-        <v>4.627128e-05</v>
+        <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
+        <v>4.222752e-05</v>
       </c>
       <c r="U13" s="2">
-        <f>IF(COUNT('Turns'!F43)=1,SUM('Turns'!F43),"Unknown")</f>
-        <v>5.28e-05</v>
+        <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
+        <v>4.8e-05</v>
       </c>
       <c r="V13" s="2">
         <v>0</v>
@@ -5447,26 +5368,26 @@
         <v>0</v>
       </c>
       <c r="Y13" s="2">
-        <f>IF(COUNT('Turns'!E47)=1,SUM('Turns'!E47),"Unknown")</f>
-        <v>9.622323e-05</v>
+        <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
+        <v>8.9205636e-05</v>
       </c>
       <c r="Z13" s="2">
-        <f>IF(COUNT('Turns'!F47)=1,SUM('Turns'!F47),"Unknown")</f>
-        <v>0.0001098</v>
+        <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
+        <v>0.0001014</v>
       </c>
       <c r="AA13" s="5">
         <f>IF(ISNUMBER(Y13),ROUND(Y13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="AB13" s="5">
         <f>IF(ISNUMBER(Z13),ROUND(Z13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="AC13" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AD13" s="1">
-        <v>1607.712</v>
+        <v>897.296</v>
       </c>
       <c r="AE13" s="1" t="s">
         <v>191</v>
@@ -5498,27 +5419,27 @@
         <v>49</v>
       </c>
       <c r="J14" s="2">
-        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
-        <v>369.0</v>
+        <f>IF(COUNT('Turns'!D49)=1,SUM('Turns'!D49),"Unknown")</f>
+        <v>364.0</v>
       </c>
       <c r="K14" s="2">
-        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>6.467463e-05</v>
+        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
+        <v>6.4045072e-05</v>
       </c>
       <c r="L14" s="2">
-        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
-        <v>7.38e-05</v>
+        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
+        <v>7.28e-05</v>
       </c>
       <c r="M14" s="2">
-        <f>IF(COUNT('Turns'!D49)=1,SUM('Turns'!D49),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D48)=1,SUM('Turns'!D48),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N14" s="2">
-        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E48)=1,SUM('Turns'!E48),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O14" s="2">
-        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F48)=1,SUM('Turns'!F48),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P14" s="2">
@@ -5531,15 +5452,15 @@
         <v>0</v>
       </c>
       <c r="S14" s="2">
-        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D54)=1,SUM('Turns'!D54),"Unknown")</f>
         <v>21.0</v>
       </c>
       <c r="T14" s="2">
-        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
-        <v>2.208402e-05</v>
+        <f>IF(COUNT('Turns'!E54)=1,SUM('Turns'!E54),"Unknown")</f>
+        <v>2.2169448e-05</v>
       </c>
       <c r="U14" s="2">
-        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F54)=1,SUM('Turns'!F54),"Unknown")</f>
         <v>2.52e-05</v>
       </c>
       <c r="V14" s="2">
@@ -5552,12 +5473,12 @@
         <v>0</v>
       </c>
       <c r="Y14" s="2">
-        <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
-        <v>8.675865e-05</v>
+        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
+        <v>8.621452e-05</v>
       </c>
       <c r="Z14" s="2">
-        <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
-        <v>9.9e-05</v>
+        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
+        <v>9.8e-05</v>
       </c>
       <c r="AA14" s="5">
         <f>IF(ISNUMBER(Y14),ROUND(Y14*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5568,7 +5489,7 @@
         <v>10.0</v>
       </c>
       <c r="AD14" s="1">
-        <v>1131.682</v>
+        <v>915.265</v>
       </c>
       <c r="AE14" s="1" t="s">
         <v>184</v>
@@ -5591,39 +5512,39 @@
         <v>110</v>
       </c>
       <c r="F15" s="1">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>190</v>
       </c>
       <c r="H15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I15" t="s">
         <v>210</v>
       </c>
       <c r="J15" s="2">
-        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
-        <v>369.0</v>
+        <f>IF(COUNT('Turns'!D49)=1,SUM('Turns'!D49),"Unknown")</f>
+        <v>364.0</v>
       </c>
       <c r="K15" s="2">
-        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>6.467463e-05</v>
+        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
+        <v>6.4045072e-05</v>
       </c>
       <c r="L15" s="2">
-        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
-        <v>7.38e-05</v>
+        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
+        <v>7.28e-05</v>
       </c>
       <c r="M15" s="2">
-        <f>IF(COUNT('Turns'!D49)=1,SUM('Turns'!D49),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D48)=1,SUM('Turns'!D48),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N15" s="2">
-        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E48)=1,SUM('Turns'!E48),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O15" s="2">
-        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F48)=1,SUM('Turns'!F48),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P15" s="2">
@@ -5636,15 +5557,15 @@
         <v>0</v>
       </c>
       <c r="S15" s="2">
-        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D54)=1,SUM('Turns'!D54),"Unknown")</f>
         <v>21.0</v>
       </c>
       <c r="T15" s="2">
-        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
-        <v>2.208402e-05</v>
+        <f>IF(COUNT('Turns'!E54)=1,SUM('Turns'!E54),"Unknown")</f>
+        <v>2.2169448e-05</v>
       </c>
       <c r="U15" s="2">
-        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F54)=1,SUM('Turns'!F54),"Unknown")</f>
         <v>2.52e-05</v>
       </c>
       <c r="V15" s="2">
@@ -5657,12 +5578,12 @@
         <v>0</v>
       </c>
       <c r="Y15" s="2">
-        <f>IF(COUNT('Turns'!E59)=1,SUM('Turns'!E59),"Unknown")</f>
-        <v>8.675865e-05</v>
+        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
+        <v>8.621452e-05</v>
       </c>
       <c r="Z15" s="2">
-        <f>IF(COUNT('Turns'!F59)=1,SUM('Turns'!F59),"Unknown")</f>
-        <v>9.9e-05</v>
+        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
+        <v>9.8e-05</v>
       </c>
       <c r="AA15" s="5">
         <f>IF(ISNUMBER(Y15),ROUND(Y15*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5673,10 +5594,10 @@
         <v>10.0</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD15" s="1">
-        <v>1128.269</v>
+        <v>914.054</v>
       </c>
       <c r="AE15" s="1" t="s">
         <v>191</v>
@@ -5705,27 +5626,27 @@
         <v>211</v>
       </c>
       <c r="J16" s="2">
-        <f>IF(COUNT('Turns'!D63,'Turns'!D77,'Turns'!D94,'Turns'!D106)=4,SUM('Turns'!D63,'Turns'!D77,'Turns'!D94,'Turns'!D106),"Unknown")</f>
-        <v>1432.0</v>
+        <f>IF(COUNT('Turns'!D62,'Turns'!D76,'Turns'!D92,'Turns'!D104)=4,SUM('Turns'!D62,'Turns'!D76,'Turns'!D92,'Turns'!D104),"Unknown")</f>
+        <v>1438.0</v>
       </c>
       <c r="K16" s="2">
-        <f>IF(COUNT('Turns'!E63,'Turns'!E77,'Turns'!E94,'Turns'!E106)=4,SUM('Turns'!E63,'Turns'!E77,'Turns'!E94,'Turns'!E106),"Unknown")</f>
-        <v>0.00025098664</v>
+        <f>IF(COUNT('Turns'!E62,'Turns'!E76,'Turns'!E92,'Turns'!E104)=4,SUM('Turns'!E62,'Turns'!E76,'Turns'!E92,'Turns'!E104),"Unknown")</f>
+        <v>0.000253013224</v>
       </c>
       <c r="L16" s="2">
-        <f>IF(COUNT('Turns'!F63,'Turns'!F77,'Turns'!F94,'Turns'!F106)=4,SUM('Turns'!F63,'Turns'!F77,'Turns'!F94,'Turns'!F106),"Unknown")</f>
-        <v>0.0002864</v>
+        <f>IF(COUNT('Turns'!F62,'Turns'!F76,'Turns'!F92,'Turns'!F104)=4,SUM('Turns'!F62,'Turns'!F76,'Turns'!F92,'Turns'!F104),"Unknown")</f>
+        <v>0.0002876</v>
       </c>
       <c r="M16" s="2">
-        <f>IF(COUNT('Turns'!D62,'Turns'!D93,'Turns'!D105)=3,SUM('Turns'!D62,'Turns'!D93,'Turns'!D105),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D61,'Turns'!D91,'Turns'!D103)=3,SUM('Turns'!D61,'Turns'!D91,'Turns'!D103),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N16" s="2">
-        <f>IF(COUNT('Turns'!E62,'Turns'!E93,'Turns'!E105)=3,SUM('Turns'!E62,'Turns'!E93,'Turns'!E105),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E61,'Turns'!E91,'Turns'!E103)=3,SUM('Turns'!E61,'Turns'!E91,'Turns'!E103),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O16" s="2">
-        <f>IF(COUNT('Turns'!F62,'Turns'!F93,'Turns'!F105)=3,SUM('Turns'!F62,'Turns'!F93,'Turns'!F105),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F61,'Turns'!F91,'Turns'!F103)=3,SUM('Turns'!F61,'Turns'!F91,'Turns'!F103),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P16" s="2">
@@ -5738,36 +5659,33 @@
         <v>0</v>
       </c>
       <c r="S16" s="2">
-        <f>IF(COUNT('Turns'!D68,'Turns'!D84,'Turns'!D99,'Turns'!D111)=4,SUM('Turns'!D68,'Turns'!D84,'Turns'!D99,'Turns'!D111),"Unknown")</f>
-        <v>181.0</v>
+        <f>IF(COUNT('Turns'!D67,'Turns'!D82,'Turns'!D97,'Turns'!D109)=4,SUM('Turns'!D67,'Turns'!D82,'Turns'!D97,'Turns'!D109),"Unknown")</f>
+        <v>188.0</v>
       </c>
       <c r="T16" s="2">
-        <f>IF(COUNT('Turns'!E68,'Turns'!E84,'Turns'!E99,'Turns'!E111)=4,SUM('Turns'!E68,'Turns'!E84,'Turns'!E99,'Turns'!E111),"Unknown")</f>
-        <v>0.00019034322</v>
+        <f>IF(COUNT('Turns'!E67,'Turns'!E82,'Turns'!E97,'Turns'!E109)=4,SUM('Turns'!E67,'Turns'!E82,'Turns'!E97,'Turns'!E109),"Unknown")</f>
+        <v>0.000198469344</v>
       </c>
       <c r="U16" s="2">
-        <f>IF(COUNT('Turns'!F68,'Turns'!F84,'Turns'!F99,'Turns'!F111)=4,SUM('Turns'!F68,'Turns'!F84,'Turns'!F99,'Turns'!F111),"Unknown")</f>
-        <v>0.0002172</v>
+        <f>IF(COUNT('Turns'!F67,'Turns'!F82,'Turns'!F97,'Turns'!F109)=4,SUM('Turns'!F67,'Turns'!F82,'Turns'!F97,'Turns'!F109),"Unknown")</f>
+        <v>0.0002256</v>
       </c>
       <c r="V16" s="2">
-        <f>IF(COUNT('Turns'!D83)=1,SUM('Turns'!D83),"Unknown")</f>
-        <v>9.0</v>
+        <v>0</v>
       </c>
       <c r="W16" s="2">
-        <f>IF(COUNT('Turns'!E83)=1,SUM('Turns'!E83),"Unknown")</f>
-        <v>9.46458e-06</v>
+        <v>0</v>
       </c>
       <c r="X16" s="2">
-        <f>IF(COUNT('Turns'!F83)=1,SUM('Turns'!F83),"Unknown")</f>
-        <v>1.08e-05</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="2">
-        <f>IF(COUNT('Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115)=4,SUM('Turns'!E72,'Turns'!E88,'Turns'!E103,'Turns'!E115),"Unknown")</f>
-        <v>0.00045079444</v>
+        <f>IF(COUNT('Turns'!E71,'Turns'!E86,'Turns'!E101,'Turns'!E113)=4,SUM('Turns'!E71,'Turns'!E86,'Turns'!E101,'Turns'!E113),"Unknown")</f>
+        <v>0.000451482568</v>
       </c>
       <c r="Z16" s="2">
-        <f>IF(COUNT('Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115)=4,SUM('Turns'!F72,'Turns'!F88,'Turns'!F103,'Turns'!F115),"Unknown")</f>
-        <v>0.0005144</v>
+        <f>IF(COUNT('Turns'!F71,'Turns'!F86,'Turns'!F101,'Turns'!F113)=4,SUM('Turns'!F71,'Turns'!F86,'Turns'!F101,'Turns'!F113),"Unknown")</f>
+        <v>0.0005132</v>
       </c>
       <c r="AA16" s="5">
         <f>IF(ISNUMBER(Y16),ROUND(Y16*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5778,7 +5696,7 @@
         <v>51.0</v>
       </c>
       <c r="AD16" s="1">
-        <v>4625.912</v>
+        <v>6026.143</v>
       </c>
       <c r="AE16" s="1" t="s">
         <v>184</v>
@@ -5810,27 +5728,27 @@
         <v>211</v>
       </c>
       <c r="J17" s="2">
-        <f>IF(COUNT('Turns'!D63)=1,SUM('Turns'!D63),"Unknown")</f>
-        <v>407.0</v>
+        <f>IF(COUNT('Turns'!D62)=1,SUM('Turns'!D62),"Unknown")</f>
+        <v>402.0</v>
       </c>
       <c r="K17" s="2">
-        <f>IF(COUNT('Turns'!E63)=1,SUM('Turns'!E63),"Unknown")</f>
-        <v>7.133489e-05</v>
+        <f>IF(COUNT('Turns'!E62)=1,SUM('Turns'!E62),"Unknown")</f>
+        <v>7.0731096e-05</v>
       </c>
       <c r="L17" s="2">
-        <f>IF(COUNT('Turns'!F63)=1,SUM('Turns'!F63),"Unknown")</f>
-        <v>8.14e-05</v>
+        <f>IF(COUNT('Turns'!F62)=1,SUM('Turns'!F62),"Unknown")</f>
+        <v>8.04e-05</v>
       </c>
       <c r="M17" s="2">
-        <f>IF(COUNT('Turns'!D62)=1,SUM('Turns'!D62),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D61)=1,SUM('Turns'!D61),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N17" s="2">
-        <f>IF(COUNT('Turns'!E62)=1,SUM('Turns'!E62),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E61)=1,SUM('Turns'!E61),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O17" s="2">
-        <f>IF(COUNT('Turns'!F62)=1,SUM('Turns'!F62),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F61)=1,SUM('Turns'!F61),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P17" s="2">
@@ -5843,16 +5761,16 @@
         <v>0</v>
       </c>
       <c r="S17" s="2">
-        <f>IF(COUNT('Turns'!D68)=1,SUM('Turns'!D68),"Unknown")</f>
-        <v>60.0</v>
+        <f>IF(COUNT('Turns'!D67)=1,SUM('Turns'!D67),"Unknown")</f>
+        <v>67.0</v>
       </c>
       <c r="T17" s="2">
-        <f>IF(COUNT('Turns'!E68)=1,SUM('Turns'!E68),"Unknown")</f>
-        <v>6.30972e-05</v>
+        <f>IF(COUNT('Turns'!E67)=1,SUM('Turns'!E67),"Unknown")</f>
+        <v>7.0731096e-05</v>
       </c>
       <c r="U17" s="2">
-        <f>IF(COUNT('Turns'!F68)=1,SUM('Turns'!F68),"Unknown")</f>
-        <v>7.2e-05</v>
+        <f>IF(COUNT('Turns'!F67)=1,SUM('Turns'!F67),"Unknown")</f>
+        <v>8.04e-05</v>
       </c>
       <c r="V17" s="2">
         <v>0</v>
@@ -5864,23 +5782,23 @@
         <v>0</v>
       </c>
       <c r="Y17" s="2">
-        <f>IF(COUNT('Turns'!E72)=1,SUM('Turns'!E72),"Unknown")</f>
-        <v>0.00013443209</v>
+        <f>IF(COUNT('Turns'!E71)=1,SUM('Turns'!E71),"Unknown")</f>
+        <v>0.000141462192</v>
       </c>
       <c r="Z17" s="2">
-        <f>IF(COUNT('Turns'!F72)=1,SUM('Turns'!F72),"Unknown")</f>
-        <v>0.0001534</v>
+        <f>IF(COUNT('Turns'!F71)=1,SUM('Turns'!F71),"Unknown")</f>
+        <v>0.0001608</v>
       </c>
       <c r="AA17" s="5">
         <f>IF(ISNUMBER(Y17),ROUND(Y17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="AB17" s="5">
         <f>IF(ISNUMBER(Z17),ROUND(Z17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="AD17" s="1">
-        <v>1279.76</v>
+        <v>1308.409</v>
       </c>
       <c r="AE17" s="1" t="s">
         <v>184</v>
@@ -5903,39 +5821,39 @@
         <v>110</v>
       </c>
       <c r="F18" s="1">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>190</v>
       </c>
       <c r="H18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I18" t="s">
         <v>212</v>
       </c>
       <c r="J18" s="2">
-        <f>IF(COUNT('Turns'!D63)=1,SUM('Turns'!D63),"Unknown")</f>
-        <v>407.0</v>
+        <f>IF(COUNT('Turns'!D62)=1,SUM('Turns'!D62),"Unknown")</f>
+        <v>402.0</v>
       </c>
       <c r="K18" s="2">
-        <f>IF(COUNT('Turns'!E63)=1,SUM('Turns'!E63),"Unknown")</f>
-        <v>7.133489e-05</v>
+        <f>IF(COUNT('Turns'!E62)=1,SUM('Turns'!E62),"Unknown")</f>
+        <v>7.0731096e-05</v>
       </c>
       <c r="L18" s="2">
-        <f>IF(COUNT('Turns'!F63)=1,SUM('Turns'!F63),"Unknown")</f>
-        <v>8.14e-05</v>
+        <f>IF(COUNT('Turns'!F62)=1,SUM('Turns'!F62),"Unknown")</f>
+        <v>8.04e-05</v>
       </c>
       <c r="M18" s="2">
-        <f>IF(COUNT('Turns'!D62)=1,SUM('Turns'!D62),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D61)=1,SUM('Turns'!D61),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N18" s="2">
-        <f>IF(COUNT('Turns'!E62)=1,SUM('Turns'!E62),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E61)=1,SUM('Turns'!E61),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O18" s="2">
-        <f>IF(COUNT('Turns'!F62)=1,SUM('Turns'!F62),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F61)=1,SUM('Turns'!F61),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P18" s="2">
@@ -5948,16 +5866,16 @@
         <v>0</v>
       </c>
       <c r="S18" s="2">
-        <f>IF(COUNT('Turns'!D68)=1,SUM('Turns'!D68),"Unknown")</f>
-        <v>60.0</v>
+        <f>IF(COUNT('Turns'!D67)=1,SUM('Turns'!D67),"Unknown")</f>
+        <v>67.0</v>
       </c>
       <c r="T18" s="2">
-        <f>IF(COUNT('Turns'!E68)=1,SUM('Turns'!E68),"Unknown")</f>
-        <v>6.30972e-05</v>
+        <f>IF(COUNT('Turns'!E67)=1,SUM('Turns'!E67),"Unknown")</f>
+        <v>7.0731096e-05</v>
       </c>
       <c r="U18" s="2">
-        <f>IF(COUNT('Turns'!F68)=1,SUM('Turns'!F68),"Unknown")</f>
-        <v>7.2e-05</v>
+        <f>IF(COUNT('Turns'!F67)=1,SUM('Turns'!F67),"Unknown")</f>
+        <v>8.04e-05</v>
       </c>
       <c r="V18" s="2">
         <v>0</v>
@@ -5969,26 +5887,26 @@
         <v>0</v>
       </c>
       <c r="Y18" s="2">
-        <f>IF(COUNT('Turns'!E72)=1,SUM('Turns'!E72),"Unknown")</f>
-        <v>0.00013443209</v>
+        <f>IF(COUNT('Turns'!E71)=1,SUM('Turns'!E71),"Unknown")</f>
+        <v>0.000141462192</v>
       </c>
       <c r="Z18" s="2">
-        <f>IF(COUNT('Turns'!F72)=1,SUM('Turns'!F72),"Unknown")</f>
-        <v>0.0001534</v>
+        <f>IF(COUNT('Turns'!F71)=1,SUM('Turns'!F71),"Unknown")</f>
+        <v>0.0001608</v>
       </c>
       <c r="AA18" s="5">
         <f>IF(ISNUMBER(Y18),ROUND(Y18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="AB18" s="5">
         <f>IF(ISNUMBER(Z18),ROUND(Z18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="AC18" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AD18" s="1">
-        <v>1277.459</v>
+        <v>1307.183</v>
       </c>
       <c r="AE18" s="1" t="s">
         <v>191</v>
@@ -6020,27 +5938,27 @@
         <v>211</v>
       </c>
       <c r="J19" s="2">
-        <f>IF(COUNT('Turns'!D77,'Turns'!D94)=2,SUM('Turns'!D77,'Turns'!D94),"Unknown")</f>
-        <v>494.0</v>
+        <f>IF(COUNT('Turns'!D76,'Turns'!D92)=2,SUM('Turns'!D76,'Turns'!D92),"Unknown")</f>
+        <v>501.0</v>
       </c>
       <c r="K19" s="2">
-        <f>IF(COUNT('Turns'!E77,'Turns'!E94)=2,SUM('Turns'!E77,'Turns'!E94),"Unknown")</f>
-        <v>8.658338e-05</v>
+        <f>IF(COUNT('Turns'!E76,'Turns'!E92)=2,SUM('Turns'!E76,'Turns'!E92),"Unknown")</f>
+        <v>8.8149948e-05</v>
       </c>
       <c r="L19" s="2">
-        <f>IF(COUNT('Turns'!F77,'Turns'!F94)=2,SUM('Turns'!F77,'Turns'!F94),"Unknown")</f>
-        <v>9.88e-05</v>
+        <f>IF(COUNT('Turns'!F76,'Turns'!F92)=2,SUM('Turns'!F76,'Turns'!F92),"Unknown")</f>
+        <v>0.0001002</v>
       </c>
       <c r="M19" s="2">
-        <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D91)=1,SUM('Turns'!D91),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N19" s="2">
-        <f>IF(COUNT('Turns'!E93)=1,SUM('Turns'!E93),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E91)=1,SUM('Turns'!E91),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O19" s="2">
-        <f>IF(COUNT('Turns'!F93)=1,SUM('Turns'!F93),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F91)=1,SUM('Turns'!F91),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P19" s="2">
@@ -6053,36 +5971,33 @@
         <v>0</v>
       </c>
       <c r="S19" s="2">
-        <f>IF(COUNT('Turns'!D84,'Turns'!D99)=2,SUM('Turns'!D84,'Turns'!D99),"Unknown")</f>
-        <v>98.0</v>
+        <f>IF(COUNT('Turns'!D82,'Turns'!D97)=2,SUM('Turns'!D82,'Turns'!D97),"Unknown")</f>
+        <v>102.0</v>
       </c>
       <c r="T19" s="2">
-        <f>IF(COUNT('Turns'!E84,'Turns'!E99)=2,SUM('Turns'!E84,'Turns'!E99),"Unknown")</f>
-        <v>0.00010305876</v>
+        <f>IF(COUNT('Turns'!E82,'Turns'!E97)=2,SUM('Turns'!E82,'Turns'!E97),"Unknown")</f>
+        <v>0.000107680176</v>
       </c>
       <c r="U19" s="2">
-        <f>IF(COUNT('Turns'!F84,'Turns'!F99)=2,SUM('Turns'!F84,'Turns'!F99),"Unknown")</f>
-        <v>0.0001176</v>
+        <f>IF(COUNT('Turns'!F82,'Turns'!F97)=2,SUM('Turns'!F82,'Turns'!F97),"Unknown")</f>
+        <v>0.0001224</v>
       </c>
       <c r="V19" s="2">
-        <f>IF(COUNT('Turns'!D83)=1,SUM('Turns'!D83),"Unknown")</f>
-        <v>9.0</v>
+        <v>0</v>
       </c>
       <c r="W19" s="2">
-        <f>IF(COUNT('Turns'!E83)=1,SUM('Turns'!E83),"Unknown")</f>
-        <v>9.46458e-06</v>
+        <v>0</v>
       </c>
       <c r="X19" s="2">
-        <f>IF(COUNT('Turns'!F83)=1,SUM('Turns'!F83),"Unknown")</f>
-        <v>1.08e-05</v>
+        <v>0</v>
       </c>
       <c r="Y19" s="2">
-        <f>IF(COUNT('Turns'!E88,'Turns'!E103)=2,SUM('Turns'!E88,'Turns'!E103),"Unknown")</f>
-        <v>0.00019910672</v>
+        <f>IF(COUNT('Turns'!E86,'Turns'!E101)=2,SUM('Turns'!E86,'Turns'!E101),"Unknown")</f>
+        <v>0.000195830124</v>
       </c>
       <c r="Z19" s="2">
-        <f>IF(COUNT('Turns'!F88,'Turns'!F103)=2,SUM('Turns'!F88,'Turns'!F103),"Unknown")</f>
-        <v>0.0002272</v>
+        <f>IF(COUNT('Turns'!F86,'Turns'!F101)=2,SUM('Turns'!F86,'Turns'!F101),"Unknown")</f>
+        <v>0.0002226</v>
       </c>
       <c r="AA19" s="5">
         <f>IF(ISNUMBER(Y19),ROUND(Y19*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6090,10 +6005,10 @@
       </c>
       <c r="AB19" s="5">
         <f>IF(ISNUMBER(Z19),ROUND(Z19*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="AD19" s="1">
-        <v>2400.625</v>
+        <v>3753.883</v>
       </c>
       <c r="AE19" s="1" t="s">
         <v>184</v>
@@ -6119,33 +6034,33 @@
         <v>197</v>
       </c>
       <c r="H20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I20" t="s">
         <v>213</v>
       </c>
       <c r="J20" s="2">
-        <f>IF(COUNT('Turns'!D77,'Turns'!D94)=2,SUM('Turns'!D77,'Turns'!D94),"Unknown")</f>
-        <v>494.0</v>
+        <f>IF(COUNT('Turns'!D76,'Turns'!D92)=2,SUM('Turns'!D76,'Turns'!D92),"Unknown")</f>
+        <v>501.0</v>
       </c>
       <c r="K20" s="2">
-        <f>IF(COUNT('Turns'!E77,'Turns'!E94)=2,SUM('Turns'!E77,'Turns'!E94),"Unknown")</f>
-        <v>8.658338e-05</v>
+        <f>IF(COUNT('Turns'!E76,'Turns'!E92)=2,SUM('Turns'!E76,'Turns'!E92),"Unknown")</f>
+        <v>8.8149948e-05</v>
       </c>
       <c r="L20" s="2">
-        <f>IF(COUNT('Turns'!F77,'Turns'!F94)=2,SUM('Turns'!F77,'Turns'!F94),"Unknown")</f>
-        <v>9.88e-05</v>
+        <f>IF(COUNT('Turns'!F76,'Turns'!F92)=2,SUM('Turns'!F76,'Turns'!F92),"Unknown")</f>
+        <v>0.0001002</v>
       </c>
       <c r="M20" s="2">
-        <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D91)=1,SUM('Turns'!D91),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N20" s="2">
-        <f>IF(COUNT('Turns'!E93)=1,SUM('Turns'!E93),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E91)=1,SUM('Turns'!E91),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O20" s="2">
-        <f>IF(COUNT('Turns'!F93)=1,SUM('Turns'!F93),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F91)=1,SUM('Turns'!F91),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P20" s="2">
@@ -6158,36 +6073,33 @@
         <v>0</v>
       </c>
       <c r="S20" s="2">
-        <f>IF(COUNT('Turns'!D84,'Turns'!D99)=2,SUM('Turns'!D84,'Turns'!D99),"Unknown")</f>
-        <v>98.0</v>
+        <f>IF(COUNT('Turns'!D82,'Turns'!D97)=2,SUM('Turns'!D82,'Turns'!D97),"Unknown")</f>
+        <v>102.0</v>
       </c>
       <c r="T20" s="2">
-        <f>IF(COUNT('Turns'!E84,'Turns'!E99)=2,SUM('Turns'!E84,'Turns'!E99),"Unknown")</f>
-        <v>0.00010305876</v>
+        <f>IF(COUNT('Turns'!E82,'Turns'!E97)=2,SUM('Turns'!E82,'Turns'!E97),"Unknown")</f>
+        <v>0.000107680176</v>
       </c>
       <c r="U20" s="2">
-        <f>IF(COUNT('Turns'!F84,'Turns'!F99)=2,SUM('Turns'!F84,'Turns'!F99),"Unknown")</f>
-        <v>0.0001176</v>
+        <f>IF(COUNT('Turns'!F82,'Turns'!F97)=2,SUM('Turns'!F82,'Turns'!F97),"Unknown")</f>
+        <v>0.0001224</v>
       </c>
       <c r="V20" s="2">
-        <f>IF(COUNT('Turns'!D83)=1,SUM('Turns'!D83),"Unknown")</f>
-        <v>9.0</v>
+        <v>0</v>
       </c>
       <c r="W20" s="2">
-        <f>IF(COUNT('Turns'!E83)=1,SUM('Turns'!E83),"Unknown")</f>
-        <v>9.46458e-06</v>
+        <v>0</v>
       </c>
       <c r="X20" s="2">
-        <f>IF(COUNT('Turns'!F83)=1,SUM('Turns'!F83),"Unknown")</f>
-        <v>1.08e-05</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="2">
-        <f>IF(COUNT('Turns'!E88,'Turns'!E103)=2,SUM('Turns'!E88,'Turns'!E103),"Unknown")</f>
-        <v>0.00019910672</v>
+        <f>IF(COUNT('Turns'!E86,'Turns'!E101)=2,SUM('Turns'!E86,'Turns'!E101),"Unknown")</f>
+        <v>0.000195830124</v>
       </c>
       <c r="Z20" s="2">
-        <f>IF(COUNT('Turns'!F88,'Turns'!F103)=2,SUM('Turns'!F88,'Turns'!F103),"Unknown")</f>
-        <v>0.0002272</v>
+        <f>IF(COUNT('Turns'!F86,'Turns'!F101)=2,SUM('Turns'!F86,'Turns'!F101),"Unknown")</f>
+        <v>0.0002226</v>
       </c>
       <c r="AA20" s="5">
         <f>IF(ISNUMBER(Y20),ROUND(Y20*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6195,10 +6107,10 @@
       </c>
       <c r="AB20" s="5">
         <f>IF(ISNUMBER(Z20),ROUND(Z20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="AD20" s="1">
-        <v>2398.465</v>
+        <v>3752.964</v>
       </c>
       <c r="AE20" s="1" t="s">
         <v>184</v>
@@ -6227,30 +6139,30 @@
         <v>216</v>
       </c>
       <c r="I21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J21" s="2">
-        <f>IF(COUNT('Turns'!D77,'Turns'!D94)=2,SUM('Turns'!D77,'Turns'!D94),"Unknown")</f>
-        <v>494.0</v>
+        <f>IF(COUNT('Turns'!D76,'Turns'!D92)=2,SUM('Turns'!D76,'Turns'!D92),"Unknown")</f>
+        <v>501.0</v>
       </c>
       <c r="K21" s="2">
-        <f>IF(COUNT('Turns'!E77,'Turns'!E94)=2,SUM('Turns'!E77,'Turns'!E94),"Unknown")</f>
-        <v>8.658338e-05</v>
+        <f>IF(COUNT('Turns'!E76,'Turns'!E92)=2,SUM('Turns'!E76,'Turns'!E92),"Unknown")</f>
+        <v>8.8149948e-05</v>
       </c>
       <c r="L21" s="2">
-        <f>IF(COUNT('Turns'!F77,'Turns'!F94)=2,SUM('Turns'!F77,'Turns'!F94),"Unknown")</f>
-        <v>9.88e-05</v>
+        <f>IF(COUNT('Turns'!F76,'Turns'!F92)=2,SUM('Turns'!F76,'Turns'!F92),"Unknown")</f>
+        <v>0.0001002</v>
       </c>
       <c r="M21" s="2">
-        <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D91)=1,SUM('Turns'!D91),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N21" s="2">
-        <f>IF(COUNT('Turns'!E93)=1,SUM('Turns'!E93),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E91)=1,SUM('Turns'!E91),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O21" s="2">
-        <f>IF(COUNT('Turns'!F93)=1,SUM('Turns'!F93),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F91)=1,SUM('Turns'!F91),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P21" s="2">
@@ -6263,36 +6175,33 @@
         <v>0</v>
       </c>
       <c r="S21" s="2">
-        <f>IF(COUNT('Turns'!D84,'Turns'!D99)=2,SUM('Turns'!D84,'Turns'!D99),"Unknown")</f>
-        <v>98.0</v>
+        <f>IF(COUNT('Turns'!D82,'Turns'!D97)=2,SUM('Turns'!D82,'Turns'!D97),"Unknown")</f>
+        <v>102.0</v>
       </c>
       <c r="T21" s="2">
-        <f>IF(COUNT('Turns'!E84,'Turns'!E99)=2,SUM('Turns'!E84,'Turns'!E99),"Unknown")</f>
-        <v>0.00010305876</v>
+        <f>IF(COUNT('Turns'!E82,'Turns'!E97)=2,SUM('Turns'!E82,'Turns'!E97),"Unknown")</f>
+        <v>0.000107680176</v>
       </c>
       <c r="U21" s="2">
-        <f>IF(COUNT('Turns'!F84,'Turns'!F99)=2,SUM('Turns'!F84,'Turns'!F99),"Unknown")</f>
-        <v>0.0001176</v>
+        <f>IF(COUNT('Turns'!F82,'Turns'!F97)=2,SUM('Turns'!F82,'Turns'!F97),"Unknown")</f>
+        <v>0.0001224</v>
       </c>
       <c r="V21" s="2">
-        <f>IF(COUNT('Turns'!D83)=1,SUM('Turns'!D83),"Unknown")</f>
-        <v>9.0</v>
+        <v>0</v>
       </c>
       <c r="W21" s="2">
-        <f>IF(COUNT('Turns'!E83)=1,SUM('Turns'!E83),"Unknown")</f>
-        <v>9.46458e-06</v>
+        <v>0</v>
       </c>
       <c r="X21" s="2">
-        <f>IF(COUNT('Turns'!F83)=1,SUM('Turns'!F83),"Unknown")</f>
-        <v>1.08e-05</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="2">
-        <f>IF(COUNT('Turns'!E88,'Turns'!E103)=2,SUM('Turns'!E88,'Turns'!E103),"Unknown")</f>
-        <v>0.00019910672</v>
+        <f>IF(COUNT('Turns'!E86,'Turns'!E101)=2,SUM('Turns'!E86,'Turns'!E101),"Unknown")</f>
+        <v>0.000195830124</v>
       </c>
       <c r="Z21" s="2">
-        <f>IF(COUNT('Turns'!F88,'Turns'!F103)=2,SUM('Turns'!F88,'Turns'!F103),"Unknown")</f>
-        <v>0.0002272</v>
+        <f>IF(COUNT('Turns'!F86,'Turns'!F101)=2,SUM('Turns'!F86,'Turns'!F101),"Unknown")</f>
+        <v>0.0002226</v>
       </c>
       <c r="AA21" s="5">
         <f>IF(ISNUMBER(Y21),ROUND(Y21*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6300,10 +6209,10 @@
       </c>
       <c r="AB21" s="5">
         <f>IF(ISNUMBER(Z21),ROUND(Z21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="AD21" s="1">
-        <v>2396.452</v>
+        <v>3751.748</v>
       </c>
       <c r="AE21" s="1" t="s">
         <v>184</v>
@@ -6335,16 +6244,16 @@
         <v>216</v>
       </c>
       <c r="J22" s="2">
-        <f>IF(COUNT('Turns'!D77)=1,SUM('Turns'!D77),"Unknown")</f>
-        <v>194.0</v>
+        <f>IF(COUNT('Turns'!D76)=1,SUM('Turns'!D76),"Unknown")</f>
+        <v>201.0</v>
       </c>
       <c r="K22" s="2">
-        <f>IF(COUNT('Turns'!E77)=1,SUM('Turns'!E77),"Unknown")</f>
-        <v>3.400238e-05</v>
+        <f>IF(COUNT('Turns'!E76)=1,SUM('Turns'!E76),"Unknown")</f>
+        <v>3.5365548e-05</v>
       </c>
       <c r="L22" s="2">
-        <f>IF(COUNT('Turns'!F77)=1,SUM('Turns'!F77),"Unknown")</f>
-        <v>3.88e-05</v>
+        <f>IF(COUNT('Turns'!F76)=1,SUM('Turns'!F76),"Unknown")</f>
+        <v>4.02e-05</v>
       </c>
       <c r="M22" s="2">
         <v>0</v>
@@ -6365,47 +6274,44 @@
         <v>0</v>
       </c>
       <c r="S22" s="2">
-        <f>IF(COUNT('Turns'!D84)=1,SUM('Turns'!D84),"Unknown")</f>
-        <v>40.0</v>
+        <f>IF(COUNT('Turns'!D82)=1,SUM('Turns'!D82),"Unknown")</f>
+        <v>42.0</v>
       </c>
       <c r="T22" s="2">
-        <f>IF(COUNT('Turns'!E84)=1,SUM('Turns'!E84),"Unknown")</f>
-        <v>4.20648e-05</v>
+        <f>IF(COUNT('Turns'!E82)=1,SUM('Turns'!E82),"Unknown")</f>
+        <v>4.4338896e-05</v>
       </c>
       <c r="U22" s="2">
-        <f>IF(COUNT('Turns'!F84)=1,SUM('Turns'!F84),"Unknown")</f>
-        <v>4.8e-05</v>
+        <f>IF(COUNT('Turns'!F82)=1,SUM('Turns'!F82),"Unknown")</f>
+        <v>5.04e-05</v>
       </c>
       <c r="V22" s="2">
-        <f>IF(COUNT('Turns'!D83)=1,SUM('Turns'!D83),"Unknown")</f>
-        <v>9.0</v>
+        <v>0</v>
       </c>
       <c r="W22" s="2">
-        <f>IF(COUNT('Turns'!E83)=1,SUM('Turns'!E83),"Unknown")</f>
-        <v>9.46458e-06</v>
+        <v>0</v>
       </c>
       <c r="X22" s="2">
-        <f>IF(COUNT('Turns'!F83)=1,SUM('Turns'!F83),"Unknown")</f>
-        <v>1.08e-05</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="2">
-        <f>IF(COUNT('Turns'!E88)=1,SUM('Turns'!E88),"Unknown")</f>
-        <v>8.553176e-05</v>
+        <f>IF(COUNT('Turns'!E86)=1,SUM('Turns'!E86),"Unknown")</f>
+        <v>7.9704444e-05</v>
       </c>
       <c r="Z22" s="2">
-        <f>IF(COUNT('Turns'!F88)=1,SUM('Turns'!F88),"Unknown")</f>
-        <v>9.76e-05</v>
+        <f>IF(COUNT('Turns'!F86)=1,SUM('Turns'!F86),"Unknown")</f>
+        <v>9.06e-05</v>
       </c>
       <c r="AA22" s="5">
         <f>IF(ISNUMBER(Y22),ROUND(Y22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="AB22" s="5">
         <f>IF(ISNUMBER(Z22),ROUND(Z22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="AD22" s="1">
-        <v>1155.481</v>
+        <v>2623.669</v>
       </c>
       <c r="AE22" s="1" t="s">
         <v>184</v>
@@ -6428,28 +6334,28 @@
         <v>110</v>
       </c>
       <c r="F23" s="1">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>190</v>
       </c>
       <c r="H23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I23" t="s">
         <v>217</v>
       </c>
       <c r="J23" s="2">
-        <f>IF(COUNT('Turns'!D77)=1,SUM('Turns'!D77),"Unknown")</f>
-        <v>194.0</v>
+        <f>IF(COUNT('Turns'!D76)=1,SUM('Turns'!D76),"Unknown")</f>
+        <v>201.0</v>
       </c>
       <c r="K23" s="2">
-        <f>IF(COUNT('Turns'!E77)=1,SUM('Turns'!E77),"Unknown")</f>
-        <v>3.400238e-05</v>
+        <f>IF(COUNT('Turns'!E76)=1,SUM('Turns'!E76),"Unknown")</f>
+        <v>3.5365548e-05</v>
       </c>
       <c r="L23" s="2">
-        <f>IF(COUNT('Turns'!F77)=1,SUM('Turns'!F77),"Unknown")</f>
-        <v>3.88e-05</v>
+        <f>IF(COUNT('Turns'!F76)=1,SUM('Turns'!F76),"Unknown")</f>
+        <v>4.02e-05</v>
       </c>
       <c r="M23" s="2">
         <v>0</v>
@@ -6470,50 +6376,47 @@
         <v>0</v>
       </c>
       <c r="S23" s="2">
-        <f>IF(COUNT('Turns'!D84)=1,SUM('Turns'!D84),"Unknown")</f>
-        <v>40.0</v>
+        <f>IF(COUNT('Turns'!D82)=1,SUM('Turns'!D82),"Unknown")</f>
+        <v>42.0</v>
       </c>
       <c r="T23" s="2">
-        <f>IF(COUNT('Turns'!E84)=1,SUM('Turns'!E84),"Unknown")</f>
-        <v>4.20648e-05</v>
+        <f>IF(COUNT('Turns'!E82)=1,SUM('Turns'!E82),"Unknown")</f>
+        <v>4.4338896e-05</v>
       </c>
       <c r="U23" s="2">
-        <f>IF(COUNT('Turns'!F84)=1,SUM('Turns'!F84),"Unknown")</f>
-        <v>4.8e-05</v>
+        <f>IF(COUNT('Turns'!F82)=1,SUM('Turns'!F82),"Unknown")</f>
+        <v>5.04e-05</v>
       </c>
       <c r="V23" s="2">
-        <f>IF(COUNT('Turns'!D83)=1,SUM('Turns'!D83),"Unknown")</f>
-        <v>9.0</v>
+        <v>0</v>
       </c>
       <c r="W23" s="2">
-        <f>IF(COUNT('Turns'!E83)=1,SUM('Turns'!E83),"Unknown")</f>
-        <v>9.46458e-06</v>
+        <v>0</v>
       </c>
       <c r="X23" s="2">
-        <f>IF(COUNT('Turns'!F83)=1,SUM('Turns'!F83),"Unknown")</f>
-        <v>1.08e-05</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="2">
-        <f>IF(COUNT('Turns'!E88)=1,SUM('Turns'!E88),"Unknown")</f>
-        <v>8.553176e-05</v>
+        <f>IF(COUNT('Turns'!E86)=1,SUM('Turns'!E86),"Unknown")</f>
+        <v>7.9704444e-05</v>
       </c>
       <c r="Z23" s="2">
-        <f>IF(COUNT('Turns'!F88)=1,SUM('Turns'!F88),"Unknown")</f>
-        <v>9.76e-05</v>
+        <f>IF(COUNT('Turns'!F86)=1,SUM('Turns'!F86),"Unknown")</f>
+        <v>9.06e-05</v>
       </c>
       <c r="AA23" s="5">
         <f>IF(ISNUMBER(Y23),ROUND(Y23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="AB23" s="5">
         <f>IF(ISNUMBER(Z23),ROUND(Z23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="AC23" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AD23" s="1">
-        <v>1150.346</v>
+        <v>2621.446</v>
       </c>
       <c r="AE23" s="1" t="s">
         <v>191</v>
@@ -6545,7 +6448,7 @@
         <v>216</v>
       </c>
       <c r="AD24" s="1">
-        <v>3.775</v>
+        <v>1.503</v>
       </c>
       <c r="AE24" s="1" t="s">
         <v>206</v>
@@ -6571,13 +6474,13 @@
         <v>220</v>
       </c>
       <c r="H25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I25" t="s">
         <v>218</v>
       </c>
       <c r="AD25" s="1">
-        <v>1.128</v>
+        <v>0.445</v>
       </c>
       <c r="AE25" s="1" t="s">
         <v>206</v>
@@ -6609,27 +6512,27 @@
         <v>216</v>
       </c>
       <c r="J26" s="2">
-        <f>IF(COUNT('Turns'!D94)=1,SUM('Turns'!D94),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D92)=1,SUM('Turns'!D92),"Unknown")</f>
         <v>300.0</v>
       </c>
       <c r="K26" s="2">
-        <f>IF(COUNT('Turns'!E94)=1,SUM('Turns'!E94),"Unknown")</f>
-        <v>5.2581e-05</v>
+        <f>IF(COUNT('Turns'!E92)=1,SUM('Turns'!E92),"Unknown")</f>
+        <v>5.27844e-05</v>
       </c>
       <c r="L26" s="2">
-        <f>IF(COUNT('Turns'!F94)=1,SUM('Turns'!F94),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F92)=1,SUM('Turns'!F92),"Unknown")</f>
         <v>6e-05</v>
       </c>
       <c r="M26" s="2">
-        <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D91)=1,SUM('Turns'!D91),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N26" s="2">
-        <f>IF(COUNT('Turns'!E93)=1,SUM('Turns'!E93),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E91)=1,SUM('Turns'!E91),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O26" s="2">
-        <f>IF(COUNT('Turns'!F93)=1,SUM('Turns'!F93),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F91)=1,SUM('Turns'!F91),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P26" s="2">
@@ -6642,16 +6545,16 @@
         <v>0</v>
       </c>
       <c r="S26" s="2">
-        <f>IF(COUNT('Turns'!D99)=1,SUM('Turns'!D99),"Unknown")</f>
-        <v>58.0</v>
+        <f>IF(COUNT('Turns'!D97)=1,SUM('Turns'!D97),"Unknown")</f>
+        <v>60.0</v>
       </c>
       <c r="T26" s="2">
-        <f>IF(COUNT('Turns'!E99)=1,SUM('Turns'!E99),"Unknown")</f>
-        <v>6.099396e-05</v>
+        <f>IF(COUNT('Turns'!E97)=1,SUM('Turns'!E97),"Unknown")</f>
+        <v>6.334128e-05</v>
       </c>
       <c r="U26" s="2">
-        <f>IF(COUNT('Turns'!F99)=1,SUM('Turns'!F99),"Unknown")</f>
-        <v>6.96e-05</v>
+        <f>IF(COUNT('Turns'!F97)=1,SUM('Turns'!F97),"Unknown")</f>
+        <v>7.2e-05</v>
       </c>
       <c r="V26" s="2">
         <v>0</v>
@@ -6663,23 +6566,23 @@
         <v>0</v>
       </c>
       <c r="Y26" s="2">
-        <f>IF(COUNT('Turns'!E103)=1,SUM('Turns'!E103),"Unknown")</f>
-        <v>0.00011357496</v>
+        <f>IF(COUNT('Turns'!E101)=1,SUM('Turns'!E101),"Unknown")</f>
+        <v>0.00011612568</v>
       </c>
       <c r="Z26" s="2">
-        <f>IF(COUNT('Turns'!F103)=1,SUM('Turns'!F103),"Unknown")</f>
-        <v>0.0001296</v>
+        <f>IF(COUNT('Turns'!F101)=1,SUM('Turns'!F101),"Unknown")</f>
+        <v>0.000132</v>
       </c>
       <c r="AA26" s="5">
         <f>IF(ISNUMBER(Y26),ROUND(Y26*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="AB26" s="5">
         <f>IF(ISNUMBER(Z26),ROUND(Z26*'Reference data'!$B$2,0),"Unknown")</f>
         <v>13.0</v>
       </c>
       <c r="AD26" s="1">
-        <v>1231.425</v>
+        <v>1123.121</v>
       </c>
       <c r="AE26" s="1" t="s">
         <v>184</v>
@@ -6708,33 +6611,33 @@
         <v>190</v>
       </c>
       <c r="H27" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I27" t="s">
         <v>221</v>
       </c>
       <c r="J27" s="2">
-        <f>IF(COUNT('Turns'!D94)=1,SUM('Turns'!D94),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D92)=1,SUM('Turns'!D92),"Unknown")</f>
         <v>300.0</v>
       </c>
       <c r="K27" s="2">
-        <f>IF(COUNT('Turns'!E94)=1,SUM('Turns'!E94),"Unknown")</f>
-        <v>5.2581e-05</v>
+        <f>IF(COUNT('Turns'!E92)=1,SUM('Turns'!E92),"Unknown")</f>
+        <v>5.27844e-05</v>
       </c>
       <c r="L27" s="2">
-        <f>IF(COUNT('Turns'!F94)=1,SUM('Turns'!F94),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F92)=1,SUM('Turns'!F92),"Unknown")</f>
         <v>6e-05</v>
       </c>
       <c r="M27" s="2">
-        <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D91)=1,SUM('Turns'!D91),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N27" s="2">
-        <f>IF(COUNT('Turns'!E93)=1,SUM('Turns'!E93),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E91)=1,SUM('Turns'!E91),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O27" s="2">
-        <f>IF(COUNT('Turns'!F93)=1,SUM('Turns'!F93),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F91)=1,SUM('Turns'!F91),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P27" s="2">
@@ -6747,16 +6650,16 @@
         <v>0</v>
       </c>
       <c r="S27" s="2">
-        <f>IF(COUNT('Turns'!D99)=1,SUM('Turns'!D99),"Unknown")</f>
-        <v>58.0</v>
+        <f>IF(COUNT('Turns'!D97)=1,SUM('Turns'!D97),"Unknown")</f>
+        <v>60.0</v>
       </c>
       <c r="T27" s="2">
-        <f>IF(COUNT('Turns'!E99)=1,SUM('Turns'!E99),"Unknown")</f>
-        <v>6.099396e-05</v>
+        <f>IF(COUNT('Turns'!E97)=1,SUM('Turns'!E97),"Unknown")</f>
+        <v>6.334128e-05</v>
       </c>
       <c r="U27" s="2">
-        <f>IF(COUNT('Turns'!F99)=1,SUM('Turns'!F99),"Unknown")</f>
-        <v>6.96e-05</v>
+        <f>IF(COUNT('Turns'!F97)=1,SUM('Turns'!F97),"Unknown")</f>
+        <v>7.2e-05</v>
       </c>
       <c r="V27" s="2">
         <v>0</v>
@@ -6768,26 +6671,26 @@
         <v>0</v>
       </c>
       <c r="Y27" s="2">
-        <f>IF(COUNT('Turns'!E103)=1,SUM('Turns'!E103),"Unknown")</f>
-        <v>0.00011357496</v>
+        <f>IF(COUNT('Turns'!E101)=1,SUM('Turns'!E101),"Unknown")</f>
+        <v>0.00011612568</v>
       </c>
       <c r="Z27" s="2">
-        <f>IF(COUNT('Turns'!F103)=1,SUM('Turns'!F103),"Unknown")</f>
-        <v>0.0001296</v>
+        <f>IF(COUNT('Turns'!F101)=1,SUM('Turns'!F101),"Unknown")</f>
+        <v>0.000132</v>
       </c>
       <c r="AA27" s="5">
         <f>IF(ISNUMBER(Y27),ROUND(Y27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="AB27" s="5">
         <f>IF(ISNUMBER(Z27),ROUND(Z27*'Reference data'!$B$2,0),"Unknown")</f>
         <v>13.0</v>
       </c>
       <c r="AC27" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AD27" s="1">
-        <v>1229.024</v>
+        <v>1121.278</v>
       </c>
       <c r="AE27" s="1" t="s">
         <v>191</v>
@@ -6819,27 +6722,27 @@
         <v>211</v>
       </c>
       <c r="J28" s="2">
-        <f>IF(COUNT('Turns'!D106)=1,SUM('Turns'!D106),"Unknown")</f>
-        <v>531.0</v>
+        <f>IF(COUNT('Turns'!D104)=1,SUM('Turns'!D104),"Unknown")</f>
+        <v>535.0</v>
       </c>
       <c r="K28" s="2">
-        <f>IF(COUNT('Turns'!E106)=1,SUM('Turns'!E106),"Unknown")</f>
-        <v>9.306837e-05</v>
+        <f>IF(COUNT('Turns'!E104)=1,SUM('Turns'!E104),"Unknown")</f>
+        <v>9.413218e-05</v>
       </c>
       <c r="L28" s="2">
-        <f>IF(COUNT('Turns'!F106)=1,SUM('Turns'!F106),"Unknown")</f>
-        <v>0.0001062</v>
+        <f>IF(COUNT('Turns'!F104)=1,SUM('Turns'!F104),"Unknown")</f>
+        <v>0.000107</v>
       </c>
       <c r="M28" s="2">
-        <f>IF(COUNT('Turns'!D105)=1,SUM('Turns'!D105),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D103)=1,SUM('Turns'!D103),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N28" s="2">
-        <f>IF(COUNT('Turns'!E105)=1,SUM('Turns'!E105),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E103)=1,SUM('Turns'!E103),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O28" s="2">
-        <f>IF(COUNT('Turns'!F105)=1,SUM('Turns'!F105),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F103)=1,SUM('Turns'!F103),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P28" s="2">
@@ -6852,16 +6755,16 @@
         <v>0</v>
       </c>
       <c r="S28" s="2">
-        <f>IF(COUNT('Turns'!D111)=1,SUM('Turns'!D111),"Unknown")</f>
-        <v>23.0</v>
+        <f>IF(COUNT('Turns'!D109)=1,SUM('Turns'!D109),"Unknown")</f>
+        <v>19.0</v>
       </c>
       <c r="T28" s="2">
-        <f>IF(COUNT('Turns'!E111)=1,SUM('Turns'!E111),"Unknown")</f>
-        <v>2.418726e-05</v>
+        <f>IF(COUNT('Turns'!E109)=1,SUM('Turns'!E109),"Unknown")</f>
+        <v>2.0058072e-05</v>
       </c>
       <c r="U28" s="2">
-        <f>IF(COUNT('Turns'!F111)=1,SUM('Turns'!F111),"Unknown")</f>
-        <v>2.76e-05</v>
+        <f>IF(COUNT('Turns'!F109)=1,SUM('Turns'!F109),"Unknown")</f>
+        <v>2.28e-05</v>
       </c>
       <c r="V28" s="2">
         <v>0</v>
@@ -6873,23 +6776,23 @@
         <v>0</v>
       </c>
       <c r="Y28" s="2">
-        <f>IF(COUNT('Turns'!E115)=1,SUM('Turns'!E115),"Unknown")</f>
-        <v>0.00011725563</v>
+        <f>IF(COUNT('Turns'!E113)=1,SUM('Turns'!E113),"Unknown")</f>
+        <v>0.000114190252</v>
       </c>
       <c r="Z28" s="2">
-        <f>IF(COUNT('Turns'!F115)=1,SUM('Turns'!F115),"Unknown")</f>
-        <v>0.0001338</v>
+        <f>IF(COUNT('Turns'!F113)=1,SUM('Turns'!F113),"Unknown")</f>
+        <v>0.0001298</v>
       </c>
       <c r="AA28" s="5">
         <f>IF(ISNUMBER(Y28),ROUND(Y28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="AB28" s="5">
         <f>IF(ISNUMBER(Z28),ROUND(Z28*'Reference data'!$B$2,0),"Unknown")</f>
         <v>13.0</v>
       </c>
       <c r="AD28" s="1">
-        <v>937.609</v>
+        <v>960.659</v>
       </c>
       <c r="AE28" s="1" t="s">
         <v>184</v>
@@ -6912,39 +6815,39 @@
         <v>110</v>
       </c>
       <c r="F29" s="1">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>190</v>
       </c>
       <c r="H29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I29" t="s">
         <v>222</v>
       </c>
       <c r="J29" s="2">
-        <f>IF(COUNT('Turns'!D106)=1,SUM('Turns'!D106),"Unknown")</f>
-        <v>531.0</v>
+        <f>IF(COUNT('Turns'!D104)=1,SUM('Turns'!D104),"Unknown")</f>
+        <v>535.0</v>
       </c>
       <c r="K29" s="2">
-        <f>IF(COUNT('Turns'!E106)=1,SUM('Turns'!E106),"Unknown")</f>
-        <v>9.306837e-05</v>
+        <f>IF(COUNT('Turns'!E104)=1,SUM('Turns'!E104),"Unknown")</f>
+        <v>9.413218e-05</v>
       </c>
       <c r="L29" s="2">
-        <f>IF(COUNT('Turns'!F106)=1,SUM('Turns'!F106),"Unknown")</f>
-        <v>0.0001062</v>
+        <f>IF(COUNT('Turns'!F104)=1,SUM('Turns'!F104),"Unknown")</f>
+        <v>0.000107</v>
       </c>
       <c r="M29" s="2">
-        <f>IF(COUNT('Turns'!D105)=1,SUM('Turns'!D105),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D103)=1,SUM('Turns'!D103),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N29" s="2">
-        <f>IF(COUNT('Turns'!E105)=1,SUM('Turns'!E105),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E103)=1,SUM('Turns'!E103),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O29" s="2">
-        <f>IF(COUNT('Turns'!F105)=1,SUM('Turns'!F105),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F103)=1,SUM('Turns'!F103),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P29" s="2">
@@ -6957,16 +6860,16 @@
         <v>0</v>
       </c>
       <c r="S29" s="2">
-        <f>IF(COUNT('Turns'!D111)=1,SUM('Turns'!D111),"Unknown")</f>
-        <v>23.0</v>
+        <f>IF(COUNT('Turns'!D109)=1,SUM('Turns'!D109),"Unknown")</f>
+        <v>19.0</v>
       </c>
       <c r="T29" s="2">
-        <f>IF(COUNT('Turns'!E111)=1,SUM('Turns'!E111),"Unknown")</f>
-        <v>2.418726e-05</v>
+        <f>IF(COUNT('Turns'!E109)=1,SUM('Turns'!E109),"Unknown")</f>
+        <v>2.0058072e-05</v>
       </c>
       <c r="U29" s="2">
-        <f>IF(COUNT('Turns'!F111)=1,SUM('Turns'!F111),"Unknown")</f>
-        <v>2.76e-05</v>
+        <f>IF(COUNT('Turns'!F109)=1,SUM('Turns'!F109),"Unknown")</f>
+        <v>2.28e-05</v>
       </c>
       <c r="V29" s="2">
         <v>0</v>
@@ -6978,26 +6881,26 @@
         <v>0</v>
       </c>
       <c r="Y29" s="2">
-        <f>IF(COUNT('Turns'!E115)=1,SUM('Turns'!E115),"Unknown")</f>
-        <v>0.00011725563</v>
+        <f>IF(COUNT('Turns'!E113)=1,SUM('Turns'!E113),"Unknown")</f>
+        <v>0.000114190252</v>
       </c>
       <c r="Z29" s="2">
-        <f>IF(COUNT('Turns'!F115)=1,SUM('Turns'!F115),"Unknown")</f>
-        <v>0.0001338</v>
+        <f>IF(COUNT('Turns'!F113)=1,SUM('Turns'!F113),"Unknown")</f>
+        <v>0.0001298</v>
       </c>
       <c r="AA29" s="5">
         <f>IF(ISNUMBER(Y29),ROUND(Y29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="AB29" s="5">
         <f>IF(ISNUMBER(Z29),ROUND(Z29*'Reference data'!$B$2,0),"Unknown")</f>
         <v>13.0</v>
       </c>
       <c r="AC29" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AD29" s="1">
-        <v>934.571</v>
+        <v>959.207</v>
       </c>
       <c r="AE29" s="1" t="s">
         <v>191</v>
@@ -7026,27 +6929,27 @@
         <v>223</v>
       </c>
       <c r="J30" s="2">
-        <f>IF(COUNT('Turns'!D119,'Turns'!D133,'Turns'!D150,'Turns'!D162)=4,SUM('Turns'!D119,'Turns'!D133,'Turns'!D150,'Turns'!D162),"Unknown")</f>
-        <v>1728.0</v>
+        <f>IF(COUNT('Turns'!D117,'Turns'!D131,'Turns'!D148,'Turns'!D160)=4,SUM('Turns'!D117,'Turns'!D131,'Turns'!D148,'Turns'!D160),"Unknown")</f>
+        <v>1723.0</v>
       </c>
       <c r="K30" s="2">
-        <f>IF(COUNT('Turns'!E119,'Turns'!E133,'Turns'!E150,'Turns'!E162)=4,SUM('Turns'!E119,'Turns'!E133,'Turns'!E150,'Turns'!E162),"Unknown")</f>
-        <v>0.00030286656</v>
+        <f>IF(COUNT('Turns'!E117,'Turns'!E131,'Turns'!E148,'Turns'!E160)=4,SUM('Turns'!E117,'Turns'!E131,'Turns'!E148,'Turns'!E160),"Unknown")</f>
+        <v>0.000303158404</v>
       </c>
       <c r="L30" s="2">
-        <f>IF(COUNT('Turns'!F119,'Turns'!F133,'Turns'!F150,'Turns'!F162)=4,SUM('Turns'!F119,'Turns'!F133,'Turns'!F150,'Turns'!F162),"Unknown")</f>
-        <v>0.0003456</v>
+        <f>IF(COUNT('Turns'!F117,'Turns'!F131,'Turns'!F148,'Turns'!F160)=4,SUM('Turns'!F117,'Turns'!F131,'Turns'!F148,'Turns'!F160),"Unknown")</f>
+        <v>0.0003446</v>
       </c>
       <c r="M30" s="2">
-        <f>IF(COUNT('Turns'!D118,'Turns'!D149,'Turns'!D161)=3,SUM('Turns'!D118,'Turns'!D149,'Turns'!D161),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D116,'Turns'!D147,'Turns'!D159)=3,SUM('Turns'!D116,'Turns'!D147,'Turns'!D159),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N30" s="2">
-        <f>IF(COUNT('Turns'!E118,'Turns'!E149,'Turns'!E161)=3,SUM('Turns'!E118,'Turns'!E149,'Turns'!E161),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E116,'Turns'!E147,'Turns'!E159)=3,SUM('Turns'!E116,'Turns'!E147,'Turns'!E159),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O30" s="2">
-        <f>IF(COUNT('Turns'!F118,'Turns'!F149,'Turns'!F161)=3,SUM('Turns'!F118,'Turns'!F149,'Turns'!F161),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F116,'Turns'!F147,'Turns'!F159)=3,SUM('Turns'!F116,'Turns'!F147,'Turns'!F159),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P30" s="2">
@@ -7059,36 +6962,36 @@
         <v>0</v>
       </c>
       <c r="S30" s="2">
-        <f>IF(COUNT('Turns'!D124,'Turns'!D140,'Turns'!D155,'Turns'!D167)=4,SUM('Turns'!D124,'Turns'!D140,'Turns'!D155,'Turns'!D167),"Unknown")</f>
-        <v>158.0</v>
+        <f>IF(COUNT('Turns'!D122,'Turns'!D138,'Turns'!D153,'Turns'!D165)=4,SUM('Turns'!D122,'Turns'!D138,'Turns'!D153,'Turns'!D165),"Unknown")</f>
+        <v>155.0</v>
       </c>
       <c r="T30" s="2">
-        <f>IF(COUNT('Turns'!E124,'Turns'!E140,'Turns'!E155,'Turns'!E167)=4,SUM('Turns'!E124,'Turns'!E140,'Turns'!E155,'Turns'!E167),"Unknown")</f>
-        <v>0.00016615596</v>
+        <f>IF(COUNT('Turns'!E122,'Turns'!E138,'Turns'!E153,'Turns'!E165)=4,SUM('Turns'!E122,'Turns'!E138,'Turns'!E153,'Turns'!E165),"Unknown")</f>
+        <v>0.00016363164</v>
       </c>
       <c r="U30" s="2">
-        <f>IF(COUNT('Turns'!F124,'Turns'!F140,'Turns'!F155,'Turns'!F167)=4,SUM('Turns'!F124,'Turns'!F140,'Turns'!F155,'Turns'!F167),"Unknown")</f>
-        <v>0.0001896</v>
+        <f>IF(COUNT('Turns'!F122,'Turns'!F138,'Turns'!F153,'Turns'!F165)=4,SUM('Turns'!F122,'Turns'!F138,'Turns'!F153,'Turns'!F165),"Unknown")</f>
+        <v>0.000186</v>
       </c>
       <c r="V30" s="2">
-        <f>IF(COUNT('Turns'!D139)=1,SUM('Turns'!D139),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D137)=1,SUM('Turns'!D137),"Unknown")</f>
         <v>9.0</v>
       </c>
       <c r="W30" s="2">
-        <f>IF(COUNT('Turns'!E139)=1,SUM('Turns'!E139),"Unknown")</f>
-        <v>9.46458e-06</v>
+        <f>IF(COUNT('Turns'!E137)=1,SUM('Turns'!E137),"Unknown")</f>
+        <v>9.501192e-06</v>
       </c>
       <c r="X30" s="2">
-        <f>IF(COUNT('Turns'!F139)=1,SUM('Turns'!F139),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F137)=1,SUM('Turns'!F137),"Unknown")</f>
         <v>1.08e-05</v>
       </c>
       <c r="Y30" s="2">
-        <f>IF(COUNT('Turns'!E128,'Turns'!E144,'Turns'!E159,'Turns'!E171)=4,SUM('Turns'!E128,'Turns'!E144,'Turns'!E159,'Turns'!E171),"Unknown")</f>
-        <v>0.0004784871</v>
+        <f>IF(COUNT('Turns'!E126,'Turns'!E142,'Turns'!E157,'Turns'!E169)=4,SUM('Turns'!E126,'Turns'!E142,'Turns'!E157,'Turns'!E169),"Unknown")</f>
+        <v>0.000476291236</v>
       </c>
       <c r="Z30" s="2">
-        <f>IF(COUNT('Turns'!F128,'Turns'!F144,'Turns'!F159,'Turns'!F171)=4,SUM('Turns'!F128,'Turns'!F144,'Turns'!F159,'Turns'!F171),"Unknown")</f>
-        <v>0.000546</v>
+        <f>IF(COUNT('Turns'!F126,'Turns'!F142,'Turns'!F157,'Turns'!F169)=4,SUM('Turns'!F126,'Turns'!F142,'Turns'!F157,'Turns'!F169),"Unknown")</f>
+        <v>0.0005414</v>
       </c>
       <c r="AA30" s="5">
         <f>IF(ISNUMBER(Y30),ROUND(Y30*'Reference data'!$B$2,0),"Unknown")</f>
@@ -7096,10 +6999,10 @@
       </c>
       <c r="AB30" s="5">
         <f>IF(ISNUMBER(Z30),ROUND(Z30*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>55.0</v>
+        <v>54.0</v>
       </c>
       <c r="AD30" s="1">
-        <v>4756.339</v>
+        <v>5087.24</v>
       </c>
       <c r="AE30" s="1" t="s">
         <v>184</v>
@@ -7131,27 +7034,27 @@
         <v>223</v>
       </c>
       <c r="J31" s="2">
-        <f>IF(COUNT('Turns'!D119)=1,SUM('Turns'!D119),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D117)=1,SUM('Turns'!D117),"Unknown")</f>
         <v>569.0</v>
       </c>
       <c r="K31" s="2">
-        <f>IF(COUNT('Turns'!E119)=1,SUM('Turns'!E119),"Unknown")</f>
-        <v>9.972863e-05</v>
+        <f>IF(COUNT('Turns'!E117)=1,SUM('Turns'!E117),"Unknown")</f>
+        <v>0.000100114412</v>
       </c>
       <c r="L31" s="2">
-        <f>IF(COUNT('Turns'!F119)=1,SUM('Turns'!F119),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F117)=1,SUM('Turns'!F117),"Unknown")</f>
         <v>0.0001138</v>
       </c>
       <c r="M31" s="2">
-        <f>IF(COUNT('Turns'!D118)=1,SUM('Turns'!D118),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D116)=1,SUM('Turns'!D116),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N31" s="2">
-        <f>IF(COUNT('Turns'!E118)=1,SUM('Turns'!E118),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E116)=1,SUM('Turns'!E116),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O31" s="2">
-        <f>IF(COUNT('Turns'!F118)=1,SUM('Turns'!F118),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F116)=1,SUM('Turns'!F116),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P31" s="2">
@@ -7164,16 +7067,16 @@
         <v>0</v>
       </c>
       <c r="S31" s="2">
-        <f>IF(COUNT('Turns'!D124)=1,SUM('Turns'!D124),"Unknown")</f>
-        <v>54.0</v>
+        <f>IF(COUNT('Turns'!D122)=1,SUM('Turns'!D122),"Unknown")</f>
+        <v>53.0</v>
       </c>
       <c r="T31" s="2">
-        <f>IF(COUNT('Turns'!E124)=1,SUM('Turns'!E124),"Unknown")</f>
-        <v>5.678748e-05</v>
+        <f>IF(COUNT('Turns'!E122)=1,SUM('Turns'!E122),"Unknown")</f>
+        <v>5.5951464e-05</v>
       </c>
       <c r="U31" s="2">
-        <f>IF(COUNT('Turns'!F124)=1,SUM('Turns'!F124),"Unknown")</f>
-        <v>6.48e-05</v>
+        <f>IF(COUNT('Turns'!F122)=1,SUM('Turns'!F122),"Unknown")</f>
+        <v>6.36e-05</v>
       </c>
       <c r="V31" s="2">
         <v>0</v>
@@ -7185,12 +7088,12 @@
         <v>0</v>
       </c>
       <c r="Y31" s="2">
-        <f>IF(COUNT('Turns'!E128)=1,SUM('Turns'!E128),"Unknown")</f>
-        <v>0.00015651611</v>
+        <f>IF(COUNT('Turns'!E126)=1,SUM('Turns'!E126),"Unknown")</f>
+        <v>0.000156065876</v>
       </c>
       <c r="Z31" s="2">
-        <f>IF(COUNT('Turns'!F128)=1,SUM('Turns'!F128),"Unknown")</f>
-        <v>0.0001786</v>
+        <f>IF(COUNT('Turns'!F126)=1,SUM('Turns'!F126),"Unknown")</f>
+        <v>0.0001774</v>
       </c>
       <c r="AA31" s="5">
         <f>IF(ISNUMBER(Y31),ROUND(Y31*'Reference data'!$B$2,0),"Unknown")</f>
@@ -7201,7 +7104,7 @@
         <v>18.0</v>
       </c>
       <c r="AD31" s="1">
-        <v>1106.929</v>
+        <v>1279.051</v>
       </c>
       <c r="AE31" s="1" t="s">
         <v>184</v>
@@ -7230,33 +7133,33 @@
         <v>190</v>
       </c>
       <c r="H32" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I32" t="s">
         <v>224</v>
       </c>
       <c r="J32" s="2">
-        <f>IF(COUNT('Turns'!D119)=1,SUM('Turns'!D119),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D117)=1,SUM('Turns'!D117),"Unknown")</f>
         <v>569.0</v>
       </c>
       <c r="K32" s="2">
-        <f>IF(COUNT('Turns'!E119)=1,SUM('Turns'!E119),"Unknown")</f>
-        <v>9.972863e-05</v>
+        <f>IF(COUNT('Turns'!E117)=1,SUM('Turns'!E117),"Unknown")</f>
+        <v>0.000100114412</v>
       </c>
       <c r="L32" s="2">
-        <f>IF(COUNT('Turns'!F119)=1,SUM('Turns'!F119),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F117)=1,SUM('Turns'!F117),"Unknown")</f>
         <v>0.0001138</v>
       </c>
       <c r="M32" s="2">
-        <f>IF(COUNT('Turns'!D118)=1,SUM('Turns'!D118),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D116)=1,SUM('Turns'!D116),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N32" s="2">
-        <f>IF(COUNT('Turns'!E118)=1,SUM('Turns'!E118),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E116)=1,SUM('Turns'!E116),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O32" s="2">
-        <f>IF(COUNT('Turns'!F118)=1,SUM('Turns'!F118),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F116)=1,SUM('Turns'!F116),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P32" s="2">
@@ -7269,16 +7172,16 @@
         <v>0</v>
       </c>
       <c r="S32" s="2">
-        <f>IF(COUNT('Turns'!D124)=1,SUM('Turns'!D124),"Unknown")</f>
-        <v>54.0</v>
+        <f>IF(COUNT('Turns'!D122)=1,SUM('Turns'!D122),"Unknown")</f>
+        <v>53.0</v>
       </c>
       <c r="T32" s="2">
-        <f>IF(COUNT('Turns'!E124)=1,SUM('Turns'!E124),"Unknown")</f>
-        <v>5.678748e-05</v>
+        <f>IF(COUNT('Turns'!E122)=1,SUM('Turns'!E122),"Unknown")</f>
+        <v>5.5951464e-05</v>
       </c>
       <c r="U32" s="2">
-        <f>IF(COUNT('Turns'!F124)=1,SUM('Turns'!F124),"Unknown")</f>
-        <v>6.48e-05</v>
+        <f>IF(COUNT('Turns'!F122)=1,SUM('Turns'!F122),"Unknown")</f>
+        <v>6.36e-05</v>
       </c>
       <c r="V32" s="2">
         <v>0</v>
@@ -7290,12 +7193,12 @@
         <v>0</v>
       </c>
       <c r="Y32" s="2">
-        <f>IF(COUNT('Turns'!E128)=1,SUM('Turns'!E128),"Unknown")</f>
-        <v>0.00015651611</v>
+        <f>IF(COUNT('Turns'!E126)=1,SUM('Turns'!E126),"Unknown")</f>
+        <v>0.000156065876</v>
       </c>
       <c r="Z32" s="2">
-        <f>IF(COUNT('Turns'!F128)=1,SUM('Turns'!F128),"Unknown")</f>
-        <v>0.0001786</v>
+        <f>IF(COUNT('Turns'!F126)=1,SUM('Turns'!F126),"Unknown")</f>
+        <v>0.0001774</v>
       </c>
       <c r="AA32" s="5">
         <f>IF(ISNUMBER(Y32),ROUND(Y32*'Reference data'!$B$2,0),"Unknown")</f>
@@ -7306,10 +7209,10 @@
         <v>18.0</v>
       </c>
       <c r="AC32" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AD32" s="1">
-        <v>1104.188</v>
+        <v>1276.855</v>
       </c>
       <c r="AE32" s="1" t="s">
         <v>191</v>
@@ -7341,27 +7244,27 @@
         <v>223</v>
       </c>
       <c r="J33" s="2">
-        <f>IF(COUNT('Turns'!D133,'Turns'!D150)=2,SUM('Turns'!D133,'Turns'!D150),"Unknown")</f>
-        <v>482.0</v>
+        <f>IF(COUNT('Turns'!D131,'Turns'!D148)=2,SUM('Turns'!D131,'Turns'!D148),"Unknown")</f>
+        <v>476.0</v>
       </c>
       <c r="K33" s="2">
-        <f>IF(COUNT('Turns'!E133,'Turns'!E150)=2,SUM('Turns'!E133,'Turns'!E150),"Unknown")</f>
-        <v>8.448014e-05</v>
+        <f>IF(COUNT('Turns'!E131,'Turns'!E148)=2,SUM('Turns'!E131,'Turns'!E148),"Unknown")</f>
+        <v>8.3751248e-05</v>
       </c>
       <c r="L33" s="2">
-        <f>IF(COUNT('Turns'!F133,'Turns'!F150)=2,SUM('Turns'!F133,'Turns'!F150),"Unknown")</f>
-        <v>9.64e-05</v>
+        <f>IF(COUNT('Turns'!F131,'Turns'!F148)=2,SUM('Turns'!F131,'Turns'!F148),"Unknown")</f>
+        <v>9.52e-05</v>
       </c>
       <c r="M33" s="2">
-        <f>IF(COUNT('Turns'!D149)=1,SUM('Turns'!D149),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D147)=1,SUM('Turns'!D147),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N33" s="2">
-        <f>IF(COUNT('Turns'!E149)=1,SUM('Turns'!E149),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E147)=1,SUM('Turns'!E147),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O33" s="2">
-        <f>IF(COUNT('Turns'!F149)=1,SUM('Turns'!F149),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F147)=1,SUM('Turns'!F147),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P33" s="2">
@@ -7374,36 +7277,36 @@
         <v>0</v>
       </c>
       <c r="S33" s="2">
-        <f>IF(COUNT('Turns'!D140,'Turns'!D155)=2,SUM('Turns'!D140,'Turns'!D155),"Unknown")</f>
-        <v>84.0</v>
+        <f>IF(COUNT('Turns'!D138,'Turns'!D153)=2,SUM('Turns'!D138,'Turns'!D153),"Unknown")</f>
+        <v>82.0</v>
       </c>
       <c r="T33" s="2">
-        <f>IF(COUNT('Turns'!E140,'Turns'!E155)=2,SUM('Turns'!E140,'Turns'!E155),"Unknown")</f>
-        <v>8.833608e-05</v>
+        <f>IF(COUNT('Turns'!E138,'Turns'!E153)=2,SUM('Turns'!E138,'Turns'!E153),"Unknown")</f>
+        <v>8.6566416e-05</v>
       </c>
       <c r="U33" s="2">
-        <f>IF(COUNT('Turns'!F140,'Turns'!F155)=2,SUM('Turns'!F140,'Turns'!F155),"Unknown")</f>
-        <v>0.0001008</v>
+        <f>IF(COUNT('Turns'!F138,'Turns'!F153)=2,SUM('Turns'!F138,'Turns'!F153),"Unknown")</f>
+        <v>9.84e-05</v>
       </c>
       <c r="V33" s="2">
-        <f>IF(COUNT('Turns'!D139)=1,SUM('Turns'!D139),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D137)=1,SUM('Turns'!D137),"Unknown")</f>
         <v>9.0</v>
       </c>
       <c r="W33" s="2">
-        <f>IF(COUNT('Turns'!E139)=1,SUM('Turns'!E139),"Unknown")</f>
-        <v>9.46458e-06</v>
+        <f>IF(COUNT('Turns'!E137)=1,SUM('Turns'!E137),"Unknown")</f>
+        <v>9.501192e-06</v>
       </c>
       <c r="X33" s="2">
-        <f>IF(COUNT('Turns'!F139)=1,SUM('Turns'!F139),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F137)=1,SUM('Turns'!F137),"Unknown")</f>
         <v>1.08e-05</v>
       </c>
       <c r="Y33" s="2">
-        <f>IF(COUNT('Turns'!E144,'Turns'!E159)=2,SUM('Turns'!E144,'Turns'!E159),"Unknown")</f>
-        <v>0.0001822808</v>
+        <f>IF(COUNT('Turns'!E142,'Turns'!E157)=2,SUM('Turns'!E142,'Turns'!E157),"Unknown")</f>
+        <v>0.000179818856</v>
       </c>
       <c r="Z33" s="2">
-        <f>IF(COUNT('Turns'!F144,'Turns'!F159)=2,SUM('Turns'!F144,'Turns'!F159),"Unknown")</f>
-        <v>0.000208</v>
+        <f>IF(COUNT('Turns'!F142,'Turns'!F157)=2,SUM('Turns'!F142,'Turns'!F157),"Unknown")</f>
+        <v>0.0002044</v>
       </c>
       <c r="AA33" s="5">
         <f>IF(ISNUMBER(Y33),ROUND(Y33*'Reference data'!$B$2,0),"Unknown")</f>
@@ -7411,10 +7314,10 @@
       </c>
       <c r="AB33" s="5">
         <f>IF(ISNUMBER(Z33),ROUND(Z33*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="AD33" s="1">
-        <v>2809.288</v>
+        <v>2900.45</v>
       </c>
       <c r="AE33" s="1" t="s">
         <v>184</v>
@@ -7440,33 +7343,33 @@
         <v>197</v>
       </c>
       <c r="H34" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I34" t="s">
         <v>225</v>
       </c>
       <c r="J34" s="2">
-        <f>IF(COUNT('Turns'!D133,'Turns'!D150)=2,SUM('Turns'!D133,'Turns'!D150),"Unknown")</f>
-        <v>482.0</v>
+        <f>IF(COUNT('Turns'!D131,'Turns'!D148)=2,SUM('Turns'!D131,'Turns'!D148),"Unknown")</f>
+        <v>476.0</v>
       </c>
       <c r="K34" s="2">
-        <f>IF(COUNT('Turns'!E133,'Turns'!E150)=2,SUM('Turns'!E133,'Turns'!E150),"Unknown")</f>
-        <v>8.448014e-05</v>
+        <f>IF(COUNT('Turns'!E131,'Turns'!E148)=2,SUM('Turns'!E131,'Turns'!E148),"Unknown")</f>
+        <v>8.3751248e-05</v>
       </c>
       <c r="L34" s="2">
-        <f>IF(COUNT('Turns'!F133,'Turns'!F150)=2,SUM('Turns'!F133,'Turns'!F150),"Unknown")</f>
-        <v>9.64e-05</v>
+        <f>IF(COUNT('Turns'!F131,'Turns'!F148)=2,SUM('Turns'!F131,'Turns'!F148),"Unknown")</f>
+        <v>9.52e-05</v>
       </c>
       <c r="M34" s="2">
-        <f>IF(COUNT('Turns'!D149)=1,SUM('Turns'!D149),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D147)=1,SUM('Turns'!D147),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N34" s="2">
-        <f>IF(COUNT('Turns'!E149)=1,SUM('Turns'!E149),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E147)=1,SUM('Turns'!E147),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O34" s="2">
-        <f>IF(COUNT('Turns'!F149)=1,SUM('Turns'!F149),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F147)=1,SUM('Turns'!F147),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P34" s="2">
@@ -7479,36 +7382,36 @@
         <v>0</v>
       </c>
       <c r="S34" s="2">
-        <f>IF(COUNT('Turns'!D140,'Turns'!D155)=2,SUM('Turns'!D140,'Turns'!D155),"Unknown")</f>
-        <v>84.0</v>
+        <f>IF(COUNT('Turns'!D138,'Turns'!D153)=2,SUM('Turns'!D138,'Turns'!D153),"Unknown")</f>
+        <v>82.0</v>
       </c>
       <c r="T34" s="2">
-        <f>IF(COUNT('Turns'!E140,'Turns'!E155)=2,SUM('Turns'!E140,'Turns'!E155),"Unknown")</f>
-        <v>8.833608e-05</v>
+        <f>IF(COUNT('Turns'!E138,'Turns'!E153)=2,SUM('Turns'!E138,'Turns'!E153),"Unknown")</f>
+        <v>8.6566416e-05</v>
       </c>
       <c r="U34" s="2">
-        <f>IF(COUNT('Turns'!F140,'Turns'!F155)=2,SUM('Turns'!F140,'Turns'!F155),"Unknown")</f>
-        <v>0.0001008</v>
+        <f>IF(COUNT('Turns'!F138,'Turns'!F153)=2,SUM('Turns'!F138,'Turns'!F153),"Unknown")</f>
+        <v>9.84e-05</v>
       </c>
       <c r="V34" s="2">
-        <f>IF(COUNT('Turns'!D139)=1,SUM('Turns'!D139),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D137)=1,SUM('Turns'!D137),"Unknown")</f>
         <v>9.0</v>
       </c>
       <c r="W34" s="2">
-        <f>IF(COUNT('Turns'!E139)=1,SUM('Turns'!E139),"Unknown")</f>
-        <v>9.46458e-06</v>
+        <f>IF(COUNT('Turns'!E137)=1,SUM('Turns'!E137),"Unknown")</f>
+        <v>9.501192e-06</v>
       </c>
       <c r="X34" s="2">
-        <f>IF(COUNT('Turns'!F139)=1,SUM('Turns'!F139),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F137)=1,SUM('Turns'!F137),"Unknown")</f>
         <v>1.08e-05</v>
       </c>
       <c r="Y34" s="2">
-        <f>IF(COUNT('Turns'!E144,'Turns'!E159)=2,SUM('Turns'!E144,'Turns'!E159),"Unknown")</f>
-        <v>0.0001822808</v>
+        <f>IF(COUNT('Turns'!E142,'Turns'!E157)=2,SUM('Turns'!E142,'Turns'!E157),"Unknown")</f>
+        <v>0.000179818856</v>
       </c>
       <c r="Z34" s="2">
-        <f>IF(COUNT('Turns'!F144,'Turns'!F159)=2,SUM('Turns'!F144,'Turns'!F159),"Unknown")</f>
-        <v>0.000208</v>
+        <f>IF(COUNT('Turns'!F142,'Turns'!F157)=2,SUM('Turns'!F142,'Turns'!F157),"Unknown")</f>
+        <v>0.0002044</v>
       </c>
       <c r="AA34" s="5">
         <f>IF(ISNUMBER(Y34),ROUND(Y34*'Reference data'!$B$2,0),"Unknown")</f>
@@ -7516,10 +7419,10 @@
       </c>
       <c r="AB34" s="5">
         <f>IF(ISNUMBER(Z34),ROUND(Z34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="AD34" s="1">
-        <v>2807.139</v>
+        <v>2899.258</v>
       </c>
       <c r="AE34" s="1" t="s">
         <v>184</v>
@@ -7548,30 +7451,30 @@
         <v>228</v>
       </c>
       <c r="I35" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J35" s="2">
-        <f>IF(COUNT('Turns'!D133,'Turns'!D150)=2,SUM('Turns'!D133,'Turns'!D150),"Unknown")</f>
-        <v>482.0</v>
+        <f>IF(COUNT('Turns'!D131,'Turns'!D148)=2,SUM('Turns'!D131,'Turns'!D148),"Unknown")</f>
+        <v>476.0</v>
       </c>
       <c r="K35" s="2">
-        <f>IF(COUNT('Turns'!E133,'Turns'!E150)=2,SUM('Turns'!E133,'Turns'!E150),"Unknown")</f>
-        <v>8.448014e-05</v>
+        <f>IF(COUNT('Turns'!E131,'Turns'!E148)=2,SUM('Turns'!E131,'Turns'!E148),"Unknown")</f>
+        <v>8.3751248e-05</v>
       </c>
       <c r="L35" s="2">
-        <f>IF(COUNT('Turns'!F133,'Turns'!F150)=2,SUM('Turns'!F133,'Turns'!F150),"Unknown")</f>
-        <v>9.64e-05</v>
+        <f>IF(COUNT('Turns'!F131,'Turns'!F148)=2,SUM('Turns'!F131,'Turns'!F148),"Unknown")</f>
+        <v>9.52e-05</v>
       </c>
       <c r="M35" s="2">
-        <f>IF(COUNT('Turns'!D149)=1,SUM('Turns'!D149),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D147)=1,SUM('Turns'!D147),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N35" s="2">
-        <f>IF(COUNT('Turns'!E149)=1,SUM('Turns'!E149),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E147)=1,SUM('Turns'!E147),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O35" s="2">
-        <f>IF(COUNT('Turns'!F149)=1,SUM('Turns'!F149),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F147)=1,SUM('Turns'!F147),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P35" s="2">
@@ -7584,36 +7487,36 @@
         <v>0</v>
       </c>
       <c r="S35" s="2">
-        <f>IF(COUNT('Turns'!D140,'Turns'!D155)=2,SUM('Turns'!D140,'Turns'!D155),"Unknown")</f>
-        <v>84.0</v>
+        <f>IF(COUNT('Turns'!D138,'Turns'!D153)=2,SUM('Turns'!D138,'Turns'!D153),"Unknown")</f>
+        <v>82.0</v>
       </c>
       <c r="T35" s="2">
-        <f>IF(COUNT('Turns'!E140,'Turns'!E155)=2,SUM('Turns'!E140,'Turns'!E155),"Unknown")</f>
-        <v>8.833608e-05</v>
+        <f>IF(COUNT('Turns'!E138,'Turns'!E153)=2,SUM('Turns'!E138,'Turns'!E153),"Unknown")</f>
+        <v>8.6566416e-05</v>
       </c>
       <c r="U35" s="2">
-        <f>IF(COUNT('Turns'!F140,'Turns'!F155)=2,SUM('Turns'!F140,'Turns'!F155),"Unknown")</f>
-        <v>0.0001008</v>
+        <f>IF(COUNT('Turns'!F138,'Turns'!F153)=2,SUM('Turns'!F138,'Turns'!F153),"Unknown")</f>
+        <v>9.84e-05</v>
       </c>
       <c r="V35" s="2">
-        <f>IF(COUNT('Turns'!D139)=1,SUM('Turns'!D139),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D137)=1,SUM('Turns'!D137),"Unknown")</f>
         <v>9.0</v>
       </c>
       <c r="W35" s="2">
-        <f>IF(COUNT('Turns'!E139)=1,SUM('Turns'!E139),"Unknown")</f>
-        <v>9.46458e-06</v>
+        <f>IF(COUNT('Turns'!E137)=1,SUM('Turns'!E137),"Unknown")</f>
+        <v>9.501192e-06</v>
       </c>
       <c r="X35" s="2">
-        <f>IF(COUNT('Turns'!F139)=1,SUM('Turns'!F139),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F137)=1,SUM('Turns'!F137),"Unknown")</f>
         <v>1.08e-05</v>
       </c>
       <c r="Y35" s="2">
-        <f>IF(COUNT('Turns'!E144,'Turns'!E159)=2,SUM('Turns'!E144,'Turns'!E159),"Unknown")</f>
-        <v>0.0001822808</v>
+        <f>IF(COUNT('Turns'!E142,'Turns'!E157)=2,SUM('Turns'!E142,'Turns'!E157),"Unknown")</f>
+        <v>0.000179818856</v>
       </c>
       <c r="Z35" s="2">
-        <f>IF(COUNT('Turns'!F144,'Turns'!F159)=2,SUM('Turns'!F144,'Turns'!F159),"Unknown")</f>
-        <v>0.000208</v>
+        <f>IF(COUNT('Turns'!F142,'Turns'!F157)=2,SUM('Turns'!F142,'Turns'!F157),"Unknown")</f>
+        <v>0.0002044</v>
       </c>
       <c r="AA35" s="5">
         <f>IF(ISNUMBER(Y35),ROUND(Y35*'Reference data'!$B$2,0),"Unknown")</f>
@@ -7621,10 +7524,10 @@
       </c>
       <c r="AB35" s="5">
         <f>IF(ISNUMBER(Z35),ROUND(Z35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="AD35" s="1">
-        <v>2805.076</v>
+        <v>2898.057</v>
       </c>
       <c r="AE35" s="1" t="s">
         <v>184</v>
@@ -7656,16 +7559,16 @@
         <v>228</v>
       </c>
       <c r="J36" s="2">
-        <f>IF(COUNT('Turns'!D133)=1,SUM('Turns'!D133),"Unknown")</f>
-        <v>186.0</v>
+        <f>IF(COUNT('Turns'!D131)=1,SUM('Turns'!D131),"Unknown")</f>
+        <v>185.0</v>
       </c>
       <c r="K36" s="2">
-        <f>IF(COUNT('Turns'!E133)=1,SUM('Turns'!E133),"Unknown")</f>
-        <v>3.260022e-05</v>
+        <f>IF(COUNT('Turns'!E131)=1,SUM('Turns'!E131),"Unknown")</f>
+        <v>3.255038e-05</v>
       </c>
       <c r="L36" s="2">
-        <f>IF(COUNT('Turns'!F133)=1,SUM('Turns'!F133),"Unknown")</f>
-        <v>3.72e-05</v>
+        <f>IF(COUNT('Turns'!F131)=1,SUM('Turns'!F131),"Unknown")</f>
+        <v>3.7e-05</v>
       </c>
       <c r="M36" s="2">
         <v>0</v>
@@ -7686,36 +7589,36 @@
         <v>0</v>
       </c>
       <c r="S36" s="2">
-        <f>IF(COUNT('Turns'!D140)=1,SUM('Turns'!D140),"Unknown")</f>
-        <v>36.0</v>
+        <f>IF(COUNT('Turns'!D138)=1,SUM('Turns'!D138),"Unknown")</f>
+        <v>32.0</v>
       </c>
       <c r="T36" s="2">
-        <f>IF(COUNT('Turns'!E140)=1,SUM('Turns'!E140),"Unknown")</f>
-        <v>3.785832e-05</v>
+        <f>IF(COUNT('Turns'!E138)=1,SUM('Turns'!E138),"Unknown")</f>
+        <v>3.3782016e-05</v>
       </c>
       <c r="U36" s="2">
-        <f>IF(COUNT('Turns'!F140)=1,SUM('Turns'!F140),"Unknown")</f>
-        <v>4.32e-05</v>
+        <f>IF(COUNT('Turns'!F138)=1,SUM('Turns'!F138),"Unknown")</f>
+        <v>3.84e-05</v>
       </c>
       <c r="V36" s="2">
-        <f>IF(COUNT('Turns'!D139)=1,SUM('Turns'!D139),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D137)=1,SUM('Turns'!D137),"Unknown")</f>
         <v>9.0</v>
       </c>
       <c r="W36" s="2">
-        <f>IF(COUNT('Turns'!E139)=1,SUM('Turns'!E139),"Unknown")</f>
-        <v>9.46458e-06</v>
+        <f>IF(COUNT('Turns'!E137)=1,SUM('Turns'!E137),"Unknown")</f>
+        <v>9.501192e-06</v>
       </c>
       <c r="X36" s="2">
-        <f>IF(COUNT('Turns'!F139)=1,SUM('Turns'!F139),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F137)=1,SUM('Turns'!F137),"Unknown")</f>
         <v>1.08e-05</v>
       </c>
       <c r="Y36" s="2">
-        <f>IF(COUNT('Turns'!E144)=1,SUM('Turns'!E144),"Unknown")</f>
-        <v>7.992312e-05</v>
+        <f>IF(COUNT('Turns'!E142)=1,SUM('Turns'!E142),"Unknown")</f>
+        <v>7.5833588e-05</v>
       </c>
       <c r="Z36" s="2">
-        <f>IF(COUNT('Turns'!F144)=1,SUM('Turns'!F144),"Unknown")</f>
-        <v>9.12e-05</v>
+        <f>IF(COUNT('Turns'!F142)=1,SUM('Turns'!F142),"Unknown")</f>
+        <v>8.62e-05</v>
       </c>
       <c r="AA36" s="5">
         <f>IF(ISNUMBER(Y36),ROUND(Y36*'Reference data'!$B$2,0),"Unknown")</f>
@@ -7726,7 +7629,7 @@
         <v>9.0</v>
       </c>
       <c r="AD36" s="1">
-        <v>1523.87</v>
+        <v>1037.289</v>
       </c>
       <c r="AE36" s="1" t="s">
         <v>184</v>
@@ -7749,28 +7652,28 @@
         <v>110</v>
       </c>
       <c r="F37" s="1">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>190</v>
       </c>
       <c r="H37" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I37" t="s">
         <v>229</v>
       </c>
       <c r="J37" s="2">
-        <f>IF(COUNT('Turns'!D133)=1,SUM('Turns'!D133),"Unknown")</f>
-        <v>186.0</v>
+        <f>IF(COUNT('Turns'!D131)=1,SUM('Turns'!D131),"Unknown")</f>
+        <v>185.0</v>
       </c>
       <c r="K37" s="2">
-        <f>IF(COUNT('Turns'!E133)=1,SUM('Turns'!E133),"Unknown")</f>
-        <v>3.260022e-05</v>
+        <f>IF(COUNT('Turns'!E131)=1,SUM('Turns'!E131),"Unknown")</f>
+        <v>3.255038e-05</v>
       </c>
       <c r="L37" s="2">
-        <f>IF(COUNT('Turns'!F133)=1,SUM('Turns'!F133),"Unknown")</f>
-        <v>3.72e-05</v>
+        <f>IF(COUNT('Turns'!F131)=1,SUM('Turns'!F131),"Unknown")</f>
+        <v>3.7e-05</v>
       </c>
       <c r="M37" s="2">
         <v>0</v>
@@ -7791,36 +7694,36 @@
         <v>0</v>
       </c>
       <c r="S37" s="2">
-        <f>IF(COUNT('Turns'!D140)=1,SUM('Turns'!D140),"Unknown")</f>
-        <v>36.0</v>
+        <f>IF(COUNT('Turns'!D138)=1,SUM('Turns'!D138),"Unknown")</f>
+        <v>32.0</v>
       </c>
       <c r="T37" s="2">
-        <f>IF(COUNT('Turns'!E140)=1,SUM('Turns'!E140),"Unknown")</f>
-        <v>3.785832e-05</v>
+        <f>IF(COUNT('Turns'!E138)=1,SUM('Turns'!E138),"Unknown")</f>
+        <v>3.3782016e-05</v>
       </c>
       <c r="U37" s="2">
-        <f>IF(COUNT('Turns'!F140)=1,SUM('Turns'!F140),"Unknown")</f>
-        <v>4.32e-05</v>
+        <f>IF(COUNT('Turns'!F138)=1,SUM('Turns'!F138),"Unknown")</f>
+        <v>3.84e-05</v>
       </c>
       <c r="V37" s="2">
-        <f>IF(COUNT('Turns'!D139)=1,SUM('Turns'!D139),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D137)=1,SUM('Turns'!D137),"Unknown")</f>
         <v>9.0</v>
       </c>
       <c r="W37" s="2">
-        <f>IF(COUNT('Turns'!E139)=1,SUM('Turns'!E139),"Unknown")</f>
-        <v>9.46458e-06</v>
+        <f>IF(COUNT('Turns'!E137)=1,SUM('Turns'!E137),"Unknown")</f>
+        <v>9.501192e-06</v>
       </c>
       <c r="X37" s="2">
-        <f>IF(COUNT('Turns'!F139)=1,SUM('Turns'!F139),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F137)=1,SUM('Turns'!F137),"Unknown")</f>
         <v>1.08e-05</v>
       </c>
       <c r="Y37" s="2">
-        <f>IF(COUNT('Turns'!E144)=1,SUM('Turns'!E144),"Unknown")</f>
-        <v>7.992312e-05</v>
+        <f>IF(COUNT('Turns'!E142)=1,SUM('Turns'!E142),"Unknown")</f>
+        <v>7.5833588e-05</v>
       </c>
       <c r="Z37" s="2">
-        <f>IF(COUNT('Turns'!F144)=1,SUM('Turns'!F144),"Unknown")</f>
-        <v>9.12e-05</v>
+        <f>IF(COUNT('Turns'!F142)=1,SUM('Turns'!F142),"Unknown")</f>
+        <v>8.62e-05</v>
       </c>
       <c r="AA37" s="5">
         <f>IF(ISNUMBER(Y37),ROUND(Y37*'Reference data'!$B$2,0),"Unknown")</f>
@@ -7831,10 +7734,10 @@
         <v>9.0</v>
       </c>
       <c r="AC37" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AD37" s="1">
-        <v>1519.66</v>
+        <v>1033.674</v>
       </c>
       <c r="AE37" s="1" t="s">
         <v>191</v>
@@ -7866,7 +7769,7 @@
         <v>228</v>
       </c>
       <c r="AD38" s="1">
-        <v>3.392</v>
+        <v>2.105</v>
       </c>
       <c r="AE38" s="1" t="s">
         <v>206</v>
@@ -7898,7 +7801,7 @@
         <v>230</v>
       </c>
       <c r="AD39" s="1">
-        <v>1.148</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AE39" s="1" t="s">
         <v>206</v>
@@ -7930,27 +7833,27 @@
         <v>228</v>
       </c>
       <c r="J40" s="2">
-        <f>IF(COUNT('Turns'!D150)=1,SUM('Turns'!D150),"Unknown")</f>
-        <v>296.0</v>
+        <f>IF(COUNT('Turns'!D148)=1,SUM('Turns'!D148),"Unknown")</f>
+        <v>291.0</v>
       </c>
       <c r="K40" s="2">
-        <f>IF(COUNT('Turns'!E150)=1,SUM('Turns'!E150),"Unknown")</f>
-        <v>5.187992e-05</v>
+        <f>IF(COUNT('Turns'!E148)=1,SUM('Turns'!E148),"Unknown")</f>
+        <v>5.1200868e-05</v>
       </c>
       <c r="L40" s="2">
-        <f>IF(COUNT('Turns'!F150)=1,SUM('Turns'!F150),"Unknown")</f>
-        <v>5.92e-05</v>
+        <f>IF(COUNT('Turns'!F148)=1,SUM('Turns'!F148),"Unknown")</f>
+        <v>5.82e-05</v>
       </c>
       <c r="M40" s="2">
-        <f>IF(COUNT('Turns'!D149)=1,SUM('Turns'!D149),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D147)=1,SUM('Turns'!D147),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N40" s="2">
-        <f>IF(COUNT('Turns'!E149)=1,SUM('Turns'!E149),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E147)=1,SUM('Turns'!E147),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O40" s="2">
-        <f>IF(COUNT('Turns'!F149)=1,SUM('Turns'!F149),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F147)=1,SUM('Turns'!F147),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P40" s="2">
@@ -7963,16 +7866,16 @@
         <v>0</v>
       </c>
       <c r="S40" s="2">
-        <f>IF(COUNT('Turns'!D155)=1,SUM('Turns'!D155),"Unknown")</f>
-        <v>48.0</v>
+        <f>IF(COUNT('Turns'!D153)=1,SUM('Turns'!D153),"Unknown")</f>
+        <v>50.0</v>
       </c>
       <c r="T40" s="2">
-        <f>IF(COUNT('Turns'!E155)=1,SUM('Turns'!E155),"Unknown")</f>
-        <v>5.047776e-05</v>
+        <f>IF(COUNT('Turns'!E153)=1,SUM('Turns'!E153),"Unknown")</f>
+        <v>5.27844e-05</v>
       </c>
       <c r="U40" s="2">
-        <f>IF(COUNT('Turns'!F155)=1,SUM('Turns'!F155),"Unknown")</f>
-        <v>5.76e-05</v>
+        <f>IF(COUNT('Turns'!F153)=1,SUM('Turns'!F153),"Unknown")</f>
+        <v>6e-05</v>
       </c>
       <c r="V40" s="2">
         <v>0</v>
@@ -7984,12 +7887,12 @@
         <v>0</v>
       </c>
       <c r="Y40" s="2">
-        <f>IF(COUNT('Turns'!E159)=1,SUM('Turns'!E159),"Unknown")</f>
-        <v>0.00010235768</v>
+        <f>IF(COUNT('Turns'!E157)=1,SUM('Turns'!E157),"Unknown")</f>
+        <v>0.000103985268</v>
       </c>
       <c r="Z40" s="2">
-        <f>IF(COUNT('Turns'!F159)=1,SUM('Turns'!F159),"Unknown")</f>
-        <v>0.0001168</v>
+        <f>IF(COUNT('Turns'!F157)=1,SUM('Turns'!F157),"Unknown")</f>
+        <v>0.0001182</v>
       </c>
       <c r="AA40" s="5">
         <f>IF(ISNUMBER(Y40),ROUND(Y40*'Reference data'!$B$2,0),"Unknown")</f>
@@ -8000,7 +7903,7 @@
         <v>12.0</v>
       </c>
       <c r="AD40" s="1">
-        <v>1272.585</v>
+        <v>1854.657</v>
       </c>
       <c r="AE40" s="1" t="s">
         <v>184</v>
@@ -8023,7 +7926,7 @@
         <v>110</v>
       </c>
       <c r="F41" s="1">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>190</v>
@@ -8035,27 +7938,27 @@
         <v>233</v>
       </c>
       <c r="J41" s="2">
-        <f>IF(COUNT('Turns'!D150)=1,SUM('Turns'!D150),"Unknown")</f>
-        <v>296.0</v>
+        <f>IF(COUNT('Turns'!D148)=1,SUM('Turns'!D148),"Unknown")</f>
+        <v>291.0</v>
       </c>
       <c r="K41" s="2">
-        <f>IF(COUNT('Turns'!E150)=1,SUM('Turns'!E150),"Unknown")</f>
-        <v>5.187992e-05</v>
+        <f>IF(COUNT('Turns'!E148)=1,SUM('Turns'!E148),"Unknown")</f>
+        <v>5.1200868e-05</v>
       </c>
       <c r="L41" s="2">
-        <f>IF(COUNT('Turns'!F150)=1,SUM('Turns'!F150),"Unknown")</f>
-        <v>5.92e-05</v>
+        <f>IF(COUNT('Turns'!F148)=1,SUM('Turns'!F148),"Unknown")</f>
+        <v>5.82e-05</v>
       </c>
       <c r="M41" s="2">
-        <f>IF(COUNT('Turns'!D149)=1,SUM('Turns'!D149),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D147)=1,SUM('Turns'!D147),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N41" s="2">
-        <f>IF(COUNT('Turns'!E149)=1,SUM('Turns'!E149),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E147)=1,SUM('Turns'!E147),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O41" s="2">
-        <f>IF(COUNT('Turns'!F149)=1,SUM('Turns'!F149),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F147)=1,SUM('Turns'!F147),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P41" s="2">
@@ -8068,16 +7971,16 @@
         <v>0</v>
       </c>
       <c r="S41" s="2">
-        <f>IF(COUNT('Turns'!D155)=1,SUM('Turns'!D155),"Unknown")</f>
-        <v>48.0</v>
+        <f>IF(COUNT('Turns'!D153)=1,SUM('Turns'!D153),"Unknown")</f>
+        <v>50.0</v>
       </c>
       <c r="T41" s="2">
-        <f>IF(COUNT('Turns'!E155)=1,SUM('Turns'!E155),"Unknown")</f>
-        <v>5.047776e-05</v>
+        <f>IF(COUNT('Turns'!E153)=1,SUM('Turns'!E153),"Unknown")</f>
+        <v>5.27844e-05</v>
       </c>
       <c r="U41" s="2">
-        <f>IF(COUNT('Turns'!F155)=1,SUM('Turns'!F155),"Unknown")</f>
-        <v>5.76e-05</v>
+        <f>IF(COUNT('Turns'!F153)=1,SUM('Turns'!F153),"Unknown")</f>
+        <v>6e-05</v>
       </c>
       <c r="V41" s="2">
         <v>0</v>
@@ -8089,12 +7992,12 @@
         <v>0</v>
       </c>
       <c r="Y41" s="2">
-        <f>IF(COUNT('Turns'!E159)=1,SUM('Turns'!E159),"Unknown")</f>
-        <v>0.00010235768</v>
+        <f>IF(COUNT('Turns'!E157)=1,SUM('Turns'!E157),"Unknown")</f>
+        <v>0.000103985268</v>
       </c>
       <c r="Z41" s="2">
-        <f>IF(COUNT('Turns'!F159)=1,SUM('Turns'!F159),"Unknown")</f>
-        <v>0.0001168</v>
+        <f>IF(COUNT('Turns'!F157)=1,SUM('Turns'!F157),"Unknown")</f>
+        <v>0.0001182</v>
       </c>
       <c r="AA41" s="5">
         <f>IF(ISNUMBER(Y41),ROUND(Y41*'Reference data'!$B$2,0),"Unknown")</f>
@@ -8108,7 +8011,7 @@
         <v>174</v>
       </c>
       <c r="AD41" s="1">
-        <v>1270.302</v>
+        <v>1853.468</v>
       </c>
       <c r="AE41" s="1" t="s">
         <v>191</v>
@@ -8140,27 +8043,27 @@
         <v>223</v>
       </c>
       <c r="J42" s="2">
-        <f>IF(COUNT('Turns'!D162)=1,SUM('Turns'!D162),"Unknown")</f>
-        <v>677.0</v>
+        <f>IF(COUNT('Turns'!D160)=1,SUM('Turns'!D160),"Unknown")</f>
+        <v>678.0</v>
       </c>
       <c r="K42" s="2">
-        <f>IF(COUNT('Turns'!E162)=1,SUM('Turns'!E162),"Unknown")</f>
-        <v>0.00011865779</v>
+        <f>IF(COUNT('Turns'!E160)=1,SUM('Turns'!E160),"Unknown")</f>
+        <v>0.000119292744</v>
       </c>
       <c r="L42" s="2">
-        <f>IF(COUNT('Turns'!F162)=1,SUM('Turns'!F162),"Unknown")</f>
-        <v>0.0001354</v>
+        <f>IF(COUNT('Turns'!F160)=1,SUM('Turns'!F160),"Unknown")</f>
+        <v>0.0001356</v>
       </c>
       <c r="M42" s="2">
-        <f>IF(COUNT('Turns'!D161)=1,SUM('Turns'!D161),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D159)=1,SUM('Turns'!D159),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N42" s="2">
-        <f>IF(COUNT('Turns'!E161)=1,SUM('Turns'!E161),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E159)=1,SUM('Turns'!E159),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O42" s="2">
-        <f>IF(COUNT('Turns'!F161)=1,SUM('Turns'!F161),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F159)=1,SUM('Turns'!F159),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P42" s="2">
@@ -8173,15 +8076,15 @@
         <v>0</v>
       </c>
       <c r="S42" s="2">
-        <f>IF(COUNT('Turns'!D167)=1,SUM('Turns'!D167),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D165)=1,SUM('Turns'!D165),"Unknown")</f>
         <v>20.0</v>
       </c>
       <c r="T42" s="2">
-        <f>IF(COUNT('Turns'!E167)=1,SUM('Turns'!E167),"Unknown")</f>
-        <v>2.10324e-05</v>
+        <f>IF(COUNT('Turns'!E165)=1,SUM('Turns'!E165),"Unknown")</f>
+        <v>2.111376e-05</v>
       </c>
       <c r="U42" s="2">
-        <f>IF(COUNT('Turns'!F167)=1,SUM('Turns'!F167),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F165)=1,SUM('Turns'!F165),"Unknown")</f>
         <v>2.4e-05</v>
       </c>
       <c r="V42" s="2">
@@ -8194,12 +8097,12 @@
         <v>0</v>
       </c>
       <c r="Y42" s="2">
-        <f>IF(COUNT('Turns'!E171)=1,SUM('Turns'!E171),"Unknown")</f>
-        <v>0.00013969019</v>
+        <f>IF(COUNT('Turns'!E169)=1,SUM('Turns'!E169),"Unknown")</f>
+        <v>0.000140406504</v>
       </c>
       <c r="Z42" s="2">
-        <f>IF(COUNT('Turns'!F171)=1,SUM('Turns'!F171),"Unknown")</f>
-        <v>0.0001594</v>
+        <f>IF(COUNT('Turns'!F169)=1,SUM('Turns'!F169),"Unknown")</f>
+        <v>0.0001596</v>
       </c>
       <c r="AA42" s="5">
         <f>IF(ISNUMBER(Y42),ROUND(Y42*'Reference data'!$B$2,0),"Unknown")</f>
@@ -8210,7 +8113,7 @@
         <v>16.0</v>
       </c>
       <c r="AD42" s="1">
-        <v>832.677</v>
+        <v>903.617</v>
       </c>
       <c r="AE42" s="1" t="s">
         <v>184</v>
@@ -8233,7 +8136,7 @@
         <v>110</v>
       </c>
       <c r="F43" s="1">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>190</v>
@@ -8245,27 +8148,27 @@
         <v>234</v>
       </c>
       <c r="J43" s="2">
-        <f>IF(COUNT('Turns'!D162)=1,SUM('Turns'!D162),"Unknown")</f>
-        <v>677.0</v>
+        <f>IF(COUNT('Turns'!D160)=1,SUM('Turns'!D160),"Unknown")</f>
+        <v>678.0</v>
       </c>
       <c r="K43" s="2">
-        <f>IF(COUNT('Turns'!E162)=1,SUM('Turns'!E162),"Unknown")</f>
-        <v>0.00011865779</v>
+        <f>IF(COUNT('Turns'!E160)=1,SUM('Turns'!E160),"Unknown")</f>
+        <v>0.000119292744</v>
       </c>
       <c r="L43" s="2">
-        <f>IF(COUNT('Turns'!F162)=1,SUM('Turns'!F162),"Unknown")</f>
-        <v>0.0001354</v>
+        <f>IF(COUNT('Turns'!F160)=1,SUM('Turns'!F160),"Unknown")</f>
+        <v>0.0001356</v>
       </c>
       <c r="M43" s="2">
-        <f>IF(COUNT('Turns'!D161)=1,SUM('Turns'!D161),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D159)=1,SUM('Turns'!D159),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="N43" s="2">
-        <f>IF(COUNT('Turns'!E161)=1,SUM('Turns'!E161),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E159)=1,SUM('Turns'!E159),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="O43" s="2">
-        <f>IF(COUNT('Turns'!F161)=1,SUM('Turns'!F161),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F159)=1,SUM('Turns'!F159),"Unknown")</f>
         <v>0.0</v>
       </c>
       <c r="P43" s="2">
@@ -8278,15 +8181,15 @@
         <v>0</v>
       </c>
       <c r="S43" s="2">
-        <f>IF(COUNT('Turns'!D167)=1,SUM('Turns'!D167),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D165)=1,SUM('Turns'!D165),"Unknown")</f>
         <v>20.0</v>
       </c>
       <c r="T43" s="2">
-        <f>IF(COUNT('Turns'!E167)=1,SUM('Turns'!E167),"Unknown")</f>
-        <v>2.10324e-05</v>
+        <f>IF(COUNT('Turns'!E165)=1,SUM('Turns'!E165),"Unknown")</f>
+        <v>2.111376e-05</v>
       </c>
       <c r="U43" s="2">
-        <f>IF(COUNT('Turns'!F167)=1,SUM('Turns'!F167),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F165)=1,SUM('Turns'!F165),"Unknown")</f>
         <v>2.4e-05</v>
       </c>
       <c r="V43" s="2">
@@ -8299,12 +8202,12 @@
         <v>0</v>
       </c>
       <c r="Y43" s="2">
-        <f>IF(COUNT('Turns'!E171)=1,SUM('Turns'!E171),"Unknown")</f>
-        <v>0.00013969019</v>
+        <f>IF(COUNT('Turns'!E169)=1,SUM('Turns'!E169),"Unknown")</f>
+        <v>0.000140406504</v>
       </c>
       <c r="Z43" s="2">
-        <f>IF(COUNT('Turns'!F171)=1,SUM('Turns'!F171),"Unknown")</f>
-        <v>0.0001594</v>
+        <f>IF(COUNT('Turns'!F169)=1,SUM('Turns'!F169),"Unknown")</f>
+        <v>0.0001596</v>
       </c>
       <c r="AA43" s="5">
         <f>IF(ISNUMBER(Y43),ROUND(Y43*'Reference data'!$B$2,0),"Unknown")</f>
@@ -8318,7 +8221,7 @@
         <v>177</v>
       </c>
       <c r="AD43" s="1">
-        <v>829.279</v>
+        <v>901.759</v>
       </c>
       <c r="AE43" s="1" t="s">
         <v>191</v>
@@ -8376,7 +8279,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87635</v>
+        <v>0.87974</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>
